--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
         <is>
-          <t>ustawienie po stronie GitHuba (Settings → Branches → Add rule), nie da się go zapisać w repo</t>
+          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>Reklasyfikacja jak X-01 — nie spełnia żadnego z czterech warunków blokera. Do zrobienia ręcznie przez PM: reguła na main z wymaganym statusem joba CI. Procedura krok po kroku: docs/zadania/X-02-status-wymagany-do-merge.md. Bez tego bramka testowa jest dobrowolna.</t>
+          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2108</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="19">
@@ -927,7 +927,7 @@
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Stan CZĘŚCIOWE do pierwszego zielonego przebiegu — dopiero on daje D2.</t>
+          <t>SPROSTOWANIE: pierwotny zapis „katalog .github NIE ISTNIEJE" był mój błąd — .github wypadło z archiwum, na którym pracowałem, i wziąłem to za brak w repo. CI istniało i było sensowne, ale chodziło wyłącznie na main/master, podczas gdy praca toczy się na feature/support-v2 (301 commitów do przodu) — czyli faktycznie nie chodziło nigdzie. Od 2026-08-21 uruchamiane na push do każdej gałęzi, na PR i ręcznie. Pierwszy zielony przebieg: CI #18, commit e122ae4, 2026-08-21, 2m17s — cztery joby zielone, „API unit tests" wykonane: 37 zestawów, 194 testy, wszystkie przeszły. Poziom dowodu D2 osiągnięty. Przebieg #17 (pierwszy w ogóle) był czerwony na dwóch rzeczach zastanych: zły tag akcji Trivy i apps/www niePrzechodzący typechecku — obie naprawione w e122ae4.</t>
         </is>
       </c>
       <c r="P2" s="10" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit fcf58db). Dwie warstwy: walidacja DTO i twardy warunek w serwisie. Osiem przypadków testowych, sprawdzone też w drugą stronę — na starym kodzie test świeci na czerwono. Dodatkowo @RateLimit 10/h na POST /subscriptions. Pełne D2 po pierwszym zielonym przebiegu CI. Dokumentacja: docs/zadania/Z-02-blokada-zamowienia-uslugi-bez-oplaty.md</t>
+          <t>Zamknięte 2026-08-21 (commit fcf58db). Dwie warstwy: walidacja DTO i twardy warunek w serwisie. Osiem przypadków testowych, sprawdzone też w drugą stronę — na starym kodzie test świeci na czerwono. Dodatkowo @RateLimit 10/h na POST /subscriptions. D2 potwierdzone w CI #18 (2026-08-21): 194 testy zielone, w tym 8 przypadków tego zadania. Dokumentacja: docs/zadania/Z-02-blokada-zamowienia-uslugi-bez-oplaty.md</t>
         </is>
       </c>
       <c r="P5" s="10" t="inlineStr">
@@ -6529,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13907,8 +13907,63 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>X-11</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K136"/>
+  <autoFilter ref="A1:K137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2114</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>70.5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>node-migration-worker.sh:250,253 — eval z interpolacją ${db}; :217 lftp -e z ${spath}; dto/migration.dto.ts:88-89 remotePath tylko @MaxLength, :108-109 database tylko @MaxLength, :95-96 protocol bez @IsIn; wartości przekazywane bez zmian (migration-orchestrator.service.ts:643,1277); skrypt działa jako root</t>
+          <t>dto/migration.dto.ts — MIGRACJA_WZORCE + @Matches na 17 polach; ops/scripts/lib/migration-input-guard.sh — vg_require; node-migration-worker.sh — fail-closed source + zero eval</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>Wykonanie dowolnego polecenia jako root na węźle hostingowym, z formularza migracji w panelu klienta. Jeden klient przejmuje węzeł i wszystkie konta pozostałych. Ta sama klasa błędu w node-wp-install.sh:132 i node-app-install.sh:46,64 (tam bez eskalacji uprawnień).</t>
+          <t>Zamknięte 2026-08-21. Trzy wektory: eval z nazwą bazy, łańcuch poleceń lftp ze ścieżką zdalną, eval przy imporcie — wszystkie usunięte, plus allowlista znaków na obu warstwach (DTO i węzeł). Worker startuje fail-closed bez biblioteki walidacji (kod 78), sprawdzone zachowaniem w teście. 70 przypadków testowych, 48 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy dostępu. Dokumentacja: docs/zadania/Z-03-walidacja-danych-migracji.md</t>
         </is>
       </c>
       <c r="P8" s="10" t="inlineStr">
@@ -6529,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12001,17 +12001,17 @@
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>Z-09</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Reseller jako produkt</t>
+          <t>Bezpieczeństwo jako funkcja</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>O — Multi-user i reseller</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
@@ -12044,19 +12044,19 @@
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="I103" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
@@ -12104,14 +12104,14 @@
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -12154,19 +12154,19 @@
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>bez tego reseller nie jest produktem</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -12201,27 +12201,27 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I105" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>bez tego reseller nie jest produktem</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
@@ -12264,19 +12264,19 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K106" s="11" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -12315,33 +12315,33 @@
         </is>
       </c>
       <c r="I107" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Dostępność i zgodność w produkcie</t>
+          <t>Reseller jako produkt</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -12356,37 +12356,37 @@
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I108" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="I109" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
@@ -12434,14 +12434,14 @@
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -12480,23 +12480,23 @@
         </is>
       </c>
       <c r="I110" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -12531,27 +12531,27 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I111" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>poza kodem</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -12576,47 +12576,47 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I112" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>DNS: DNSSEC i zarządzanie strefą</t>
+          <t>Dostępność i zgodność w produkcie</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -12631,37 +12631,37 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Link do strefy DNS w DirectAdmin</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I113" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:350</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>DNSSEC</t>
+          <t>Link do strefy DNS w DirectAdmin</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -12696,27 +12696,27 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
+          <t>services.controller.ts:350</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Zmiana TTL rekordów</t>
+          <t>DNSSEC</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -12755,23 +12755,23 @@
         </is>
       </c>
       <c r="I115" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>zależne od F-01</t>
+          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Anycast DNS</t>
+          <t>Zmiana TTL rekordów</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -12806,37 +12806,37 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>tylko nazwa.pl na rynku PL</t>
+          <t>zależne od F-01</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Automatyzacja: API zapisu i webhooki</t>
+          <t>DNS: DNSSEC i zarządzanie strefą</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
@@ -12851,21 +12851,21 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Zadanie cron — edycja</t>
+          <t>Anycast DNS</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>L — Automatyzacja</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I117" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
@@ -12874,14 +12874,14 @@
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>obecnie usuń i dodaj ponownie</t>
+          <t>tylko nazwa.pl na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Cron z interwałem 1 minuty</t>
+          <t>Zadanie cron — edycja</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I118" s="10" t="n">
@@ -12924,19 +12924,19 @@
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>zależne od konfiguracji DA</t>
+          <t>obecnie usuń i dodaj ponownie</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Cron z wyborem wersji PHP</t>
+          <t>Cron z interwałem 1 minuty</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I119" s="10" t="n">
@@ -12979,19 +12979,19 @@
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>seohost to reklamuje</t>
+          <t>zależne od konfiguracji DA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Podgląd wyniku ostatniego wykonania crona</t>
+          <t>Cron z wyborem wersji PHP</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -13030,19 +13030,23 @@
         </is>
       </c>
       <c r="I120" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K120" s="11" t="inlineStr"/>
+      <c r="K120" s="11" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -13067,7 +13071,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Publiczne API — zapis</t>
+          <t>Podgląd wyniku ostatniego wykonania crona</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -13081,23 +13085,19 @@
         </is>
       </c>
       <c r="I121" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K121" s="11" t="inlineStr">
-        <is>
-          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
-        </is>
-      </c>
+      <c r="K121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Tokeny API z zakresami uprawnień</t>
+          <t>Publiczne API — zapis</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -13132,27 +13132,27 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I122" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K122" s="11" t="inlineStr">
         <is>
-          <t>api-tokens.controller.ts:35</t>
+          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-09</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Webhooki dla klienta</t>
+          <t>Tokeny API z zakresami uprawnień</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -13191,19 +13191,23 @@
         </is>
       </c>
       <c r="I123" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K123" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>api-tokens.controller.ts:35</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -13228,7 +13232,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Asystent AI w panelu</t>
+          <t>Webhooki dla klienta</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -13238,27 +13242,23 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I124" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
-        </is>
-      </c>
-      <c r="K124" s="11" t="inlineStr">
-        <is>
-          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Prognoza zużycia zasobów (AI)</t>
+          <t>Asystent AI w panelu</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I125" s="10" t="n">
@@ -13306,53 +13306,53 @@
       </c>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
+          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Rozszerzenia oferty</t>
+          <t>Automatyzacja: API zapisu i webhooki</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>NISKI</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>Prognoza zużycia zasobów (AI)</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>L — Automatyzacja</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I126" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
@@ -13361,14 +13361,14 @@
       </c>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I127" s="10" t="n">
@@ -13411,15 +13411,19 @@
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K127" s="11" t="inlineStr"/>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -13444,7 +13448,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -13470,7 +13474,7 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -13495,7 +13499,7 @@
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -13505,7 +13509,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I129" s="10" t="n">
@@ -13513,49 +13517,45 @@
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K129" s="11" t="inlineStr">
-        <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
+          <t>Rozszerzenia oferty</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>ciągłe</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>NISKI</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>X — Infrastruktura jakości</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -13564,23 +13564,23 @@
         </is>
       </c>
       <c r="I130" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I131" s="10" t="n">
@@ -13628,14 +13628,14 @@
       </c>
       <c r="K131" s="11" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
@@ -13670,11 +13670,11 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I132" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
@@ -13683,14 +13683,14 @@
       </c>
       <c r="K132" s="11" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -13738,14 +13738,14 @@
       </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -13793,14 +13793,14 @@
       </c>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -13839,7 +13839,7 @@
         </is>
       </c>
       <c r="I135" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
@@ -13848,14 +13848,14 @@
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -13894,76 +13894,131 @@
         </is>
       </c>
       <c r="I136" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>ATRAPA</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
           <t>X-11</t>
         </is>
       </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>E-09</t>
         </is>
       </c>
-      <c r="C137" s="11" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>Pokrycie testowe warstw krytycznych</t>
         </is>
       </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>ciągłe</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr">
+      <c r="E138" s="10" t="inlineStr">
         <is>
           <t>WYSOKI</t>
         </is>
       </c>
-      <c r="F137" s="11" t="inlineStr">
+      <c r="F138" s="11" t="inlineStr">
         <is>
           <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
-      <c r="G137" s="10" t="inlineStr">
+      <c r="G138" s="10" t="inlineStr">
         <is>
           <t>X — Infrastruktura jakości</t>
         </is>
       </c>
-      <c r="H137" s="10" t="inlineStr">
+      <c r="H138" s="10" t="inlineStr">
         <is>
           <t>ŚREDNIA</t>
         </is>
       </c>
-      <c r="I137" s="10" t="n">
+      <c r="I138" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J137" s="10" t="inlineStr">
+      <c r="J138" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K137" s="11" t="inlineStr">
+      <c r="K138" s="11" t="inlineStr">
         <is>
           <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K137"/>
+  <autoFilter ref="A1:K138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2130</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>71</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="19">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>customer-permissions.guard.ts:75 — inferCustomerRoutePermissions kończy się return [] (zezwól) dla trasy niedopasowanej; addons/* i vps nie pasują do żadnej gałęzi; addon.service.ts:105 i vps.service.ts:174 zdejmują środki z portfela; jwt.strategy.ts:94 ustawia userId = customerOwnerId</t>
+          <t>customer-permissions.guard.ts — typ WymogTrasy, REGULY_TRAS, domyślne 'ODMOWA'; customer-permissions-coverage.spec.ts — 55 tras zamkniętych, lista jawna</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>Subkonto zaproszone wyłącznie z uprawnieniem TICKETS_READ może wydawać środki z portfela właściciela i kupować VPS na jego rachunek. Guard musi domyślnie odmawiać, nie zezwalać.</t>
+          <t>Zamknięte 2026-08-21. Przemiatanie tras pokazało większą skalę niż pierwotny opis: 148 z 347 tras dostępnych dla konta klienckiego nie wymagało żadnego uprawnienia, w tym POST /me/account-deletion (usunięcie konta właściciela), POST /partners/me/payouts/bank (wypłata prowizji na konto bankowe) i POST /users/iam/invites. Domyślna odpowiedź odwrócona na odmowę; rzeczy właściciela zamknięte twardo, niezależnie od nadanych uprawnień. Testy na zachowaniu strażnika, nie na metadanych — 15 z 28 czerwieniło się na starej wersji. Dokumentacja: docs/zadania/Z-04-guard-uprawnien-subkont.md</t>
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr">
@@ -6529,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12386,17 +12386,17 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Dostępność i zgodność w produkcie</t>
+          <t>Reseller jako produkt</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -12411,37 +12411,37 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I109" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -12480,7 +12480,7 @@
         </is>
       </c>
       <c r="I110" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
@@ -12489,14 +12489,14 @@
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -12535,23 +12535,23 @@
         </is>
       </c>
       <c r="I111" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -12586,27 +12586,27 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I112" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>poza kodem</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -12631,47 +12631,47 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I113" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>DNS: DNSSEC i zarządzanie strefą</t>
+          <t>Dostępność i zgodność w produkcie</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -12686,37 +12686,37 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Link do strefy DNS w DirectAdmin</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:350</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>DNSSEC</t>
+          <t>Link do strefy DNS w DirectAdmin</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -12751,27 +12751,27 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I115" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
+          <t>services.controller.ts:350</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Zmiana TTL rekordów</t>
+          <t>DNSSEC</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -12810,23 +12810,23 @@
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>zależne od F-01</t>
+          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Anycast DNS</t>
+          <t>Zmiana TTL rekordów</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
@@ -12861,37 +12861,37 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I117" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>tylko nazwa.pl na rynku PL</t>
+          <t>zależne od F-01</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Automatyzacja: API zapisu i webhooki</t>
+          <t>DNS: DNSSEC i zarządzanie strefą</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -12906,21 +12906,21 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Zadanie cron — edycja</t>
+          <t>Anycast DNS</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>L — Automatyzacja</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I118" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
@@ -12929,14 +12929,14 @@
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>obecnie usuń i dodaj ponownie</t>
+          <t>tylko nazwa.pl na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Cron z interwałem 1 minuty</t>
+          <t>Zadanie cron — edycja</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I119" s="10" t="n">
@@ -12979,19 +12979,19 @@
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>zależne od konfiguracji DA</t>
+          <t>obecnie usuń i dodaj ponownie</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Cron z wyborem wersji PHP</t>
+          <t>Cron z interwałem 1 minuty</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I120" s="10" t="n">
@@ -13034,19 +13034,19 @@
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>seohost to reklamuje</t>
+          <t>zależne od konfiguracji DA</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Podgląd wyniku ostatniego wykonania crona</t>
+          <t>Cron z wyborem wersji PHP</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -13085,19 +13085,23 @@
         </is>
       </c>
       <c r="I121" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K121" s="11" t="inlineStr"/>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -13122,7 +13126,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Publiczne API — zapis</t>
+          <t>Podgląd wyniku ostatniego wykonania crona</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -13136,23 +13140,19 @@
         </is>
       </c>
       <c r="I122" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K122" s="11" t="inlineStr">
-        <is>
-          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
-        </is>
-      </c>
+      <c r="K122" s="11" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Tokeny API z zakresami uprawnień</t>
+          <t>Publiczne API — zapis</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -13187,27 +13187,27 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I123" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>api-tokens.controller.ts:35</t>
+          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-09</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Webhooki dla klienta</t>
+          <t>Tokeny API z zakresami uprawnień</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -13246,19 +13246,23 @@
         </is>
       </c>
       <c r="I124" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K124" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>api-tokens.controller.ts:35</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -13283,7 +13287,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Asystent AI w panelu</t>
+          <t>Webhooki dla klienta</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -13293,27 +13297,23 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I125" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
-        </is>
-      </c>
-      <c r="K125" s="11" t="inlineStr">
-        <is>
-          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Prognoza zużycia zasobów (AI)</t>
+          <t>Asystent AI w panelu</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I126" s="10" t="n">
@@ -13361,53 +13361,53 @@
       </c>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
+          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Rozszerzenia oferty</t>
+          <t>Automatyzacja: API zapisu i webhooki</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>NISKI</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>Prognoza zużycia zasobów (AI)</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>L — Automatyzacja</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I127" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
@@ -13416,14 +13416,14 @@
       </c>
       <c r="K127" s="11" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I128" s="10" t="n">
@@ -13466,15 +13466,19 @@
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K128" s="11" t="inlineStr"/>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -13499,7 +13503,7 @@
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -13525,7 +13529,7 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -13550,7 +13554,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
@@ -13560,7 +13564,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I130" s="10" t="n">
@@ -13568,49 +13572,45 @@
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K130" s="11" t="inlineStr">
-        <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
+          <t>Rozszerzenia oferty</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>ciągłe</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>NISKI</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>X — Infrastruktura jakości</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -13619,23 +13619,23 @@
         </is>
       </c>
       <c r="I131" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K131" s="11" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I132" s="10" t="n">
@@ -13683,14 +13683,14 @@
       </c>
       <c r="K132" s="11" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -13725,11 +13725,11 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I133" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
@@ -13738,14 +13738,14 @@
       </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -13793,14 +13793,14 @@
       </c>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -13848,14 +13848,14 @@
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -13894,7 +13894,7 @@
         </is>
       </c>
       <c r="I136" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
@@ -13903,14 +13903,14 @@
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -13949,76 +13949,131 @@
         </is>
       </c>
       <c r="I137" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>ATRAPA</t>
+        </is>
+      </c>
+      <c r="K138" s="11" t="inlineStr">
+        <is>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
           <t>X-11</t>
         </is>
       </c>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>E-09</t>
         </is>
       </c>
-      <c r="C138" s="11" t="inlineStr">
+      <c r="C139" s="11" t="inlineStr">
         <is>
           <t>Pokrycie testowe warstw krytycznych</t>
         </is>
       </c>
-      <c r="D138" s="10" t="inlineStr">
+      <c r="D139" s="10" t="inlineStr">
         <is>
           <t>ciągłe</t>
         </is>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="E139" s="10" t="inlineStr">
         <is>
           <t>WYSOKI</t>
         </is>
       </c>
-      <c r="F138" s="11" t="inlineStr">
+      <c r="F139" s="11" t="inlineStr">
         <is>
           <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
-      <c r="G138" s="10" t="inlineStr">
+      <c r="G139" s="10" t="inlineStr">
         <is>
           <t>X — Infrastruktura jakości</t>
         </is>
       </c>
-      <c r="H138" s="10" t="inlineStr">
+      <c r="H139" s="10" t="inlineStr">
         <is>
           <t>ŚREDNIA</t>
         </is>
       </c>
-      <c r="I138" s="10" t="n">
+      <c r="I139" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J138" s="10" t="inlineStr">
+      <c r="J139" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K138" s="11" t="inlineStr">
+      <c r="K139" s="11" t="inlineStr">
         <is>
           <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K138"/>
+  <autoFilter ref="A1:K139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -6529,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6605,7 +6605,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per katalog</t>
+          <t>Zmiana wersji PHP dla całego konta</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
@@ -6640,23 +6640,27 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I2" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K2" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -6681,7 +6685,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>Włączanie/wyłączanie rozszerzeń PHP</t>
+          <t>Zmiana wersji PHP per katalog</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -6691,7 +6695,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I3" s="10" t="n">
@@ -6707,7 +6711,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>B-05</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -6732,7 +6736,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Edycja dyrektyw php.ini z panelu</t>
+          <t>Włączanie/wyłączanie rozszerzeń PHP</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -6742,7 +6746,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I4" s="10" t="n">
@@ -6753,16 +6757,12 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>4 z 5 hostingów PL to ma</t>
-        </is>
-      </c>
+      <c r="K4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>B-06</t>
+          <t>B-05</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Podgląd aktualnej konfiguracji PHP (phpinfo)</t>
+          <t>Edycja dyrektyw php.ini z panelu</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -6797,23 +6797,27 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>4 z 5 hostingów PL to ma</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>B-08</t>
+          <t>B-06</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -6838,7 +6842,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Aplikacje Node.js</t>
+          <t>Podgląd aktualnej konfiguracji PHP (phpinfo)</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -6852,23 +6856,19 @@
         </is>
       </c>
       <c r="I6" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>żaden z 5 hostingów PL tego nie ma</t>
-        </is>
-      </c>
+      <c r="K6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>B-09</t>
+          <t>B-08</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Aplikacje Python</t>
+          <t>Aplikacje Node.js</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -6914,12 +6914,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>żaden z 5 hostingów PL tego nie ma</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>B-17</t>
+          <t>B-09</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -6944,7 +6948,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Własne strony błędów</t>
+          <t>Aplikacje Python</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -6958,7 +6962,7 @@
         </is>
       </c>
       <c r="I8" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
@@ -6970,7 +6974,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>B-18</t>
+          <t>B-17</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -6995,7 +6999,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Menedżer indeksowania katalogu</t>
+          <t>Własne strony błędów</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -7021,7 +7025,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>B-19</t>
+          <t>B-18</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -7046,7 +7050,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Kreator stron WWW</t>
+          <t>Menedżer indeksowania katalogu</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -7060,23 +7064,19 @@
         </is>
       </c>
       <c r="I10" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>SiteBuilderTab.tsx (1612 l.) wyłączony w page.tsx:65,296</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>C-14</t>
+          <t>B-19</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwanie plików</t>
+          <t>Kreator stron WWW</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -7115,19 +7115,23 @@
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr"/>
+          <t>ATRAPA</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>SiteBuilderTab.tsx (1612 l.) wyłączony w page.tsx:65,296</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>C-15</t>
+          <t>C-14</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -7152,7 +7156,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zajętości katalogów (disk usage)</t>
+          <t>Wyszukiwanie plików</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -7162,7 +7166,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
@@ -7173,16 +7177,12 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>częste źródło ticketów „skończyło się miejsce”</t>
-        </is>
-      </c>
+      <c r="K12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>C-19</t>
+          <t>C-15</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — limit powierzchni (quota)</t>
+          <t>Podgląd zajętości katalogów (disk usage)</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
@@ -7228,12 +7228,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr"/>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>częste źródło ticketów „skończyło się miejsce”</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>C-21</t>
+          <t>C-19</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -7258,7 +7262,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Dostęp SSH</t>
+          <t>Konto FTP — limit powierzchni (quota)</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -7268,27 +7272,23 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>ServiceConnectionCard.tsx:235 — tylko odczyt flagi</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>C-22</t>
+          <t>C-21</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Zarządzanie kluczami SSH konta hostingowego</t>
+          <t>Dostęp SSH</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -7331,19 +7331,19 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>klucze są tylko dla VPS, nie dla hostingu</t>
+          <t>ServiceConnectionCard.tsx:235 — tylko odczyt flagi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>C-25</t>
+          <t>C-22</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Klonowanie repozytorium Git z panelu</t>
+          <t>Zarządzanie kluczami SSH konta hostingowego</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>DeployTab.tsx:192 przyznaje brak</t>
+          <t>klucze są tylko dla VPS, nie dla hostingu</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>C-26</t>
+          <t>C-25</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Deploy z repozytorium (pull na żądanie)</t>
+          <t>Klonowanie repozytorium Git z panelu</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -7441,19 +7441,19 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:717; directadmin.service.ts:2450</t>
+          <t>DeployTab.tsx:192 przyznaje brak</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>C-27</t>
+          <t>C-26</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Webhook deploy z GitHuba</t>
+          <t>Deploy z repozytorium (pull na żądanie)</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I18" s="10" t="n">
@@ -7496,15 +7496,19 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:717; directadmin.service.ts:2450</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>C-28</t>
+          <t>C-27</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -7529,7 +7533,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Composer / narzędzia CLI przez SSH</t>
+          <t>Webhook deploy z GitHuba</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -7539,27 +7543,23 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I19" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>zależne od C-21</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>C-28</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Nadawanie uprawnień użytkownikowi bazy</t>
+          <t>Composer / narzędzia CLI przez SSH</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -7598,19 +7598,23 @@
         </is>
       </c>
       <c r="I20" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>zależne od C-21</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7635,7 +7639,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — dostęp</t>
+          <t>Nadawanie uprawnień użytkownikowi bazy</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -7653,19 +7657,15 @@
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>link do DA zamiast SSO</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Import / eksport bazy z panelu</t>
+          <t>phpMyAdmin — dostęp</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -7700,27 +7700,27 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I22" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>standard u wszystkich 5 hostingów PL</t>
+          <t>link do DA zamiast SSO</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Kopia bazy na żądanie</t>
+          <t>Import / eksport bazy z panelu</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -7755,27 +7755,27 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>w ramach backupu konta</t>
+          <t>standard u wszystkich 5 hostingów PL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Kopia bazy na żądanie</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -7810,27 +7810,27 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I24" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
-          <t>2 z 5 hostingów PL</t>
+          <t>w ramach backupu konta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Podgląd rozmiaru bazy</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -7869,23 +7869,23 @@
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>w statystykach konta</t>
+          <t>2 z 5 hostingów PL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-17</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Naprawa / optymalizacja tabel</t>
+          <t>Podgląd rozmiaru bazy</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -7928,15 +7928,19 @@
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>w statystykach konta</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>K-03</t>
+          <t>D-18</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -7961,17 +7965,17 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Licznik inodów</t>
+          <t>Naprawa / optymalizacja tabel</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I27" s="10" t="n">
@@ -7982,16 +7986,12 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
-        <is>
-          <t>żaden hosting PL nie publikuje — okazja na transparentność</t>
-        </is>
-      </c>
+      <c r="K27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>K-04</t>
+          <t>K-03</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Logi dostępu WWW (access log)</t>
+          <t>Licznik inodów</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -8026,11 +8026,11 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I28" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
@@ -8039,14 +8039,14 @@
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to ma; seohost reklamuje jako darmowe</t>
+          <t>żaden hosting PL nie publikuje — okazja na transparentność</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>K-05</t>
+          <t>K-04</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>Logi błędów PHP</t>
+          <t>Logi dostępu WWW (access log)</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -8094,14 +8094,14 @@
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>j.w. — bez tego klient nie zdiagnozuje własnej strony</t>
+          <t>wszystkie 5 hostingów PL to ma; seohost reklamuje jako darmowe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>K-06</t>
+          <t>K-05</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Surowe logi do pobrania</t>
+          <t>Logi błędów PHP</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -8136,23 +8136,27 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I30" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>j.w. — bez tego klient nie zdiagnozuje własnej strony</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>K-08</t>
+          <t>K-06</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -8177,7 +8181,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienia o przekroczeniu limitów</t>
+          <t>Surowe logi do pobrania</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -8195,19 +8199,15 @@
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>monitoring dostępności działa; brak alertów o limitach zasobów</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>K-14</t>
+          <t>K-08</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Wolne zapytania SQL</t>
+          <t>Powiadomienia o przekroczeniu limitów</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -8242,33 +8242,37 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I32" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>monitoring dostępności działa; brak alertów o limitach zasobów</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>K-14</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Wydajność: cache i skalowanie</t>
+          <t>Runtime, pliki i diagnostyka</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -8283,17 +8287,17 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Redis / cache obiektowy dla klienta</t>
+          <t>Wolne zapytania SQL</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I33" s="10" t="n">
@@ -8304,16 +8308,12 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>3 z 5 hostingów PL ma w cenie — realny wyróżnik dla WordPressa</t>
-        </is>
-      </c>
+      <c r="K33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Memcached</t>
+          <t>Redis / cache obiektowy dla klienta</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I34" s="10" t="n">
@@ -8359,12 +8359,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>3 z 5 hostingów PL ma w cenie — realny wyróżnik dla WordPressa</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>J-01</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -8389,37 +8393,33 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>LiteSpeed / serwer o wysokiej wydajności</t>
+          <t>Memcached</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I35" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
-        </is>
-      </c>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>decyzja infrastrukturalna, poza kodem panelu</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>J-02</t>
+          <t>J-01</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Cache stron (LSCache) sterowany z panelu</t>
+          <t>LiteSpeed / serwer o wysokiej wydajności</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -8458,19 +8458,23 @@
         </is>
       </c>
       <c r="I36" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K36" s="11" t="inlineStr"/>
+          <t>b.d.</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>decyzja infrastrukturalna, poza kodem panelu</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>J-03</t>
+          <t>J-02</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -8495,7 +8499,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Cache obiektowy (Redis) dla WordPressa</t>
+          <t>Cache stron (LSCache) sterowany z panelu</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -8516,16 +8520,12 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>patrz D-15</t>
-        </is>
-      </c>
+      <c r="K37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>J-04</t>
+          <t>J-03</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>HTTP/3</t>
+          <t>Cache obiektowy (Redis) dla WordPressa</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -8560,27 +8560,27 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I38" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
         <is>
-          <t>poza kodem panelu</t>
+          <t>patrz D-15</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>J-05</t>
+          <t>J-04</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>HTTP/3</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -8615,27 +8615,27 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>na rynku PL płatny dodatek</t>
+          <t>poza kodem panelu</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>J-06</t>
+          <t>J-05</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>Optymalizacja obrazów</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -8674,19 +8674,23 @@
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>na rynku PL płatny dodatek</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>J-07</t>
+          <t>J-06</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -8711,7 +8715,7 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Dedykowany adres IP</t>
+          <t>Optymalizacja obrazów</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -8721,37 +8725,33 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I41" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K41" s="11" t="inlineStr">
-        <is>
-          <t>addons — jako dodatek typu workorder</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>J-07</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Backup: granularność i retencja</t>
+          <t>Wydajność: cache i skalowanie</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -8766,21 +8766,21 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Retencja co najmniej 28 dni w cenie</t>
+          <t>Dedykowany adres IP</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I42" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
@@ -8789,14 +8789,14 @@
       </c>
       <c r="K42" s="11" t="inlineStr">
         <is>
-          <t>off-site: 30 dni (node-offsite-backup.sh:101)</t>
+          <t>addons — jako dodatek typu workorder</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Odtworzenie pojedynczego pliku</t>
+          <t>Retencja co najmniej 28 dni w cenie</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -8839,19 +8839,19 @@
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>JetBackup/Plesk to mają; seohost i dhosting też</t>
+          <t>off-site: 30 dni (node-offsite-backup.sh:101)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zawartości archiwum przed odtworzeniem</t>
+          <t>Odtworzenie pojedynczego pliku</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -8894,19 +8894,19 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:788-793 — buduje z BIEŻĄCEGO inwentarza konta, nie z archiwum</t>
+          <t>JetBackup/Plesk to mają; seohost i dhosting też</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>H-13</t>
+          <t>H-11</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>Pobranie archiwum kopii lokalnie</t>
+          <t>Podgląd zawartości archiwum przed odtworzeniem</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -8941,27 +8941,27 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I45" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:855 — kopiuje na konto, nie do przeglądarki</t>
+          <t>services.controller.ts:788-793 — buduje z BIEŻĄCEGO inwentarza konta, nie z archiwum</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>H-16</t>
+          <t>H-13</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>ODTWORZENIE KONTA NA INNY WĘZEŁ</t>
+          <t>Pobranie archiwum kopii lokalnie</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -8996,27 +8996,27 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I46" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts:125 kieruje zadanie na account.serverId; node-account-restore.sh:76 przerywa gdy brak katalogu</t>
+          <t>services.controller.ts:855 — kopiuje na konto, nie do przeglądarki</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>H-18</t>
+          <t>H-16</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>Odtworzenie konta przez operatora z panelu</t>
+          <t>ODTWORZENIE KONTA NA INNY WĘZEŁ</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -9051,27 +9051,27 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I47" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:69,86 — zero wywołań w admin-panel</t>
+          <t>offsite-restore.service.ts:125 kieruje zadanie na account.serverId; node-account-restore.sh:76 przerywa gdy brak katalogu</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>H-19</t>
+          <t>H-18</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>Automatyczna konfiguracja backupu przy wdrożeniu węzła</t>
+          <t>Odtworzenie konta przez operatora z panelu</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -9106,37 +9106,37 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I48" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>node-onboard-live.sh:240-244 tylko log_warn; wizard węzła (wizard-content.ts:21-40) nie ma kroku backupu</t>
+          <t>subscriptions.admin.controller.ts:69,86 — zero wywołań w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>H-19</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Rozliczenia: dokończenie</t>
+          <t>Backup: granularność i retencja</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -9151,17 +9151,17 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>DUPLIKAT FAKTURY</t>
+          <t>Automatyczna konfiguracja backupu przy wdrożeniu węzła</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I49" s="10" t="n">
@@ -9174,14 +9174,14 @@
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>brak flagi isDuplicate, brak endpointu</t>
+          <t>node-onboard-live.sh:240-244 tylko log_warn; wizard węzła (wizard-content.ts:21-40) nie ma kroku backupu</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>Stawki VAT inne niż 23%</t>
+          <t>DUPLIKAT FAKTURY</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I50" s="10" t="n">
@@ -9229,14 +9229,14 @@
       </c>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:17 — DEFAULT_VAT_RATE = 23 na sztywno</t>
+          <t>brak flagi isDuplicate, brak endpointu</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Faktury w walucie obcej z przeliczeniem VAT</t>
+          <t>Stawki VAT inne niż 23%</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -9279,19 +9279,19 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>invoice-pdf.service.ts:61 formatuje PLN/EUR/USD; brak kursu i przeliczenia (art. 31a)</t>
+          <t>invoices.service.ts:17 — DEFAULT_VAT_RATE = 23 na sztywno</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Proforma przed odnowieniem</t>
+          <t>Faktury w walucie obcej z przeliczeniem VAT</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I52" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
@@ -9339,14 +9339,14 @@
       </c>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>renewal-reminder.scheduler.ts — przypomnienie, nie proforma</t>
+          <t>invoice-pdf.service.ts:61 formatuje PLN/EUR/USD; brak kursu i przeliczenia (art. 31a)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>M-27</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>Dodanie karty niezależnie od zakupu</t>
+          <t>Proforma przed odnowieniem</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -9389,19 +9389,19 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>karta zapisuje się tylko przy okazji Stripe Checkout</t>
+          <t>renewal-reminder.scheduler.ts — przypomnienie, nie proforma</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>M-28</t>
+          <t>M-27</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Eksport historii transakcji do CSV</t>
+          <t>Dodanie karty niezależnie od zakupu</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I54" s="10" t="n">
@@ -9444,19 +9444,19 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:70 — zero odwołań w panelu</t>
+          <t>karta zapisuje się tylko przy okazji Stripe Checkout</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>M-33</t>
+          <t>M-28</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>Dodatki płatne (IP, wsparcie priorytetowe)</t>
+          <t>Eksport historii transakcji do CSV</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -9495,23 +9495,23 @@
         </is>
       </c>
       <c r="I55" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>addon.service.ts:120 — 2 z 3 to workorder do BOK</t>
+          <t>billing.controller.ts:70 — zero odwołań w panelu</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Z-07</t>
+          <t>M-33</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>Ponowienie płatności portfelem w okresie karencji</t>
+          <t>Dodatki płatne (IP, wsparcie priorytetowe)</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I56" s="10" t="n">
@@ -9554,19 +9554,19 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
+          <t>addon.service.ts:120 — 2 z 3 to workorder do BOK</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Z-08</t>
+          <t>Z-07</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
+          <t>Ponowienie płatności portfelem w okresie karencji</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -9601,11 +9601,11 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I57" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
@@ -9614,24 +9614,24 @@
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
+          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>Z-08</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie i ops: kolejka abuse</t>
+          <t>Rozliczenia: dokończenie</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -9646,17 +9646,17 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I58" s="10" t="n">
@@ -9664,19 +9664,19 @@
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I59" s="10" t="n">
@@ -9719,19 +9719,19 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -9766,27 +9766,27 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I60" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
@@ -9821,11 +9821,11 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I61" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
@@ -9834,14 +9834,14 @@
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
@@ -9876,27 +9876,27 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I62" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -9931,27 +9931,27 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I63" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -9990,38 +9990,38 @@
         </is>
       </c>
       <c r="I64" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>WordPress Toolkit</t>
+          <t>Wsparcie i ops: kolejka abuse</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -10031,21 +10031,21 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>Automatyczne aktualizacje WordPressa</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I65" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
@@ -10054,14 +10054,14 @@
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL to ma</t>
+          <t>poza produktem</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>I-05</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Aktualizacje wtyczek i motywów z panelu</t>
+          <t>Automatyczne aktualizacje WordPressa</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I66" s="10" t="n">
@@ -10107,12 +10107,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr">
+        <is>
+          <t>4 z 5 hostingów PL to ma</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>I-07</t>
+          <t>I-05</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -10137,7 +10141,7 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Skanowanie podatności WordPressa</t>
+          <t>Aktualizacje wtyczek i motywów z panelu</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -10151,23 +10155,19 @@
         </is>
       </c>
       <c r="I67" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K67" s="11" t="inlineStr">
-        <is>
-          <t>Plesk używa Patchstack</t>
-        </is>
-      </c>
+      <c r="K67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>I-08</t>
+          <t>I-07</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Hardening WordPressa (checklist)</t>
+          <t>Skanowanie podatności WordPressa</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -10206,19 +10206,23 @@
         </is>
       </c>
       <c r="I68" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>Plesk używa Patchstack</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>I-13</t>
+          <t>I-08</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -10243,7 +10247,7 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>Klonowanie strony między domenami</t>
+          <t>Hardening WordPressa (checklist)</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -10269,7 +10273,7 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>I-14</t>
+          <t>I-13</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -10294,7 +10298,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Masowe zarządzanie wieloma instalacjami WP</t>
+          <t>Klonowanie strony między domenami</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -10304,27 +10308,23 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I70" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>realna przewaga dla agencji</t>
-        </is>
-      </c>
+      <c r="K70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>I-15</t>
+          <t>I-14</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>Tryb konserwacji WordPressa</t>
+          <t>Masowe zarządzanie wieloma instalacjami WP</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -10363,19 +10363,23 @@
         </is>
       </c>
       <c r="I71" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>realna przewaga dla agencji</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>I-16</t>
+          <t>I-15</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -10400,7 +10404,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>WP-CLI</t>
+          <t>Tryb konserwacji WordPressa</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
@@ -10410,7 +10414,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I72" s="10" t="n">
@@ -10418,19 +10422,15 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K72" s="11" t="inlineStr">
-        <is>
-          <t>używane wewnętrznie przy WP_INSTALL</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>I-18</t>
+          <t>I-16</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>Migracja — test poświadczeń (preflight)</t>
+          <t>WP-CLI</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -10478,14 +10478,14 @@
       </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:1001</t>
+          <t>używane wewnętrznie przy WP_INSTALL</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>I-22</t>
+          <t>I-18</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Migracja — cockpit operatora</t>
+          <t>Migracja — test poświadczeń (preflight)</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -10533,24 +10533,24 @@
       </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
-          <t>migrations.staff.controller.ts:75,90,126</t>
+          <t>services.controller.ts:1001</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>I-22</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Domeny jako produkt</t>
+          <t>WordPress Toolkit</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>Zmiana document root domeny</t>
+          <t>Migracja — cockpit operatora</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I75" s="10" t="n">
@@ -10583,19 +10583,19 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>DA to potrafi; brak UI</t>
+          <t>migrations.staff.controller.ts:75,90,126</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>A-08</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Rejestracja domeny z panelu</t>
+          <t>Zmiana document root domeny</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -10630,27 +10630,27 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I76" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:118</t>
+          <t>DA to potrafi; brak UI</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-08</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>Transfer domeny (kod authinfo)</t>
+          <t>Rejestracja domeny z panelu</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I77" s="10" t="n">
@@ -10698,14 +10698,14 @@
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:123</t>
+          <t>domains.controller.ts:118</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>A-10</t>
+          <t>A-09</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Odnowienie domeny przez klienta</t>
+          <t>Transfer domeny (kod authinfo)</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -10740,27 +10740,27 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I78" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:133</t>
+          <t>domains.controller.ts:123</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>A-12</t>
+          <t>A-10</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Cennik rejestracji na 1–10 lat</t>
+          <t>Odnowienie domeny przez klienta</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -10803,19 +10803,19 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:59</t>
+          <t>domains.controller.ts:133</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>A-12</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Zmiana danych abonenta domeny</t>
+          <t>Cennik rejestracji na 1–10 lat</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -10850,27 +10850,27 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I80" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>wymóg operatorski przy własnej rejestracji</t>
+          <t>domains.controller.ts:59</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>A-13</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>Ukrycie danych WHOIS / domain privacy</t>
+          <t>Zmiana danych abonenta domeny</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -10905,23 +10905,27 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I81" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>wymóg operatorski przy własnej rejestracji</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>A-15</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -10946,7 +10950,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Blokada transferu domeny (transfer lock)</t>
+          <t>Ukrycie danych WHOIS / domain privacy</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -10956,7 +10960,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I82" s="10" t="n">
@@ -10972,7 +10976,7 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>A-16</t>
+          <t>A-15</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -10997,7 +11001,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>Weryfikacja własności domeny</t>
+          <t>Blokada transferu domeny (transfer lock)</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -11007,27 +11011,23 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I83" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K83" s="11" t="inlineStr">
-        <is>
-          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-16</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Zakładanie konta klienta przez operatora</t>
+          <t>Weryfikacja własności domeny</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -11070,29 +11070,29 @@
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>brak @Post w users.admin.controller.ts</t>
+          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Katalog aplikacji</t>
+          <t>Domeny jako produkt</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -11102,17 +11102,17 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Autoinstalator aplikacji</t>
+          <t>Zakładanie konta klienta przez operatora</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -11125,29 +11125,29 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+          <t>brak @Post w users.admin.controller.ts</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Poczta: filtry, kalendarz, limity</t>
+          <t>Katalog aplikacji</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -11162,33 +11162,37 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zużycia skrzynki</t>
+          <t>Autoinstalator aplikacji</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I86" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K86" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr">
+        <is>
+          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -11213,7 +11217,7 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>Reguły filtrowania poczty (Sieve)</t>
+          <t>Podgląd zużycia skrzynki</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -11227,23 +11231,19 @@
         </is>
       </c>
       <c r="I87" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to ma</t>
-        </is>
-      </c>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Webmail — dostęp</t>
+          <t>Reguły filtrowania poczty (Sieve)</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -11282,23 +11282,23 @@
         </is>
       </c>
       <c r="I88" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>link do DA</t>
+          <t>wszystkie 5 hostingów PL to ma</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>E-18</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>Sprawdzenie obecności na RBL</t>
+          <t>Webmail — dostęp</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -11341,19 +11341,19 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>link do DA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>E-19</t>
+          <t>E-18</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Podgląd kolejki i logów dostarczania</t>
+          <t>Sprawdzenie obecności na RBL</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -11392,23 +11392,23 @@
         </is>
       </c>
       <c r="I90" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>E-20</t>
+          <t>E-19</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>Limity wysyłki pokazane klientowi</t>
+          <t>Podgląd kolejki i logów dostarczania</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="I91" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
@@ -11456,14 +11456,14 @@
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
+          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>E-21</t>
+          <t>E-20</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Samodzielny import skrzynek przez IMAP</t>
+          <t>Limity wysyłki pokazane klientowi</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -11506,19 +11506,19 @@
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>w ramach migracji, nie jako osobne narzędzie</t>
+          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>E-23</t>
+          <t>E-21</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
+          <t>Samodzielny import skrzynek przez IMAP</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -11553,27 +11553,27 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I93" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
+          <t>w ramach migracji, nie jako osobne narzędzie</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>E-24</t>
+          <t>E-23</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>2FA dla webmaila</t>
+          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="I94" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
@@ -11621,29 +11621,29 @@
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>E-24</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Bezpieczeństwo jako funkcja</t>
+          <t>Poczta: filtry, kalendarz, limity</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -11653,12 +11653,12 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>HSTS</t>
+          <t>2FA dla webmaila</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -11667,19 +11667,23 @@
         </is>
       </c>
       <c r="I95" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K95" s="11" t="inlineStr"/>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>G-08</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -11704,7 +11708,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Sprzedaż certyfikatów DV/OV/EV</t>
+          <t>HSTS</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -11718,23 +11722,19 @@
         </is>
       </c>
       <c r="I96" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K96" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to sprzedaje</t>
-        </is>
-      </c>
+      <c r="K96" s="11" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>G-08</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>Skaner malware dla klienta</t>
+          <t>Sprzedaż certyfikatów DV/OV/EV</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -11769,11 +11769,11 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I97" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
@@ -11782,14 +11782,14 @@
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+          <t>wszystkie 5 hostingów PL to sprzedaje</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>G-12</t>
+          <t>G-11</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Czyszczenie zainfekowanych plików</t>
+          <t>Skaner malware dla klienta</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I98" s="10" t="n">
@@ -11835,12 +11835,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>G-19</t>
+          <t>G-12</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -11865,7 +11869,7 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>Auto-wylogowanie po bezczynności</t>
+          <t>Czyszczenie zainfekowanych plików</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -11879,23 +11883,19 @@
         </is>
       </c>
       <c r="I99" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>session-idle-guard.tsx</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>G-21</t>
+          <t>G-19</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Anty-DDoS</t>
+          <t>Auto-wylogowanie po bezczynności</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -11934,23 +11934,23 @@
         </is>
       </c>
       <c r="I100" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+          <t>session-idle-guard.tsx</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>G-22</t>
+          <t>G-21</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienie o podejrzanym logowaniu</t>
+          <t>Anty-DDoS</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -11985,23 +11985,27 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I101" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K101" s="11" t="inlineStr"/>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Z-09</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -12026,7 +12030,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
+          <t>Powiadomienie o podejrzanym logowaniu</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -12036,37 +12040,33 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I102" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K102" s="11" t="inlineStr">
-        <is>
-          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
-        </is>
-      </c>
+      <c r="K102" s="11" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>Z-09</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Reseller jako produkt</t>
+          <t>Bezpieczeństwo jako funkcja</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>O — Multi-user i reseller</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
@@ -12099,19 +12099,19 @@
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="I104" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
@@ -12159,14 +12159,14 @@
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -12209,19 +12209,19 @@
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
-          <t>bez tego reseller nie jest produktem</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
@@ -12256,27 +12256,27 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I106" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K106" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>bez tego reseller nie jest produktem</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -12319,19 +12319,19 @@
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -12370,23 +12370,23 @@
         </is>
       </c>
       <c r="I108" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I109" s="10" t="n">
@@ -12429,29 +12429,29 @@
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Dostępność i zgodność w produkcie</t>
+          <t>Reseller jako produkt</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -12466,37 +12466,37 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I110" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -12535,7 +12535,7 @@
         </is>
       </c>
       <c r="I111" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
@@ -12544,14 +12544,14 @@
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -12590,23 +12590,23 @@
         </is>
       </c>
       <c r="I112" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -12641,27 +12641,27 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I113" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>poza kodem</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -12686,47 +12686,47 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>DNS: DNSSEC i zarządzanie strefą</t>
+          <t>Dostępność i zgodność w produkcie</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -12741,37 +12741,37 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Link do strefy DNS w DirectAdmin</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I115" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:350</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>DNSSEC</t>
+          <t>Link do strefy DNS w DirectAdmin</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -12806,27 +12806,27 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
+          <t>services.controller.ts:350</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Zmiana TTL rekordów</t>
+          <t>DNSSEC</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
@@ -12865,23 +12865,23 @@
         </is>
       </c>
       <c r="I117" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>zależne od F-01</t>
+          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Anycast DNS</t>
+          <t>Zmiana TTL rekordów</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -12916,37 +12916,37 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I118" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>tylko nazwa.pl na rynku PL</t>
+          <t>zależne od F-01</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Automatyzacja: API zapisu i webhooki</t>
+          <t>DNS: DNSSEC i zarządzanie strefą</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -12961,21 +12961,21 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Zadanie cron — edycja</t>
+          <t>Anycast DNS</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>L — Automatyzacja</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I119" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
@@ -12984,14 +12984,14 @@
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>obecnie usuń i dodaj ponownie</t>
+          <t>tylko nazwa.pl na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Cron z interwałem 1 minuty</t>
+          <t>Zadanie cron — edycja</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I120" s="10" t="n">
@@ -13034,19 +13034,19 @@
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>zależne od konfiguracji DA</t>
+          <t>obecnie usuń i dodaj ponownie</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Cron z wyborem wersji PHP</t>
+          <t>Cron z interwałem 1 minuty</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I121" s="10" t="n">
@@ -13089,19 +13089,19 @@
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>seohost to reklamuje</t>
+          <t>zależne od konfiguracji DA</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Podgląd wyniku ostatniego wykonania crona</t>
+          <t>Cron z wyborem wersji PHP</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -13140,19 +13140,23 @@
         </is>
       </c>
       <c r="I122" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K122" s="11" t="inlineStr"/>
+      <c r="K122" s="11" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -13177,7 +13181,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Publiczne API — zapis</t>
+          <t>Podgląd wyniku ostatniego wykonania crona</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -13191,23 +13195,19 @@
         </is>
       </c>
       <c r="I123" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K123" s="11" t="inlineStr">
-        <is>
-          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
-        </is>
-      </c>
+      <c r="K123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Tokeny API z zakresami uprawnień</t>
+          <t>Publiczne API — zapis</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -13242,27 +13242,27 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I124" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr">
         <is>
-          <t>api-tokens.controller.ts:35</t>
+          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-09</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Webhooki dla klienta</t>
+          <t>Tokeny API z zakresami uprawnień</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -13301,19 +13301,23 @@
         </is>
       </c>
       <c r="I125" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K125" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>api-tokens.controller.ts:35</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -13338,7 +13342,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Asystent AI w panelu</t>
+          <t>Webhooki dla klienta</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -13348,27 +13352,23 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I126" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
-        </is>
-      </c>
-      <c r="K126" s="11" t="inlineStr">
-        <is>
-          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>Prognoza zużycia zasobów (AI)</t>
+          <t>Asystent AI w panelu</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I127" s="10" t="n">
@@ -13416,53 +13416,53 @@
       </c>
       <c r="K127" s="11" t="inlineStr">
         <is>
-          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
+          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Rozszerzenia oferty</t>
+          <t>Automatyzacja: API zapisu i webhooki</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>NISKI</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>Prognoza zużycia zasobów (AI)</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>L — Automatyzacja</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I128" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
@@ -13471,14 +13471,14 @@
       </c>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I129" s="10" t="n">
@@ -13521,15 +13521,19 @@
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K129" s="11" t="inlineStr"/>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -13554,7 +13558,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
@@ -13580,7 +13584,7 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -13605,7 +13609,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -13615,7 +13619,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I131" s="10" t="n">
@@ -13623,49 +13627,45 @@
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K131" s="11" t="inlineStr">
-        <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
+          <t>Rozszerzenia oferty</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>ciągłe</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>NISKI</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>X — Infrastruktura jakości</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -13674,23 +13674,23 @@
         </is>
       </c>
       <c r="I132" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K132" s="11" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I133" s="10" t="n">
@@ -13738,14 +13738,14 @@
       </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -13780,11 +13780,11 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I134" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
@@ -13793,14 +13793,14 @@
       </c>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -13848,14 +13848,14 @@
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -13903,14 +13903,14 @@
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="I137" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
@@ -13958,14 +13958,14 @@
       </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -14004,76 +14004,131 @@
         </is>
       </c>
       <c r="I138" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K138" s="11" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="I139" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J139" s="10" t="inlineStr">
+        <is>
+          <t>ATRAPA</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
           <t>X-11</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>E-09</t>
         </is>
       </c>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="C140" s="11" t="inlineStr">
         <is>
           <t>Pokrycie testowe warstw krytycznych</t>
         </is>
       </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>ciągłe</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
+      <c r="E140" s="10" t="inlineStr">
         <is>
           <t>WYSOKI</t>
         </is>
       </c>
-      <c r="F139" s="11" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
-      <c r="G139" s="10" t="inlineStr">
+      <c r="G140" s="10" t="inlineStr">
         <is>
           <t>X — Infrastruktura jakości</t>
         </is>
       </c>
-      <c r="H139" s="10" t="inlineStr">
+      <c r="H140" s="10" t="inlineStr">
         <is>
           <t>ŚREDNIA</t>
         </is>
       </c>
-      <c r="I139" s="10" t="n">
+      <c r="I140" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J139" s="10" t="inlineStr">
+      <c r="J140" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K139" s="11" t="inlineStr">
+      <c r="K140" s="11" t="inlineStr">
         <is>
           <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K139"/>
+  <autoFilter ref="A1:K140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L3" s="11" t="inlineStr">
         <is>
-          <t>ruleset „main — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna; wymagane 3 checki z ci.yml</t>
+          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 3 checki z ci.yml</t>
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
+          <t>Wykonane 2026-08-21 w interfejsie GitHuba. Użyty ruleset zamiast klasycznej ochrony gałęzi, bo klasyczny formularz pozwala wybrać wyłącznie checki widziane w ciągu ostatniego tygodnia, a CI nie przebiegło jeszcze ani razu — ruleset przyjmuje check po nazwie. Rozszerzony 2026-08-21 na live-release-readiness — to z niej idą realne wdrożenia, więc ochrona samego main nie pilnowała niczego, co trafia na serwer. Konsekwencja: scalanie na gałąź wdrożeniową przez PR albo fast-forward; lokalny merge commit zostanie zablokowany, bo nie ma własnego przebiegu CI. Obejście: Repository admin (wyjście awaryjne dla jednoosobowego zespołu). Konfiguracja NIE jest w repozytorium — jej jedyny zapis to docs/zadania/X-02-status-wymagany-do-merge.md. Poziom dowodu D4.</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2170</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>addon.service.ts:110 — idempotencyKey zawiera Date.now(), więc mechanizm z wallet-ledger.service.ts:94-105 nigdy nie zadziała; addon.controller.ts:17 dopuszcza 10 wywołań na godzinę</t>
+          <t>addon.service.ts — kluczIdempotencji + sprawdzenie duplikatu przed obciążeniem + obsługa P2002; schema.prisma — PurchasedAddon.idempotencyKey @unique; migracja 20260821220000_addon_idempotency</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>Podwójne kliknięcie, ponowienie przeglądarki albo timeout = do 10 obciążeń za ten sam dodatek w godzinę. Bez ścieżki zwrotu w systemie, bo nie ma ani refundu, ani korekty faktury.</t>
+          <t>Zamknięte 2026-08-21. Mechanizm idempotencji w księdze portfela był poprawny — nie miał czego porównywać, bo Date.now() w kluczu dawał inny klucz przy każdym kliknięciu. Poprawka na dwóch drogach: klucz od klienta (panel, useRef, jeden na decyzję zakupu) i okno czasu jako zapas. Sprawdzenie duplikatu idzie PRZED obciążeniem, więc nie powtarzają się też skutki uboczne — bez tego klient dostawałby dziesięć zgłoszeń do BOK-u przy jednym obciążeniu. Wyścig domyka unikalny indeks w bazie. 20 testów, 10 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy pieniędzy. Dokumentacja: docs/zadania/Z-06-klucz-idempotencji-dodatku.md</t>
         </is>
       </c>
       <c r="P9" s="10" t="inlineStr">
@@ -6529,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9676,17 +9676,17 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>Z-11</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie i ops: kolejka abuse</t>
+          <t>Rozliczenia: dokończenie</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -9701,37 +9701,37 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I59" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I60" s="10" t="n">
@@ -9774,19 +9774,19 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
@@ -9821,27 +9821,27 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I61" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
@@ -9876,11 +9876,11 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I62" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
@@ -9889,14 +9889,14 @@
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -9931,27 +9931,27 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I63" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -9986,27 +9986,27 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I64" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -10045,38 +10045,38 @@
         </is>
       </c>
       <c r="I65" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>WordPress Toolkit</t>
+          <t>Wsparcie i ops: kolejka abuse</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -10086,21 +10086,21 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Automatyczne aktualizacje WordPressa</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I66" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
@@ -10109,14 +10109,14 @@
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL to ma</t>
+          <t>poza produktem</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>I-05</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Aktualizacje wtyczek i motywów z panelu</t>
+          <t>Automatyczne aktualizacje WordPressa</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I67" s="10" t="n">
@@ -10162,12 +10162,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>4 z 5 hostingów PL to ma</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>I-07</t>
+          <t>I-05</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -10192,7 +10196,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Skanowanie podatności WordPressa</t>
+          <t>Aktualizacje wtyczek i motywów z panelu</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -10206,23 +10210,19 @@
         </is>
       </c>
       <c r="I68" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K68" s="11" t="inlineStr">
-        <is>
-          <t>Plesk używa Patchstack</t>
-        </is>
-      </c>
+      <c r="K68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>I-08</t>
+          <t>I-07</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>Hardening WordPressa (checklist)</t>
+          <t>Skanowanie podatności WordPressa</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -10261,19 +10261,23 @@
         </is>
       </c>
       <c r="I69" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>Plesk używa Patchstack</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>I-13</t>
+          <t>I-08</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -10298,7 +10302,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Klonowanie strony między domenami</t>
+          <t>Hardening WordPressa (checklist)</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -10324,7 +10328,7 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>I-14</t>
+          <t>I-13</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -10349,7 +10353,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>Masowe zarządzanie wieloma instalacjami WP</t>
+          <t>Klonowanie strony między domenami</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -10359,27 +10363,23 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I71" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K71" s="11" t="inlineStr">
-        <is>
-          <t>realna przewaga dla agencji</t>
-        </is>
-      </c>
+      <c r="K71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>I-15</t>
+          <t>I-14</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Tryb konserwacji WordPressa</t>
+          <t>Masowe zarządzanie wieloma instalacjami WP</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
@@ -10418,19 +10418,23 @@
         </is>
       </c>
       <c r="I72" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>realna przewaga dla agencji</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>I-16</t>
+          <t>I-15</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -10455,7 +10459,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>WP-CLI</t>
+          <t>Tryb konserwacji WordPressa</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -10465,7 +10469,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I73" s="10" t="n">
@@ -10473,19 +10477,15 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K73" s="11" t="inlineStr">
-        <is>
-          <t>używane wewnętrznie przy WP_INSTALL</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>I-18</t>
+          <t>I-16</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Migracja — test poświadczeń (preflight)</t>
+          <t>WP-CLI</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -10533,14 +10533,14 @@
       </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:1001</t>
+          <t>używane wewnętrznie przy WP_INSTALL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>I-22</t>
+          <t>I-18</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>Migracja — cockpit operatora</t>
+          <t>Migracja — test poświadczeń (preflight)</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -10588,24 +10588,24 @@
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>migrations.staff.controller.ts:75,90,126</t>
+          <t>services.controller.ts:1001</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>I-22</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>Domeny jako produkt</t>
+          <t>WordPress Toolkit</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -10620,17 +10620,17 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Zmiana document root domeny</t>
+          <t>Migracja — cockpit operatora</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I76" s="10" t="n">
@@ -10638,19 +10638,19 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>DA to potrafi; brak UI</t>
+          <t>migrations.staff.controller.ts:75,90,126</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>A-08</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>Rejestracja domeny z panelu</t>
+          <t>Zmiana document root domeny</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -10685,27 +10685,27 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I77" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:118</t>
+          <t>DA to potrafi; brak UI</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-08</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Transfer domeny (kod authinfo)</t>
+          <t>Rejestracja domeny z panelu</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I78" s="10" t="n">
@@ -10753,14 +10753,14 @@
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:123</t>
+          <t>domains.controller.ts:118</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>A-10</t>
+          <t>A-09</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Odnowienie domeny przez klienta</t>
+          <t>Transfer domeny (kod authinfo)</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -10795,27 +10795,27 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I79" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:133</t>
+          <t>domains.controller.ts:123</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>A-12</t>
+          <t>A-10</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Cennik rejestracji na 1–10 lat</t>
+          <t>Odnowienie domeny przez klienta</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -10858,19 +10858,19 @@
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:59</t>
+          <t>domains.controller.ts:133</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>A-12</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>Zmiana danych abonenta domeny</t>
+          <t>Cennik rejestracji na 1–10 lat</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -10905,27 +10905,27 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I81" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>wymóg operatorski przy własnej rejestracji</t>
+          <t>domains.controller.ts:59</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>A-13</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Ukrycie danych WHOIS / domain privacy</t>
+          <t>Zmiana danych abonenta domeny</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -10960,23 +10960,27 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I82" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>wymóg operatorski przy własnej rejestracji</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>A-15</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -11001,7 +11005,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>Blokada transferu domeny (transfer lock)</t>
+          <t>Ukrycie danych WHOIS / domain privacy</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -11011,7 +11015,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I83" s="10" t="n">
@@ -11027,7 +11031,7 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>A-16</t>
+          <t>A-15</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -11052,7 +11056,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Weryfikacja własności domeny</t>
+          <t>Blokada transferu domeny (transfer lock)</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -11062,27 +11066,23 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I84" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K84" s="11" t="inlineStr">
-        <is>
-          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-16</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Zakładanie konta klienta przez operatora</t>
+          <t>Weryfikacja własności domeny</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -11125,29 +11125,29 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>brak @Post w users.admin.controller.ts</t>
+          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Katalog aplikacji</t>
+          <t>Domeny jako produkt</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -11157,17 +11157,17 @@
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Autoinstalator aplikacji</t>
+          <t>Zakładanie konta klienta przez operatora</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
@@ -11180,29 +11180,29 @@
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+          <t>brak @Post w users.admin.controller.ts</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Poczta: filtry, kalendarz, limity</t>
+          <t>Katalog aplikacji</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
@@ -11217,33 +11217,37 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zużycia skrzynki</t>
+          <t>Autoinstalator aplikacji</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I87" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -11268,7 +11272,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Reguły filtrowania poczty (Sieve)</t>
+          <t>Podgląd zużycia skrzynki</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -11282,23 +11286,19 @@
         </is>
       </c>
       <c r="I88" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K88" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to ma</t>
-        </is>
-      </c>
+      <c r="K88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>Webmail — dostęp</t>
+          <t>Reguły filtrowania poczty (Sieve)</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -11337,23 +11337,23 @@
         </is>
       </c>
       <c r="I89" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>link do DA</t>
+          <t>wszystkie 5 hostingów PL to ma</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>E-18</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Sprawdzenie obecności na RBL</t>
+          <t>Webmail — dostęp</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -11396,19 +11396,19 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>link do DA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>E-19</t>
+          <t>E-18</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>Podgląd kolejki i logów dostarczania</t>
+          <t>Sprawdzenie obecności na RBL</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -11447,23 +11447,23 @@
         </is>
       </c>
       <c r="I91" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>E-20</t>
+          <t>E-19</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Limity wysyłki pokazane klientowi</t>
+          <t>Podgląd kolejki i logów dostarczania</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="I92" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
@@ -11511,14 +11511,14 @@
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
+          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>E-21</t>
+          <t>E-20</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Samodzielny import skrzynek przez IMAP</t>
+          <t>Limity wysyłki pokazane klientowi</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -11561,19 +11561,19 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>w ramach migracji, nie jako osobne narzędzie</t>
+          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>E-23</t>
+          <t>E-21</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
+          <t>Samodzielny import skrzynek przez IMAP</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -11608,27 +11608,27 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I94" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
+          <t>w ramach migracji, nie jako osobne narzędzie</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>E-24</t>
+          <t>E-23</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>2FA dla webmaila</t>
+          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="I95" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
@@ -11676,29 +11676,29 @@
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>E-24</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Bezpieczeństwo jako funkcja</t>
+          <t>Poczta: filtry, kalendarz, limity</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>HSTS</t>
+          <t>2FA dla webmaila</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -11722,19 +11722,23 @@
         </is>
       </c>
       <c r="I96" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>G-08</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -11759,7 +11763,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>Sprzedaż certyfikatów DV/OV/EV</t>
+          <t>HSTS</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -11773,23 +11777,19 @@
         </is>
       </c>
       <c r="I97" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K97" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to sprzedaje</t>
-        </is>
-      </c>
+      <c r="K97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>G-08</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Skaner malware dla klienta</t>
+          <t>Sprzedaż certyfikatów DV/OV/EV</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -11824,11 +11824,11 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I98" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
@@ -11837,14 +11837,14 @@
       </c>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+          <t>wszystkie 5 hostingów PL to sprzedaje</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>G-12</t>
+          <t>G-11</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>Czyszczenie zainfekowanych plików</t>
+          <t>Skaner malware dla klienta</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I99" s="10" t="n">
@@ -11890,12 +11890,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>G-19</t>
+          <t>G-12</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -11920,7 +11924,7 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Auto-wylogowanie po bezczynności</t>
+          <t>Czyszczenie zainfekowanych plików</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -11934,23 +11938,19 @@
         </is>
       </c>
       <c r="I100" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K100" s="11" t="inlineStr">
-        <is>
-          <t>session-idle-guard.tsx</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K100" s="11" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>G-21</t>
+          <t>G-19</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Anty-DDoS</t>
+          <t>Auto-wylogowanie po bezczynności</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -11989,23 +11989,23 @@
         </is>
       </c>
       <c r="I101" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+          <t>session-idle-guard.tsx</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>G-22</t>
+          <t>G-21</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienie o podejrzanym logowaniu</t>
+          <t>Anty-DDoS</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -12040,23 +12040,27 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I102" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Z-09</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -12081,7 +12085,7 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
+          <t>Powiadomienie o podejrzanym logowaniu</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -12091,37 +12095,33 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I103" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K103" s="11" t="inlineStr">
-        <is>
-          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
-        </is>
-      </c>
+      <c r="K103" s="11" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>Z-09</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Reseller jako produkt</t>
+          <t>Bezpieczeństwo jako funkcja</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -12136,12 +12136,12 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>O — Multi-user i reseller</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -12154,19 +12154,19 @@
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="I105" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
@@ -12214,14 +12214,14 @@
       </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
@@ -12264,19 +12264,19 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K106" s="11" t="inlineStr">
         <is>
-          <t>bez tego reseller nie jest produktem</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -12311,27 +12311,27 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I107" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>bez tego reseller nie jest produktem</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -12374,19 +12374,19 @@
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -12425,23 +12425,23 @@
         </is>
       </c>
       <c r="I109" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I110" s="10" t="n">
@@ -12484,29 +12484,29 @@
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Dostępność i zgodność w produkcie</t>
+          <t>Reseller jako produkt</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -12521,37 +12521,37 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I111" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="I112" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
@@ -12599,14 +12599,14 @@
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -12645,23 +12645,23 @@
         </is>
       </c>
       <c r="I113" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -12696,27 +12696,27 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>poza kodem</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -12741,47 +12741,47 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I115" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>DNS: DNSSEC i zarządzanie strefą</t>
+          <t>Dostępność i zgodność w produkcie</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -12796,37 +12796,37 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Link do strefy DNS w DirectAdmin</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:350</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>DNSSEC</t>
+          <t>Link do strefy DNS w DirectAdmin</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
@@ -12861,27 +12861,27 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I117" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
+          <t>services.controller.ts:350</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Zmiana TTL rekordów</t>
+          <t>DNSSEC</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -12920,23 +12920,23 @@
         </is>
       </c>
       <c r="I118" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>zależne od F-01</t>
+          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Anycast DNS</t>
+          <t>Zmiana TTL rekordów</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -12971,37 +12971,37 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I119" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>tylko nazwa.pl na rynku PL</t>
+          <t>zależne od F-01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Automatyzacja: API zapisu i webhooki</t>
+          <t>DNS: DNSSEC i zarządzanie strefą</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -13016,21 +13016,21 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Zadanie cron — edycja</t>
+          <t>Anycast DNS</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>L — Automatyzacja</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I120" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
@@ -13039,14 +13039,14 @@
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>obecnie usuń i dodaj ponownie</t>
+          <t>tylko nazwa.pl na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Cron z interwałem 1 minuty</t>
+          <t>Zadanie cron — edycja</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I121" s="10" t="n">
@@ -13089,19 +13089,19 @@
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>zależne od konfiguracji DA</t>
+          <t>obecnie usuń i dodaj ponownie</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Cron z wyborem wersji PHP</t>
+          <t>Cron z interwałem 1 minuty</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I122" s="10" t="n">
@@ -13144,19 +13144,19 @@
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K122" s="11" t="inlineStr">
         <is>
-          <t>seohost to reklamuje</t>
+          <t>zależne od konfiguracji DA</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Podgląd wyniku ostatniego wykonania crona</t>
+          <t>Cron z wyborem wersji PHP</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -13195,19 +13195,23 @@
         </is>
       </c>
       <c r="I123" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K123" s="11" t="inlineStr"/>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -13232,7 +13236,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Publiczne API — zapis</t>
+          <t>Podgląd wyniku ostatniego wykonania crona</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -13246,23 +13250,19 @@
         </is>
       </c>
       <c r="I124" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K124" s="11" t="inlineStr">
-        <is>
-          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
-        </is>
-      </c>
+      <c r="K124" s="11" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Tokeny API z zakresami uprawnień</t>
+          <t>Publiczne API — zapis</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -13297,27 +13297,27 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I125" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>api-tokens.controller.ts:35</t>
+          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-09</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Webhooki dla klienta</t>
+          <t>Tokeny API z zakresami uprawnień</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -13356,19 +13356,23 @@
         </is>
       </c>
       <c r="I126" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K126" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>api-tokens.controller.ts:35</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -13393,7 +13397,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>Asystent AI w panelu</t>
+          <t>Webhooki dla klienta</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -13403,27 +13407,23 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I127" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
-        </is>
-      </c>
-      <c r="K127" s="11" t="inlineStr">
-        <is>
-          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Prognoza zużycia zasobów (AI)</t>
+          <t>Asystent AI w panelu</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I128" s="10" t="n">
@@ -13471,53 +13471,53 @@
       </c>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
+          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Rozszerzenia oferty</t>
+          <t>Automatyzacja: API zapisu i webhooki</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>NISKI</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>Prognoza zużycia zasobów (AI)</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>L — Automatyzacja</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I129" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
@@ -13526,14 +13526,14 @@
       </c>
       <c r="K129" s="11" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I130" s="10" t="n">
@@ -13576,15 +13576,19 @@
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K130" s="11" t="inlineStr"/>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr">
+        <is>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -13609,7 +13613,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -13635,7 +13639,7 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -13660,7 +13664,7 @@
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
@@ -13670,7 +13674,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I132" s="10" t="n">
@@ -13678,49 +13682,45 @@
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K132" s="11" t="inlineStr">
-        <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
+          <t>Rozszerzenia oferty</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>ciągłe</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>NISKI</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>X — Infrastruktura jakości</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H133" s="10" t="inlineStr">
@@ -13729,23 +13729,23 @@
         </is>
       </c>
       <c r="I133" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I134" s="10" t="n">
@@ -13793,14 +13793,14 @@
       </c>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -13835,11 +13835,11 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I135" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
@@ -13848,14 +13848,14 @@
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -13903,14 +13903,14 @@
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -13958,14 +13958,14 @@
       </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="I138" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
@@ -14013,14 +14013,14 @@
       </c>
       <c r="K138" s="11" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -14059,76 +14059,131 @@
         </is>
       </c>
       <c r="I139" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K139" s="11" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>X-10</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="I140" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J140" s="10" t="inlineStr">
+        <is>
+          <t>ATRAPA</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
           <t>X-11</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>E-09</t>
         </is>
       </c>
-      <c r="C140" s="11" t="inlineStr">
+      <c r="C141" s="11" t="inlineStr">
         <is>
           <t>Pokrycie testowe warstw krytycznych</t>
         </is>
       </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>ciągłe</t>
         </is>
       </c>
-      <c r="E140" s="10" t="inlineStr">
+      <c r="E141" s="10" t="inlineStr">
         <is>
           <t>WYSOKI</t>
         </is>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
-      <c r="G140" s="10" t="inlineStr">
+      <c r="G141" s="10" t="inlineStr">
         <is>
           <t>X — Infrastruktura jakości</t>
         </is>
       </c>
-      <c r="H140" s="10" t="inlineStr">
+      <c r="H141" s="10" t="inlineStr">
         <is>
           <t>ŚREDNIA</t>
         </is>
       </c>
-      <c r="I140" s="10" t="n">
+      <c r="I141" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J140" s="10" t="inlineStr">
+      <c r="J141" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K140" s="11" t="inlineStr">
+      <c r="K141" s="11" t="inlineStr">
         <is>
           <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K140"/>
+  <autoFilter ref="A1:K141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19 sprintów · 30 h netto na sprint · wygenerowane 2026-08-21 z audyt/dane/</t>
+          <t>19 sprintów · 30 h netto na sprint · wygenerowane 2026-08-22 z audyt/dane/</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2186</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>72.90000000000001</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="19">
@@ -6529,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14127,63 +14127,8 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="10" t="inlineStr">
-        <is>
-          <t>X-11</t>
-        </is>
-      </c>
-      <c r="B141" s="10" t="inlineStr">
-        <is>
-          <t>E-09</t>
-        </is>
-      </c>
-      <c r="C141" s="11" t="inlineStr">
-        <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
-        </is>
-      </c>
-      <c r="D141" s="10" t="inlineStr">
-        <is>
-          <t>ciągłe</t>
-        </is>
-      </c>
-      <c r="E141" s="10" t="inlineStr">
-        <is>
-          <t>WYSOKI</t>
-        </is>
-      </c>
-      <c r="F141" s="11" t="inlineStr">
-        <is>
-          <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
-        </is>
-      </c>
-      <c r="G141" s="10" t="inlineStr">
-        <is>
-          <t>X — Infrastruktura jakości</t>
-        </is>
-      </c>
-      <c r="H141" s="10" t="inlineStr">
-        <is>
-          <t>ŚREDNIA</t>
-        </is>
-      </c>
-      <c r="I141" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J141" s="10" t="inlineStr">
-        <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K141" s="11" t="inlineStr">
-        <is>
-          <t>ci.yml: job „Static checks (lint + typecheck)" — krok „API unit tests" wykonuje się po kroku „Typecheck"</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K141"/>
+  <autoFilter ref="A1:K140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L3" s="11" t="inlineStr">
         <is>
-          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 3 checki z ci.yml</t>
+          <t>ruleset „gałęzie wdrożeniowe — wymagaj zielonego CI" (id 21161479), Active, zakres: gałąź domyślna + live-release-readiness; wymagane 4 checki z ci.yml</t>
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19 sprintów · 30 h netto na sprint · wygenerowane 2026-08-22 z audyt/dane/</t>
+          <t>20 sprintów · 30 h netto na sprint · wygenerowane 2026-08-22 z audyt/dane/</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$61)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$64)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
     </row>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>570</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$61,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$61,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$64,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$64,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$61,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$64,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$61,"zrobione",'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$64,"zrobione",'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1505,12 +1505,12 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts:444-453 — wiersz stripeWebhookEvent zapisywany PRZED handlerem (:455), poza transakcją, bez cofnięcia przy wyjątku; ponowienie ze Stripe trafia w :448-451 i zwraca duplicate:true; uznanie portfela (:523) nigdy nie następuje</t>
+          <t>provisioning.service.ts:299-301 zwiększa allocatedCpu/allocatedMemory/allocatedDisk o pełne limity planu; node-selector.service.ts:109-115 wpuszcza konto tylko gdy total-allocated ≥ limit planu + headroom; schema.prisma:474 reservedHeadroomPercent Int @default(0)</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>Klient zapłacił, saldo się nie pojawiło, system uważa zdarzenie za obsłużone i odrzuca ponowienia. Odzysk wyłącznie ręcznie w bazie — brak endpointu do ponownego przetworzenia.</t>
+          <t>Odkryte przy PB-01. Węzeł księguje 8 GB RAM i 2 vCPU na każde konto, mimo że w LVE to sufity burst, a nie rezerwacje. Skutek arytmetyczny: 128 GB / 8 GB = 16 kont na węzeł i selektor przestaje wpuszczać kolejne. Próg rentowności przy cenie 45 zł to 58 kont. Oznacza to, że przy dzisiejszym kodzie każdy węzeł domyka się na stracie ok. 1 074 zł/mies. i nie da się tego naprawić sprzedażą — selektor po prostu odmówi provisioningu. To nie jest optymalizacja kosztu, to warunek istnienia oferty. Do zrobienia: współczynniki nadsubskrypcji per węzeł (overcommitCpu/Ram/Disk) użyte w node-selector, oddzielenie księgowania 'sprzedane' od 'realnie zajęte', alarm gdy realne zużycie zbliża się do pojemności. Dysk traktować ostrożniej niż RAM i CPU: quota dyskowa jest realnie egzekwowana i klient może ją wypełnić w całości. Model: docs/strategy/PB-01_unit_economics_wezla.xlsx</t>
         </is>
       </c>
       <c r="P10" s="10" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>seed.ts:40-112 zawiera wyłącznie starter/pro/business (19,99/49,99/99,99 zł); apps/www/.../Pricing.tsx:120 sprzedaje 45 zł/399 zł, hosting/page.tsx:77 opisuje bazę 50 GB / 8 GB / 2 vCPU — planu o takich limitach nie ma w żadnym seedzie ani migracji</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1647,7 +1647,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr"/>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>Odkryte przy PB-01. Strona sprzedaje pakiet, którego nie ma po stronie produktu. Trzy plany w seedzie to próbki z czasów prototypu i mają inne ceny oraz inne limity niż cokolwiek, co Verris ogłasza publicznie. Dopóki plan nie istnieje jako rekord z cpuLimit/ramLimitMb/diskLimitMb, nie działa ani wycena, ani placement, ani synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh czyta limity z Planu). Do zrobienia: migracja tworząca plan produkcyjny z limitami zgodnymi z treścią oferty, wycofanie planów próbnych z isPublic, test sprawdzający, że każda cena widoczna na www ma odpowiadający jej aktywny plan.</t>
+        </is>
+      </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -1657,27 +1661,27 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
@@ -1703,7 +1707,7 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -1718,12 +1722,12 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
@@ -1735,12 +1739,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1759,7 +1763,7 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>4</v>
@@ -1786,12 +1790,12 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
+          <t>billing.service.ts:444-453 — wiersz stripeWebhookEvent zapisywany PRZED handlerem (:455), poza transakcją, bez cofnięcia przy wyjątku; ponowienie ze Stripe trafia w :448-451 i zwraca duplicate:true; uznanie portfela (:523) nigdy nie następuje</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
@@ -1801,7 +1805,7 @@
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
+          <t>Klient zapłacił, saldo się nie pojawiło, system uważa zdarzenie za obsłużone i odrzuca ponowienia. Odzysk wyłącznie ręcznie w bazie — brak endpointu do ponownego przetworzenia.</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
@@ -1813,12 +1817,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1833,14 +1837,14 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
@@ -1849,12 +1853,12 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
@@ -1864,12 +1868,12 @@
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
@@ -1877,11 +1881,7 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
-        </is>
-      </c>
+      <c r="O14" s="11" t="inlineStr"/>
       <c r="P14" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -1891,12 +1891,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1906,19 +1906,19 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P15" s="10" t="inlineStr">
@@ -1969,31 +1969,31 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>5</v>
@@ -2015,27 +2015,27 @@
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr">
@@ -2047,12 +2047,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>6</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
+          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
+          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
@@ -2125,12 +2125,12 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>H-20</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>ops/scripts/restore-drill-isolated.sh istnieje jako procedura ręczna; live-readiness.service.ts:175-177 sprawdza tylko czy backup się WYKONAŁ</t>
+          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>PB-02 (drill wykonujemy na węźle #1)</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker. Runbook wymaga drilla przed LIVE (OFFSITE_RESTORE_RUNBOOK.md:37-40) i nie ma w repo śladu jego wykonania. Backupy i DR wymagają poziomu D4 — data, wynik, właściciel. Bez tego cała warstwa DR jest niepotwierdzona.</t>
+          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G21" s="10" t="n">
         <v>8</v>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
@@ -2437,58 +2437,58 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Dodatkowy użytkownik bazy — utworzenie</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr">
@@ -2515,12 +2515,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>H-20</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — usunięcie</t>
+          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2530,16 +2530,16 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>9</v>
@@ -2561,17 +2561,17 @@
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
+          <t>ops/scripts/restore-drill-isolated.sh istnieje jako procedura ręczna; live-readiness.service.ts:175-177 sprawdza tylko czy backup się WYKONAŁ</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>PB-02 (drill wykonujemy na węźle #1)</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker. Runbook wymaga drilla przed LIVE (OFFSITE_RESTORE_RUNBOOK.md:37-40) i nie ma w repo śladu jego wykonania. Backupy i DR wymagają poziomu D4 — data, wynik, właściciel. Bez tego cała warstwa DR jest niepotwierdzona.</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
@@ -2593,12 +2593,12 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — zmiana hasła</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2608,16 +2608,16 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>9</v>
@@ -2639,17 +2639,17 @@
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — lista</t>
+          <t>Dodatkowy użytkownik bazy — utworzenie</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — auto-logowanie (SSO)</t>
+          <t>Użytkownik bazy — usunięcie</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2776,7 +2776,7 @@
         <v>6</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
+          <t>Użytkownik bazy — zmiana hasła</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
@@ -2873,27 +2873,27 @@
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
@@ -2905,12 +2905,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SRV / CAA</t>
+          <t>Użytkownik bazy — lista</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="10" t="n">
@@ -2951,25 +2951,29 @@
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>F-01 (ten sam edytor)</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
-        </is>
-      </c>
-      <c r="O28" s="11" t="inlineStr"/>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+        </is>
+      </c>
       <c r="P28" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -2979,12 +2983,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Webmail — auto-logowanie (SSO)</t>
+          <t>phpMyAdmin — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2994,7 +2998,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -3030,7 +3034,7 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -3057,12 +3061,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per domena</t>
+          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3072,19 +3076,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>B — Runtime WWW</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
@@ -3093,22 +3097,22 @@
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
+          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3118,12 +3122,12 @@
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3135,12 +3139,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SPF — kreator</t>
+          <t>Rekordy SRV / CAA</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3150,7 +3154,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -3181,29 +3185,25 @@
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-01 (ten sam edytor)</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
-        </is>
-      </c>
-      <c r="O31" s="11" t="inlineStr">
-        <is>
-          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
-        </is>
-      </c>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr"/>
       <c r="P31" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3213,12 +3213,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Rekordy DKIM — konfiguracja</t>
+          <t>Webmail — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
@@ -3259,27 +3259,27 @@
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>E-15 (ten sam panel dostarczalności)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr">
@@ -3291,12 +3291,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Rekord DMARC — konfiguracja</t>
+          <t>Zmiana wersji PHP per domena</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
@@ -3369,12 +3369,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
+          <t>Rekordy SPF — kreator</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -3396,7 +3396,7 @@
         <v>6</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
@@ -3405,22 +3405,22 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
+          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -3447,12 +3447,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Usunięcie zapisanej karty przez klienta</t>
+          <t>Rekordy DKIM — konfiguracja</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -3474,7 +3474,7 @@
         <v>6</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -3483,37 +3483,37 @@
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15 (ten sam panel dostarczalności)</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>wymóg konsumencki</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Ręczne zawieszenie usługi przez operatora</t>
+          <t>Rekord DMARC — konfiguracja</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:192</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
@@ -3603,12 +3603,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Ręczne odwieszenie usługi przez operatora</t>
+          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -3649,27 +3649,27 @@
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:210</t>
+          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>A-25 (ten sam widok)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
+          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
@@ -3681,12 +3681,12 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>M-26</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Usunięcie zapisanej karty przez klienta</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>wymóg konsumencki</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3759,12 +3759,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>A-25</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>Ręczne zawieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -3786,7 +3786,7 @@
         <v>6</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>subscriptions.admin.controller.ts:192</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
@@ -3837,12 +3837,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>H-22</t>
+          <t>A-26</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Panel odtwarzania w widocznym miejscu</t>
+          <t>Ręczne odwieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -3864,7 +3864,7 @@
         <v>6</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
@@ -3873,37 +3873,37 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
+          <t>subscriptions.admin.controller.ts:210</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-25 (ten sam widok)</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>klient w kryzysie tego nie znajdzie</t>
+          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>H-09</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>hosting-restore.service.ts:167</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>H-17</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -4039,27 +4039,27 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>G-20</t>
+          <t>H-22</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Ochrona przed atakiem słownikowym na panel</t>
+          <t>Panel odtwarzania w widocznym miejscu</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>rate-limit.guard.ts — ZERO testów</t>
+          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>brak dowodu D2 na krytycznym guardzie</t>
+          <t>klient w kryzysie tego nie znajdzie</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
@@ -4149,12 +4149,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>H-09</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Staging — publikacja na produkcję</t>
+          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -4176,7 +4176,7 @@
         <v>6</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -4185,12 +4185,12 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:187</t>
+          <t>hosting-restore.service.ts:167</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -4227,34 +4227,34 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>H-17</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
+          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -4263,37 +4263,37 @@
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
         </is>
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 17 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 17, inaczej blokuje start.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
+          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr">
@@ -4305,12 +4305,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>G-20</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Ochrona przed atakiem słownikowym na panel</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -4351,27 +4351,27 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>rate-limit.guard.ts — ZERO testów</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
-          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>brak dowodu D2 na krytycznym guardzie</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwarka wolnych domen</t>
+          <t>Staging — publikacja na produkcję</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:54</t>
+          <t>services.controller.ts:187</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -4444,10 +4444,14 @@
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
-        </is>
-      </c>
-      <c r="O47" s="11" t="inlineStr"/>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+        </is>
+      </c>
+      <c r="O47" s="11" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+        </is>
+      </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4457,27 +4461,27 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Spakowanie do archiwum</t>
+          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
@@ -4503,12 +4507,12 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>files.service.ts:320 — tylko extract</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
@@ -4518,12 +4522,12 @@
       </c>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>standard we wszystkich panelach</t>
+          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr">
@@ -4535,73 +4539,73 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 3 — Wejście na rynek</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
         </is>
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
@@ -4613,31 +4617,31 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+          <t>Wyszukiwarka wolnych domen</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>15</v>
@@ -4659,29 +4663,25 @@
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>domains.controller.ts:54</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N50" s="11" t="inlineStr">
         <is>
-          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
-        </is>
-      </c>
-      <c r="O50" s="11" t="inlineStr">
-        <is>
-          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
-        </is>
-      </c>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+        </is>
+      </c>
+      <c r="O50" s="11" t="inlineStr"/>
       <c r="P50" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4691,31 +4691,31 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Treści i cennik na verris.pl</t>
+          <t>Spakowanie do archiwum</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>15</v>
@@ -4737,27 +4737,27 @@
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>files.service.ts:320 — tylko extract</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L51" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M51" s="11" t="inlineStr">
-        <is>
-          <t>PB-01 (cennik zależy od unit economics)</t>
-        </is>
-      </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+          <t>standard we wszystkich panelach</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
@@ -4769,12 +4769,12 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Landing /przenies-strone</t>
+          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
@@ -4805,12 +4805,12 @@
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
@@ -4825,17 +4825,17 @@
       </c>
       <c r="M52" s="11" t="inlineStr">
         <is>
-          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="11" t="inlineStr">
         <is>
-          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
         </is>
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr">
@@ -4847,12 +4847,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+          <t>Finalizacja dokumentów prawnych 1.0.0</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
@@ -4925,34 +4925,34 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>KSeF — walidacja XSD przed wysyłką</t>
+          <t>Treści i cennik na verris.pl</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
@@ -4961,37 +4961,37 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
-          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M54" s="11" t="inlineStr">
         <is>
-          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+          <t>PB-01 (cennik zależy od unit economics)</t>
         </is>
       </c>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
         </is>
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>smoke na api-test MF nie został wykonany</t>
+          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
@@ -5003,27 +5003,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>KSeF — tryb offline/awaryjny</t>
+          <t>Landing /przenies-strone</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
@@ -5049,27 +5049,27 @@
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
         </is>
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -5081,31 +5081,31 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>KSeF — pobranie UPO przez operatora</t>
+          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>17</v>
@@ -5127,27 +5127,27 @@
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M56" s="11" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
         </is>
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -5159,12 +5159,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>KSeF — numer i UPO widoczne dla klienta</t>
+          <t>KSeF — walidacja XSD przed wysyłką</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień „ksef” w apps/client-panel</t>
+          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+          <t>smoke na api-test MF nie został wykonany</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -5237,27 +5237,27 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy — 20 artykułów startowych</t>
+          <t>KSeF — tryb offline/awaryjny</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
@@ -5283,27 +5283,27 @@
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
         </is>
       </c>
       <c r="N58" s="11" t="inlineStr">
         <is>
-          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
@@ -5315,31 +5315,31 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+          <t>KSeF — pobranie UPO przez operatora</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>18</v>
@@ -5361,27 +5361,27 @@
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>PB-06 (kampania kieruje na landing)</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -5393,31 +5393,31 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Test end-to-end „pierwszy klient”</t>
+          <t>KSeF — numer i UPO widoczne dla klienta</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>19</v>
@@ -5439,27 +5439,27 @@
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zero wystąpień „ksef” w apps/client-panel</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
         <is>
-          <t>wszystkie blokery zamknięte (sprint 8)</t>
+          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
         </is>
       </c>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -5471,12 +5471,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Runbook startu i decyzja GO</t>
+          <t>Baza wiedzy — 20 artykułów startowych</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -5491,11 +5491,11 @@
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>19</v>
@@ -5527,28 +5527,254 @@
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="11" t="inlineStr">
+        <is>
+          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+        </is>
+      </c>
+      <c r="O61" s="11" t="inlineStr">
+        <is>
+          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+        </is>
+      </c>
+      <c r="P61" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>PB-10</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNI</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>PB-06 (kampania kieruje na landing)</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr">
+        <is>
+          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+        </is>
+      </c>
+      <c r="O62" s="11" t="inlineStr">
+        <is>
+          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+        </is>
+      </c>
+      <c r="P62" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>PB-05</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Test end-to-end „pierwszy klient”</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>wszystkie blokery zamknięte (sprint 8)</t>
+        </is>
+      </c>
+      <c r="N63" s="11" t="inlineStr">
+        <is>
+          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+        </is>
+      </c>
+      <c r="O63" s="11" t="inlineStr">
+        <is>
+          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+        </is>
+      </c>
+      <c r="P63" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>PB-12</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Runbook startu i decyzja GO</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H64" s="10" t="inlineStr"/>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
           <t>PB-05 (decyzja GO po przejściu ścieżki na produkcji)</t>
         </is>
       </c>
-      <c r="N61" s="11" t="inlineStr">
+      <c r="N64" s="11" t="inlineStr">
         <is>
           <t>Każdy z 11 blokerów ma wpis: co zrobiono, gdzie jest dowód, kto potwierdził. Bez formuły „warunkowe GO”.</t>
         </is>
       </c>
-      <c r="O61" s="11" t="inlineStr">
+      <c r="O64" s="11" t="inlineStr">
         <is>
           <t>Domknięcie: przegląd wszystkich blokerów z dowodem zamknięcia, decyzja GO/NO-GO zapisana z datą.</t>
         </is>
       </c>
-      <c r="P61" s="10" t="inlineStr">
+      <c r="P64" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P61"/>
-  <conditionalFormatting sqref="E2:E61">
+  <autoFilter ref="A1:P64"/>
+  <conditionalFormatting sqref="E2:E64">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>
@@ -5568,7 +5794,7 @@
       <formula>"ŚREDNI"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P61">
+  <conditionalFormatting sqref="P2:P64">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"zrobione"</formula>
     </cfRule>
@@ -5586,7 +5812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5678,11 +5904,11 @@
         </is>
       </c>
       <c r="F2" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A2)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A2)</f>
         <v/>
       </c>
       <c r="G2" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A2,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A2,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H2" s="10" t="n">
@@ -5723,11 +5949,11 @@
         </is>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A3)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A3)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A3,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A3,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H3" s="10" t="n">
@@ -5764,15 +5990,15 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Odporność płatności i porządek w fakturach</t>
+          <t>Pojemność węzła i plan produkcyjny</t>
         </is>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A4)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A4)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A4,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A4,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H4" s="10" t="n">
@@ -5784,7 +6010,7 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Z-05 wymaga przeniesienia zapisu zdarzenia do tej samej transakcji co handler. Przy okazji sprawdzić, czy inne webhooki nie mają tego samego wzorca.</t>
+          <t>Sprintu nie było w planie z 2026-08. Dołożony po PB-01, które pokazało, że przy dzisiejszym placemencie na węźle mieści się 16 kont, a próg rentowności przy cenie 45 zł to 58. Dopóki Z-12 jest otwarte, sprzedaż zatrzymuje się na szesnastym koncie niezależnie od popytu — selektor odmówi provisioningu. Z-13 idzie razem, bo bez planu produkcyjnego w bazie nie ma czego umieszczać ani na czym testować nadsubskrypcji. PB-14 zamyka sprint, bo wybór dostawcy przesądza o rentowności bardziej niż cokolwiek innego w tym modelu, a decyzja musi zapaść przed zamówieniem serwera w sprincie 8.</t>
         </is>
       </c>
     </row>
@@ -5809,15 +6035,15 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Faktura dla każdej płatności — część 1</t>
+          <t>Odporność płatności i porządek w fakturach</t>
         </is>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A5)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A5)</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A5,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A5,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n">
@@ -5829,7 +6055,7 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>Największa pojedyncza pozycja w planie i zmiana architektoniczna: wszystkie obciążenia portfela muszą przechodzić przez InvoicesService. Jeśli ma się rozjechać, rozjedzie się tutaj.</t>
+          <t>Z-05 wymaga przeniesienia zapisu zdarzenia do tej samej transakcji co handler. Przy okazji sprawdzić, czy inne webhooki nie mają tego samego wzorca.</t>
         </is>
       </c>
     </row>
@@ -5854,15 +6080,15 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Faktura dla każdej płatności — domknięcie, DPA, abuse</t>
+          <t>Faktura dla każdej płatności — część 1</t>
         </is>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A6)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A6)</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A6,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A6,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n">
@@ -5874,7 +6100,7 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>P-15 zaczyna się tu, bo podpisanie DPA zależy od tempa dostawców, nie od nas. Wysłać wnioski w poniedziałek sprintu.</t>
+          <t>Największa pojedyncza pozycja w planie i zmiana architektoniczna: wszystkie obciążenia portfela muszą przechodzić przez InvoicesService. Jeśli ma się rozjechać, rozjedzie się tutaj.</t>
         </is>
       </c>
     </row>
@@ -5899,15 +6125,15 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Faktury korygujące — część 1</t>
+          <t>Faktura dla każdej płatności — domknięcie, DPA, abuse</t>
         </is>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A7)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A7,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A7,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n">
@@ -5919,7 +6145,7 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>Korekta pociąga za sobą model danych, PDF i portfel naraz. Nie da się jej zrobić w połowie. Wysyłkę korekty do KSeF zostawiamy na sprint 17 — model musi ją przewidzieć już teraz.</t>
+          <t>P-15 zaczyna się tu, bo podpisanie DPA zależy od tempa dostawców, nie od nas. Wysłać wnioski w poniedziałek sprintu.</t>
         </is>
       </c>
     </row>
@@ -5944,15 +6170,15 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Faktury korygujące — domknięcie, węzeł produkcyjny</t>
+          <t>Faktury korygujące — część 1</t>
         </is>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A8)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A8)</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A8,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A8,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n">
@@ -5964,7 +6190,7 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Węzeł #1 musi stanąć przed sprintem 8, bo drill odtworzeniowy wykonujemy na nim.</t>
+          <t>Korekta pociąga za sobą model danych, PDF i portfel naraz. Nie da się jej zrobić w połowie. Wysyłkę korekty do KSeF zostawiamy na sprint 18 — model musi ją przewidzieć już teraz.</t>
         </is>
       </c>
     </row>
@@ -5989,15 +6215,15 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Dowód odtworzenia kopii i domknięcie DPA</t>
+          <t>Faktury korygujące — domknięcie, węzeł produkcyjny</t>
         </is>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A9)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A9)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A9,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A9,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n">
@@ -6009,7 +6235,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>Kamień milowy: po tym sprincie zamknięte są wszystkie blokery poza KSeF-em, który świadomie stoi na końcu. Drill może wykazać, że odtworzenie nie działa — wtedy sprint się przedłuża i tak ma być.</t>
+          <t>Węzeł #1 musi stanąć przed sprintem 9, bo drill odtworzeniowy wykonujemy na nim.</t>
         </is>
       </c>
     </row>
@@ -6034,15 +6260,15 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Odzyskanie funkcji-widm: bazy danych</t>
+          <t>Dowód odtworzenia kopii i domknięcie DPA</t>
         </is>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A10)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A10)</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A10,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A10,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n">
@@ -6054,7 +6280,7 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>Pięć pozycji, jeden kontroler. Najlepszy stosunek wartości do pracy w całym planie.</t>
+          <t>Kamień milowy: po tym sprincie zamknięte są wszystkie blokery poza KSeF-em, który świadomie stoi na końcu. Drill może wykazać, że odtworzenie nie działa — wtedy sprint się przedłuża i tak ma być.</t>
         </is>
       </c>
     </row>
@@ -6079,15 +6305,15 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>DNS i SSO — koniec z wysyłaniem klienta do DirectAdmina</t>
+          <t>Odzyskanie funkcji-widm: bazy danych</t>
         </is>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A11)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A11)</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A11,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A11,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n">
@@ -6099,7 +6325,7 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>Trasa hosting-sso-url nie istnieje w API — to nowy endpoint, nie podpięcie istniejącego. Nie mylić z SSO admina do węzłów, które działa. Import i eksport bazy świadomie zostaje w epiku E-01 po starcie — phpMyAdmin z działającym SSO załatwia ten scenariusz na start.</t>
+          <t>Pięć pozycji, jeden kontroler. Najlepszy stosunek wartości do pracy w całym planie.</t>
         </is>
       </c>
     </row>
@@ -6124,15 +6350,15 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Poczta: dostarczalność i zarządzanie skrzynkami</t>
+          <t>DNS i SSO — koniec z wysyłaniem klienta do DirectAdmina</t>
         </is>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A12)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A12)</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A12,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A12,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n">
@@ -6144,7 +6370,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>Brak SPF/DKIM w panelu to najczęstsza przyczyna „moja poczta trafia do spamu”. Backend działa — to jest wyłącznie podpięcie osieroconego komponentu.</t>
+          <t>Trasa hosting-sso-url nie istnieje w API — to nowy endpoint, nie podpięcie istniejącego. Nie mylić z SSO admina do węzłów, które działa. Import i eksport bazy świadomie zostaje w epiku E-01 po starcie — phpMyAdmin z działającym SSO załatwia ten scenariusz na start.</t>
         </is>
       </c>
     </row>
@@ -6169,15 +6395,15 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Warstwa operatorska: zatrzymywanie szkody</t>
+          <t>Poczta: dostarczalność i zarządzanie skrzynkami</t>
         </is>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A13)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A13)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A13,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A13,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n">
@@ -6189,7 +6415,7 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>Bez tego pierwszy incydent obsługujesz curlem o drugiej w nocy. Wszystkie cztery pierwsze pozycje to endpointy, które już działają.</t>
+          <t>Brak SPF/DKIM w panelu to najczęstsza przyczyna „moja poczta trafia do spamu”. Backend działa — to jest wyłącznie podpięcie osieroconego komponentu.</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6440,15 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Backup, staging i decyzja o kierunku fakturowania</t>
+          <t>Warstwa operatorska: zatrzymywanie szkody</t>
         </is>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A14)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A14)</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A14,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A14,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n">
@@ -6234,7 +6460,7 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>PB-13 musi zapaść tutaj, nie później — od niej zależy zakres sprintu 17. Odkładanie tej decyzji jest jedynym sposobem, żeby KSeF stał się blokerem w ostatnim tygodniu.</t>
+          <t>Bez tego pierwszy incydent obsługujesz curlem o drugiej w nocy. Wszystkie cztery pierwsze pozycje to endpointy, które już działają.</t>
         </is>
       </c>
     </row>
@@ -6259,15 +6485,15 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Rozliczenia od strony klienta i odporność operacyjna</t>
+          <t>Backup, staging i decyzja o kierunku fakturowania</t>
         </is>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A15)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A15)</f>
         <v/>
       </c>
       <c r="G15" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A15,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A15,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n">
@@ -6279,7 +6505,7 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>N-16 to włączenie flagi plus check w live-readiness — ale regulamin obiecuje kredyty, więc najpierw przeliczyć je na realnych danych z probe'ów.</t>
+          <t>PB-13 musi zapaść tutaj, nie później — od niej zależy zakres sprintu 18. Odkładanie tej decyzji jest jedynym sposobem, żeby KSeF stał się blokerem w ostatnim tygodniu.</t>
         </is>
       </c>
     </row>
@@ -6304,15 +6530,15 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Dokumenty prawne i treści produktowe</t>
+          <t>Rozliczenia od strony klienta i odporność operacyjna</t>
         </is>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A16)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A16)</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A16,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A16,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n">
@@ -6324,7 +6550,7 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>Cennik musi być zgodny z wynikiem PB-01. Jeśli unit economics wyszło źle, ten sprint jest momentem korekty ceny — nie później.</t>
+          <t>N-16 to włączenie flagi plus check w live-readiness — ale regulamin obiecuje kredyty, więc najpierw przeliczyć je na realnych danych z probe'ów.</t>
         </is>
       </c>
     </row>
@@ -6349,15 +6575,15 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Landing migracyjny i pomiar</t>
+          <t>Dokumenty prawne i treści produktowe</t>
         </is>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A17)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A17)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A17,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A17,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n">
@@ -6369,7 +6595,7 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>Landing nie może obiecywać funkcji ze statusem LUKA lub ATRAPA. Każde zdanie sprawdzić wobec macierzy — to jest dokładnie ten błąd, który audyt wykrył w oferta.md.</t>
+          <t>Cennik musi być zgodny z wynikiem PB-01. Jeśli unit economics wyszło źle, ten sprint jest momentem korekty ceny — nie później.</t>
         </is>
       </c>
     </row>
@@ -6394,15 +6620,15 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>KSeF — domknięcie tuż przed sprzedażą</t>
+          <t>Landing migracyjny i pomiar</t>
         </is>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A18)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A18)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A18,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A18,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n">
@@ -6414,7 +6640,7 @@
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>Zakres tego sprintu zależy od PB-13. Jeśli wybrana integracja z programem księgowym — te trzy pozycje zamienią się na wdrożenie eksportu i sprint będzie krótszy. Smoke na api-test MF wykonać w poniedziałek, nie w czwartek: rozbieżność schematu ujawnia się dopiero na środowisku MF.</t>
+          <t>Landing nie może obiecywać funkcji ze statusem LUKA lub ATRAPA. Każde zdanie sprawdzić wobec macierzy — to jest dokładnie ten błąd, który audyt wykrył w oferta.md.</t>
         </is>
       </c>
     </row>
@@ -6439,15 +6665,15 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy, KSeF od strony klienta, kampania</t>
+          <t>KSeF — domknięcie tuż przed sprzedażą</t>
         </is>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A19)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A19)</f>
         <v/>
       </c>
       <c r="G19" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A19,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A19,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n">
@@ -6459,7 +6685,7 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>Kampania powstaje wstrzymana. Uruchomienie dopiero po PB-05 w sprincie 19.</t>
+          <t>Zakres tego sprintu zależy od PB-13. Jeśli wybrana integracja z programem księgowym — te trzy pozycje zamienią się na wdrożenie eksportu i sprint będzie krótszy. Smoke na api-test MF wykonać w poniedziałek, nie w czwartek: rozbieżność schematu ujawnia się dopiero na środowisku MF.</t>
         </is>
       </c>
     </row>
@@ -6484,15 +6710,15 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Ścieżka pierwszego klienta na produkcji i decyzja GO</t>
+          <t>Baza wiedzy, KSeF od strony klienta, kampania</t>
         </is>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$61,A20)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A20)</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$61,A20,'Backlog do startu'!$F$2:$F$61)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A20,'Backlog do startu'!$F$2:$F$64)</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n">
@@ -6504,13 +6730,54 @@
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
+          <t>Kampania powstaje wstrzymana. Uruchomienie dopiero po PB-05 w sprincie 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Ścieżka pierwszego klienta na produkcji i decyzja GO</t>
+        </is>
+      </c>
+      <c r="F21" s="10">
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="10">
+        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A21,'Backlog do startu'!$F$2:$F$64)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="12">
+        <f>IFERROR(G21/H21,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
           <t>Jedyny moment w całym planie, w którym powstaje dowód poziomu D3. Każdy nieudany krok wraca do backlogu jako bloker i przesuwa start. Zaplanowane 24 h zostawiają zapas na to, co wyjdzie.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J20"/>
-  <conditionalFormatting sqref="G2:G20">
+  <autoFilter ref="A1:J21"/>
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2180</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>72.7</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="10" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>provisioning.service.ts:299-301 zwiększa allocatedCpu/allocatedMemory/allocatedDisk o pełne limity planu; node-selector.service.ts:109-115 wpuszcza konto tylko gdy total-allocated ≥ limit planu + headroom; schema.prisma:474 reservedHeadroomPercent Int @default(0)</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>Odkryte przy PB-01. Węzeł księguje 8 GB RAM i 2 vCPU na każde konto, mimo że w LVE to sufity burst, a nie rezerwacje. Skutek arytmetyczny: 128 GB / 8 GB = 16 kont na węzeł i selektor przestaje wpuszczać kolejne. Próg rentowności przy cenie 45 zł to 58 kont. Oznacza to, że przy dzisiejszym kodzie każdy węzeł domyka się na stracie ok. 1 074 zł/mies. i nie da się tego naprawić sprzedażą — selektor po prostu odmówi provisioningu. To nie jest optymalizacja kosztu, to warunek istnienia oferty. Do zrobienia: współczynniki nadsubskrypcji per węzeł (overcommitCpu/Ram/Disk) użyte w node-selector, oddzielenie księgowania 'sprzedane' od 'realnie zajęte', alarm gdy realne zużycie zbliża się do pojemności. Dysk traktować ostrożniej niż RAM i CPU: quota dyskowa jest realnie egzekwowana i klient może ją wypełnić w całości. Model: docs/strategy/PB-01_unit_economics_wezla.xlsx</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P10" s="10" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8580,17 +8580,17 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>Z-15</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Wydajność: cache i skalowanie</t>
+          <t>Runtime, pliki i diagnostyka</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -8605,21 +8605,21 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Redis / cache obiektowy dla klienta</t>
+          <t>Alert wyprzedzający, gdy realne zużycie węzła zbliża się do progu</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I34" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="K34" s="11" t="inlineStr">
         <is>
-          <t>3 z 5 hostingów PL ma w cenie — realny wyróżnik dla WordPressa</t>
+          <t>node-capacity.ts — bramka fizyczna odmawia po przekroczeniu progu, nie przed</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Memcached</t>
+          <t>Redis / cache obiektowy dla klienta</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I35" s="10" t="n">
@@ -8681,12 +8681,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>3 z 5 hostingów PL ma w cenie — realny wyróżnik dla WordPressa</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>J-01</t>
+          <t>D-16</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -8711,37 +8715,33 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>LiteSpeed / serwer o wysokiej wydajności</t>
+          <t>Memcached</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I36" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
-        </is>
-      </c>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>decyzja infrastrukturalna, poza kodem panelu</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>J-02</t>
+          <t>J-01</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Cache stron (LSCache) sterowany z panelu</t>
+          <t>LiteSpeed / serwer o wysokiej wydajności</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -8780,19 +8780,23 @@
         </is>
       </c>
       <c r="I37" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr"/>
+          <t>b.d.</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>decyzja infrastrukturalna, poza kodem panelu</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>J-03</t>
+          <t>J-02</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -8817,7 +8821,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Cache obiektowy (Redis) dla WordPressa</t>
+          <t>Cache stron (LSCache) sterowany z panelu</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -8838,16 +8842,12 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
-        <is>
-          <t>patrz D-15</t>
-        </is>
-      </c>
+      <c r="K38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>J-04</t>
+          <t>J-03</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>HTTP/3</t>
+          <t>Cache obiektowy (Redis) dla WordPressa</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -8882,27 +8882,27 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I39" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
         <is>
-          <t>poza kodem panelu</t>
+          <t>patrz D-15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>J-05</t>
+          <t>J-04</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>HTTP/3</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -8937,27 +8937,27 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I40" s="10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
-          <t>na rynku PL płatny dodatek</t>
+          <t>poza kodem panelu</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>J-06</t>
+          <t>J-05</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Optymalizacja obrazów</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -8996,19 +8996,23 @@
         </is>
       </c>
       <c r="I41" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>na rynku PL płatny dodatek</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>J-07</t>
+          <t>J-06</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -9033,7 +9037,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Dedykowany adres IP</t>
+          <t>Optymalizacja obrazów</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -9043,37 +9047,33 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I42" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K42" s="11" t="inlineStr">
-        <is>
-          <t>addons — jako dodatek typu workorder</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>J-07</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Backup: granularność i retencja</t>
+          <t>Wydajność: cache i skalowanie</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -9088,21 +9088,21 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Retencja co najmniej 28 dni w cenie</t>
+          <t>Dedykowany adres IP</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I43" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="K43" s="11" t="inlineStr">
         <is>
-          <t>off-site: 30 dni (node-offsite-backup.sh:101)</t>
+          <t>addons — jako dodatek typu workorder</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>Odtworzenie pojedynczego pliku</t>
+          <t>Retencja co najmniej 28 dni w cenie</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -9161,19 +9161,19 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>JetBackup/Plesk to mają; seohost i dhosting też</t>
+          <t>off-site: 30 dni (node-offsite-backup.sh:101)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zawartości archiwum przed odtworzeniem</t>
+          <t>Odtworzenie pojedynczego pliku</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -9216,19 +9216,19 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:788-793 — buduje z BIEŻĄCEGO inwentarza konta, nie z archiwum</t>
+          <t>JetBackup/Plesk to mają; seohost i dhosting też</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>H-13</t>
+          <t>H-11</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>Pobranie archiwum kopii lokalnie</t>
+          <t>Podgląd zawartości archiwum przed odtworzeniem</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -9263,27 +9263,27 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I46" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:855 — kopiuje na konto, nie do przeglądarki</t>
+          <t>services.controller.ts:788-793 — buduje z BIEŻĄCEGO inwentarza konta, nie z archiwum</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>H-16</t>
+          <t>H-13</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>ODTWORZENIE KONTA NA INNY WĘZEŁ</t>
+          <t>Pobranie archiwum kopii lokalnie</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -9318,27 +9318,27 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I47" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts:125 kieruje zadanie na account.serverId; node-account-restore.sh:76 przerywa gdy brak katalogu</t>
+          <t>services.controller.ts:855 — kopiuje na konto, nie do przeglądarki</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>H-18</t>
+          <t>H-16</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>Odtworzenie konta przez operatora z panelu</t>
+          <t>ODTWORZENIE KONTA NA INNY WĘZEŁ</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -9373,27 +9373,27 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I48" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:69,86 — zero wywołań w admin-panel</t>
+          <t>offsite-restore.service.ts:125 kieruje zadanie na account.serverId; node-account-restore.sh:76 przerywa gdy brak katalogu</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>H-19</t>
+          <t>H-18</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>Automatyczna konfiguracja backupu przy wdrożeniu węzła</t>
+          <t>Odtworzenie konta przez operatora z panelu</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -9428,37 +9428,37 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I49" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>node-onboard-live.sh:240-244 tylko log_warn; wizard węzła (wizard-content.ts:21-40) nie ma kroku backupu</t>
+          <t>subscriptions.admin.controller.ts:69,86 — zero wywołań w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>H-19</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Rozliczenia: dokończenie</t>
+          <t>Backup: granularność i retencja</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -9473,17 +9473,17 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>DUPLIKAT FAKTURY</t>
+          <t>Automatyczna konfiguracja backupu przy wdrożeniu węzła</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I50" s="10" t="n">
@@ -9496,14 +9496,14 @@
       </c>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>brak flagi isDuplicate, brak endpointu</t>
+          <t>node-onboard-live.sh:240-244 tylko log_warn; wizard węzła (wizard-content.ts:21-40) nie ma kroku backupu</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Stawki VAT inne niż 23%</t>
+          <t>DUPLIKAT FAKTURY</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I51" s="10" t="n">
@@ -9551,14 +9551,14 @@
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:17 — DEFAULT_VAT_RATE = 23 na sztywno</t>
+          <t>brak flagi isDuplicate, brak endpointu</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Faktury w walucie obcej z przeliczeniem VAT</t>
+          <t>Stawki VAT inne niż 23%</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -9601,19 +9601,19 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>invoice-pdf.service.ts:61 formatuje PLN/EUR/USD; brak kursu i przeliczenia (art. 31a)</t>
+          <t>invoices.service.ts:17 — DEFAULT_VAT_RATE = 23 na sztywno</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>Proforma przed odnowieniem</t>
+          <t>Faktury w walucie obcej z przeliczeniem VAT</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I53" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
@@ -9661,14 +9661,14 @@
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>renewal-reminder.scheduler.ts — przypomnienie, nie proforma</t>
+          <t>invoice-pdf.service.ts:61 formatuje PLN/EUR/USD; brak kursu i przeliczenia (art. 31a)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>M-27</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Dodanie karty niezależnie od zakupu</t>
+          <t>Proforma przed odnowieniem</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -9711,19 +9711,19 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>karta zapisuje się tylko przy okazji Stripe Checkout</t>
+          <t>renewal-reminder.scheduler.ts — przypomnienie, nie proforma</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>M-28</t>
+          <t>M-27</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>Eksport historii transakcji do CSV</t>
+          <t>Dodanie karty niezależnie od zakupu</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I55" s="10" t="n">
@@ -9766,19 +9766,19 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:70 — zero odwołań w panelu</t>
+          <t>karta zapisuje się tylko przy okazji Stripe Checkout</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>M-33</t>
+          <t>M-28</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>Dodatki płatne (IP, wsparcie priorytetowe)</t>
+          <t>Eksport historii transakcji do CSV</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -9817,23 +9817,23 @@
         </is>
       </c>
       <c r="I56" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>addon.service.ts:120 — 2 z 3 to workorder do BOK</t>
+          <t>billing.controller.ts:70 — zero odwołań w panelu</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Z-07</t>
+          <t>M-33</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>Ponowienie płatności portfelem w okresie karencji</t>
+          <t>Dodatki płatne (IP, wsparcie priorytetowe)</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I57" s="10" t="n">
@@ -9876,19 +9876,19 @@
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
+          <t>addon.service.ts:120 — 2 z 3 to workorder do BOK</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Z-08</t>
+          <t>Z-07</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
+          <t>Ponowienie płatności portfelem w okresie karencji</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
@@ -9923,11 +9923,11 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I58" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
@@ -9936,14 +9936,14 @@
       </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
+          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Z-11</t>
+          <t>Z-08</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
+          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -9982,33 +9982,33 @@
         </is>
       </c>
       <c r="I59" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
+          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>Z-11</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie i ops: kolejka abuse</t>
+          <t>Rozliczenia: dokończenie</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -10023,37 +10023,37 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I60" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I61" s="10" t="n">
@@ -10096,19 +10096,19 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
@@ -10143,27 +10143,27 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I62" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -10198,11 +10198,11 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I63" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
@@ -10211,14 +10211,14 @@
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -10253,27 +10253,27 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I64" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -10308,27 +10308,27 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I65" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -10367,38 +10367,38 @@
         </is>
       </c>
       <c r="I66" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>WordPress Toolkit</t>
+          <t>Wsparcie i ops: kolejka abuse</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -10408,21 +10408,21 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Automatyczne aktualizacje WordPressa</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I67" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
@@ -10431,14 +10431,14 @@
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL to ma</t>
+          <t>poza produktem</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>I-05</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Aktualizacje wtyczek i motywów z panelu</t>
+          <t>Automatyczne aktualizacje WordPressa</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I68" s="10" t="n">
@@ -10484,12 +10484,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>4 z 5 hostingów PL to ma</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>I-07</t>
+          <t>I-05</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -10514,7 +10518,7 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>Skanowanie podatności WordPressa</t>
+          <t>Aktualizacje wtyczek i motywów z panelu</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -10528,23 +10532,19 @@
         </is>
       </c>
       <c r="I69" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K69" s="11" t="inlineStr">
-        <is>
-          <t>Plesk używa Patchstack</t>
-        </is>
-      </c>
+      <c r="K69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>I-08</t>
+          <t>I-07</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Hardening WordPressa (checklist)</t>
+          <t>Skanowanie podatności WordPressa</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -10583,19 +10583,23 @@
         </is>
       </c>
       <c r="I70" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr">
+        <is>
+          <t>Plesk używa Patchstack</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>I-13</t>
+          <t>I-08</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -10620,7 +10624,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>Klonowanie strony między domenami</t>
+          <t>Hardening WordPressa (checklist)</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -10646,7 +10650,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>I-14</t>
+          <t>I-13</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -10671,7 +10675,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Masowe zarządzanie wieloma instalacjami WP</t>
+          <t>Klonowanie strony między domenami</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
@@ -10681,27 +10685,23 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I72" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K72" s="11" t="inlineStr">
-        <is>
-          <t>realna przewaga dla agencji</t>
-        </is>
-      </c>
+      <c r="K72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>I-15</t>
+          <t>I-14</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>Tryb konserwacji WordPressa</t>
+          <t>Masowe zarządzanie wieloma instalacjami WP</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -10740,19 +10740,23 @@
         </is>
       </c>
       <c r="I73" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>realna przewaga dla agencji</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>I-16</t>
+          <t>I-15</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -10777,7 +10781,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>WP-CLI</t>
+          <t>Tryb konserwacji WordPressa</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -10787,7 +10791,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I74" s="10" t="n">
@@ -10795,19 +10799,15 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>używane wewnętrznie przy WP_INSTALL</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>I-18</t>
+          <t>I-16</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>Migracja — test poświadczeń (preflight)</t>
+          <t>WP-CLI</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -10855,14 +10855,14 @@
       </c>
       <c r="K75" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:1001</t>
+          <t>używane wewnętrznie przy WP_INSTALL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>I-22</t>
+          <t>I-18</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Migracja — cockpit operatora</t>
+          <t>Migracja — test poświadczeń (preflight)</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -10910,24 +10910,24 @@
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>migrations.staff.controller.ts:75,90,126</t>
+          <t>services.controller.ts:1001</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>I-22</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Domeny jako produkt</t>
+          <t>WordPress Toolkit</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -10942,17 +10942,17 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>Zmiana document root domeny</t>
+          <t>Migracja — cockpit operatora</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I77" s="10" t="n">
@@ -10960,19 +10960,19 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>DA to potrafi; brak UI</t>
+          <t>migrations.staff.controller.ts:75,90,126</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>A-08</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Rejestracja domeny z panelu</t>
+          <t>Zmiana document root domeny</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -11007,27 +11007,27 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I78" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:118</t>
+          <t>DA to potrafi; brak UI</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-08</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Transfer domeny (kod authinfo)</t>
+          <t>Rejestracja domeny z panelu</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I79" s="10" t="n">
@@ -11075,14 +11075,14 @@
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:123</t>
+          <t>domains.controller.ts:118</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>A-10</t>
+          <t>A-09</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Odnowienie domeny przez klienta</t>
+          <t>Transfer domeny (kod authinfo)</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -11117,27 +11117,27 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I80" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:133</t>
+          <t>domains.controller.ts:123</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>A-12</t>
+          <t>A-10</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>Cennik rejestracji na 1–10 lat</t>
+          <t>Odnowienie domeny przez klienta</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -11180,19 +11180,19 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:59</t>
+          <t>domains.controller.ts:133</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>A-12</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Zmiana danych abonenta domeny</t>
+          <t>Cennik rejestracji na 1–10 lat</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -11227,27 +11227,27 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I82" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>wymóg operatorski przy własnej rejestracji</t>
+          <t>domains.controller.ts:59</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>A-13</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>Ukrycie danych WHOIS / domain privacy</t>
+          <t>Zmiana danych abonenta domeny</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -11282,23 +11282,27 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I83" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>wymóg operatorski przy własnej rejestracji</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>A-15</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -11323,7 +11327,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Blokada transferu domeny (transfer lock)</t>
+          <t>Ukrycie danych WHOIS / domain privacy</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -11333,7 +11337,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I84" s="10" t="n">
@@ -11349,7 +11353,7 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>A-16</t>
+          <t>A-15</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -11374,7 +11378,7 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Weryfikacja własności domeny</t>
+          <t>Blokada transferu domeny (transfer lock)</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -11384,27 +11388,23 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I85" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K85" s="11" t="inlineStr">
-        <is>
-          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-16</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Zakładanie konta klienta przez operatora</t>
+          <t>Weryfikacja własności domeny</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -11447,29 +11447,29 @@
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>brak @Post w users.admin.controller.ts</t>
+          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Katalog aplikacji</t>
+          <t>Domeny jako produkt</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
@@ -11479,17 +11479,17 @@
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>Autoinstalator aplikacji</t>
+          <t>Zakładanie konta klienta przez operatora</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -11502,29 +11502,29 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+          <t>brak @Post w users.admin.controller.ts</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Poczta: filtry, kalendarz, limity</t>
+          <t>Katalog aplikacji</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -11539,33 +11539,37 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zużycia skrzynki</t>
+          <t>Autoinstalator aplikacji</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I88" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K88" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="inlineStr">
+        <is>
+          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -11590,7 +11594,7 @@
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>Reguły filtrowania poczty (Sieve)</t>
+          <t>Podgląd zużycia skrzynki</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -11604,23 +11608,19 @@
         </is>
       </c>
       <c r="I89" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K89" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to ma</t>
-        </is>
-      </c>
+      <c r="K89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Webmail — dostęp</t>
+          <t>Reguły filtrowania poczty (Sieve)</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -11659,23 +11659,23 @@
         </is>
       </c>
       <c r="I90" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>link do DA</t>
+          <t>wszystkie 5 hostingów PL to ma</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>E-18</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>Sprawdzenie obecności na RBL</t>
+          <t>Webmail — dostęp</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -11718,19 +11718,19 @@
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>link do DA</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>E-19</t>
+          <t>E-18</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Podgląd kolejki i logów dostarczania</t>
+          <t>Sprawdzenie obecności na RBL</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -11769,23 +11769,23 @@
         </is>
       </c>
       <c r="I92" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>E-20</t>
+          <t>E-19</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Limity wysyłki pokazane klientowi</t>
+          <t>Podgląd kolejki i logów dostarczania</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="I93" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
@@ -11833,14 +11833,14 @@
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
+          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>E-21</t>
+          <t>E-20</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Samodzielny import skrzynek przez IMAP</t>
+          <t>Limity wysyłki pokazane klientowi</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -11883,19 +11883,19 @@
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>w ramach migracji, nie jako osobne narzędzie</t>
+          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>E-23</t>
+          <t>E-21</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
+          <t>Samodzielny import skrzynek przez IMAP</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -11930,27 +11930,27 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I95" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
+          <t>w ramach migracji, nie jako osobne narzędzie</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>E-24</t>
+          <t>E-23</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>2FA dla webmaila</t>
+          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="I96" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
@@ -11998,29 +11998,29 @@
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>E-24</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Bezpieczeństwo jako funkcja</t>
+          <t>Poczta: filtry, kalendarz, limity</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>HSTS</t>
+          <t>2FA dla webmaila</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
@@ -12044,19 +12044,23 @@
         </is>
       </c>
       <c r="I97" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K97" s="11" t="inlineStr"/>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>G-08</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -12081,7 +12085,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Sprzedaż certyfikatów DV/OV/EV</t>
+          <t>HSTS</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -12095,23 +12099,19 @@
         </is>
       </c>
       <c r="I98" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K98" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to sprzedaje</t>
-        </is>
-      </c>
+      <c r="K98" s="11" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>G-08</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>Skaner malware dla klienta</t>
+          <t>Sprzedaż certyfikatów DV/OV/EV</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -12146,11 +12146,11 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I99" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
@@ -12159,14 +12159,14 @@
       </c>
       <c r="K99" s="11" t="inlineStr">
         <is>
-          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+          <t>wszystkie 5 hostingów PL to sprzedaje</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>G-12</t>
+          <t>G-11</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Czyszczenie zainfekowanych plików</t>
+          <t>Skaner malware dla klienta</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I100" s="10" t="n">
@@ -12212,12 +12212,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K100" s="11" t="inlineStr"/>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>G-19</t>
+          <t>G-12</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -12242,7 +12246,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Auto-wylogowanie po bezczynności</t>
+          <t>Czyszczenie zainfekowanych plików</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -12256,23 +12260,19 @@
         </is>
       </c>
       <c r="I101" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K101" s="11" t="inlineStr">
-        <is>
-          <t>session-idle-guard.tsx</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>G-21</t>
+          <t>G-19</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Anty-DDoS</t>
+          <t>Auto-wylogowanie po bezczynności</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -12311,23 +12311,23 @@
         </is>
       </c>
       <c r="I102" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+          <t>session-idle-guard.tsx</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>G-22</t>
+          <t>G-21</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienie o podejrzanym logowaniu</t>
+          <t>Anty-DDoS</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -12362,23 +12362,27 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I103" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K103" s="11" t="inlineStr"/>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Z-09</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -12403,7 +12407,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
+          <t>Powiadomienie o podejrzanym logowaniu</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -12413,37 +12417,33 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I104" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K104" s="11" t="inlineStr">
-        <is>
-          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
-        </is>
-      </c>
+      <c r="K104" s="11" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>Z-09</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Reseller jako produkt</t>
+          <t>Bezpieczeństwo jako funkcja</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -12458,12 +12458,12 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>O — Multi-user i reseller</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -12476,19 +12476,19 @@
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="I106" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
@@ -12536,14 +12536,14 @@
       </c>
       <c r="K106" s="11" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -12586,19 +12586,19 @@
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>bez tego reseller nie jest produktem</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -12633,27 +12633,27 @@
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I108" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>bez tego reseller nie jest produktem</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -12696,19 +12696,19 @@
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -12747,23 +12747,23 @@
         </is>
       </c>
       <c r="I110" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I111" s="10" t="n">
@@ -12806,29 +12806,29 @@
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Dostępność i zgodność w produkcie</t>
+          <t>Reseller jako produkt</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -12843,37 +12843,37 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I112" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -12912,7 +12912,7 @@
         </is>
       </c>
       <c r="I113" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
@@ -12921,14 +12921,14 @@
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -12967,23 +12967,23 @@
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -13018,27 +13018,27 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I115" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>poza kodem</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -13063,47 +13063,47 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>DNS: DNSSEC i zarządzanie strefą</t>
+          <t>Dostępność i zgodność w produkcie</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
@@ -13118,37 +13118,37 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Link do strefy DNS w DirectAdmin</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I117" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:350</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>DNSSEC</t>
+          <t>Link do strefy DNS w DirectAdmin</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -13183,27 +13183,27 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I118" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
+          <t>services.controller.ts:350</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Zmiana TTL rekordów</t>
+          <t>DNSSEC</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -13242,23 +13242,23 @@
         </is>
       </c>
       <c r="I119" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>zależne od F-01</t>
+          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Anycast DNS</t>
+          <t>Zmiana TTL rekordów</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -13293,37 +13293,37 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I120" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>tylko nazwa.pl na rynku PL</t>
+          <t>zależne od F-01</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Automatyzacja: API zapisu i webhooki</t>
+          <t>DNS: DNSSEC i zarządzanie strefą</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -13338,21 +13338,21 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Zadanie cron — edycja</t>
+          <t>Anycast DNS</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>L — Automatyzacja</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I121" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
@@ -13361,14 +13361,14 @@
       </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>obecnie usuń i dodaj ponownie</t>
+          <t>tylko nazwa.pl na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Cron z interwałem 1 minuty</t>
+          <t>Zadanie cron — edycja</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I122" s="10" t="n">
@@ -13411,19 +13411,19 @@
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K122" s="11" t="inlineStr">
         <is>
-          <t>zależne od konfiguracji DA</t>
+          <t>obecnie usuń i dodaj ponownie</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Cron z wyborem wersji PHP</t>
+          <t>Cron z interwałem 1 minuty</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I123" s="10" t="n">
@@ -13466,19 +13466,19 @@
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>seohost to reklamuje</t>
+          <t>zależne od konfiguracji DA</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Podgląd wyniku ostatniego wykonania crona</t>
+          <t>Cron z wyborem wersji PHP</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -13517,19 +13517,23 @@
         </is>
       </c>
       <c r="I124" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K124" s="11" t="inlineStr"/>
+      <c r="K124" s="11" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -13554,7 +13558,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Publiczne API — zapis</t>
+          <t>Podgląd wyniku ostatniego wykonania crona</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -13568,23 +13572,19 @@
         </is>
       </c>
       <c r="I125" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K125" s="11" t="inlineStr">
-        <is>
-          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
-        </is>
-      </c>
+      <c r="K125" s="11" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Tokeny API z zakresami uprawnień</t>
+          <t>Publiczne API — zapis</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -13619,27 +13619,27 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I126" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K126" s="11" t="inlineStr">
         <is>
-          <t>api-tokens.controller.ts:35</t>
+          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-09</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>Webhooki dla klienta</t>
+          <t>Tokeny API z zakresami uprawnień</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -13678,19 +13678,23 @@
         </is>
       </c>
       <c r="I127" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K127" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>api-tokens.controller.ts:35</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -13715,7 +13719,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Asystent AI w panelu</t>
+          <t>Webhooki dla klienta</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -13725,27 +13729,23 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I128" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
-        </is>
-      </c>
-      <c r="K128" s="11" t="inlineStr">
-        <is>
-          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>Prognoza zużycia zasobów (AI)</t>
+          <t>Asystent AI w panelu</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I129" s="10" t="n">
@@ -13793,53 +13793,53 @@
       </c>
       <c r="K129" s="11" t="inlineStr">
         <is>
-          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
+          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Rozszerzenia oferty</t>
+          <t>Automatyzacja: API zapisu i webhooki</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>NISKI</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>Prognoza zużycia zasobów (AI)</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>L — Automatyzacja</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I130" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
@@ -13848,14 +13848,14 @@
       </c>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I131" s="10" t="n">
@@ -13898,15 +13898,19 @@
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K131" s="11" t="inlineStr"/>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -13931,7 +13935,7 @@
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
@@ -13957,7 +13961,7 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -13982,7 +13986,7 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -13992,7 +13996,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I133" s="10" t="n">
@@ -14000,49 +14004,45 @@
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K133" s="11" t="inlineStr">
-        <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
+          <t>Rozszerzenia oferty</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>ciągłe</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>NISKI</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>X — Infrastruktura jakości</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
@@ -14051,23 +14051,23 @@
         </is>
       </c>
       <c r="I134" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K134" s="11" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I135" s="10" t="n">
@@ -14115,14 +14115,14 @@
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -14157,11 +14157,11 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I136" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
@@ -14170,14 +14170,14 @@
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -14225,14 +14225,14 @@
       </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -14280,14 +14280,14 @@
       </c>
       <c r="K138" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -14326,7 +14326,7 @@
         </is>
       </c>
       <c r="I139" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
@@ -14335,67 +14335,122 @@
       </c>
       <c r="K139" s="11" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>X-09</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testami DirectAdminService</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="I140" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J140" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K140" s="11" t="inlineStr">
+        <is>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
           <t>X-10</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>E-09</t>
         </is>
       </c>
-      <c r="C140" s="11" t="inlineStr">
+      <c r="C141" s="11" t="inlineStr">
         <is>
           <t>Pokrycie testowe warstw krytycznych</t>
         </is>
       </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>ciągłe</t>
         </is>
       </c>
-      <c r="E140" s="10" t="inlineStr">
+      <c r="E141" s="10" t="inlineStr">
         <is>
           <t>WYSOKI</t>
         </is>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="F141" s="11" t="inlineStr">
         <is>
           <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
         </is>
       </c>
-      <c r="G140" s="10" t="inlineStr">
+      <c r="G141" s="10" t="inlineStr">
         <is>
           <t>X — Infrastruktura jakości</t>
         </is>
       </c>
-      <c r="H140" s="10" t="inlineStr">
+      <c r="H141" s="10" t="inlineStr">
         <is>
           <t>WYSOKA</t>
         </is>
       </c>
-      <c r="I140" s="10" t="n">
+      <c r="I141" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="J140" s="10" t="inlineStr">
+      <c r="J141" s="10" t="inlineStr">
         <is>
           <t>ATRAPA</t>
         </is>
       </c>
-      <c r="K140" s="11" t="inlineStr">
+      <c r="K141" s="11" t="inlineStr">
         <is>
           <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K140"/>
+  <autoFilter ref="A1:K141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$64)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$65)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$64,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$64,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$65,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$65,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$64,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$65,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$64,"zrobione",'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$65,"zrobione",'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>seed.ts:40-112 zawiera wyłącznie starter/pro/business (19,99/49,99/99,99 zł); apps/www/.../Pricing.tsx:120 sprzedaje 45 zł/399 zł, hosting/page.tsx:77 opisuje bazę 50 GB / 8 GB / 2 vCPU — planu o takich limitach nie ma w żadnym seedzie ani migracji</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Odkryte przy PB-01. Strona sprzedaje pakiet, którego nie ma po stronie produktu. Trzy plany w seedzie to próbki z czasów prototypu i mają inne ceny oraz inne limity niż cokolwiek, co Verris ogłasza publicznie. Dopóki plan nie istnieje jako rekord z cpuLimit/ramLimitMb/diskLimitMb, nie działa ani wycena, ani placement, ani synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh czyta limity z Planu). Do zrobienia: migracja tworząca plan produkcyjny z limitami zgodnymi z treścią oferty, wycofanie planów próbnych z isPublic, test sprawdzający, że każda cena widoczna na www ma odpowiadający jej aktywny plan.</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
@@ -1661,31 +1661,31 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>3</v>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>autoscaling-engine.service.ts:287 — Math.min(value, 10) przycina krotność niezależnie od planu, więc sufit CPU (12×) i dysku (20×) z oferty jest nieosiągalny; w całym pliku nie ma ani jednego odwołania do Server/allocated — silnik skaluje konto bez pytania węzła o pojemność i bez aktualizacji allocatedCpu/Memory/Disk</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Odkryte przy zamykaniu Z-13. Dwie rzeczy, jedna przyczyna — silnik autoskalowania nie wie nic o węźle, na którym stoi konto. | PIERWSZA: oferta obiecuje skalowanie do 24 vCPU i 1000 GB, a przycięcie do 10× daje realnie 20 vCPU i 500 GB. Klient płacący za nadwyżkę godzinowo nie dostanie tego, za co zapłacił, i będzie miał rację w reklamacji. | DRUGA i groźniejsza: silnik podnosi limity konta w DirectAdminie, nie sprawdzając, czy węzeł ma te zasoby, i nie zapisując ich w allocated*. Po Z-12 znaczy to, że dwie warstwy nadsubskrybują niezależnie od siebie i żadna nie widzi drugiej: placement liczy sprzedane limity BAZOWE, autoskalowanie dokłada do nich nadwyżkę poza księgą. Jedno konto może urosnąć do 1000 GB na węźle 1,92 TB — połowa dysku dla jednego klienta, o czym selektor się nie dowie. | Do zrobienia: sprawdzenie pojemności węzła przed skalowaniem w górę (ten sam node-capacity.ts), skalowanie częściowe zamiast odmowy, zapis nadwyżki w allocated* albo osobnej kolumnie, podniesienie progu 10× po dołożeniu tego zabezpieczenia — w tej kolejności, nie odwrotnie. | Rozbieżność sufitu jest utrwalona testem plan-produkcyjny.spec.ts, który zapali się przy zmianie progu i wymusi przejrzenie oferty.</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
@@ -1739,58 +1739,58 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts:444-453 — wiersz stripeWebhookEvent zapisywany PRZED handlerem (:455), poza transakcją, bez cofnięcia przy wyjątku; ponowienie ze Stripe trafia w :448-451 i zwraca duplicate:true; uznanie portfela (:523) nigdy nie następuje</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Klient zapłacił, saldo się nie pojawiło, system uważa zdarzenie za obsłużone i odrzuca ponowienia. Odzysk wyłącznie ręcznie w bazie — brak endpointu do ponownego przetworzenia.</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
@@ -1817,12 +1817,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1837,11 +1837,11 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>4</v>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>billing.service.ts:444-453 — wiersz stripeWebhookEvent zapisywany PRZED handlerem (:455), poza transakcją, bez cofnięcia przy wyjątku; ponowienie ze Stripe trafia w :448-451 i zwraca duplicate:true; uznanie portfela (:523) nigdy nie następuje</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1881,7 +1881,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr"/>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>Klient zapłacił, saldo się nie pojawiło, system uważa zdarzenie za obsłużone i odrzuca ponowienia. Odzysk wyłącznie ręcznie w bazie — brak endpointu do ponownego przetworzenia.</t>
+        </is>
+      </c>
       <c r="P14" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -1891,12 +1895,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1906,7 +1910,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -1942,24 +1946,20 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
-        <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
-        </is>
-      </c>
+      <c r="O15" s="11" t="inlineStr"/>
       <c r="P15" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -1969,12 +1969,12 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1984,19 +1984,19 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
@@ -2125,12 +2125,12 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>6</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -2203,27 +2203,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
@@ -2249,27 +2249,27 @@
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
@@ -2281,34 +2281,34 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
@@ -2317,37 +2317,37 @@
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
@@ -2437,31 +2437,31 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>8</v>
@@ -2483,27 +2483,27 @@
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr">
@@ -2515,73 +2515,73 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>H-20</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
         <v>16</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>ops/scripts/restore-drill-isolated.sh istnieje jako procedura ręczna; live-readiness.service.ts:175-177 sprawdza tylko czy backup się WYKONAŁ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>PB-02 (drill wykonujemy na węźle #1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker. Runbook wymaga drilla przed LIVE (OFFSITE_RESTORE_RUNBOOK.md:37-40) i nie ma w repo śladu jego wykonania. Backupy i DR wymagają poziomu D4 — data, wynik, właściciel. Bez tego cała warstwa DR jest niepotwierdzona.</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
@@ -2593,12 +2593,12 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>H-20</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>9</v>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>ops/scripts/restore-drill-isolated.sh istnieje jako procedura ręczna; live-readiness.service.ts:175-177 sprawdza tylko czy backup się WYKONAŁ</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-02 (drill wykonujemy na węźle #1)</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>POTWIERDZONE jako bloker. Runbook wymaga drilla przed LIVE (OFFSITE_RESTORE_RUNBOOK.md:37-40) i nie ma w repo śladu jego wykonania. Backupy i DR wymagają poziomu D4 — data, wynik, właściciel. Bez tego cała warstwa DR jest niepotwierdzona.</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Dodatkowy użytkownik bazy — utworzenie</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2686,50 +2686,50 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
-        </is>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — usunięcie</t>
+          <t>Dodatkowy użytkownik bazy — utworzenie</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — zmiana hasła</t>
+          <t>Użytkownik bazy — usunięcie</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -2905,12 +2905,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — lista</t>
+          <t>Użytkownik bazy — zmiana hasła</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2983,12 +2983,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — auto-logowanie (SSO)</t>
+          <t>Użytkownik bazy — lista</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
+          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
+          <t>phpMyAdmin — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3076,19 +3076,19 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
@@ -3097,22 +3097,22 @@
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SRV / CAA</t>
+          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>F-01 (ten sam edytor)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
@@ -3203,7 +3203,11 @@
           <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+        </is>
+      </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3213,12 +3217,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Webmail — auto-logowanie (SSO)</t>
+          <t>Rekordy SRV / CAA</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3228,12 +3232,12 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
@@ -3259,29 +3263,25 @@
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-01 (ten sam edytor)</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O32" s="11" t="inlineStr">
-        <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
-        </is>
-      </c>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr"/>
       <c r="P32" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3291,12 +3291,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per domena</t>
+          <t>Webmail — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>B — Runtime WWW</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
@@ -3369,12 +3369,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SPF — kreator</t>
+          <t>Zmiana wersji PHP per domena</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -3384,19 +3384,19 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
@@ -3405,22 +3405,22 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
+          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -3447,12 +3447,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Rekordy DKIM — konfiguracja</t>
+          <t>Rekordy SPF — kreator</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>E-15 (ten sam panel dostarczalności)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Rekord DMARC — konfiguracja</t>
+          <t>Rekordy DKIM — konfiguracja</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-15 (ten sam panel dostarczalności)</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -3603,12 +3603,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
+          <t>Rekord DMARC — konfiguracja</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -3649,27 +3649,27 @@
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
@@ -3681,12 +3681,12 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Usunięcie zapisanej karty przez klienta</t>
+          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>wymóg konsumencki</t>
+          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3759,12 +3759,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>M-26</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Ręczne zawieszenie usługi przez operatora</t>
+          <t>Usunięcie zapisanej karty przez klienta</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -3786,7 +3786,7 @@
         <v>6</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -3795,22 +3795,22 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:192</t>
+          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
+          <t>wymóg konsumencki</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
@@ -3837,12 +3837,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>A-25</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Ręczne odwieszenie usługi przez operatora</t>
+          <t>Ręczne zawieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:210</t>
+          <t>subscriptions.admin.controller.ts:192</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>A-25 (ten sam widok)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
+          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>A-26</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Ręczne odwieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>subscriptions.admin.controller.ts:210</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-25 (ten sam widok)</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>H-22</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Panel odtwarzania w widocznym miejscu</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -4117,12 +4117,12 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>klient w kryzysie tego nie znajdzie</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
@@ -4149,12 +4149,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>H-09</t>
+          <t>H-22</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
+          <t>Panel odtwarzania w widocznym miejscu</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -4176,7 +4176,7 @@
         <v>6</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -4185,12 +4185,12 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>hosting-restore.service.ts:167</t>
+          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
+          <t>klient w kryzysie tego nie znajdzie</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -4227,12 +4227,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>H-17</t>
+          <t>H-09</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
+          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4273,27 +4273,27 @@
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
+          <t>hosting-restore.service.ts:167</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
+          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr">
@@ -4305,12 +4305,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>G-20</t>
+          <t>H-17</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Ochrona przed atakiem słownikowym na panel</t>
+          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -4351,27 +4351,27 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>rate-limit.guard.ts — ZERO testów</t>
+          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
         </is>
       </c>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>brak dowodu D2 na krytycznym guardzie</t>
+          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>G-20</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Staging — publikacja na produkcję</t>
+          <t>Ochrona przed atakiem słownikowym na panel</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:187</t>
+          <t>rate-limit.guard.ts — ZERO testów</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+          <t>brak dowodu D2 na krytycznym guardzie</t>
         </is>
       </c>
       <c r="P47" s="10" t="inlineStr">
@@ -4461,27 +4461,27 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
+          <t>Staging — publikacja na produkcję</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
@@ -4507,27 +4507,27 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:187</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L48" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M48" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
+          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr">
@@ -4539,73 +4539,73 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
@@ -4617,12 +4617,12 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwarka wolnych domen</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:54</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
         </is>
       </c>
       <c r="N50" s="11" t="inlineStr">
@@ -4681,7 +4681,11 @@
           <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
         </is>
       </c>
-      <c r="O50" s="11" t="inlineStr"/>
+      <c r="O50" s="11" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
       <c r="P50" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4691,12 +4695,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Spakowanie do archiwum</t>
+          <t>Wyszukiwarka wolnych domen</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4706,12 +4710,12 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
@@ -4737,12 +4741,12 @@
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>files.service.ts:320 — tylko extract</t>
+          <t>domains.controller.ts:54</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -4752,14 +4756,10 @@
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O51" s="11" t="inlineStr">
-        <is>
-          <t>standard we wszystkich panelach</t>
-        </is>
-      </c>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+        </is>
+      </c>
+      <c r="O51" s="11" t="inlineStr"/>
       <c r="P51" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4769,31 +4769,31 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+          <t>Spakowanie do archiwum</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>15</v>
@@ -4815,27 +4815,27 @@
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>files.service.ts:320 — tylko extract</t>
+        </is>
+      </c>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L52" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M52" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N52" s="11" t="inlineStr">
         <is>
-          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+          <t>standard we wszystkich panelach</t>
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr">
@@ -4847,12 +4847,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
+          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
+          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Treści i cennik na verris.pl</t>
+          <t>Finalizacja dokumentów prawnych 1.0.0</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="M54" s="11" t="inlineStr">
         <is>
-          <t>PB-01 (cennik zależy od unit economics)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
         </is>
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
@@ -5003,12 +5003,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Landing /przenies-strone</t>
+          <t>Treści i cennik na verris.pl</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -5030,7 +5030,7 @@
         <v>16</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
@@ -5059,17 +5059,17 @@
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
+          <t>PB-01 (cennik zależy od unit economics)</t>
         </is>
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -5081,12 +5081,12 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+          <t>Landing /przenies-strone</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
@@ -5137,17 +5137,17 @@
       </c>
       <c r="M56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
         </is>
       </c>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
         </is>
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -5159,34 +5159,34 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>KSeF — walidacja XSD przed wysyłką</t>
+          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
@@ -5195,37 +5195,37 @@
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
         </is>
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>smoke na api-test MF nie został wykonany</t>
+          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -5237,12 +5237,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>KSeF — tryb offline/awaryjny</t>
+          <t>KSeF — walidacja XSD przed wysyłką</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="F58" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>18</v>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
         </is>
       </c>
       <c r="N58" s="11" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+          <t>smoke na api-test MF nie został wykonany</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
@@ -5315,12 +5315,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>KSeF — pobranie UPO przez operatora</t>
+          <t>KSeF — tryb offline/awaryjny</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5335,11 +5335,11 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>18</v>
@@ -5361,27 +5361,27 @@
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
         </is>
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>KSeF — numer i UPO widoczne dla klienta</t>
+          <t>KSeF — pobranie UPO przez operatora</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -5413,14 +5413,14 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
@@ -5429,37 +5429,37 @@
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień „ksef” w apps/client-panel</t>
+          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
         <is>
-          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -5471,31 +5471,31 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy — 20 artykułów startowych</t>
+          <t>KSeF — numer i UPO widoczne dla klienta</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>19</v>
@@ -5517,27 +5517,27 @@
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zero wystąpień „ksef” w apps/client-panel</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
         </is>
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
@@ -5549,12 +5549,12 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+          <t>Baza wiedzy — 20 artykułów startowych</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>19</v>
@@ -5605,17 +5605,17 @@
       </c>
       <c r="M62" s="11" t="inlineStr">
         <is>
-          <t>PB-06 (kampania kieruje na landing)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
         </is>
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr">
@@ -5627,12 +5627,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Test end-to-end „pierwszy klient”</t>
+          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -5647,24 +5647,28 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H63" s="10" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
@@ -5679,17 +5683,17 @@
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>wszystkie blokery zamknięte (sprint 8)</t>
+          <t>PB-06 (kampania kieruje na landing)</t>
         </is>
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
@@ -5701,12 +5705,12 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Runbook startu i decyzja GO</t>
+          <t>Test end-to-end „pierwszy klient”</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -5725,7 +5729,7 @@
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G64" s="10" t="n">
         <v>20</v>
@@ -5753,28 +5757,102 @@
       </c>
       <c r="M64" s="11" t="inlineStr">
         <is>
+          <t>wszystkie blokery zamknięte (sprint 8)</t>
+        </is>
+      </c>
+      <c r="N64" s="11" t="inlineStr">
+        <is>
+          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+        </is>
+      </c>
+      <c r="O64" s="11" t="inlineStr">
+        <is>
+          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+        </is>
+      </c>
+      <c r="P64" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>PB-12</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Runbook startu i decyzja GO</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H65" s="10" t="inlineStr"/>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
           <t>PB-05 (decyzja GO po przejściu ścieżki na produkcji)</t>
         </is>
       </c>
-      <c r="N64" s="11" t="inlineStr">
+      <c r="N65" s="11" t="inlineStr">
         <is>
           <t>Każdy z 11 blokerów ma wpis: co zrobiono, gdzie jest dowód, kto potwierdził. Bez formuły „warunkowe GO”.</t>
         </is>
       </c>
-      <c r="O64" s="11" t="inlineStr">
+      <c r="O65" s="11" t="inlineStr">
         <is>
           <t>Domknięcie: przegląd wszystkich blokerów z dowodem zamknięcia, decyzja GO/NO-GO zapisana z datą.</t>
         </is>
       </c>
-      <c r="P64" s="10" t="inlineStr">
+      <c r="P65" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P64"/>
-  <conditionalFormatting sqref="E2:E64">
+  <autoFilter ref="A1:P65"/>
+  <conditionalFormatting sqref="E2:E65">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>
@@ -5794,7 +5872,7 @@
       <formula>"ŚREDNI"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P64">
+  <conditionalFormatting sqref="P2:P65">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"zrobione"</formula>
     </cfRule>
@@ -5904,11 +5982,11 @@
         </is>
       </c>
       <c r="F2" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A2)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A2)</f>
         <v/>
       </c>
       <c r="G2" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A2,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A2,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H2" s="10" t="n">
@@ -5949,11 +6027,11 @@
         </is>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A3)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A3)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A3,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A3,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H3" s="10" t="n">
@@ -5994,11 +6072,11 @@
         </is>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A4)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A4)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A4,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A4,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H4" s="10" t="n">
@@ -6010,7 +6088,7 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Sprintu nie było w planie z 2026-08. Dołożony po PB-01, które pokazało, że przy dzisiejszym placemencie na węźle mieści się 16 kont, a próg rentowności przy cenie 45 zł to 58. Dopóki Z-12 jest otwarte, sprzedaż zatrzymuje się na szesnastym koncie niezależnie od popytu — selektor odmówi provisioningu. Z-13 idzie razem, bo bez planu produkcyjnego w bazie nie ma czego umieszczać ani na czym testować nadsubskrypcji. PB-14 zamyka sprint, bo wybór dostawcy przesądza o rentowności bardziej niż cokolwiek innego w tym modelu, a decyzja musi zapaść przed zamówieniem serwera w sprincie 8.</t>
+          <t>Sprintu nie było w planie z 2026-08. Dołożony po PB-01, które pokazało, że przy dzisiejszym placemencie na węźle mieści się 16 kont, a próg rentowności przy cenie 45 zł to 58. Dopóki Z-12 jest otwarte, sprzedaż zatrzymuje się na szesnastym koncie niezależnie od popytu — selektor odmówi provisioningu. Z-13 idzie razem, bo bez planu produkcyjnego w bazie nie ma czego umieszczać ani na czym testować nadsubskrypcji. PB-14 zamyka sprint, bo wybór dostawcy przesądza o rentowności bardziej niż cokolwiek innego w tym modelu, a decyzja musi zapaść przed zamówieniem serwera w sprincie 8. AKTUALIZACJA 2026-08-22: Z-12 i Z-13 zamknięte tego samego dnia, a przy nich wyszło Z-16 — autoskalowanie nie pyta węzła o pojemność i nie dowozi sufitu z oferty. Dołożone do tego samego sprintu, bo to trzecia strona tej samej sprawy: pojemność węzła musi być liczona w jednym miejscu, a nie w trzech niezależnych.</t>
         </is>
       </c>
     </row>
@@ -6039,11 +6117,11 @@
         </is>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A5)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A5)</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A5,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A5,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n">
@@ -6084,11 +6162,11 @@
         </is>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A6)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A6)</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A6,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A6,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n">
@@ -6129,11 +6207,11 @@
         </is>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A7)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A7,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A7,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n">
@@ -6174,11 +6252,11 @@
         </is>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A8)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A8)</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A8,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A8,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n">
@@ -6219,11 +6297,11 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A9)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A9)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A9,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A9,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n">
@@ -6264,11 +6342,11 @@
         </is>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A10)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A10)</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A10,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A10,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n">
@@ -6309,11 +6387,11 @@
         </is>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A11)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A11)</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A11,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A11,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n">
@@ -6354,11 +6432,11 @@
         </is>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A12)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A12)</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A12,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A12,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n">
@@ -6399,11 +6477,11 @@
         </is>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A13)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A13)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A13,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A13,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n">
@@ -6444,11 +6522,11 @@
         </is>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A14)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A14)</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A14,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A14,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n">
@@ -6489,11 +6567,11 @@
         </is>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A15)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A15)</f>
         <v/>
       </c>
       <c r="G15" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A15,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A15,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n">
@@ -6534,11 +6612,11 @@
         </is>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A16)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A16)</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A16,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A16,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n">
@@ -6579,11 +6657,11 @@
         </is>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A17)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A17)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A17,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A17,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n">
@@ -6624,11 +6702,11 @@
         </is>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A18)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A18)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A18,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A18,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n">
@@ -6669,11 +6747,11 @@
         </is>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A19)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A19)</f>
         <v/>
       </c>
       <c r="G19" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A19,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A19,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n">
@@ -6714,11 +6792,11 @@
         </is>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A20)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A20)</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A20,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A20,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n">
@@ -6755,11 +6833,11 @@
         </is>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$64,A21)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A21)</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$64,A21,'Backlog do startu'!$F$2:$F$64)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A21,'Backlog do startu'!$F$2:$F$65)</f>
         <v/>
       </c>
       <c r="H21" s="10" t="n">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2186</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
@@ -1707,12 +1707,12 @@
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>autoscaling-engine.service.ts:287 — Math.min(value, 10) przycina krotność niezależnie od planu, więc sufit CPU (12×) i dysku (20×) z oferty jest nieosiągalny; w całym pliku nie ma ani jednego odwołania do Server/allocated — silnik skaluje konto bez pytania węzła o pojemność i bez aktualizacji allocatedCpu/Memory/Disk</t>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Odkryte przy zamykaniu Z-13. Dwie rzeczy, jedna przyczyna — silnik autoskalowania nie wie nic o węźle, na którym stoi konto. | PIERWSZA: oferta obiecuje skalowanie do 24 vCPU i 1000 GB, a przycięcie do 10× daje realnie 20 vCPU i 500 GB. Klient płacący za nadwyżkę godzinowo nie dostanie tego, za co zapłacił, i będzie miał rację w reklamacji. | DRUGA i groźniejsza: silnik podnosi limity konta w DirectAdminie, nie sprawdzając, czy węzeł ma te zasoby, i nie zapisując ich w allocated*. Po Z-12 znaczy to, że dwie warstwy nadsubskrybują niezależnie od siebie i żadna nie widzi drugiej: placement liczy sprzedane limity BAZOWE, autoskalowanie dokłada do nich nadwyżkę poza księgą. Jedno konto może urosnąć do 1000 GB na węźle 1,92 TB — połowa dysku dla jednego klienta, o czym selektor się nie dowie. | Do zrobienia: sprawdzenie pojemności węzła przed skalowaniem w górę (ten sam node-capacity.ts), skalowanie częściowe zamiast odmowy, zapis nadwyżki w allocated* albo osobnej kolumnie, podniesienie progu 10× po dołożeniu tego zabezpieczenia — w tej kolejności, nie odwrotnie. | Rozbieżność sufitu jest utrwalona testem plan-produkcyjny.spec.ts, który zapali się przy zmianie progu i wymusi przejrzenie oferty.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
@@ -6874,7 +6874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9196,17 +9196,17 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>Z-17</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Backup: granularność i retencja</t>
+          <t>Wydajność: cache i skalowanie</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -9221,37 +9221,37 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>Retencja co najmniej 28 dni w cenie</t>
+          <t>Klient widzi, że autoskalowanie dało mu mniej, niż potrzebował</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I44" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
         <is>
-          <t>off-site: 30 dni (node-offsite-backup.sh:101)</t>
+          <t>autoscaling-engine.service.ts — obcięcie zostawia wpis w dzienniku audytu i warn w logu, ale panel klienta nie pokazuje niczego</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>H-10</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>Odtworzenie pojedynczego pliku</t>
+          <t>Retencja co najmniej 28 dni w cenie</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -9294,19 +9294,19 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
-          <t>JetBackup/Plesk to mają; seohost i dhosting też</t>
+          <t>off-site: 30 dni (node-offsite-backup.sh:101)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>H-11</t>
+          <t>H-10</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zawartości archiwum przed odtworzeniem</t>
+          <t>Odtworzenie pojedynczego pliku</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -9349,19 +9349,19 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:788-793 — buduje z BIEŻĄCEGO inwentarza konta, nie z archiwum</t>
+          <t>JetBackup/Plesk to mają; seohost i dhosting też</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>H-13</t>
+          <t>H-11</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>Pobranie archiwum kopii lokalnie</t>
+          <t>Podgląd zawartości archiwum przed odtworzeniem</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -9396,27 +9396,27 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I47" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:855 — kopiuje na konto, nie do przeglądarki</t>
+          <t>services.controller.ts:788-793 — buduje z BIEŻĄCEGO inwentarza konta, nie z archiwum</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>H-16</t>
+          <t>H-13</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>ODTWORZENIE KONTA NA INNY WĘZEŁ</t>
+          <t>Pobranie archiwum kopii lokalnie</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -9451,27 +9451,27 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I48" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts:125 kieruje zadanie na account.serverId; node-account-restore.sh:76 przerywa gdy brak katalogu</t>
+          <t>services.controller.ts:855 — kopiuje na konto, nie do przeglądarki</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>H-18</t>
+          <t>H-16</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>Odtworzenie konta przez operatora z panelu</t>
+          <t>ODTWORZENIE KONTA NA INNY WĘZEŁ</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -9506,27 +9506,27 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I49" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:69,86 — zero wywołań w admin-panel</t>
+          <t>offsite-restore.service.ts:125 kieruje zadanie na account.serverId; node-account-restore.sh:76 przerywa gdy brak katalogu</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>H-19</t>
+          <t>H-18</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>Automatyczna konfiguracja backupu przy wdrożeniu węzła</t>
+          <t>Odtworzenie konta przez operatora z panelu</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -9561,37 +9561,37 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I50" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>node-onboard-live.sh:240-244 tylko log_warn; wizard węzła (wizard-content.ts:21-40) nie ma kroku backupu</t>
+          <t>subscriptions.admin.controller.ts:69,86 — zero wywołań w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>H-19</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Rozliczenia: dokończenie</t>
+          <t>Backup: granularność i retencja</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -9606,17 +9606,17 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>DUPLIKAT FAKTURY</t>
+          <t>Automatyczna konfiguracja backupu przy wdrożeniu węzła</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I51" s="10" t="n">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="K51" s="11" t="inlineStr">
         <is>
-          <t>brak flagi isDuplicate, brak endpointu</t>
+          <t>node-onboard-live.sh:240-244 tylko log_warn; wizard węzła (wizard-content.ts:21-40) nie ma kroku backupu</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Stawki VAT inne niż 23%</t>
+          <t>DUPLIKAT FAKTURY</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I52" s="10" t="n">
@@ -9684,14 +9684,14 @@
       </c>
       <c r="K52" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:17 — DEFAULT_VAT_RATE = 23 na sztywno</t>
+          <t>brak flagi isDuplicate, brak endpointu</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>Faktury w walucie obcej z przeliczeniem VAT</t>
+          <t>Stawki VAT inne niż 23%</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -9734,19 +9734,19 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
         <is>
-          <t>invoice-pdf.service.ts:61 formatuje PLN/EUR/USD; brak kursu i przeliczenia (art. 31a)</t>
+          <t>invoices.service.ts:17 — DEFAULT_VAT_RATE = 23 na sztywno</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Proforma przed odnowieniem</t>
+          <t>Faktury w walucie obcej z przeliczeniem VAT</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -9781,11 +9781,11 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I54" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
@@ -9794,14 +9794,14 @@
       </c>
       <c r="K54" s="11" t="inlineStr">
         <is>
-          <t>renewal-reminder.scheduler.ts — przypomnienie, nie proforma</t>
+          <t>invoice-pdf.service.ts:61 formatuje PLN/EUR/USD; brak kursu i przeliczenia (art. 31a)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>M-27</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>Dodanie karty niezależnie od zakupu</t>
+          <t>Proforma przed odnowieniem</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -9844,19 +9844,19 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
         <is>
-          <t>karta zapisuje się tylko przy okazji Stripe Checkout</t>
+          <t>renewal-reminder.scheduler.ts — przypomnienie, nie proforma</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>M-28</t>
+          <t>M-27</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>Eksport historii transakcji do CSV</t>
+          <t>Dodanie karty niezależnie od zakupu</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I56" s="10" t="n">
@@ -9899,19 +9899,19 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:70 — zero odwołań w panelu</t>
+          <t>karta zapisuje się tylko przy okazji Stripe Checkout</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>M-33</t>
+          <t>M-28</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>Dodatki płatne (IP, wsparcie priorytetowe)</t>
+          <t>Eksport historii transakcji do CSV</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -9950,23 +9950,23 @@
         </is>
       </c>
       <c r="I57" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
         <is>
-          <t>addon.service.ts:120 — 2 z 3 to workorder do BOK</t>
+          <t>billing.controller.ts:70 — zero odwołań w panelu</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Z-07</t>
+          <t>M-33</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>Ponowienie płatności portfelem w okresie karencji</t>
+          <t>Dodatki płatne (IP, wsparcie priorytetowe)</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I58" s="10" t="n">
@@ -10009,19 +10009,19 @@
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
-          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
+          <t>addon.service.ts:120 — 2 z 3 to workorder do BOK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Z-08</t>
+          <t>Z-07</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
+          <t>Ponowienie płatności portfelem w okresie karencji</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -10056,11 +10056,11 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I59" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
@@ -10069,14 +10069,14 @@
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
+          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Z-11</t>
+          <t>Z-08</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
+          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -10115,33 +10115,33 @@
         </is>
       </c>
       <c r="I60" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
+          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>Z-11</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie i ops: kolejka abuse</t>
+          <t>Rozliczenia: dokończenie</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -10156,37 +10156,37 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I61" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I62" s="10" t="n">
@@ -10229,19 +10229,19 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -10276,27 +10276,27 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I63" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -10331,11 +10331,11 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I64" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
@@ -10344,14 +10344,14 @@
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -10386,27 +10386,27 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I65" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -10441,27 +10441,27 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I66" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -10500,38 +10500,38 @@
         </is>
       </c>
       <c r="I67" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>WordPress Toolkit</t>
+          <t>Wsparcie i ops: kolejka abuse</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -10541,21 +10541,21 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Automatyczne aktualizacje WordPressa</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I68" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
@@ -10564,14 +10564,14 @@
       </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL to ma</t>
+          <t>poza produktem</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>I-05</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>Aktualizacje wtyczek i motywów z panelu</t>
+          <t>Automatyczne aktualizacje WordPressa</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I69" s="10" t="n">
@@ -10617,12 +10617,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>4 z 5 hostingów PL to ma</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>I-07</t>
+          <t>I-05</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -10647,7 +10651,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Skanowanie podatności WordPressa</t>
+          <t>Aktualizacje wtyczek i motywów z panelu</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -10661,23 +10665,19 @@
         </is>
       </c>
       <c r="I70" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K70" s="11" t="inlineStr">
-        <is>
-          <t>Plesk używa Patchstack</t>
-        </is>
-      </c>
+      <c r="K70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>I-08</t>
+          <t>I-07</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>Hardening WordPressa (checklist)</t>
+          <t>Skanowanie podatności WordPressa</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -10716,19 +10716,23 @@
         </is>
       </c>
       <c r="I71" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>Plesk używa Patchstack</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>I-13</t>
+          <t>I-08</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -10753,7 +10757,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Klonowanie strony między domenami</t>
+          <t>Hardening WordPressa (checklist)</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
@@ -10779,7 +10783,7 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>I-14</t>
+          <t>I-13</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -10804,7 +10808,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>Masowe zarządzanie wieloma instalacjami WP</t>
+          <t>Klonowanie strony między domenami</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -10814,27 +10818,23 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I73" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K73" s="11" t="inlineStr">
-        <is>
-          <t>realna przewaga dla agencji</t>
-        </is>
-      </c>
+      <c r="K73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>I-15</t>
+          <t>I-14</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Tryb konserwacji WordPressa</t>
+          <t>Masowe zarządzanie wieloma instalacjami WP</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -10873,19 +10873,23 @@
         </is>
       </c>
       <c r="I74" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>realna przewaga dla agencji</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>I-16</t>
+          <t>I-15</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -10910,7 +10914,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>WP-CLI</t>
+          <t>Tryb konserwacji WordPressa</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -10920,7 +10924,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I75" s="10" t="n">
@@ -10928,19 +10932,15 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K75" s="11" t="inlineStr">
-        <is>
-          <t>używane wewnętrznie przy WP_INSTALL</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>I-18</t>
+          <t>I-16</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Migracja — test poświadczeń (preflight)</t>
+          <t>WP-CLI</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -10988,14 +10988,14 @@
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:1001</t>
+          <t>używane wewnętrznie przy WP_INSTALL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>I-22</t>
+          <t>I-18</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>Migracja — cockpit operatora</t>
+          <t>Migracja — test poświadczeń (preflight)</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -11043,24 +11043,24 @@
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>migrations.staff.controller.ts:75,90,126</t>
+          <t>services.controller.ts:1001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>I-22</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Domeny jako produkt</t>
+          <t>WordPress Toolkit</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
@@ -11075,17 +11075,17 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Zmiana document root domeny</t>
+          <t>Migracja — cockpit operatora</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I78" s="10" t="n">
@@ -11093,19 +11093,19 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>DA to potrafi; brak UI</t>
+          <t>migrations.staff.controller.ts:75,90,126</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>A-08</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Rejestracja domeny z panelu</t>
+          <t>Zmiana document root domeny</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -11140,27 +11140,27 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I79" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:118</t>
+          <t>DA to potrafi; brak UI</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-08</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Transfer domeny (kod authinfo)</t>
+          <t>Rejestracja domeny z panelu</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I80" s="10" t="n">
@@ -11208,14 +11208,14 @@
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:123</t>
+          <t>domains.controller.ts:118</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>A-10</t>
+          <t>A-09</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>Odnowienie domeny przez klienta</t>
+          <t>Transfer domeny (kod authinfo)</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -11250,27 +11250,27 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I81" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:133</t>
+          <t>domains.controller.ts:123</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>A-12</t>
+          <t>A-10</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Cennik rejestracji na 1–10 lat</t>
+          <t>Odnowienie domeny przez klienta</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -11313,19 +11313,19 @@
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:59</t>
+          <t>domains.controller.ts:133</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>A-12</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>Zmiana danych abonenta domeny</t>
+          <t>Cennik rejestracji na 1–10 lat</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -11360,27 +11360,27 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I83" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>wymóg operatorski przy własnej rejestracji</t>
+          <t>domains.controller.ts:59</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>A-13</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Ukrycie danych WHOIS / domain privacy</t>
+          <t>Zmiana danych abonenta domeny</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -11415,23 +11415,27 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I84" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>wymóg operatorski przy własnej rejestracji</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>A-15</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -11456,7 +11460,7 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Blokada transferu domeny (transfer lock)</t>
+          <t>Ukrycie danych WHOIS / domain privacy</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -11466,7 +11470,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I85" s="10" t="n">
@@ -11482,7 +11486,7 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>A-16</t>
+          <t>A-15</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -11507,7 +11511,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Weryfikacja własności domeny</t>
+          <t>Blokada transferu domeny (transfer lock)</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -11517,27 +11521,23 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I86" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K86" s="11" t="inlineStr">
-        <is>
-          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-16</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>Zakładanie konta klienta przez operatora</t>
+          <t>Weryfikacja własności domeny</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -11580,29 +11580,29 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>brak @Post w users.admin.controller.ts</t>
+          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Katalog aplikacji</t>
+          <t>Domeny jako produkt</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Autoinstalator aplikacji</t>
+          <t>Zakładanie konta klienta przez operatora</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+          <t>brak @Post w users.admin.controller.ts</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Poczta: filtry, kalendarz, limity</t>
+          <t>Katalog aplikacji</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -11672,33 +11672,37 @@
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zużycia skrzynki</t>
+          <t>Autoinstalator aplikacji</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I89" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K89" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -11723,7 +11727,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Reguły filtrowania poczty (Sieve)</t>
+          <t>Podgląd zużycia skrzynki</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -11737,23 +11741,19 @@
         </is>
       </c>
       <c r="I90" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K90" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to ma</t>
-        </is>
-      </c>
+      <c r="K90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>Webmail — dostęp</t>
+          <t>Reguły filtrowania poczty (Sieve)</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -11792,23 +11792,23 @@
         </is>
       </c>
       <c r="I91" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>link do DA</t>
+          <t>wszystkie 5 hostingów PL to ma</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>E-18</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Sprawdzenie obecności na RBL</t>
+          <t>Webmail — dostęp</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -11851,19 +11851,19 @@
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>link do DA</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>E-19</t>
+          <t>E-18</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Podgląd kolejki i logów dostarczania</t>
+          <t>Sprawdzenie obecności na RBL</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -11902,23 +11902,23 @@
         </is>
       </c>
       <c r="I93" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>E-20</t>
+          <t>E-19</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Limity wysyłki pokazane klientowi</t>
+          <t>Podgląd kolejki i logów dostarczania</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="I94" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
@@ -11966,14 +11966,14 @@
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
+          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>E-21</t>
+          <t>E-20</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>Samodzielny import skrzynek przez IMAP</t>
+          <t>Limity wysyłki pokazane klientowi</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -12016,19 +12016,19 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>w ramach migracji, nie jako osobne narzędzie</t>
+          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>E-23</t>
+          <t>E-21</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
+          <t>Samodzielny import skrzynek przez IMAP</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -12063,27 +12063,27 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I96" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
+          <t>w ramach migracji, nie jako osobne narzędzie</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>E-24</t>
+          <t>E-23</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>2FA dla webmaila</t>
+          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="I97" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
@@ -12131,29 +12131,29 @@
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>E-24</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Bezpieczeństwo jako funkcja</t>
+          <t>Poczta: filtry, kalendarz, limity</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>HSTS</t>
+          <t>2FA dla webmaila</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -12177,19 +12177,23 @@
         </is>
       </c>
       <c r="I98" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>G-08</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -12214,7 +12218,7 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>Sprzedaż certyfikatów DV/OV/EV</t>
+          <t>HSTS</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -12228,23 +12232,19 @@
         </is>
       </c>
       <c r="I99" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to sprzedaje</t>
-        </is>
-      </c>
+      <c r="K99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>G-08</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Skaner malware dla klienta</t>
+          <t>Sprzedaż certyfikatów DV/OV/EV</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -12279,11 +12279,11 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I100" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
@@ -12292,14 +12292,14 @@
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
-          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+          <t>wszystkie 5 hostingów PL to sprzedaje</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>G-12</t>
+          <t>G-11</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Czyszczenie zainfekowanych plików</t>
+          <t>Skaner malware dla klienta</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I101" s="10" t="n">
@@ -12345,12 +12345,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K101" s="11" t="inlineStr"/>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>G-19</t>
+          <t>G-12</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -12375,7 +12379,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Auto-wylogowanie po bezczynności</t>
+          <t>Czyszczenie zainfekowanych plików</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -12389,23 +12393,19 @@
         </is>
       </c>
       <c r="I102" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K102" s="11" t="inlineStr">
-        <is>
-          <t>session-idle-guard.tsx</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K102" s="11" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>G-21</t>
+          <t>G-19</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Anty-DDoS</t>
+          <t>Auto-wylogowanie po bezczynności</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -12444,23 +12444,23 @@
         </is>
       </c>
       <c r="I103" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K103" s="11" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+          <t>session-idle-guard.tsx</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>G-22</t>
+          <t>G-21</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienie o podejrzanym logowaniu</t>
+          <t>Anty-DDoS</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -12495,23 +12495,27 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I104" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K104" s="11" t="inlineStr"/>
+      <c r="K104" s="11" t="inlineStr">
+        <is>
+          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Z-09</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -12536,7 +12540,7 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
+          <t>Powiadomienie o podejrzanym logowaniu</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -12546,37 +12550,33 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I105" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K105" s="11" t="inlineStr">
-        <is>
-          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
-        </is>
-      </c>
+      <c r="K105" s="11" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>Z-09</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Reseller jako produkt</t>
+          <t>Bezpieczeństwo jako funkcja</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>O — Multi-user i reseller</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -12609,19 +12609,19 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K106" s="11" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="I107" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
@@ -12669,14 +12669,14 @@
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -12719,19 +12719,19 @@
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>bez tego reseller nie jest produktem</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -12766,27 +12766,27 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I109" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>bez tego reseller nie jest produktem</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -12829,19 +12829,19 @@
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -12880,23 +12880,23 @@
         </is>
       </c>
       <c r="I111" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I112" s="10" t="n">
@@ -12939,29 +12939,29 @@
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Dostępność i zgodność w produkcie</t>
+          <t>Reseller jako produkt</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -12976,37 +12976,37 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I113" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
@@ -13054,14 +13054,14 @@
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -13100,23 +13100,23 @@
         </is>
       </c>
       <c r="I115" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -13151,27 +13151,27 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>poza kodem</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -13196,47 +13196,47 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I117" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>DNS: DNSSEC i zarządzanie strefą</t>
+          <t>Dostępność i zgodność w produkcie</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -13251,37 +13251,37 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Link do strefy DNS w DirectAdmin</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I118" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:350</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>DNSSEC</t>
+          <t>Link do strefy DNS w DirectAdmin</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -13316,27 +13316,27 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I119" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
+          <t>services.controller.ts:350</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Zmiana TTL rekordów</t>
+          <t>DNSSEC</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -13375,23 +13375,23 @@
         </is>
       </c>
       <c r="I120" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>zależne od F-01</t>
+          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Anycast DNS</t>
+          <t>Zmiana TTL rekordów</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -13426,37 +13426,37 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I121" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>tylko nazwa.pl na rynku PL</t>
+          <t>zależne od F-01</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Automatyzacja: API zapisu i webhooki</t>
+          <t>DNS: DNSSEC i zarządzanie strefą</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -13471,21 +13471,21 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Zadanie cron — edycja</t>
+          <t>Anycast DNS</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>L — Automatyzacja</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I122" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
@@ -13494,14 +13494,14 @@
       </c>
       <c r="K122" s="11" t="inlineStr">
         <is>
-          <t>obecnie usuń i dodaj ponownie</t>
+          <t>tylko nazwa.pl na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Cron z interwałem 1 minuty</t>
+          <t>Zadanie cron — edycja</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I123" s="10" t="n">
@@ -13544,19 +13544,19 @@
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>zależne od konfiguracji DA</t>
+          <t>obecnie usuń i dodaj ponownie</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Cron z wyborem wersji PHP</t>
+          <t>Cron z interwałem 1 minuty</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I124" s="10" t="n">
@@ -13599,19 +13599,19 @@
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr">
         <is>
-          <t>seohost to reklamuje</t>
+          <t>zależne od konfiguracji DA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Podgląd wyniku ostatniego wykonania crona</t>
+          <t>Cron z wyborem wersji PHP</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -13650,19 +13650,23 @@
         </is>
       </c>
       <c r="I125" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K125" s="11" t="inlineStr"/>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -13687,7 +13691,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Publiczne API — zapis</t>
+          <t>Podgląd wyniku ostatniego wykonania crona</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -13701,23 +13705,19 @@
         </is>
       </c>
       <c r="I126" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K126" s="11" t="inlineStr">
-        <is>
-          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
-        </is>
-      </c>
+      <c r="K126" s="11" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>Tokeny API z zakresami uprawnień</t>
+          <t>Publiczne API — zapis</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -13752,27 +13752,27 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I127" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K127" s="11" t="inlineStr">
         <is>
-          <t>api-tokens.controller.ts:35</t>
+          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-09</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Webhooki dla klienta</t>
+          <t>Tokeny API z zakresami uprawnień</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -13811,19 +13811,23 @@
         </is>
       </c>
       <c r="I128" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K128" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K128" s="11" t="inlineStr">
+        <is>
+          <t>api-tokens.controller.ts:35</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -13848,7 +13852,7 @@
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>Asystent AI w panelu</t>
+          <t>Webhooki dla klienta</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -13858,27 +13862,23 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I129" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
-        </is>
-      </c>
-      <c r="K129" s="11" t="inlineStr">
-        <is>
-          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>Prognoza zużycia zasobów (AI)</t>
+          <t>Asystent AI w panelu</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I130" s="10" t="n">
@@ -13926,53 +13926,53 @@
       </c>
       <c r="K130" s="11" t="inlineStr">
         <is>
-          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
+          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Rozszerzenia oferty</t>
+          <t>Automatyzacja: API zapisu i webhooki</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>NISKI</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>Prognoza zużycia zasobów (AI)</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>L — Automatyzacja</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I131" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
@@ -13981,14 +13981,14 @@
       </c>
       <c r="K131" s="11" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I132" s="10" t="n">
@@ -14031,15 +14031,19 @@
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K132" s="11" t="inlineStr"/>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="K132" s="11" t="inlineStr">
+        <is>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -14064,7 +14068,7 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -14090,7 +14094,7 @@
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -14115,7 +14119,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -14125,7 +14129,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I134" s="10" t="n">
@@ -14133,49 +14137,45 @@
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K134" s="11" t="inlineStr">
-        <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K134" s="11" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
+          <t>Rozszerzenia oferty</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>ciągłe</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>NISKI</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>X — Infrastruktura jakości</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
@@ -14184,23 +14184,23 @@
         </is>
       </c>
       <c r="I135" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K135" s="11" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I136" s="10" t="n">
@@ -14248,14 +14248,14 @@
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -14290,11 +14290,11 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I137" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
@@ -14303,14 +14303,14 @@
       </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -14358,14 +14358,14 @@
       </c>
       <c r="K138" s="11" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -14413,14 +14413,14 @@
       </c>
       <c r="K139" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="G140" s="10" t="inlineStr">
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="I140" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J140" s="10" t="inlineStr">
         <is>
@@ -14468,67 +14468,122 @@
       </c>
       <c r="K140" s="11" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
+          <t>X-09</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testami DirectAdminService</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="I141" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J141" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
           <t>X-10</t>
         </is>
       </c>
-      <c r="B141" s="10" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>E-09</t>
         </is>
       </c>
-      <c r="C141" s="11" t="inlineStr">
+      <c r="C142" s="11" t="inlineStr">
         <is>
           <t>Pokrycie testowe warstw krytycznych</t>
         </is>
       </c>
-      <c r="D141" s="10" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
         <is>
           <t>ciągłe</t>
         </is>
       </c>
-      <c r="E141" s="10" t="inlineStr">
+      <c r="E142" s="10" t="inlineStr">
         <is>
           <t>WYSOKI</t>
         </is>
       </c>
-      <c r="F141" s="11" t="inlineStr">
+      <c r="F142" s="11" t="inlineStr">
         <is>
           <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
         </is>
       </c>
-      <c r="G141" s="10" t="inlineStr">
+      <c r="G142" s="10" t="inlineStr">
         <is>
           <t>X — Infrastruktura jakości</t>
         </is>
       </c>
-      <c r="H141" s="10" t="inlineStr">
+      <c r="H142" s="10" t="inlineStr">
         <is>
           <t>WYSOKA</t>
         </is>
       </c>
-      <c r="I141" s="10" t="n">
+      <c r="I142" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="J141" s="10" t="inlineStr">
+      <c r="J142" s="10" t="inlineStr">
         <is>
           <t>ATRAPA</t>
         </is>
       </c>
-      <c r="K141" s="11" t="inlineStr">
+      <c r="K142" s="11" t="inlineStr">
         <is>
           <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K141"/>
+  <autoFilter ref="A1:K142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14243,12 +14243,12 @@
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>zero @nestjs/testing i supertest nawet w devDependencies (apps/api/package.json:52-73)</t>
+          <t>apps/api/test/integration/ — setup.ts (izolacja przez TRUNCATE CASCADE, fabryki, atrapy DirectAdmina/poczty/audytu), node-selector.int-spec.ts (9 testów placementu na prawdziwych zapytaniach), ksiega.int-spec.ts (6 testów cyklu życia księgi z prawdziwymi transakcjami); apps/api/jest.integration.cjs — maxWorkers 1, bo testy dzielą jedną bazę; .github/workflows/ci.yml — job „API integration tests” z Postgresem 16</t>
         </is>
       </c>
     </row>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2192</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>73.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -6874,7 +6874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14582,8 +14582,118 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>X-19</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>Dług lintera odsłonięty przez Next 16 i włączenie ESLinta w API</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H143" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="I143" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>libs/eslint-config/node.mjs oraz apps/*/eslint.config.mjs — reguły włączone, ale część jako ostrzeżenia; 209 ostrzeżeń w panelach, 58 w API</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>X-20</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>Decyzja i migracja na Prismę 7</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="I144" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J144" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K144" s="11" t="inlineStr">
+        <is>
+          <t>libs/database/package.json — prisma 6.19.3; schema.prisma:17 — datasource url = env("DATABASE_URL"), składnia usunięta w Prismie 7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K142"/>
+  <autoFilter ref="A1:K144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2248</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>74.90000000000001</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="19">
@@ -6874,7 +6874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K144"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14692,8 +14692,63 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>X-22</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>Eksport danych osobowych (RODO art. 20) sprawdzany testem end-to-end</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="I145" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J145" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>apps/api/src/compliance/data-export.service.ts — buildZipToFile bez żadnego testu; apps/api/src/compliance/*.spec.ts — brak pokrycia tej ścieżki</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K144"/>
+  <autoFilter ref="A1:K145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -1254,12 +1254,12 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>59 zł netto).</t>
+          <t>Arkusz z kosztem miesięcznym węzła, liczbą kont na węzeł, marżą jednostkową i progiem rentowności. Decyzja: cena zostaje albo się zmienia — zapisana w repo.</t>
         </is>
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>Policzyć pełny koszt węzła: serwer + CloudLinux + LiteSpeed + DirectAdmin + Imunify + backup S3 + amortyzacja wsparcia. Wyliczyć próg rentowności w kontach na węzeł i marżę przy 45 zł brutto (36</t>
+          <t>Policzyć pełny koszt węzła: serwer + CloudLinux + LiteSpeed + DirectAdmin + Imunify + backup S3 + amortyzacja wsparcia. Wyliczyć próg rentowności w kontach na węzeł i marżę przy 45 zł brutto (36,59 zł netto).</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts:444-453 — wiersz stripeWebhookEvent zapisywany PRZED handlerem (:455), poza transakcją, bez cofnięcia przy wyjątku; ponowienie ze Stripe trafia w :448-451 i zwraca duplicate:true; uznanie portfela (:523) nigdy nie następuje</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Klient zapłacił, saldo się nie pojawiło, system uważa zdarzenie za obsłużone i odrzuca ponowienia. Odzysk wyłącznie ręcznie w bazie — brak endpointu do ponownego przetworzenia.</t>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2264</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="18">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>75.5</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="19">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>invoices.service.ts:192 osiągalne WYŁĄCZNIE z upsertFromStripe (billing.service.ts:702,787 — zdarzenia invoice.*); doładowanie idzie przez stripe.client.ts:307 mode=payment bez invoice_creation; obciążenia portfela (subscriptions.service.ts:1208, renewal.scheduler.ts:174, autoscaling-billing.service.ts:145, addon.service.ts:105) nie wołają InvoicesService; invoices.admin.controller.ts ma same @Get</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>Klient płaci realnie i nie dostaje ŻADNEGO dokumentu księgowego. Brak obejścia w systemie — operator nie wystawi faktury ręcznie. Poważniejsze niż brak korekt: te dotyczą dokumentów, których w ogóle się nie wystawia.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -6874,7 +6874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10021,7 +10021,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Z-07</t>
+          <t>M-34</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>Ponowienie płatności portfelem w okresie karencji</t>
+          <t>Model prepaid potwierdzony z księgową — doładowanie bez faktury zaliczkowej</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -10060,23 +10060,23 @@
         </is>
       </c>
       <c r="I59" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
-          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
+          <t>faktura-za-portfel.ts — TYPY_SPRZEDAZY nie obejmuje TOPUP; billing.service.ts:handleCheckoutCompleted — doładowanie kredytuje portfel i nie tworzy dokumentu</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Z-08</t>
+          <t>Z-07</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
+          <t>Ponowienie płatności portfelem w okresie karencji</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -10111,11 +10111,11 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I60" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
@@ -10124,14 +10124,14 @@
       </c>
       <c r="K60" s="11" t="inlineStr">
         <is>
-          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
+          <t>renewal.scheduler.ts:74-78 wybiera wyłącznie status ACTIVE — subskrypcja w PAST_DUE (:236-241) nie jest ponawiana; getPaymentRetryUrl (subscriptions.service.ts:1509-1516) odrzuca wszystko poza STRIPE_CARD</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Z-11</t>
+          <t>Z-08</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
+          <t>Przegląd istniejących subskrypcji MANUAL założonych przez klientów</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
@@ -10170,33 +10170,33 @@
         </is>
       </c>
       <c r="I61" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
         <is>
-          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
+          <t>brak jakiegokolwiek zapytania/raportu; luka Z-02 była otwarta do 2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>N-05</t>
+          <t>Z-11</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie i ops: kolejka abuse</t>
+          <t>Rozliczenia: dokończenie</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -10211,37 +10211,37 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
+          <t>Przegląd wszystkich kluczy idempotencji pod kątem poprawności</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I62" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
-          <t>ai.controller.ts:53 — AI_API_KEY</t>
+          <t>brak przeglądu; sprawdzone tylko wystąpienia Date.now() w kluczach</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>N-10</t>
+          <t>N-05</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>Preferencje powiadomień e-mail</t>
+          <t>Podpowiedzi artykułów przy zgłoszeniu</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I63" s="10" t="n">
@@ -10284,19 +10284,19 @@
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
-          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
+          <t>ai.controller.ts:53 — AI_API_KEY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>N-11</t>
+          <t>N-10</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Ogłoszenia i okna serwisowe</t>
+          <t>Preferencje powiadomień e-mail</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
@@ -10331,27 +10331,27 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I64" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
+          <t>notifications-tab.tsx:70 — sekcja „Zawsze włączone” to statyczny tekst bez backendu</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>N-12</t>
+          <t>N-11</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>Feature flagi z panelu operatora</t>
+          <t>Ogłoszenia i okna serwisowe</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -10386,11 +10386,11 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I65" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
@@ -10399,14 +10399,14 @@
       </c>
       <c r="K65" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:342</t>
+          <t>product-ops.admin.controller.ts:281,307,342,427; product-ops/data.ts:78-85 to same GET-y</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>N-13</t>
+          <t>N-12</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
+          <t>Feature flagi z panelu operatora</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -10441,27 +10441,27 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I66" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
-          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
+          <t>product-ops.admin.controller.ts:342</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>N-20</t>
+          <t>N-13</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>Link ze zgłoszenia do szczegółu (admin)</t>
+          <t>KOLEJKA OBSŁUGI NADUŻYĆ (ABUSE)</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I67" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
         <is>
-          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
+          <t>brak modułu, encji i trasy; jest tylko outbound-abuse.guard.ts:7-18 bez UI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>N-21</t>
+          <t>N-20</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Wsparcie telefoniczne</t>
+          <t>Link ze zgłoszenia do szczegółu (admin)</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -10555,38 +10555,38 @@
         </is>
       </c>
       <c r="I68" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
-          <t>poza produktem</t>
+          <t>tickets/page.tsx:24 → /tickets/${id}; trasa nie istnieje w admin-panel</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>N-21</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>WordPress Toolkit</t>
+          <t>Wsparcie i ops: kolejka abuse</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
@@ -10596,21 +10596,21 @@
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>Automatyczne aktualizacje WordPressa</t>
+          <t>Wsparcie telefoniczne</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I69" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
@@ -10619,14 +10619,14 @@
       </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
-          <t>4 z 5 hostingów PL to ma</t>
+          <t>poza produktem</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>I-05</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Aktualizacje wtyczek i motywów z panelu</t>
+          <t>Automatyczne aktualizacje WordPressa</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I70" s="10" t="n">
@@ -10672,12 +10672,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr">
+        <is>
+          <t>4 z 5 hostingów PL to ma</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>I-07</t>
+          <t>I-05</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -10702,7 +10706,7 @@
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>Skanowanie podatności WordPressa</t>
+          <t>Aktualizacje wtyczek i motywów z panelu</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -10716,23 +10720,19 @@
         </is>
       </c>
       <c r="I71" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K71" s="11" t="inlineStr">
-        <is>
-          <t>Plesk używa Patchstack</t>
-        </is>
-      </c>
+      <c r="K71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>I-08</t>
+          <t>I-07</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Hardening WordPressa (checklist)</t>
+          <t>Skanowanie podatności WordPressa</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
@@ -10771,19 +10771,23 @@
         </is>
       </c>
       <c r="I72" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>Plesk używa Patchstack</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>I-13</t>
+          <t>I-08</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -10808,7 +10812,7 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>Klonowanie strony między domenami</t>
+          <t>Hardening WordPressa (checklist)</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -10834,7 +10838,7 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>I-14</t>
+          <t>I-13</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -10859,7 +10863,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Masowe zarządzanie wieloma instalacjami WP</t>
+          <t>Klonowanie strony między domenami</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -10869,27 +10873,23 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I74" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>realna przewaga dla agencji</t>
-        </is>
-      </c>
+      <c r="K74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>I-15</t>
+          <t>I-14</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>Tryb konserwacji WordPressa</t>
+          <t>Masowe zarządzanie wieloma instalacjami WP</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -10928,19 +10928,23 @@
         </is>
       </c>
       <c r="I75" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K75" s="11" t="inlineStr"/>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>realna przewaga dla agencji</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>I-16</t>
+          <t>I-15</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -10965,7 +10969,7 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>WP-CLI</t>
+          <t>Tryb konserwacji WordPressa</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -10975,7 +10979,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I76" s="10" t="n">
@@ -10983,19 +10987,15 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K76" s="11" t="inlineStr">
-        <is>
-          <t>używane wewnętrznie przy WP_INSTALL</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>I-18</t>
+          <t>I-16</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>Migracja — test poświadczeń (preflight)</t>
+          <t>WP-CLI</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -11043,14 +11043,14 @@
       </c>
       <c r="K77" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:1001</t>
+          <t>używane wewnętrznie przy WP_INSTALL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>I-22</t>
+          <t>I-18</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Migracja — cockpit operatora</t>
+          <t>Migracja — test poświadczeń (preflight)</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -11098,24 +11098,24 @@
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
-          <t>migrations.staff.controller.ts:75,90,126</t>
+          <t>services.controller.ts:1001</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>A-06</t>
+          <t>I-22</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Domeny jako produkt</t>
+          <t>WordPress Toolkit</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -11130,17 +11130,17 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>Zmiana document root domeny</t>
+          <t>Migracja — cockpit operatora</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I79" s="10" t="n">
@@ -11148,19 +11148,19 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
         <is>
-          <t>DA to potrafi; brak UI</t>
+          <t>migrations.staff.controller.ts:75,90,126</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>A-08</t>
+          <t>A-06</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Rejestracja domeny z panelu</t>
+          <t>Zmiana document root domeny</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -11195,27 +11195,27 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I80" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:118</t>
+          <t>DA to potrafi; brak UI</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>A-08</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>Transfer domeny (kod authinfo)</t>
+          <t>Rejestracja domeny z panelu</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I81" s="10" t="n">
@@ -11263,14 +11263,14 @@
       </c>
       <c r="K81" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:123</t>
+          <t>domains.controller.ts:118</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>A-10</t>
+          <t>A-09</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Odnowienie domeny przez klienta</t>
+          <t>Transfer domeny (kod authinfo)</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -11305,27 +11305,27 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I82" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:133</t>
+          <t>domains.controller.ts:123</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>A-12</t>
+          <t>A-10</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>Cennik rejestracji na 1–10 lat</t>
+          <t>Odnowienie domeny przez klienta</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -11368,19 +11368,19 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:59</t>
+          <t>domains.controller.ts:133</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>A-12</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Zmiana danych abonenta domeny</t>
+          <t>Cennik rejestracji na 1–10 lat</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -11415,27 +11415,27 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I84" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>wymóg operatorski przy własnej rejestracji</t>
+          <t>domains.controller.ts:59</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>A-13</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>Ukrycie danych WHOIS / domain privacy</t>
+          <t>Zmiana danych abonenta domeny</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -11470,23 +11470,27 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I85" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K85" s="11" t="inlineStr"/>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>wymóg operatorski przy własnej rejestracji</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>A-15</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -11511,7 +11515,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Blokada transferu domeny (transfer lock)</t>
+          <t>Ukrycie danych WHOIS / domain privacy</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -11521,7 +11525,7 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I86" s="10" t="n">
@@ -11537,7 +11541,7 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>A-16</t>
+          <t>A-15</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -11562,7 +11566,7 @@
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>Weryfikacja własności domeny</t>
+          <t>Blokada transferu domeny (transfer lock)</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -11572,27 +11576,23 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I87" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>A-24</t>
+          <t>A-16</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Zakładanie konta klienta przez operatora</t>
+          <t>Weryfikacja własności domeny</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>brak @Post w users.admin.controller.ts</t>
+          <t>domains.service.ts:92-153 — runChecklist robi resolve4/resolve6/resolveNs + handshake TLS</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-24</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Katalog aplikacji</t>
+          <t>Domeny jako produkt</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -11667,17 +11667,17 @@
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>Autoinstalator aplikacji</t>
+          <t>Zakładanie konta klienta przez operatora</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -11690,29 +11690,29 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+          <t>brak @Post w users.admin.controller.ts</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>E-10</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Poczta: filtry, kalendarz, limity</t>
+          <t>Katalog aplikacji</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -11727,33 +11727,37 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Podgląd zużycia skrzynki</t>
+          <t>Autoinstalator aplikacji</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I90" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K90" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K90" s="11" t="inlineStr">
+        <is>
+          <t>app-install.service.ts:25,32 — katalog ma 2 pozycje</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>E-12</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -11778,7 +11782,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>Reguły filtrowania poczty (Sieve)</t>
+          <t>Podgląd zużycia skrzynki</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
@@ -11792,23 +11796,19 @@
         </is>
       </c>
       <c r="I91" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K91" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to ma</t>
-        </is>
-      </c>
+      <c r="K91" s="11" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-12</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Webmail — dostęp</t>
+          <t>Reguły filtrowania poczty (Sieve)</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -11847,23 +11847,23 @@
         </is>
       </c>
       <c r="I92" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr">
         <is>
-          <t>link do DA</t>
+          <t>wszystkie 5 hostingów PL to ma</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>E-18</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>Sprawdzenie obecności na RBL</t>
+          <t>Webmail — dostęp</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
@@ -11906,19 +11906,19 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K93" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>link do DA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>E-19</t>
+          <t>E-18</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Podgląd kolejki i logów dostarczania</t>
+          <t>Sprawdzenie obecności na RBL</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
@@ -11957,23 +11957,23 @@
         </is>
       </c>
       <c r="I94" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="K94" s="11" t="inlineStr">
         <is>
-          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>E-20</t>
+          <t>E-19</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>Limity wysyłki pokazane klientowi</t>
+          <t>Podgląd kolejki i logów dostarczania</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -12012,7 +12012,7 @@
         </is>
       </c>
       <c r="I95" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
@@ -12021,14 +12021,14 @@
       </c>
       <c r="K95" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
+          <t>„gdzie jest mój mail” to najczęstszy ticket poczty</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>E-21</t>
+          <t>E-20</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Samodzielny import skrzynek przez IMAP</t>
+          <t>Limity wysyłki pokazane klientowi</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -12071,19 +12071,19 @@
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
-          <t>w ramach migracji, nie jako osobne narzędzie</t>
+          <t>cyber_Folks publikuje jawnie: 1000/dobę, 300/15 min</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>E-23</t>
+          <t>E-21</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
+          <t>Samodzielny import skrzynek przez IMAP</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -12118,27 +12118,27 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I97" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K97" s="11" t="inlineStr">
         <is>
-          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
+          <t>w ramach migracji, nie jako osobne narzędzie</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>E-24</t>
+          <t>E-23</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>2FA dla webmaila</t>
+          <t>Kalendarz i kontakty (CalDAV/CardDAV)</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="I98" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
@@ -12186,29 +12186,29 @@
       </c>
       <c r="K98" s="11" t="inlineStr">
         <is>
-          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+          <t>dhosting i home.pl mają w produkcie „poczta biznesowa”</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>E-24</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>E-06</t>
+          <t>E-10</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Bezpieczeństwo jako funkcja</t>
+          <t>Poczta: filtry, kalendarz, limity</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>HSTS</t>
+          <t>2FA dla webmaila</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -12232,19 +12232,23 @@
         </is>
       </c>
       <c r="I99" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>cyber_Folks ma nawet 2FA dla IMAP/SMTP</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>G-08</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -12269,7 +12273,7 @@
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Sprzedaż certyfikatów DV/OV/EV</t>
+          <t>HSTS</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -12283,23 +12287,19 @@
         </is>
       </c>
       <c r="I100" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K100" s="11" t="inlineStr">
-        <is>
-          <t>wszystkie 5 hostingów PL to sprzedaje</t>
-        </is>
-      </c>
+      <c r="K100" s="11" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>G-08</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>Skaner malware dla klienta</t>
+          <t>Sprzedaż certyfikatów DV/OV/EV</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -12334,11 +12334,11 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I101" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
@@ -12347,14 +12347,14 @@
       </c>
       <c r="K101" s="11" t="inlineStr">
         <is>
-          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+          <t>wszystkie 5 hostingów PL to sprzedaje</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>G-12</t>
+          <t>G-11</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Czyszczenie zainfekowanych plików</t>
+          <t>Skaner malware dla klienta</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I102" s="10" t="n">
@@ -12400,12 +12400,16 @@
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr">
+        <is>
+          <t>Imunify to koszt licencyjny — pozycja do unit economics</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>G-19</t>
+          <t>G-12</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -12430,7 +12434,7 @@
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>Auto-wylogowanie po bezczynności</t>
+          <t>Czyszczenie zainfekowanych plików</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -12444,23 +12448,19 @@
         </is>
       </c>
       <c r="I103" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K103" s="11" t="inlineStr">
-        <is>
-          <t>session-idle-guard.tsx</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>G-21</t>
+          <t>G-19</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Anty-DDoS</t>
+          <t>Auto-wylogowanie po bezczynności</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -12499,23 +12499,23 @@
         </is>
       </c>
       <c r="I104" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
-          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+          <t>session-idle-guard.tsx</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>G-22</t>
+          <t>G-21</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Powiadomienie o podejrzanym logowaniu</t>
+          <t>Anty-DDoS</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -12550,23 +12550,27 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I105" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>wszystkie 5 hostingów PL to deklaruje — brak w ofercie będzie widoczny</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Z-09</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -12591,7 +12595,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
+          <t>Powiadomienie o podejrzanym logowaniu</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
@@ -12601,37 +12605,33 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I106" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K106" s="11" t="inlineStr">
-        <is>
-          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
-        </is>
-      </c>
+      <c r="K106" s="11" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>O-03</t>
+          <t>Z-09</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>E-07</t>
+          <t>E-06</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Reseller jako produkt</t>
+          <t>Bezpieczeństwo jako funkcja</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>Dziennik audytu działań subkont</t>
+          <t>Ograniczenie hostów, do których łączy się worker migracji (SSRF z węzła)</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>O — Multi-user i reseller</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
@@ -12664,19 +12664,19 @@
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K107" s="11" t="inlineStr">
         <is>
-          <t>customer-iam.controller.ts:36</t>
+          <t>node-migration-worker.sh — host źródła pochodzi z formularza i nie jest niczym ograniczony</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>O-03</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Reseller — przegląd klientów</t>
+          <t>Dziennik audytu działań subkont</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="I108" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
@@ -12724,14 +12724,14 @@
       </c>
       <c r="K108" s="11" t="inlineStr">
         <is>
-          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
+          <t>customer-iam.controller.ts:36</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>Reseller — zakładanie kont klientom</t>
+          <t>Reseller — przegląd klientów</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -12774,19 +12774,19 @@
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K109" s="11" t="inlineStr">
         <is>
-          <t>bez tego reseller nie jest produktem</t>
+          <t>reseller.controller.ts:12,17 — 2 GET-y, zero mutacji</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>O-07</t>
+          <t>O-06</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Reseller — ustawianie własnej marży</t>
+          <t>Reseller — zakładanie kont klientom</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
@@ -12821,27 +12821,27 @@
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I110" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
+          <t>bez tego reseller nie jest produktem</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>O-08</t>
+          <t>O-07</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>Reseller — samodzielne włączenie programu</t>
+          <t>Reseller — ustawianie własnej marży</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -12884,19 +12884,19 @@
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr">
         <is>
-          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
+          <t>reseller.admin.controller.ts:44,50 — tylko operator, nie reseller</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-08</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>White-label / własna marka resellera</t>
+          <t>Reseller — samodzielne włączenie programu</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -12935,23 +12935,23 @@
         </is>
       </c>
       <c r="I112" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K112" s="11" t="inlineStr">
         <is>
-          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
+          <t>reseller-client.tsx:49 — jedyna akcja to „Napisz do nas”</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Z-10</t>
+          <t>O-09</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
+          <t>White-label / własna marka resellera</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I113" s="10" t="n">
@@ -12994,29 +12994,29 @@
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K113" s="11" t="inlineStr">
         <is>
-          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
+          <t>reseller.admin.controller.ts:44 (brand po stronie operatora)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>Z-10</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>E-08</t>
+          <t>E-07</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Dostępność i zgodność w produkcie</t>
+          <t>Reseller jako produkt</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -13031,37 +13031,37 @@
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Rejestr czynności przetwarzania (art. 30)</t>
+          <t>Izolacja rekordów między kontami klientów + dziennik odmów subkont</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K114" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
+          <t>brak systematycznego przeglądu; każdy serwis sprawdza właściciela zasobu po swojemu</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
+          <t>Rejestr czynności przetwarzania (art. 30)</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -13100,7 +13100,7 @@
         </is>
       </c>
       <c r="I115" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
@@ -13109,14 +13109,14 @@
       </c>
       <c r="K115" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
+          <t>docs/legal/rcpd.md — sekcje A (administrator), B (procesor, art. 30 ust. 2), C (art. 32), D (przeglądy)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Deklaracja lokalizacji danych</t>
+          <t>Dostępność panelu wg WCAG 2.1 AA (EAA)</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -13155,23 +13155,23 @@
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K116" s="11" t="inlineStr">
         <is>
-          <t>poza kodem</t>
+          <t>docs/legal/EAA_AUDYT_DOSTEPNOSCI_2026-07-07.md — audyt wykonany, skip-link i focus-visible naprawione w commicie z 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>Certyfikacja ISO 27001</t>
+          <t>Deklaracja lokalizacji danych</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
@@ -13206,27 +13206,27 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I117" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K117" s="11" t="inlineStr">
         <is>
-          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
+          <t>poza kodem</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>Q-09</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -13251,47 +13251,47 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Panel responsywny na telefonie</t>
+          <t>Certyfikacja ISO 27001</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I118" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr">
         <is>
-          <t>brak audytu w repo</t>
+          <t>home.pl i nazwa.pl mają — element przetargowy w B2B</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>Q-09</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>E-11</t>
+          <t>E-08</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>DNS: DNSSEC i zarządzanie strefą</t>
+          <t>Dostępność i zgodność w produkcie</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -13306,37 +13306,37 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>Link do strefy DNS w DirectAdmin</t>
+          <t>Panel responsywny na telefonie</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I119" s="10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:350</t>
+          <t>brak audytu w repo</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>DNSSEC</t>
+          <t>Link do strefy DNS w DirectAdmin</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -13371,27 +13371,27 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I120" s="10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="K120" s="11" t="inlineStr">
         <is>
-          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
+          <t>services.controller.ts:350</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>Zmiana TTL rekordów</t>
+          <t>DNSSEC</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -13430,23 +13430,23 @@
         </is>
       </c>
       <c r="I121" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K121" s="11" t="inlineStr">
         <is>
-          <t>zależne od F-01</t>
+          <t>żaden z 5 hostingów PL nie potwierdza publicznie</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Anycast DNS</t>
+          <t>Zmiana TTL rekordów</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -13481,37 +13481,37 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I122" s="10" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K122" s="11" t="inlineStr">
         <is>
-          <t>tylko nazwa.pl na rynku PL</t>
+          <t>zależne od F-01</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>F-12</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>E-13</t>
+          <t>E-11</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Automatyzacja: API zapisu i webhooki</t>
+          <t>DNS: DNSSEC i zarządzanie strefą</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -13526,21 +13526,21 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>Zadanie cron — edycja</t>
+          <t>Anycast DNS</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>L — Automatyzacja</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I123" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
@@ -13549,14 +13549,14 @@
       </c>
       <c r="K123" s="11" t="inlineStr">
         <is>
-          <t>obecnie usuń i dodaj ponownie</t>
+          <t>tylko nazwa.pl na rynku PL</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>L-03</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Cron z interwałem 1 minuty</t>
+          <t>Zadanie cron — edycja</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I124" s="10" t="n">
@@ -13599,19 +13599,19 @@
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>b.d.</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K124" s="11" t="inlineStr">
         <is>
-          <t>zależne od konfiguracji DA</t>
+          <t>obecnie usuń i dodaj ponownie</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>L-05</t>
+          <t>L-04</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>Cron z wyborem wersji PHP</t>
+          <t>Cron z interwałem 1 minuty</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I125" s="10" t="n">
@@ -13654,19 +13654,19 @@
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>b.d.</t>
         </is>
       </c>
       <c r="K125" s="11" t="inlineStr">
         <is>
-          <t>seohost to reklamuje</t>
+          <t>zależne od konfiguracji DA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>L-06</t>
+          <t>L-05</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Podgląd wyniku ostatniego wykonania crona</t>
+          <t>Cron z wyborem wersji PHP</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -13705,19 +13705,23 @@
         </is>
       </c>
       <c r="I126" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K126" s="11" t="inlineStr"/>
+      <c r="K126" s="11" t="inlineStr">
+        <is>
+          <t>seohost to reklamuje</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>L-08</t>
+          <t>L-06</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -13742,7 +13746,7 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>Publiczne API — zapis</t>
+          <t>Podgląd wyniku ostatniego wykonania crona</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
@@ -13756,23 +13760,19 @@
         </is>
       </c>
       <c r="I127" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K127" s="11" t="inlineStr">
-        <is>
-          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
-        </is>
-      </c>
+      <c r="K127" s="11" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>L-09</t>
+          <t>L-08</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Tokeny API z zakresami uprawnień</t>
+          <t>Publiczne API — zapis</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -13807,27 +13807,27 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I128" s="10" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K128" s="11" t="inlineStr">
         <is>
-          <t>api-tokens.controller.ts:35</t>
+          <t>api-scopes.ts:3 — 3 zakresy read-only; przyznane w api-tokens-client.tsx:158</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>L-10</t>
+          <t>L-09</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>Webhooki dla klienta</t>
+          <t>Tokeny API z zakresami uprawnień</t>
         </is>
       </c>
       <c r="G129" s="10" t="inlineStr">
@@ -13866,19 +13866,23 @@
         </is>
       </c>
       <c r="I129" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K129" s="11" t="inlineStr"/>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>api-tokens.controller.ts:35</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>L-11</t>
+          <t>L-10</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -13903,7 +13907,7 @@
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>Asystent AI w panelu</t>
+          <t>Webhooki dla klienta</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
@@ -13913,27 +13917,23 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I130" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
-        </is>
-      </c>
-      <c r="K130" s="11" t="inlineStr">
-        <is>
-          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K130" s="11" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>L-12</t>
+          <t>L-11</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>Prognoza zużycia zasobów (AI)</t>
+          <t>Asystent AI w panelu</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I131" s="10" t="n">
@@ -13981,53 +13981,53 @@
       </c>
       <c r="K131" s="11" t="inlineStr">
         <is>
-          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
+          <t>HostingAssistant.tsx:61; ai-provider.service.ts:21 — AI_API_KEY domyślnie pusty</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Q-06</t>
+          <t>L-12</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-13</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Rozszerzenia oferty</t>
+          <t>Automatyzacja: API zapisu i webhooki</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>NISKI</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>VPS / cloud w tym samym panelu</t>
+          <t>Prognoza zużycia zasobów (AI)</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>Q — Przewaga</t>
+          <t>L — Automatyzacja</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I132" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
@@ -14036,14 +14036,14 @@
       </c>
       <c r="K132" s="11" t="inlineStr">
         <is>
-          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+          <t>hosting-forecast-actions.ts:7; fallback ServiceForecastPanel.tsx:97</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>Q-07</t>
+          <t>Q-06</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>VPS — konsola / VNC</t>
+          <t>VPS / cloud w tym samym panelu</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>NISKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I133" s="10" t="n">
@@ -14086,15 +14086,19 @@
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
-        </is>
-      </c>
-      <c r="K133" s="11" t="inlineStr"/>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>vps.controller.ts:53,59,69; HETZNER_API_TOKEN</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>Q-08</t>
+          <t>Q-07</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -14119,7 +14123,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>VPS — snapshoty i rebuild</t>
+          <t>VPS — konsola / VNC</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -14145,7 +14149,7 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Q-14</t>
+          <t>Q-08</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -14170,7 +14174,7 @@
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>Kreator uruchomienia węzła</t>
+          <t>VPS — snapshoty i rebuild</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -14180,7 +14184,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>NISKA</t>
         </is>
       </c>
       <c r="I135" s="10" t="n">
@@ -14188,49 +14192,45 @@
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
-        </is>
-      </c>
-      <c r="K135" s="11" t="inlineStr">
-        <is>
-          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
-        </is>
-      </c>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>X-04</t>
+          <t>Q-14</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>E-09</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testowe warstw krytycznych</t>
+          <t>Rozszerzenia oferty</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>ciągłe</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>NISKI</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Testy integracyjne / e2e API</t>
+          <t>Kreator uruchomienia węzła</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
         <is>
-          <t>X — Infrastruktura jakości</t>
+          <t>Q — Przewaga</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="I136" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
@@ -14248,14 +14248,14 @@
       </c>
       <c r="K136" s="11" t="inlineStr">
         <is>
-          <t>apps/api/test/integration/ — setup.ts (izolacja przez TRUNCATE CASCADE, fabryki, atrapy DirectAdmina/poczty/audytu), node-selector.int-spec.ts (9 testów placementu na prawdziwych zapytaniach), ksiega.int-spec.ts (6 testów cyklu życia księgi z prawdziwymi transakcjami); apps/api/jest.integration.cjs — maxWorkers 1, bo testy dzielą jedną bazę; .github/workflows/ci.yml — job „API integration tests” z Postgresem 16</t>
+          <t>node-wizard.tsx:277,288 — realnie tylko init + bootstrap; 7 z 9 kroków to treść runbooka (wizard-content.ts:21-40)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>X-05</t>
+          <t>X-04</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>Testy paneli frontowych</t>
+          <t>Testy integracyjne / e2e API</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I137" s="10" t="n">
@@ -14298,19 +14298,19 @@
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K137" s="11" t="inlineStr">
         <is>
-          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
+          <t>apps/api/test/integration/ — setup.ts (izolacja przez TRUNCATE CASCADE, fabryki, atrapy DirectAdmina/poczty/audytu), node-selector.int-spec.ts (9 testów placementu na prawdziwych zapytaniach), ksiega.int-spec.ts (6 testów cyklu życia księgi z prawdziwymi transakcjami); apps/api/jest.integration.cjs — maxWorkers 1, bo testy dzielą jedną bazę; .github/workflows/ci.yml — job „API integration tests” z Postgresem 16</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>X-06</t>
+          <t>X-05</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami modułu auth</t>
+          <t>Testy paneli frontowych</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -14345,11 +14345,11 @@
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="I138" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
@@ -14358,14 +14358,14 @@
       </c>
       <c r="K138" s="11" t="inlineStr">
         <is>
-          <t>zero plików .spec w apps/api/src/auth</t>
+          <t>admin-panel i staff-panel: 0 plików; client-panel: 1 plik bez runnera (brak skryptu test w package.json:5-11)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>X-07</t>
+          <t>X-06</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami klienta KSeF</t>
+          <t>Pokrycie testami modułu auth</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -14413,14 +14413,14 @@
       </c>
       <c r="K139" s="11" t="inlineStr">
         <is>
-          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
+          <t>zero plików .spec w apps/api/src/auth</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>X-08</t>
+          <t>X-07</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami ścieżki backup/restore</t>
+          <t>Pokrycie testami klienta KSeF</t>
         </is>
       </c>
       <c r="G140" s="10" t="inlineStr">
@@ -14468,14 +14468,14 @@
       </c>
       <c r="K140" s="11" t="inlineStr">
         <is>
-          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
+          <t>ksef-v2.client.ts (487 l. kryptografii + API skarbowe) — ZERO testów; testowany jest tylko builder XML</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>X-09</t>
+          <t>X-08</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>Pokrycie testami DirectAdminService</t>
+          <t>Pokrycie testami ścieżki backup/restore</t>
         </is>
       </c>
       <c r="G141" s="10" t="inlineStr">
@@ -14514,7 +14514,7 @@
         </is>
       </c>
       <c r="I141" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J141" s="10" t="inlineStr">
         <is>
@@ -14523,14 +14523,14 @@
       </c>
       <c r="K141" s="11" t="inlineStr">
         <is>
-          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
+          <t>offsite-restore.service.ts (regex chroniący przed path traversal na wejściu od klienta) — ZERO testów</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>X-10</t>
+          <t>X-09</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
-          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
+          <t>Pokrycie testami DirectAdminService</t>
         </is>
       </c>
       <c r="G142" s="10" t="inlineStr">
@@ -14569,23 +14569,23 @@
         </is>
       </c>
       <c r="I142" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J142" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="K142" s="11" t="inlineStr">
         <is>
-          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
+          <t>directadmin.service.ts ma 3057 linii; testowany jest wyłącznie helper mergeAdminSettingsPayload</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>X-19</t>
+          <t>X-10</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>Dług lintera odsłonięty przez Next 16 i włączenie ESLinta w API</t>
+          <t>Testy RBAC sprawdzające zachowanie, nie metadane</t>
         </is>
       </c>
       <c r="G143" s="10" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="I143" s="10" t="n">
@@ -14628,19 +14628,19 @@
       </c>
       <c r="J143" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="K143" s="11" t="inlineStr">
         <is>
-          <t>libs/eslint-config/node.mjs oraz apps/*/eslint.config.mjs — reguły włączone, ale część jako ostrzeżenia; 209 ostrzeżeń w panelach, 58 w API</t>
+          <t>3 pliki spec czytają Reflect.getMetadata(ROLES_KEY) — weryfikują, że dekorator napisano, nie że guard blokuje</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>X-20</t>
+          <t>X-19</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>Decyzja i migracja na Prismę 7</t>
+          <t>Dług lintera odsłonięty przez Next 16 i włączenie ESLinta w API</t>
         </is>
       </c>
       <c r="G144" s="10" t="inlineStr">
@@ -14679,76 +14679,131 @@
         </is>
       </c>
       <c r="I144" s="10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J144" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="K144" s="11" t="inlineStr">
         <is>
-          <t>libs/database/package.json — prisma 6.19.3; schema.prisma:17 — datasource url = env("DATABASE_URL"), składnia usunięta w Prismie 7</t>
+          <t>libs/eslint-config/node.mjs oraz apps/*/eslint.config.mjs — reguły włączone, ale część jako ostrzeżenia; 209 ostrzeżeń w panelach, 58 w API</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
+          <t>X-20</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>E-09</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>Pokrycie testowe warstw krytycznych</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>ciągłe</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>Decyzja i migracja na Prismę 7</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>X — Infrastruktura jakości</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="I145" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J145" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>libs/database/package.json — prisma 6.19.3; schema.prisma:17 — datasource url = env("DATABASE_URL"), składnia usunięta w Prismie 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
           <t>X-22</t>
         </is>
       </c>
-      <c r="B145" s="10" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>E-09</t>
         </is>
       </c>
-      <c r="C145" s="11" t="inlineStr">
+      <c r="C146" s="11" t="inlineStr">
         <is>
           <t>Pokrycie testowe warstw krytycznych</t>
         </is>
       </c>
-      <c r="D145" s="10" t="inlineStr">
+      <c r="D146" s="10" t="inlineStr">
         <is>
           <t>ciągłe</t>
         </is>
       </c>
-      <c r="E145" s="10" t="inlineStr">
+      <c r="E146" s="10" t="inlineStr">
         <is>
           <t>WYSOKI</t>
         </is>
       </c>
-      <c r="F145" s="11" t="inlineStr">
+      <c r="F146" s="11" t="inlineStr">
         <is>
           <t>Eksport danych osobowych (RODO art. 20) sprawdzany testem end-to-end</t>
         </is>
       </c>
-      <c r="G145" s="10" t="inlineStr">
+      <c r="G146" s="10" t="inlineStr">
         <is>
           <t>X — Infrastruktura jakości</t>
         </is>
       </c>
-      <c r="H145" s="10" t="inlineStr">
+      <c r="H146" s="10" t="inlineStr">
         <is>
           <t>WYSOKA</t>
         </is>
       </c>
-      <c r="I145" s="10" t="n">
+      <c r="I146" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="J145" s="10" t="inlineStr">
+      <c r="J146" s="10" t="inlineStr">
         <is>
           <t>BRAK</t>
         </is>
       </c>
-      <c r="K145" s="11" t="inlineStr">
+      <c r="K146" s="11" t="inlineStr">
         <is>
           <t>apps/api/src/compliance/data-export.service.ts — buildZipToFile bez żadnego testu; apps/api/src/compliance/*.spec.ts — brak pokrycia tej ścieżki</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K145"/>
+  <autoFilter ref="A1:K146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień korekty w apps/api i schema.prisma; fa3-xml.builder.ts:177 zawsze &lt;RodzajFaktury&gt;VAT</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>pierwszy zwrot, pierwsza rezygnacja w trakcie okresu, pierwsza literówka w NIP — i operator wychodzi poza system</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -2639,12 +2639,12 @@
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>ops/scripts/restore-drill-isolated.sh istnieje jako procedura ręczna; live-readiness.service.ts:175-177 sprawdza tylko czy backup się WYKONAŁ</t>
+          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker. Runbook wymaga drilla przed LIVE (OFFSITE_RESTORE_RUNBOOK.md:37-40) i nie ma w repo śladu jego wykonania. Backupy i DR wymagają poziomu D4 — data, wynik, właściciel. Bez tego cała warstwa DR jest niepotwierdzona.</t>
+          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$65)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$79)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$65,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$65,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$79,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$79,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$65,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$79,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$65,"zrobione",'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$79,"zrobione",'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1193,31 +1193,31 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>X-11</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Unit economics węzła vs cena 45 zł/mies. brutto (399 zł/rok)</t>
+          <t>Testy API w osobnym jobie CI, nie za typecheckiem</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>1</v>
@@ -1239,27 +1239,27 @@
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci.yml — osobny job api-tests o nazwie „API unit tests"</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>Arkusz z kosztem miesięcznym węzła, liczbą kont na węzeł, marżą jednostkową i progiem rentowności. Decyzja: cena zostaje albo się zmienia — zapisana w repo.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>Policzyć pełny koszt węzła: serwer + CloudLinux + LiteSpeed + DirectAdmin + Imunify + backup S3 + amortyzacja wsparcia. Wyliczyć próg rentowności w kontach na węzeł i marżę przy 45 zł brutto (36,59 zł netto).</t>
+          <t>Zamknięte 2026-08-21. Zasada: krok, który DOWODZI, nie może stać za krokiem, który tylko sprawdza higienę. Przy przebiegu #17 typecheck wywalił się na apps/www — panelu niezwiązanym z tamtą pracą — i 194 testy nie uruchomiły się ani razu. Koszt rozdzielenia: jeden dodatkowy pnpm install, joby i tak biegną równolegle. deploy.yml celowo zostaje z testami w jednym jobie z typecheckiem, bo zadaniem bramki jest zablokować wdrożenie, a nie dostarczyć dowód. Check „API unit tests" dopisany do rulesetu z X-02 tego samego dnia — bez tego rozdzielenie jobów otwierałoby dziurę: testy widoczne, ale niewymagane do scalenia. Dokumentacja: docs/zadania/X-11-testy-api-w-osobnym-jobie.md | KOREKTA 2026-08-22: podział jobów zabrał testom budowanie bibliotek, które wcześniej działo się przy okazji przez pnpm typecheck (Turbo, dependsOn ^build). Job „API unit tests” był przez to CZERWONY od tego commita aż do X-17, mimo że zgłosiłem pozycję jako zamkniętą na podstawie zielonych testów lokalnych. Sam przebieg CI sprawdziłem dopiero przy #56. Wniosek zapisany w X-17: pozycja dotycząca CI nie może być zamknięta bez obejrzenia przebiegu, którego dotyczy.</t>
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr">
@@ -1271,12 +1271,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Z-04</t>
+          <t>X-12</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Guard uprawnień subkont — domyślna odmowa</t>
+          <t>Skrypty węzła serwowane przez API obecne w obrazie produkcyjnym</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>O — Multi-user i reseller</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -1298,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>customer-permissions.guard.ts — typ WymogTrasy, REGULY_TRAS, domyślne 'ODMOWA'; customer-permissions-coverage.spec.ts — 55 tras zamkniętych, lista jawna</t>
+          <t>Dockerfile.api — COPY dla 10 skryptów; apps/api/src/test/dockerfile-scripts.spec.ts; D3: 2026-08-21 21:57 — `docker exec &lt;api&gt; ls -la ops/scripts/` na control-plane pokazuje 10 plików, w tym node-php-apply.sh, node-app-install.sh i node-account-restore.sh</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21. Przemiatanie tras pokazało większą skalę niż pierwotny opis: 148 z 347 tras dostępnych dla konta klienckiego nie wymagało żadnego uprawnienia, w tym POST /me/account-deletion (usunięcie konta właściciela), POST /partners/me/payouts/bank (wypłata prowizji na konto bankowe) i POST /users/iam/invites. Domyślna odpowiedź odwrócona na odmowę; rzeczy właściciela zamknięte twardo, niezależnie od nadanych uprawnień. Testy na zachowaniu strażnika, nie na metadanych — 15 z 28 czerwieniło się na starej wersji. Dokumentacja: docs/zadania/Z-04-guard-uprawnien-subkont.md</t>
+          <t>Nowa klasa błędu, której audyt nie widział: „skrypt jest w repozytorium, ale nie ma go w obrazie". Lokalnie wszystko działa, bo monorepo leży obok; w kontenerze jest tylko to, co wymienia Dockerfile. Brakowały trzy: node-account-restore.sh, node-app-install.sh, node-php-apply.sh. Skutek: trzy rodzaje zadań agenta nie wykonywały się na produkcji, przy zielonych testach i zielonym buildzie. Test statyczny wyciąga ścieżki z loaderów i porównuje z COPY — kosztuje milisekundy, zamyka całą klasę. | D3 OSIĄGNIĘTE 2026-08-21 21:57 po wdrożeniu #62: wszystkie dziesięć skryptów obecne w obrazie na serwerze. To pierwsza pozycja w tym audycie z dowodem poziomu D3.</t>
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Z-03</t>
+          <t>X-13</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Walidacja danych migracji przed użyciem w poleceniu powłoki</t>
+          <t>Jedna gałąź wdrożeniowa — main</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>dto/migration.dto.ts — MIGRACJA_WZORCE + @Matches na 17 polach; ops/scripts/lib/migration-input-guard.sh — vg_require; node-migration-worker.sh — fail-closed source + zero eval</t>
+          <t>.github/workflows/deploy.yml — on.push.branches: [main]</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21. Trzy wektory: eval z nazwą bazy, łańcuch poleceń lftp ze ścieżką zdalną, eval przy imporcie — wszystkie usunięte, plus allowlista znaków na obu warstwach (DTO i węzeł). Worker startuje fail-closed bez biblioteki walidacji (kod 78), sprawdzone zachowaniem w teście. 70 przypadków testowych, 48 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy dostępu. Dokumentacja: docs/zadania/Z-03-walidacja-danych-migracji.md</t>
+          <t>Do 2026-08-21 wdrożenie wyzwalały trzy gałęzie: main, master i live-release-readiness. Realne wdrożenia szły z live-release-readiness, master w repozytorium nie istniał, a main stał od czerwca. Trzy wyzwalacze to trzy odpowiedzi na pytanie „co jest na produkcji" — czyli brak odpowiedzi. Decyzja PM-a: zostaje sam main, chroniony rulesetem z X-02 i bramką testową z X-03. Konsekwencja: live-release-readiness przestaje być gałęzią wdrożeniową i zostaje jako zapis historii do czasu wycofania.</t>
         </is>
       </c>
       <c r="P8" s="10" t="inlineStr">
@@ -1427,12 +1427,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Z-06</t>
+          <t>X-14</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Klucz idempotencji obciążenia za dodatek</t>
+          <t>CI sprawdza DANE po migracji, nie tylko czy migracja się wykonała</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -1454,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>addon.service.ts — kluczIdempotencji + sprawdzenie duplikatu przed obciążeniem + obsługa P2002; schema.prisma — PurchasedAddon.idempotencyKey @unique; migracja 20260821220000_addon_idempotency</t>
+          <t>.github/workflows/ci.yml — job migrations: kroki „Seed reference data” i „Verify migrated data (Z-12, Z-13, Z-16)”; ops/sql/sprawdz-baze-po-migracji.sql — 5 bloków asercji kończących się RAISE EXCEPTION</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21. Mechanizm idempotencji w księdze portfela był poprawny — nie miał czego porównywać, bo Date.now() w kluczu dawał inny klucz przy każdym kliknięciu. Poprawka na dwóch drogach: klucz od klienta (panel, useRef, jeden na decyzję zakupu) i okno czasu jako zapas. Sprawdzenie duplikatu idzie PRZED obciążeniem, więc nie powtarzają się też skutki uboczne — bez tego klient dostawałby dziesięć zgłoszeń do BOK-u przy jednym obciążeniu. Wyścig domyka unikalny indeks w bazie. 20 testów, 10 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy pieniędzy. Dokumentacja: docs/zadania/Z-06-klucz-idempotencji-dodatku.md</t>
+          <t>Zamknięte 2026-08-22. Job migrations sprawdzał wyłącznie, czy migracje dają się zastosować i czy schemat nie ma dryfu. Nie sprawdzał, czy DANE, które migracje wstawiają, tam są i mają właściwe wartości — a Z-12 i Z-13 to migracje danych, których poprawność testy jednostkowe potwierdzały wyłącznie przez czytanie SQL-a jako TEKSTU. | Teraz CI odpytuje bazę: czy plan verris-hosting istnieje z ceną 45,00 brutto i limitami 200/8192/51200, czy publiczny pakiet hostingowy jest dokładnie jeden, czy prototypy są wycofane ale nie zdezaktywowane, czy kolumny overcommit mają NEUTRALNĄ domyślną 1, czy księga pojemności zgadza się z sumą limitów kont żywych. | Sprawdzone na prawdziwym Postgresie 16 ze wszystkimi 100 migracjami: komplet przechodzi, a podmiana ceny na 49,00 i podniesienie domyślnej nadsubskrypcji do 4 wywalają job z kodem 3. | ODKRYTE PRZY TESTOWANIU: na bazie z samych migracji plany prototypowe w ogóle nie istnieją (tworzy je seed), więc asercja o ich wycofaniu przechodziła TRYWIALNIE — w logu CI wygląda to identycznie jak prawdziwe „wszystko w porządku”. Stąd krok seeda przed asercjami plus jawny warunek: zero znalezionych prototypów to błąd, nie sukces. Przy okazji CI po raz pierwszy weryfikuje, że seed w ogóle wykonuje się na świeżej bazie. | Dokumentacja: docs/zadania/X-14-asercje-danych-po-migracji.md</t>
         </is>
       </c>
       <c r="P9" s="10" t="inlineStr">
@@ -1505,12 +1505,12 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Z-12</t>
+          <t>X-15</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+          <t>Niezmiennik księgi pojemności sprawdzany liczbowo, nie tekstowo</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
+          <t>apps/api/src/subscriptions/ksiega-niezmiennik.spec.ts — 15 testów: losowe ciągi operacji (założenie konta, skalowanie w górę i w dół, zmiana planu, usunięcie) z porównaniem księgi z prawdą po KAŻDYM kroku; node-capacity.ts — deltaKsiegi/limityEfektywne/ksiegaUpdateData jako jedyna arytmetyka księgi w projekcie</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
+          <t>Zamknięte 2026-08-22. Strażniki z Z-16 były statyczne — czytały tekst źródłowy. Złapią usunięcie linii (i złapały, gdy arytmetyka poszła do wspólnych funkcji), ale nie złapią błędu w ZNAKU delty ani pomylonych argumentów: deltaKsiegi(po, przed) zamiast deltaKsiegi(przed, po) przechodzi każdy test tekstowy i rozjeżdża księgę przy pierwszej operacji. | Test sprawdza jedyną rzecz, która musi być prawdziwa: allocated* równa się sumie limitów efektywnych kont żywych po dowolnym ciągu operacji. Deterministyczny generator, sześć ziaren, sprawdzenie po każdym kroku — żeby dwa błędy nie zniosły się nawzajem. | Uczciwość testu polega na tym, że symulator używa DOKŁADNIE tych samych funkcji co produkcja; gdyby liczył po swojemu, sprawdzałby siebie. Warunkiem było wyciągnięcie arytmetyki z czterech serwisów do node-capacity.ts — przy okazji piąty rozjazd nie ma już gdzie powstać. | Zweryfikowane: odwrócenie znaku w JEDNYM zasobie czerwieni 10 z 15 testów niezmiennika. Test statyczny tego nie widzi. | Czego to nie sprawdza: czy serwisy wołają te funkcje w odpowiednim momencie i z odpowiednimi argumentami — to jest rola X-04. Tu weryfikowana jest arytmetyka, tam okablowanie.</t>
         </is>
       </c>
       <c r="P10" s="10" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Z-13</t>
+          <t>X-17</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+          <t>Joby CI budują zależności workspace'u zanim uruchomią testy</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -1610,7 +1610,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
+          <t>.github/workflows/ci.yml — krok „Build workspace libraries” w jobie api-tests, „Generate Prisma client” w jobie migrations; turbo.json — zadanie test dostaje dependsOn ^build; apps/api/src/test/ci-joby.spec.ts — 6 testów strażnika</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
+          <t>Zamknięte 2026-08-22 po przejrzeniu przebiegu CI #56. To jest MÓJ błąd i dokładnie ten wzorzec, który X-11 miał naprawiać. | @verris/database ma main: dist/index.js. Bez zbudowanego dist/ jest nie rozwiąże modułu i 32 z 48 zestawów NIE STARTUJĄ — nie failują, tylko się nie uruchamiają. W logu wygląda to jak awaria testów, a jest awarią konfiguracji. | Przed X-11 testy biegły wewnątrz joba static-checks, którego krok pnpm typecheck idzie przez Turbo, a typecheck ma dependsOn ^build. Biblioteki budowały się PRZY OKAZJI — nikt tego nie zaprojektował, więc nikt nie zauważył, gdy zniknęło. X-11 wydzieliło testy do własnego joba, który nie budował niczego; pnpm --filter api test omija Turbo, a zadanie test nie miało dependsOn. | Job był czerwony przez trzy wdrożenia (CI #54, #55, #56) przy 415 zielonych testach na maszynie, gdzie dist/ leżało zbudowane z dawnych uruchomień. Zgłosiłem X-11 jako zamknięte, nie sprawdziwszy przebiegu CI — „zielono lokalnie” potraktowałem jako dowód, a to jest dokładnie ten skrót, przed którym skala dowodowa tego audytu ma chronić. | Drugi błąd, świeższy: krok „Seed reference data” dodany do joba migrations w commicie d381a64 wołał seed importujący @verris/database, a ten job nigdy nie generował klienta. Job przeszedł z zielonego na czerwony. | Poprawka na trzech poziomach: jawne kroki w obu jobach, dependsOn ^build w turbo.json (żeby pnpm test był poprawny też lokalnie i w każdym przyszłym jobie) oraz strażnik, który przemiata ci.yml i zapala się, gdy job uruchamia testy bez zbudowania bibliotek. | Strażnik w pierwszej wersji dał FAŁSZYWY ALARM — wzorzec \bjest\b trafiał w polskie słowo „jest” w moich własnych komentarzach. Zawężony do faktycznych wywołań komend, komentarze odfiltrowane przed dopasowaniem. Narzędzie, którego jedynym zadaniem jest nie kłamać, samo skłamało za pierwszym razem. | Dokumentacja: docs/zadania/X-17-joby-ci-buduja-zaleznosci.md | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #57 zielony w komplecie — sześć jobów, w tym „API integration tests" z Postgresem 16.</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
@@ -1661,58 +1661,58 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Z-16</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+          <t>Unit economics węzła vs cena 45 zł/mies. brutto (399 zł/rok)</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Faza 0 — Zatrzymać krwawienie</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Arkusz z kosztem miesięcznym węzła, liczbą kont na węzeł, marżą jednostkową i progiem rentowności. Decyzja: cena zostaje albo się zmienia — zapisana w repo.</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+          <t>Policzyć pełny koszt węzła: serwer + CloudLinux + LiteSpeed + DirectAdmin + Imunify + backup S3 + amortyzacja wsparcia. Wyliczyć próg rentowności w kontach na węzeł i marżę przy 45 zł brutto (36,59 zł netto).</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
@@ -1739,34 +1739,34 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-04</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Guard uprawnień subkont — domyślna odmowa</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>O — Multi-user i reseller</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -1775,37 +1775,37 @@
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>customer-permissions.guard.ts — typ WymogTrasy, REGULY_TRAS, domyślne 'ODMOWA'; customer-permissions-coverage.spec.ts — 55 tras zamkniętych, lista jawna</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Zamknięte 2026-08-21. Przemiatanie tras pokazało większą skalę niż pierwotny opis: 148 z 347 tras dostępnych dla konta klienckiego nie wymagało żadnego uprawnienia, w tym POST /me/account-deletion (usunięcie konta właściciela), POST /partners/me/payouts/bank (wypłata prowizji na konto bankowe) i POST /users/iam/invites. Domyślna odpowiedź odwrócona na odmowę; rzeczy właściciela zamknięte twardo, niezależnie od nadanych uprawnień. Testy na zachowaniu strażnika, nie na metadanych — 15 z 28 czerwieniło się na starej wersji. Dokumentacja: docs/zadania/Z-04-guard-uprawnien-subkont.md</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
@@ -1817,12 +1817,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>Z-03</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Walidacja danych migracji przed użyciem w poleceniu powłoki</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -1844,21 +1844,21 @@
         <v>16</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
+          <t>dto/migration.dto.ts — MIGRACJA_WZORCE + @Matches na 17 polach; ops/scripts/lib/migration-input-guard.sh — vg_require; node-migration-worker.sh — fail-closed source + zero eval</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+          <t>Zamknięte 2026-08-21. Trzy wektory: eval z nazwą bazy, łańcuch poleceń lftp ze ścieżką zdalną, eval przy imporcie — wszystkie usunięte, plus allowlista znaków na obu warstwach (DTO i węzeł). Worker startuje fail-closed bez biblioteki walidacji (kod 78), sprawdzone zachowaniem w teście. 70 przypadków testowych, 48 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy dostępu. Dokumentacja: docs/zadania/Z-03-walidacja-danych-migracji.md</t>
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr">
@@ -1895,12 +1895,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-06</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Klucz idempotencji obciążenia za dodatek</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1915,38 +1915,38 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>addon.service.ts — kluczIdempotencji + sprawdzenie duplikatu przed obciążeniem + obsługa P2002; schema.prisma — PurchasedAddon.idempotencyKey @unique; migracja 20260821220000_addon_idempotency</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1959,7 +1959,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr"/>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-21. Mechanizm idempotencji w księdze portfela był poprawny — nie miał czego porównywać, bo Date.now() w kluczu dawał inny klucz przy każdym kliknięciu. Poprawka na dwóch drogach: klucz od klienta (panel, useRef, jeden na decyzję zakupu) i okno czasu jako zapas. Sprawdzenie duplikatu idzie PRZED obciążeniem, więc nie powtarzają się też skutki uboczne — bez tego klient dostawałby dziesięć zgłoszeń do BOK-u przy jednym obciążeniu. Wyścig domyka unikalny indeks w bazie. 20 testów, 10 czerwieniło się na starym kodzie. D3 wymagane po wdrożeniu, bo pozycja dotyczy pieniędzy. Dokumentacja: docs/zadania/Z-06-klucz-idempotencji-dodatku.md</t>
+        </is>
+      </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -1969,12 +1973,12 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>X-18</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Zależności podniesione do najnowszych bezpiecznych wersji</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1984,50 +1988,50 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
+          <t>package.json — 16 pnpm.overrides na zależności przechodnie; apps/www next 15.4.4 → 16.3.2; wszystkie panele next 16.3.2; NestJS 11.2.1; React 19.2.8; Payload 3.88.0; recharts 3; @types/node 26; ioredis 6; bullmq 6; graphql 17; sharp 0.35.3; libs/typescript-config/nestjs.json target ES2022 + lib ES2023</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
@@ -2035,7 +2039,7 @@
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
+          <t>Zamknięte 2026-08-22. Podatności: 142 → 2 (krytyczne 2 → 0, wysokie 61 → 1, średnie 69 → 0). | NAJWAŻNIEJSZE: apps/www stało na next 15.4.4 z krytycznym RCE w protokole React flight (łatka od 15.4.8) i wysokim DoS przez Server Components (od 15.4.9). To jest PUBLICZNA strona verris.pl. Panele były na 16.2.7 i ich to nie dotyczyło. Podniesione do 16.3.2 — Payload 3.88 deklaruje wsparcie dla &gt;=16.2.6, więc to ścieżka sankcjonowana przez dostawcę, nie obejście. Build www przechodzi. | Zależności PRZECHODNIE, których nie da się podnieść przez rodzica, domknięte przez pnpm.overrides. Przy pierwszym podejściu użyłem zakresów bez górnej granicy ("&gt;=1.1.18") — pnpm podstawił NAJWYŻSZĄ pasującą wersję, dla brace-expansion@1 było to 5.0.9 o innym kształcie eksportu, co wywaliło minimatch@3 komunikatem „expand is not a function". Każdy override jest teraz ograniczony do linii majora. | CZEGO NIE PODNIOSŁEM I DLACZEGO — trzy rzeczy, w których ekosystem nie nadąża: (1) Prisma 6.19.3 → 7.x to NIE jest podniesienie wersji, tylko zmiana architektury warstwy danych: `url` znika ze schematu na rzecz prisma.config.ts, a PrismaClient wymaga driver adaptera; dotyka każdego wywołania bazy, seeda, CI i wdrożenia produkcyjnego. Osobna pozycja: X-20. (2) TypeScript 5.9.3 → 7.0.2 — ts-jest ma peer &gt;=4.3 &lt;7, typescript-eslint &gt;=4.8.4 &lt;6.1.0; podniesienie wyłączyłoby jednocześnie testy i linter. Dodany override pinujący, bo TS 7 wchodził do drzewa jako zależność przechodnia mimo "^5" wszędzie. (3) ESLint 9.39.5 → 10.9.0 — eslint-plugin-react 7.37.5 wywala się w runtime („contextOrFilename.getFilename is not a function"), a to on stoi za konfiguracją Next. | Zostały 2 podatności: deepmerge-ts (wysoka, tylko przez Prismę 6 — znika z X-20) i jedna niska. | Wymuszone zmiany w kodzie: recharts 3 usunęło prop activeIndex z &lt;Pie&gt; (podświetlenie przepisane na przezroczystość &lt;Cell&gt;); @types/node 26 zawęziło typ chunka w zdarzeniu 'data' i zmieniło response.json() z any na unknown; bullmq 6 usunęło 'paused' z JobType; Array.prototype.at wymusiło lib ES2023. | Weryfikacja: lint 7/7, typecheck 8/8, 421 testów jednostkowych, 15 integracyjnych, build www — wszystko na prawdziwym Postgresie w kontenerze. Dokumentacja: docs/zadania/X-18-podniesienie-zaleznosci.md | KOREKTA 2026-08-22 (X-21): graphql cofnięty z ^17.0.2 do ^16.14.2 — jedynym konsumentem jest Payload 3.88, który deklaruje peera ^16.8.1, a nasz kod nie importuje graphql ani razu. Podniosłem major pod biblioteką, która go nie wspiera, bo wersja była wyższa — na PUBLICZNEJ stronie. Build www przechodzi na 16, ostrzeżenie o peerze znikło. | Domknięty body-parser override'em ^2.3.0: podatności 2 → 1 (została deepmerge-ts, wysoka, tylko przez Prismę 6 — znika z X-20). | engines.node podniesione z "&gt;=22" do "&gt;=22.12" — patrz X-21.</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr">
@@ -2047,12 +2051,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>X-21</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Deklaracje typów opisują tę wersję biblioteki, która jest zainstalowana</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2062,7 +2066,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -2071,24 +2075,24 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
+          <t>apps/api/package.json — @types/archiver ^8.0.0 przy archiver ^8.0.0; apps/api/src/test/typy-zgodne-z-runtime.spec.ts — 12 testów; package.json — engines.node "&gt;=22.12"</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -2113,7 +2117,7 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+          <t>Zamknięte 2026-08-22. BŁĄD PRODUKCYJNY znaleziony przy X-18, siedzący w kodzie PRZED podniesieniem. apps/api/package.json deklarował jednocześnie archiver ^8.0.0 i @types/archiver ^7.0.0. Archiver 8 usunął fabrykę create() na rzecz klas per format — kod wołał archiver.create('zip'/'tar'), typecheck był ZIELONY, bo typy z linii 7 tę funkcję opisywały, a w runtime jej nie było. Sprawdzone realnie: Object.keys(require('archiver')) = ['Archiver','JsonArchive','TarArchive','ZipArchive'], create === undefined. | CO TO PSUŁO: (1) data-export.service.ts → buildZipToFile — eksport danych osobowych (RODO art. 20, prawo do przenoszenia) wywalał się przy KAŻDYM żądaniu; (2) default-hosting-page.assets.ts → buildDefaultHostingPageBundle — budowa paczki domyślnej strony wywalała się przy KAŻDYM provisioningu konta. Nie „czasem" — zawsze, od momentu podniesienia archivera. | DLACZEGO NIKT TEGO NIE ZOBACZYŁ: typecheck czytał typy opisujące nieistniejącą wersję, żaden test nie dotykał tych dwóch funkcji, lint nie ma reguły na „ta metoda nie istnieje w runtime". Typecheck jest bramką wdrożenia — jeżeli typy opisują inną wersję niż zainstalowana, bramka przepuszcza kod, który się nie uruchomi, i robi to cicho, na zielono. | DRUGIE DNO: archiver 8 jest czystym ESM-em ("type": "module", brak wejścia CJS), a API kompiluje się do CommonJS-a. Node obsługuje require(esm) bez flagi dopiero od 22.12, a engines.node stał na "&gt;=22". Obrazy używają taga node:22 (dziś 22.22), więc realnie nic się nie paliło, ale deklaracja pozwalała na konfigurację, która by się paliła — ERR_REQUIRE_ESM w tych samych dwóch ścieżkach. Podniesione do "&gt;=22.12". | STRAŻNIK NA CAŁĄ KLASĘ, nie na sam archiver: żadne @types/X w monorepo nie może opisywać innego majora niż zainstalowany X. Test runtime'u wywołuje osobny proces Node'a (execFileSync), bo transformacja jesta nie ładuje zależności ESM i sprawdzałaby ładowarkę jesta zamiast produkcji. | Czerwieni się na starym kodzie: cofnięcie wszystkich trzech rzeczy daje 3 czerwone z 12, każdy z wykonalnym komunikatem. | Strażnik po raz TRZECI w tym projekcie trafił sam w siebie — szukana fraza padała w treści jego własnego komunikatu błędu (ta sama pułapka co polskie „jest" w X-17). Pominięty __filename + osobny test na spreparowanym wejściu. | PRZY OKAZJI: body-parser (niska, DoS przy cichym wyłączeniu limitu rozmiaru) domknięty override'em ^2.3.0 — podatności 2 → 1; graphql cofnięty z ^17.0.2 do ^16.14.2, bo jedynym konsumentem jest Payload 3.88 deklarujący peera ^16.8.1, a nasz kod nie importuje graphql ani razu — to korekta mojego własnego błędu z X-18: podniosłem wersję, bo była wyższa, nie sprawdzając, kto z niej korzysta. | Weryfikacja: 433 testy jednostkowe, 15 integracyjnych, lint 7/7, typecheck 8/8, build www. Dokumentacja: docs/zadania/X-21-typy-klamaly-o-runtime.md</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
@@ -2125,12 +2129,12 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>X-23</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Bramka podatności zatrzymuje wdrożenie, a nie tylko dopisuje adnotację</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -2140,7 +2144,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -2149,24 +2153,24 @@
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
@@ -2176,12 +2180,12 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
+          <t>ops/ci/audyt-bramka.cjs; ops/ci/podatnosci-dopuszczone.json; .github/workflows/ci.yml — krok „Bramka podatności" bez continue-on-error; apps/api/src/test/bramka-podatnosci.spec.ts — 15 testów; krok Lint też odmiękczony; .github/dependabot.yml — 3 reguły ignore z terminem; apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -2191,7 +2195,7 @@
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+          <t>Zamknięte w kodzie 2026-08-22, D1 do czasu obejrzenia przebiegu CI. Znalezione przy oglądaniu przebiegu CI #58, który zakończył się statusem Success — a w adnotacjach miał „Security scans: Process completed with exit code 1". Krok `pnpm audit --prod --audit-level high` wychodził z kodem 1 i nie zatrzymywał niczego, bo miał continue-on-error: true. | Powód był prawdziwy: w drzewie siedzi jedna wysoka podatność (deepmerge-ts przez Prismę 6, GHSA-ggr8-5vv4-36mx), której nie da się domknąć bez migracji na Prismę 7 — czyli X-20, świadomie odłożone. Bez continue-on-error każdy przebieg byłby czerwony. SKUTEK: nowa KRYTYCZNA podatność też by nie zatrzymała wdrożenia; job świeciłby na zielono z adnotacją, która przez kilkanaście przebiegów znaczyła „to ta znana". | Ta sama klasa błędu co X-17 — bramka, która nie bramkuje. Wzorzec wart nazwania, bo wraca: kiedy alarm dzwoni na coś, czego nie da się dziś naprawić, odruchem jest wyłączenie alarmu — i to działa, do pierwszej rzeczy, którą dałoby się naprawić, gdyby ktoś o niej usłyszał. | ROZWIĄZANIE: lista świadomych zgód z terminem ważności. Czerwone gdy: (a) nowa high/critical spoza listy, (b) zgoda po terminie, (c) zgoda na podatność, której już nie ma. Punkt (c) jest najłatwiejszy do uznania za przesadę i najważniejszy w dłuższym horyzoncie — lista wyjątków, z której nic nigdy nie znika, po pół roku przestaje cokolwiek znaczyć. Termin dalszy niż 90 dni odrzucany: „zgoda do 2030" to usunięcie bramki pod inną nazwą. Zgoda wymaga powodu min. 80 znaków i wskazania istniejącej pozycji macierzy. | STAN: 1 zgoda (deepmerge-ts, termin 2026-11-15 — mniej więcej wtedy X-20 i tak musi zostać rozstrzygnięte; jeśli nie zostanie, CI o tym przypomni, zatrzymując wdrożenie). | CZEGO TO NIE ROBI: gitleaks nadal ma continue-on-error (fałszywe trafienia na przykładowych konfiguracjach w ops/, wyciszanie to osobna robota z .gitleaksignore — zaostrzenie dziś skończyłoby się ponownym wyłączeniem alarmu); pnpm audit --prod pomija zależności deweloperskie; Trivy zostaje raportujący, bo dubluje zakres pnpm audit. | Strażnik po raz CZWARTY trafił we własny komentarz (fraza --audit-level w wyjaśnieniu, dlaczego tego kroku już nie ma) — po „jest" z X-17 i archiver.create z X-21. Reguła do zapamiętania: strażnik czytający treść pliku patrzy na kod, nie na prozę; komentarze wypadają przed dopasowaniem domyślnie, nie po pierwszym fałszywym alarmie. | Czerwieni się na starym kodzie: przywrócenie kroku z continue-on-error daje 2 czerwone z 15, a przywrócenie continue-on-error na kroku Lint — kolejne 2. | DRUGIE ZNALEZISKO w tym samym pliku: krok Lint miał continue-on-error z komentarzem „lint jest miękki, bramką jest typecheck". Komentarz był kiedyś prawdziwy — dziś pnpm lint wychodzi z zerem we wszystkich siedmiu pakietach (0 błędów, 270 ostrzeżeń — dług z X-19), więc miękkość nie chroniła już przed niczym poza NOWYM błędem lintera. Zdjęta; ostrzeżenia nadal przechodzą. Do tego biała lista MIEKKIE_DOZWOLONE: dołożenie miękkiego kroku ma być widoczną decyzją, a nie linijką dopisaną, bo się świeciło na czerwono. | Pierwsza wersja strażnika miękkich kroków używała jednego wyrażenia regularnego przez cały plik i przeciekała na następny krok — meldowała „Install pnpm jest miękki", choć miękki był krok obok. Przepisane na rozkład po wcięciu myślnika: strażnik, który wskazuje nie ten element, kosztuje tyle samo co brak strażnika. Dokumentacja: docs/zadania/X-23-bramka-podatnosci.md | TRZECIE ZNALEZISKO — wyciszenia Dependabota. PR-y #15 (Prisma 7) i #16 (TypeScript 7) wracałyby co tydzień, bo świadomie zostajemy na 6.x i 5.x. Naturalnym ruchem jest reguła ignore w .github/dependabot.yml — i naturalnym skutkiem, że po pół roku nikt nie pamięta, dlaczego tam jest ani czy powód nadal obowiązuje. Każde wyciszenie ma więc obowiązkowo dwa komentarze: „# pozycja: X-nn" (kto odpowiada) i „# przegląd: RRRR-MM-DD" (do kiedy). apps/api/src/test/dependabot-wyciszenia.spec.ts — 6 testów — czerwieni CI, gdy termin minie, gdy brakuje któregoś komentarza albo gdy wskazana pozycja nie istnieje w macierzy. Parser czyta komentarze, bo parser YAML-a ich nie widzi, a to w nich siedzi odpowiedzialność. | Termin 2026-11-15 jest TEN SAM co zgoda na deepmerge-ts w liście bramki — jeden termin do pilnowania zamiast trzech, wszystkie prowadzą do X-20. | PR-y Dependabota: #15 i #16 zamknie sam Dependabot jako objęte ignore; pozostałych 11 (#4–#14, #17, #18) zamknie się samo po scaleniu feat/sprint-2 do main, bo Dependabot zamyka własne PR-y, gdy gałąź bazowa dogoni wersję. Żadnego nie zamykam ręcznie. | Weryfikacja: 457 testów jednostkowych, 15 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. | D2 OSIĄGNIĘTE 2026-08-22: przebieg CI #59 zielony w komplecie, sześć jobów, ZERO adnotacji błędu — krok „Bramka podatności" przeszedł bez continue-on-error, a adnotacja „Process completed with exit code 1", która towarzyszyła każdemu wcześniejszemu przebiegowi, zniknęła.</t>
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr">
@@ -2203,12 +2207,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>X-24</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Panel admina woła ścieżki, które API naprawdę wystawia</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2218,43 +2222,43 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>apps/api/src/test/sciezki-panelu.spec.ts — 5 testów; porównuje wywołania adminApi() z panelu z trasami zadeklarowanymi w kontrolerach API</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -2269,7 +2273,7 @@
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Odkryte przy M-06. Formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna, a kontroler wystawia /admin/invoices/reczna. Kod się kompilował, testy jednostkowe przechodziły, panel się budował — 404 wyszłoby dopiero pod palcem operatora. | To ta sama rodzina co „bliźniacze miejsca", rozciągnięta na dwa pakiety: ścieżka zapisana dwa razy, w panelu i w kontrolerze, a nic ich nie łączy. Kompilator nie pomoże, bo po obu stronach to zwykły napis. | Strażnik wyciąga wywołania adminApi() z panelu i trasy z kontrolerów, porównuje kształt ścieżki i metodę HTTP. Segmenty dynamiczne (${id} w panelu, :id w kontrolerze) pasują do wszystkiego. | STRAŻNIK ZACZĄŁ OD JEDENASTU FAŁSZYWYCH ALARMÓW: (1) czytał 220 znaków po wywołaniu szukając `method:` i łapał metodę z NASTĘPNEGO wywołania — zwykły GET raportowany jako POST; (2) zamieniał wstawkę ${qs} na gwiazdkę w miejscu, produkując segment „webhooki*", który nie pasował do niczego; (3) grupował warianty ścieżki po wartości pochodnej zamiast po oryginale, więc wariant pełny zawsze zostawał sam i zawsze wyglądał na niepokryty. Jedenaście fałszywych alarmów przy dwóch prawdziwych znaleziskach. Strażnik, który tonie we własnym szumie, zostanie wyciszony — doprowadzenie do zera fałszywych alarmów było warunkiem działania, nie dopieszczaniem. | PIĄTE wystąpienie tej rodziny: „jest" (X-17), archiver.create (X-21), --audit-level (X-23), endsWith('billing.service.ts') (Z-05), teraz ścieżki panelu. | Czerwieni się na starym kodzie: przywrócenie błędnej ścieżki daje 1 czerwony z 5. | CZEGO NIE ROBI: nie sprawdza kształtu ciała żądania ani odpowiedzi — tylko ścieżkę i metodę; nie obejmuje panelu klienta ani panelu staff (te wołają inne bazowe adresy).</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
@@ -2281,73 +2285,73 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>X-25</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Asercje po migracji biegną także na produkcji, z rollbackiem przy naruszeniu</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>ops/sql/po-migracji-niezmienniki.sql — CI I PRODUKCJA, 14 RAISE EXCEPTION (Z-01, Z-05, Z-12, Z-13, Z-16, M-06); ops/sql/po-migracji-katalog.sql — tylko CI, wartości z oferty; ops/sql/po-migracji-historia.sql — raport, ZERO RAISE EXCEPTION w kodzie; ops/scripts/prod-deploy-ghcr.sh:79-133 — krok 3.5 (bramka + rollback) i 3.6 (raport); .github/workflows/ci.yml — cztery kroki po seedzie; ops/scripts/asercje-czerwienia-sie.sh — 10 naruszeń, każde na właściwej asercji; apps/api/src/test/asercje-po-migracji.spec.ts (36). Usunięte: ops/sql/sprawdz-baze-po-migracji.sql</t>
+        </is>
+      </c>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>Stan 2026-08-22: ZAMKNIĘTE. Sześć zamkniętych blokerów zostawiło plik asercji o stanie bazy po migracjach. Plik był porządny i biegł w JEDNYM miejscu: w CI, na świeżej bazie testowej — czyli dokładnie tam, gdzie nie ma prawdziwych danych. Produkcja po `prisma migrate deploy` nie była sprawdzana NICZYM; `migrate deploy` kończy się zerem, gdy pliki SQL się wykonały, i nie mówi nic o tym, czy baza jest po nich w stanie, w którym kod policzy dobrze. | DLACZEGO NIE DAŁO SIĘ PO PROSTU DOPISAĆ TEGO PLIKU DO DEPLOYU: część twierdzeń wywaliłaby wdrożenie bez powodu. Asercja „są plany prototypowe" dotyczy rzeczy, które tworzy SEED, a seed na produkcji nie biegnie. Gorsza była druga: pilnowała, żeby verris-hosting kosztował dokładnie 45,00 — a cenę WOLNO zmienić z panelu (plans.service.ts, updatePlan). Pierwsza legalna podwyżka zamieniłaby każde kolejne wdrożenie w rollback, a wtedy ktoś słusznie wyłączyłby całe sprawdzanie. Tego nie zauważyłem od razu — zobaczyłem dopiero, gdy własny strażnik zapalił się na isPublic i zamiast go poluzować sprawdziłem, czy cena jest edytowalna. Była. | TRZY PLIKI, TRZY RÓŻNE ŻYCIA: niezmienniki (CI i produkcja, blokują) — twierdzenia, których nie unieważni żadna legalna zmiana biznesowa; katalog (TYLKO CI) — dzisiejsza decyzja handlowa, w CI zmienia się w jednym commicie razem z PLAN_PRODUKCYJNY i treścią strony; historia (CI i produkcja, tylko raport) — dane sprzed migracji, których migracja nie naprawia i nie miała naprawiać; wycofanie wdrożenia z tego powodu byłoby karą za przeszłość, nie ochroną przed błędem. | Z Z-13 do niezmienników przeszły dwa twierdzenia, których panel nie może naruszyć: istnienie wiersza o slugu verris-hosting (slug stoi na sztywno w plan-produkcyjny.ts) oraz reguła cennika, którą API wymusza przy zapisie (ceny dodatnie, rok &gt;= 6x miesiąc) — API pilnuje jej przy zapisie, baza nie pilnuje wcale, a migracja danych zapisuje Z POMINIĘCIEM API. | JEDNA REGUŁA, JEDNO MIEJSCE: blok M-06 sprawdzał sumy korekty, które obejmuje już Z-01 (korekta to wiersz w Invoice) — druga kopia nigdy by nie wystartowała, a przy zmianie zasad ktoś poprawiłby jedną z dwóch. Usunięta. | DWIE CICHE PUŁAPKI W SAMYM WYWOŁANIU: `psql -U "${POSTGRES_USER:?}"` — przy pustej zmiennej psql połączyłby się z bazą o nazwie użytkownika i asercje przeszłyby na PUSTEJ, NIEWŁAŚCIWEJ bazie; `sh -c` zamiast `sh -lc` — skrypt profilu czytający stdin zjadłby SQL i psql dostałby pusty plik. | ASERCJA, KTÓRA SIĘ NIE CZERWIENI, NIE JEST BRAMKĄ: ops/scripts/asercje-czerwienia-sie.sh psuje po jednym niezmienniku naraz w transakcji z ROLLBACK-iem i sprawdza DWIE rzeczy — kod wyjścia różny od zera ORAZ że powodem jest TA asercja. Drugi warunek nie jest ozdobą: w pierwszym przebiegu trzy przypadki M-06 świeciły na czerwono, a naprawdę odbijał je CHECK w bazie, zanim asercja zdążyła cokolwiek zobaczyć (ta sama lekcja co Z-01 i H-20). | Czerwieni się na starym kodzie: jeden plik + brak asercji w deployu → 11 z 36; `|| true` zamiast bramki → 1; RAISE EXCEPTION w pliku historii → 1; katalog wpuszczony na produkcję → 1. | CZEGO NIE ROBI: nie cofa schematu (rollback wraca do poprzedniego obrazu, migracje zostają); nie sprawdza katalogu na produkcji — cena może się tam rozjechać z PLAN_PRODUKCYJNY i deploy tego nie zauważy (to bliżej monitoringu niż bramki); asercje-czerwienia-sie.sh NIE WOLNO uruchamiać na produkcji, bo zdejmuje ograniczenia CHECK wewnątrz transakcji. | D3 powstanie przy pierwszym deployu na main, w logu wdrożenia, z datą. Dokumentacja: docs/zadania/X-25-asercje-po-migracji.md</t>
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr">
@@ -2359,12 +2363,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>X-26</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Skrypty powłoki mają bit wykonywalności — także po świeżym git clone</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2374,7 +2378,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -2383,24 +2387,24 @@
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
@@ -2410,12 +2414,12 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
+          <t>apps/api/src/test/skrypty-wykonywalne.spec.ts (3) — żaden .sh w repozytorium bez bitu wykonywalności; 82 skrypty przestawione na tryb 100755 (16 z nich miało 100644, w tym restore-drill-isolated.sh z bramki startu i pięć uruchamianych na węzłach produkcyjnych); docs/ops/RESTORE_TEST.md — usunięte obejście `chmod +x` sprzed uruchomienia</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
@@ -2425,7 +2429,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
+          <t>Odkryte przy X-25, dzień po zamknięciu mechanizmu H-20. Runbook, dokumentacja zadania i MAIL PRZYPOMINAJĄCY do administratora mówią jednym głosem: `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "…"` — a plik miał w gicie tryb 100644. Na świeżym `git clone` to polecenie kończy się „Permission denied". Czyli procedura, którą właśnie zamieniliśmy w bramkę startu sprzedaży, nie dawała się wykonać w sposób, w jaki sama każe siebie wykonywać. | Szesnaście skryptów miało ten sam problem, w tym pięć uruchamianych na węzłach produkcyjnych (node-app-install, node-db-upgrade, node-offsite-backup, node-php-apply, node-wp-install). | ŚLAD PO TYM BŁĘDZIE LEŻAŁ W REPOZYTORIUM OD DAWNA: docs/ops/RESTORE_TEST.md kazał wpisać `chmod +x` PRZED uruchomieniem, a Dockerfile.api robi `chmod +x` na entrypoincie. Obejścia działały, więc nikt nie naprawił przyczyny — a każde z nich było zapisanym w repozytorium dowodem, że przyczyna istnieje. To jest ten sam kształt co „bramka, która raportuje zamiast bramkować": objaw obsłużony, przyczyna zostaje. | REGUŁA JEST BEZWYJĄTKOWA i to jest jej najważniejsza cecha. Lista „te skrypty wolno mieć nieuruchamialne, bo woła je bash" musiałaby być utrzymywana obok prawdziwych wywołań, czyli byłaby kolejnym wystąpieniem bliźniaczych miejsc (Z-12, Z-16, M-06, X-24). Skrypt wykonywalny działa pod `bash x.sh` tak samo dobrze, więc reguła bez wyjątków nic nie kosztuje. | Strażnik czyta TRYB Z DYSKU, nie z indeksu gita: liczy się to, co dostaje maszyna po `git clone`, a actions/checkout wypisuje pliki dokładnie z trybami z indeksu. Czytanie dysku działa też tam, gdzie kopia robocza nie jest repozytorium, i nie wymaga drugiej ścieżki kodu na wypadek braku gita. | Ma też kontrolę „strażnik w ogóle coś widzi" (ponad 50 skryptów, w tym ten z bramki startu) — bez niej cała reszta przechodziłaby trywialnie na pustej liście, gdyby `find` przestał trafiać. | Czerwieni się na starym kodzie: 1 z 3 testów, z wypisaną listą wszystkich szesnastu plików. | CZEGO NIE ROBI: nie sprawdza shebangów ani tego, czy skrypt w ogóle da się uruchomić — tylko bit wykonywalności.</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
@@ -2437,12 +2441,12 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>X-27</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Obraz, który trafia na serwer, buduje się przed scaleniem</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2452,7 +2456,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -2461,24 +2465,24 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
@@ -2488,12 +2492,12 @@
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
+          <t>Dockerfile.api / Dockerfile.panel — ponowna instalacja PO `COPY libs libs`; package.json — pnpm.overrides @prisma/client 6.19.3 (drzewo znów ma jedną wersję); .github/workflows/ci.yml — job `Obraz API (build bez push)`; apps/api/src/test/obrazy-dockera.spec.ts (14). Przyczyna deployu #63: „Could not resolve @prisma/client"</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
@@ -2503,7 +2507,7 @@
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
+          <t>Zamknięte 2026-08-22, wykryte przez wdrożenie #63 — pierwsze po scaleniu sprintu 2. Wysypał się build obrazu verris-api, czyli krok PRZED dotknięciem serwera: produkcja została nietknięta, migracje nie poszły. | DWIE PRZYCZYNY, NIE JEDNA. (1) `COPY libs libs` w etapie budowania kładzie katalogi pakietów na te, które zostawił etap `deps`, i pakiet traci WŁASNE node_modules. Dopóki każda zależność lądowała w node_modules katalogu głównego (linker hoisted), nie było tego widać — założenie trzymało się PRZYPADKIEM. (2) Przestało być prawdą przy X-18: apps/www podniosło Payloada, jego adapter postgresowy ciągnie drizzle-orm, a to ma @prisma/client jako peer OPCJONALNY; pnpm dociąga takie peery samo (autoInstallPeers), więc w drzewie stanęły DWIE wersje — 7.9.1 na górze i nasza 6.19.3 w libs/database. Po COPY zostawała tylko ta z góry, a `prisma generate` z CLI 6.19.3 nie umie pracować z klientem 7.x. | Poprawki są dwie, bo błędy są dwa: pnpm.overrides sprowadza drzewo do jednej wersji klienta (to naprawia TEN przypadek i chroni też obraz runtime, który kopiuje node_modules katalogu głównego), a ponowna instalacja w obrazach znosi założenie o hoistowaniu (to chroni przed następnym pakietem w dwóch wersjach). Dockerfile.panel dostał tę samą poprawkę mimo że jeszcze nie wybuchł — naprawiona jedna kopia i zostawiona druga to wzorzec, który dał Z-12, Z-16 i X-24. | NAJWAŻNIEJSZE ZNALEZISKO STRUKTURALNE: obraz, który JAKO JEDYNY trafia na serwer, powstawał wyłącznie w workflow wdrożeniowym — czyli PO scaleniu do main. Bramka scalenia sprawdzała lint, typy, 605 testów, migracje i asercje bazy, i nie sprawdzała tej jednej rzeczy. `pnpm build` w repozytorium przechodzi, bo tam node_modules są kompletne; rozjeżdżało się wyłącznie w układzie plików wewnątrz obrazu. Dlatego CI dostało job budujący Dockerfile.api bez pushowania. | DWA RAZY UWIERZYŁEM W WYNIK, KTÓRY NICZEGO NIE DOWODZIŁ: raz pnpm nie przeliczył lockfile'a i override wyglądał na nieskuteczny; raz uproszczone repozytorium testowe nie zawierało package.json apps/www, czyli pakietu ciągnącego 7.9.1 — więc wynik wyglądał dobrze z niewłaściwego powodu. Rozstrzygnięte dopiero na pełnym drzewie zależności. Ta sama rodzina co Z-01 i H-20. | Czerwieni się na starym kodzie: 7 z 14. | CZEGO NIE ROBI: CI nie buduje obrazów paneli (własny Dockerfile, ~2,5 min każdy, bez Prismy) — jeżeli kiedyś wywali się panel, job dostanie drugą pozycję w macierzy, a nie listę wyjątków. Dokumentacja: docs/zadania/X-27-obraz-api-w-ci.md</t>
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr">
@@ -2515,73 +2519,73 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>H-24</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>Nazwa obiektu kopii i drill odtworzeniowy mają po jednym miejscu</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>ops/lib/backup-crypto.sh — backup_crypto_latest_object(), jedno źródło nazwy obiektu; ops/scripts/restore-drill-isolated.sh — nazwa z biblioteki + weryfikacja SHA-256 + deszyfrowanie age; ops/scripts/prod-health-snapshot.sh, ops/restore-postgres.sh — nazwa z biblioteki; apps/api/src/storage/object-storage.service.ts — stała OBIEKT_KOPII_LATEST; USUNIĘTY ops/backup-verify.sh (druga kopia drilla); apps/api/src/test/nazwa-obiektu-kopii.spec.ts (12)</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>Odkryte 2026-08-22 przy pierwszym prawdziwym uruchomieniu drilla z H-20. | DWA SKRYPTY DO JEDNEGO ZADANIA. ops/backup-verify.sh robił wszystko POPRAWNIE: właściwa nazwa obiektu (latest.sql.gz.age), weryfikacja SHA-256, deszyfrowanie age, odtworzenie do osobnej bazy, sanity-check. I nie wołał go NIKT — żaden cron, runbook ani dokument; jedyne wystąpienia nazwy tego pliku w repozytorium to jego własny nagłówek. Obok stał ops/scripts/restore-drill-isolated.sh: zła nazwa obiektu, bez sumy kontrolnej, bez deszyfrowania, za to wpięty w runbook, w mail przypominający i w gotowość do startu. Utwardzanie H-20 poszło w tę drugą kopię — dołożyłem progi na pięciu tabelach, tabelę RestoreDrill, właściciela, pomiar czasu i bramkę, przykręcając to wszystko do skryptu, który nie mógł zadziałać. To moja pomyłka i to na pozycji, której całym sensem było sprawdzenie, czy naprawdę potrafimy odtworzyć bazę. Rodzina „bliźniaczych miejsc": Z-12, Z-16, M-06, X-24, teraz tu — tym razem najdroższa, bo dotyczyła DR. | NAZWA OBIEKTU W CZTERECH MIEJSCACH: drill, prod-health-snapshot.sh, restore-postgres.sh i metryka Prometheusa. Trzy z czterech miały „latest.sql.gz", a backup wysyła „latest.sql.gz.age", bo szyfrowanie jest w produkcji obowiązkowe. | PRECYZYJNIE O SKUTKU, bo łatwo tu przesadzić: w sierpniu metryka pokazywała zero ZGODNIE Z PRAWDĄ — kopii nie było w ogóle, więc zła nazwa nie ukryła TAMTEJ awarii. Ukryłaby NASTĘPNĄ: po naprawie kopii metryka nadal czytałaby nieistniejący obiekt, alert VerrisPostgresBackupStale krzyczałby bez końca przy działających kopiach, a wtedy ktoś by go wyciszył. Alarm, który kłamie, kończy tak samo jak alarm, którego nie ma. | ROZWIĄZANIE: nazwa wyprowadzana z backup_crypto_latest_object(), obok backup_crypto_enabled — żeby odpowiedź na „czy .age" brała się z tego samego miejsca co decyzja o szyfrowaniu. TypeScript nie zaimportuje funkcji basha, więc stała OBIEKT_KOPII_LATEST jest wiązana z biblioteką testem czytającym oba pliki (ta sama technika co X-24 i Z-03). | Drill dostał to, czego mu brakowało: weryfikację sumy kontrolnej pobranego obiektu (bez niej dowodziłby, że da się odtworzyć TO, CO POBRAŁ, a nie to, co zapisała kopia) i deszyfrowanie przed gunzipem. | Czerwieni się na starym kodzie: 4 z 12. | CZEGO NIE ROBI: nie odpowiada, dlaczego krytyczny alert nie dotarł do nikogo przez miesiąc — to konfiguracja Alertmanagera, poza kodem repozytorium. Dokumentacja: docs/zadania/H-24-jedna-nazwa-jeden-drill.md</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
@@ -2593,12 +2597,12 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>H-20</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2608,58 +2612,58 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
         <v>16</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
-          <t>PB-02 (drill wykonujemy na węźle #1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr">
@@ -2671,12 +2675,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2686,43 +2690,43 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -2737,7 +2741,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
@@ -2749,12 +2753,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Dodatkowy użytkownik bazy — utworzenie</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2764,7 +2768,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -2773,24 +2777,24 @@
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
@@ -2800,7 +2804,7 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -2815,7 +2819,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr">
@@ -2827,73 +2831,73 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — usunięcie</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
@@ -2905,12 +2909,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — zmiana hasła</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2920,7 +2924,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -2929,24 +2933,24 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
@@ -2956,12 +2960,12 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="11" t="inlineStr">
@@ -2971,7 +2975,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr">
@@ -2983,12 +2987,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — lista</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2998,48 +3002,48 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
@@ -3047,11 +3051,7 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr">
-        <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
-        </is>
-      </c>
+      <c r="O29" s="11" t="inlineStr"/>
       <c r="P29" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3061,12 +3061,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — auto-logowanie (SSO)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3076,43 +3076,43 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3154,58 +3154,58 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SRV / CAA</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3232,56 +3232,60 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G32" s="10" t="n">
-        <v>11</v>
-      </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>F-01 (ten sam edytor)</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
-        </is>
-      </c>
-      <c r="O32" s="11" t="inlineStr"/>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+        </is>
+      </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3291,12 +3295,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Webmail — auto-logowanie (SSO)</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3306,50 +3310,50 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
-        </is>
-      </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
@@ -3357,7 +3361,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
@@ -3369,58 +3373,58 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per domena</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>B — Runtime WWW</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr">
@@ -3430,12 +3434,12 @@
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -3447,12 +3451,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SPF — kreator</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3462,58 +3466,58 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -3525,12 +3529,12 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Rekordy DKIM — konfiguracja</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -3540,58 +3544,58 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>E-15 (ten sam panel dostarczalności)</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
@@ -3603,73 +3607,73 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Rekord DMARC — konfiguracja</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
@@ -3681,12 +3685,12 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>H-20</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
+          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -3696,19 +3700,19 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
@@ -3717,37 +3721,37 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
+          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-02 (drill wykonujemy na węźle #1)</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
+          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3759,12 +3763,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Usunięcie zapisanej karty przez klienta</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -3774,19 +3778,19 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -3795,12 +3799,12 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
@@ -3810,7 +3814,7 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
@@ -3825,7 +3829,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>wymóg konsumencki</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
@@ -3837,12 +3841,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Ręczne zawieszenie usługi przez operatora</t>
+          <t>Dodatkowy użytkownik bazy — utworzenie</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -3852,19 +3856,19 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
@@ -3873,22 +3877,22 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:192</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr">
@@ -3898,12 +3902,12 @@
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
+          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -3915,12 +3919,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Ręczne odwieszenie usługi przez operatora</t>
+          <t>Użytkownik bazy — usunięcie</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -3930,19 +3934,19 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
@@ -3951,37 +3955,37 @@
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:210</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>A-25 (ten sam widok)</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
@@ -3993,12 +3997,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Użytkownik bazy — zmiana hasła</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -4008,19 +4012,19 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
@@ -4029,37 +4033,37 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -4071,12 +4075,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>Użytkownik bazy — lista</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4086,19 +4090,19 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
@@ -4107,37 +4111,37 @@
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
@@ -4149,12 +4153,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>H-22</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Panel odtwarzania w widocznym miejscu</t>
+          <t>phpMyAdmin — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -4164,19 +4168,19 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -4185,22 +4189,22 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
@@ -4210,12 +4214,12 @@
       </c>
       <c r="N44" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>klient w kryzysie tego nie znajdzie</t>
+          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -4227,12 +4231,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>H-09</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
+          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4242,7 +4246,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -4254,7 +4258,7 @@
         <v>6</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -4263,22 +4267,22 @@
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>hosting-restore.service.ts:167</t>
+          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -4288,12 +4292,12 @@
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
+          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr">
@@ -4305,12 +4309,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>H-17</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
+          <t>Rekordy SRV / CAA</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4320,7 +4324,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -4332,7 +4336,7 @@
         <v>6</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
@@ -4341,39 +4345,35 @@
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
-          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
+          <t>F-01 (ten sam edytor)</t>
         </is>
       </c>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O46" s="11" t="inlineStr">
-        <is>
-          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
-        </is>
-      </c>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+        </is>
+      </c>
+      <c r="O46" s="11" t="inlineStr"/>
       <c r="P46" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4383,12 +4383,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>G-20</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Ochrona przed atakiem słownikowym na panel</t>
+          <t>Webmail — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4398,19 +4398,19 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
@@ -4419,22 +4419,22 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>rate-limit.guard.ts — ZERO testów</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>brak dowodu D2 na krytycznym guardzie</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P47" s="10" t="inlineStr">
@@ -4461,12 +4461,12 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Staging — publikacja na produkcję</t>
+          <t>Zmiana wersji PHP per domena</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -4476,19 +4476,19 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
@@ -4497,22 +4497,22 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:187</t>
+          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr">
@@ -4539,34 +4539,34 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
+          <t>Rekordy SPF — kreator</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
@@ -4575,37 +4575,37 @@
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
+          <t>ENDPOINT BEZ UI</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:114</t>
+        </is>
+      </c>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L49" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M49" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
+          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
@@ -4617,12 +4617,12 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Rekordy DKIM — konfiguracja</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -4644,46 +4644,46 @@
         <v>6</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr">
         <is>
-          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
+          <t>E-15 (ten sam panel dostarczalności)</t>
         </is>
       </c>
       <c r="N50" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O50" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr">
@@ -4695,12 +4695,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwarka wolnych domen</t>
+          <t>Rekord DMARC — konfiguracja</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -4722,44 +4722,48 @@
         <v>6</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:54</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
-        </is>
-      </c>
-      <c r="O51" s="11" t="inlineStr"/>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+        </is>
+      </c>
+      <c r="O51" s="11" t="inlineStr">
+        <is>
+          <t>j.w.</t>
+        </is>
+      </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4769,12 +4773,12 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Spakowanie do archiwum</t>
+          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4784,33 +4788,33 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
@@ -4820,7 +4824,7 @@
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>files.service.ts:320 — tylko extract</t>
+          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
         </is>
       </c>
       <c r="M52" s="11" t="inlineStr">
@@ -4835,7 +4839,7 @@
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>standard we wszystkich panelach</t>
+          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr">
@@ -4847,73 +4851,73 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>M-26</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+          <t>Usunięcie zapisanej karty przez klienta</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L53" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M53" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+          <t>wymóg konsumencki</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
@@ -4925,73 +4929,73 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>A-25</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+          <t>Ręczne zawieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
+          <t>ENDPOINT BEZ UI</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>subscriptions.admin.controller.ts:192</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L54" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
+          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
@@ -5003,73 +5007,73 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>A-26</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Treści i cennik na verris.pl</t>
+          <t>Ręczne odwieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>subscriptions.admin.controller.ts:210</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>PB-01 (cennik zależy od unit economics)</t>
+          <t>A-25 (ten sam widok)</t>
         </is>
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -5081,73 +5085,73 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Landing /przenies-strone</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F56" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
+          <t>ENDPOINT BEZ UI</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+        </is>
+      </c>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M56" s="11" t="inlineStr">
-        <is>
-          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
-        </is>
-      </c>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -5159,73 +5163,73 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
+          <t>ENDPOINT BEZ UI</t>
+        </is>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L57" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M57" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -5237,12 +5241,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>H-22</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>KSeF — walidacja XSD przed wysyłką</t>
+          <t>Panel odtwarzania w widocznym miejscu</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -5252,58 +5256,58 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F58" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>smoke na api-test MF nie został wykonany</t>
+          <t>klient w kryzysie tego nie znajdzie</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
@@ -5315,12 +5319,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>H-09</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>KSeF — tryb offline/awaryjny</t>
+          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5330,58 +5334,58 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F59" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+          <t>hosting-restore.service.ts:167</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -5393,12 +5397,12 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>H-17</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>KSeF — pobranie UPO przez operatora</t>
+          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -5408,58 +5412,58 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
         </is>
       </c>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -5471,12 +5475,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>G-20</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>KSeF — numer i UPO widoczne dla klienta</t>
+          <t>Ochrona przed atakiem słownikowym na panel</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -5486,7 +5490,7 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -5498,46 +5502,46 @@
         <v>6</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień „ksef” w apps/client-panel</t>
+          <t>rate-limit.guard.ts — ZERO testów</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+          <t>brak dowodu D2 na krytycznym guardzie</t>
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
@@ -5549,73 +5553,73 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy — 20 artykułów startowych</t>
+          <t>Staging — publikacja na produkcję</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:187</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr">
@@ -5627,12 +5631,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -5647,28 +5651,28 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
@@ -5683,17 +5687,17 @@
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>PB-06 (kampania kieruje na landing)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
@@ -5705,69 +5709,73 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Test end-to-end „pierwszy klient”</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H64" s="10" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="M64" s="11" t="inlineStr">
         <is>
-          <t>wszystkie blokery zamknięte (sprint 8)</t>
+          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
         </is>
       </c>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
         </is>
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr">
@@ -5779,80 +5787,1164 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
+          <t>A-11</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Wyszukiwarka wolnych domen</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>audyt</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>A — Domeny i konta</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>FLAGA</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>domains.controller.ts:54</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="11" t="inlineStr">
+        <is>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+        </is>
+      </c>
+      <c r="O65" s="11" t="inlineStr"/>
+      <c r="P65" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>C-11</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Spakowanie do archiwum</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>audyt</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>C — Pliki, FTP, SSH, Git</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>files.service.ts:320 — tylko extract</t>
+        </is>
+      </c>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="11" t="inlineStr">
+        <is>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+        </is>
+      </c>
+      <c r="O66" s="11" t="inlineStr">
+        <is>
+          <t>standard we wszystkich panelach</t>
+        </is>
+      </c>
+      <c r="P66" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>PB-11</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="11" t="inlineStr">
+        <is>
+          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+        </is>
+      </c>
+      <c r="O67" s="11" t="inlineStr">
+        <is>
+          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+        </is>
+      </c>
+      <c r="P67" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>PB-03</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="11" t="inlineStr">
+        <is>
+          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
+        </is>
+      </c>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
+        </is>
+      </c>
+      <c r="P68" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>PB-07</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Treści i cennik na verris.pl</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>PB-01 (cennik zależy od unit economics)</t>
+        </is>
+      </c>
+      <c r="N69" s="11" t="inlineStr">
+        <is>
+          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+        </is>
+      </c>
+      <c r="O69" s="11" t="inlineStr">
+        <is>
+          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+        </is>
+      </c>
+      <c r="P69" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>PB-06</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Landing /przenies-strone</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="11" t="inlineStr">
+        <is>
+          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr">
+        <is>
+          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+        </is>
+      </c>
+      <c r="O70" s="11" t="inlineStr">
+        <is>
+          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+        </is>
+      </c>
+      <c r="P70" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>PB-08</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNI</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="11" t="inlineStr">
+        <is>
+          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+        </is>
+      </c>
+      <c r="O71" s="11" t="inlineStr">
+        <is>
+          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+        </is>
+      </c>
+      <c r="P71" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>M-17</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>KSeF — walidacja XSD przed wysyłką</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>audyt</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>M — Rozliczenia</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+        </is>
+      </c>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
+          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+        </is>
+      </c>
+      <c r="N72" s="11" t="inlineStr">
+        <is>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+        </is>
+      </c>
+      <c r="O72" s="11" t="inlineStr">
+        <is>
+          <t>smoke na api-test MF nie został wykonany</t>
+        </is>
+      </c>
+      <c r="P72" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>M-16</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>KSeF — tryb offline/awaryjny</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>audyt</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>M — Rozliczenia</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+        </is>
+      </c>
+      <c r="N73" s="11" t="inlineStr">
+        <is>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+        </is>
+      </c>
+      <c r="O73" s="11" t="inlineStr">
+        <is>
+          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+        </is>
+      </c>
+      <c r="P73" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>M-15</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>KSeF — pobranie UPO przez operatora</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>audyt</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>M — Rozliczenia</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNIA</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>ENDPOINT BEZ UI</t>
+        </is>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+        </is>
+      </c>
+      <c r="M74" s="11" t="inlineStr">
+        <is>
+          <t>PB-13</t>
+        </is>
+      </c>
+      <c r="N74" s="11" t="inlineStr">
+        <is>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+        </is>
+      </c>
+      <c r="O74" s="11" t="inlineStr">
+        <is>
+          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+        </is>
+      </c>
+      <c r="P74" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>M-14</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>KSeF — numer i UPO widoczne dla klienta</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>audyt</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>M — Rozliczenia</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>zero wystąpień „ksef” w apps/client-panel</t>
+        </is>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+        </is>
+      </c>
+      <c r="N75" s="11" t="inlineStr">
+        <is>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+        </is>
+      </c>
+      <c r="O75" s="11" t="inlineStr">
+        <is>
+          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+        </is>
+      </c>
+      <c r="P75" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>PB-09</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>Baza wiedzy — 20 artykułów startowych</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNI</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="11" t="inlineStr">
+        <is>
+          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+        </is>
+      </c>
+      <c r="O76" s="11" t="inlineStr">
+        <is>
+          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+        </is>
+      </c>
+      <c r="P76" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>PB-10</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>ŚREDNI</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>PB-06 (kampania kieruje na landing)</t>
+        </is>
+      </c>
+      <c r="N77" s="11" t="inlineStr">
+        <is>
+          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+        </is>
+      </c>
+      <c r="O77" s="11" t="inlineStr">
+        <is>
+          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+        </is>
+      </c>
+      <c r="P77" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>PB-05</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>Test end-to-end „pierwszy klient”</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H78" s="10" t="inlineStr"/>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>wszystkie blokery zamknięte (sprint 8)</t>
+        </is>
+      </c>
+      <c r="N78" s="11" t="inlineStr">
+        <is>
+          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+        </is>
+      </c>
+      <c r="O78" s="11" t="inlineStr">
+        <is>
+          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+        </is>
+      </c>
+      <c r="P78" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
           <t>PB-12</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>Runbook startu i decyzja GO</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>poza audytem</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
         <is>
           <t>Praca spoza audytu</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr">
         <is>
           <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F79" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="G65" s="10" t="n">
+      <c r="G79" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="H65" s="10" t="inlineStr"/>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="H79" s="10" t="inlineStr"/>
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>2027-01-04</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr">
         <is>
           <t>2027-01-08</t>
         </is>
       </c>
-      <c r="K65" s="10" t="inlineStr">
+      <c r="K79" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L65" s="11" t="inlineStr">
+      <c r="L79" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M65" s="11" t="inlineStr">
+      <c r="M79" s="11" t="inlineStr">
         <is>
           <t>PB-05 (decyzja GO po przejściu ścieżki na produkcji)</t>
         </is>
       </c>
-      <c r="N65" s="11" t="inlineStr">
+      <c r="N79" s="11" t="inlineStr">
         <is>
           <t>Każdy z 11 blokerów ma wpis: co zrobiono, gdzie jest dowód, kto potwierdził. Bez formuły „warunkowe GO”.</t>
         </is>
       </c>
-      <c r="O65" s="11" t="inlineStr">
+      <c r="O79" s="11" t="inlineStr">
         <is>
           <t>Domknięcie: przegląd wszystkich blokerów z dowodem zamknięcia, decyzja GO/NO-GO zapisana z datą.</t>
         </is>
       </c>
-      <c r="P65" s="10" t="inlineStr">
+      <c r="P79" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P65"/>
-  <conditionalFormatting sqref="E2:E65">
+  <autoFilter ref="A1:P79"/>
+  <conditionalFormatting sqref="E2:E79">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>
@@ -5872,7 +6964,7 @@
       <formula>"ŚREDNI"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P65">
+  <conditionalFormatting sqref="P2:P79">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"zrobione"</formula>
     </cfRule>
@@ -5982,11 +7074,11 @@
         </is>
       </c>
       <c r="F2" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A2)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A2)</f>
         <v/>
       </c>
       <c r="G2" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A2,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A2,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H2" s="10" t="n">
@@ -5998,7 +7090,7 @@
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>PB-01 może wywrócić cenę 45 zł. Dlatego jest w pierwszym sprincie, a nie w ostatnim — wynik zmienia treść cennika w sprincie 15.</t>
+          <t>PB-01 może wywrócić cenę 45 zł. Dlatego jest w pierwszym sprincie, a nie w ostatnim — wynik zmienia treść cennika w sprincie 15. Sprint urósł o sześć pozycji odkrytych przy włączaniu CI — nie było ich w planie z 2026-08.</t>
         </is>
       </c>
     </row>
@@ -6027,11 +7119,11 @@
         </is>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A3)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A3)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A3,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A3,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H3" s="10" t="n">
@@ -6043,7 +7135,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO.</t>
+          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o osiem pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał.</t>
         </is>
       </c>
     </row>
@@ -6072,11 +7164,11 @@
         </is>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A4)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A4)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A4,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A4,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H4" s="10" t="n">
@@ -6117,11 +7209,11 @@
         </is>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A5)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A5)</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A5,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A5,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n">
@@ -6162,11 +7254,11 @@
         </is>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A6)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A6)</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A6,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A6,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n">
@@ -6207,11 +7299,11 @@
         </is>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A7)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A7,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A7,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n">
@@ -6252,11 +7344,11 @@
         </is>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A8)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A8)</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A8,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A8,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n">
@@ -6297,11 +7389,11 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A9)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A9)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A9,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A9,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n">
@@ -6342,11 +7434,11 @@
         </is>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A10)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A10)</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A10,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A10,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n">
@@ -6387,11 +7479,11 @@
         </is>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A11)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A11)</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A11,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A11,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n">
@@ -6432,11 +7524,11 @@
         </is>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A12)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A12)</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A12,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A12,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n">
@@ -6477,11 +7569,11 @@
         </is>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A13)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A13)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A13,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A13,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n">
@@ -6522,11 +7614,11 @@
         </is>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A14)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A14)</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A14,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A14,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n">
@@ -6567,11 +7659,11 @@
         </is>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A15)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A15)</f>
         <v/>
       </c>
       <c r="G15" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A15,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A15,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n">
@@ -6612,11 +7704,11 @@
         </is>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A16)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A16)</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A16,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A16,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n">
@@ -6657,11 +7749,11 @@
         </is>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A17)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A17)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A17,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A17,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n">
@@ -6702,11 +7794,11 @@
         </is>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A18)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A18)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A18,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A18,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n">
@@ -6747,11 +7839,11 @@
         </is>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A19)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A19)</f>
         <v/>
       </c>
       <c r="G19" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A19,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A19,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n">
@@ -6792,11 +7884,11 @@
         </is>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A20)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A20)</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A20,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A20,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n">
@@ -6833,11 +7925,11 @@
         </is>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$65,A21)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A21)</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$65,A21,'Backlog do startu'!$F$2:$F$65)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A21,'Backlog do startu'!$F$2:$F$79)</f>
         <v/>
       </c>
       <c r="H21" s="10" t="n">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$79)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$80)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$79,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$79,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$80,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$80,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$79,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$80,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$79,"zrobione",'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$80,"zrobione",'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2597,12 +2597,12 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Z-12</t>
+          <t>X-28</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+          <t>Reguła alertowa ma odbiorcę, a nie tylko próg</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
+          <t>ops/observability/grafana/provisioning/alerting/rules.yaml — 13 reguł, 2 grupy, provisionowane z repo; ops/observability/prometheus.yml — bez rule_files, z opisem dlaczego; ops/observability/grafana/provisioning/datasources/datasources.yml — uid: Prometheus; docker-compose.prod.yml — bez montowania usuniętego alerts.yml; ops/observability/grafana/migracja-regul-do-grafany.py — zapis, jak powstał wynik; apps/api/src/test/routing-alertow.spec.ts (31); docs/ops/GRAFANA_ALERTING.md</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
+          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr">
@@ -2675,12 +2675,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Z-13</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G25" s="10" t="n">
         <v>3</v>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Z-16</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>3</v>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr">
@@ -2831,31 +2831,31 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>3</v>
@@ -2877,27 +2877,27 @@
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
@@ -2909,58 +2909,58 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3007,11 +3007,11 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>4</v>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -3051,7 +3051,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+        </is>
+      </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3061,12 +3065,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3076,7 +3080,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -3112,24 +3116,20 @@
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O30" s="11" t="inlineStr">
-        <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
-        </is>
-      </c>
+      <c r="O30" s="11" t="inlineStr"/>
       <c r="P30" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3139,12 +3139,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3154,48 +3154,48 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
-        </is>
-      </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
@@ -3253,12 +3253,12 @@
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
@@ -3295,12 +3295,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3310,16 +3310,16 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>6</v>
@@ -3341,17 +3341,17 @@
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
@@ -3373,27 +3373,27 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
@@ -3419,27 +3419,27 @@
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -3451,73 +3451,73 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
@@ -3607,31 +3607,31 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>8</v>
@@ -3653,27 +3653,27 @@
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
@@ -3685,73 +3685,73 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>H-20</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
         <v>16</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>PB-02 (drill wykonujemy na węźle #1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3763,12 +3763,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>H-20</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>9</v>
@@ -3809,27 +3809,27 @@
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-02 (drill wykonujemy na węźle #1)</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Dodatkowy użytkownik bazy — utworzenie</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -3856,50 +3856,50 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L40" s="11" t="inlineStr">
-        <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
-        </is>
-      </c>
-      <c r="M40" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -3919,12 +3919,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — usunięcie</t>
+          <t>Dodatkowy użytkownik bazy — utworzenie</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
@@ -3997,12 +3997,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — zmiana hasła</t>
+          <t>Użytkownik bazy — usunięcie</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — lista</t>
+          <t>Użytkownik bazy — zmiana hasła</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -4153,12 +4153,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — auto-logowanie (SSO)</t>
+          <t>Użytkownik bazy — lista</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
+          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N44" s="11" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -4231,12 +4231,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
+          <t>phpMyAdmin — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4246,19 +4246,19 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -4267,22 +4267,22 @@
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SRV / CAA</t>
+          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
-          <t>F-01 (ten sam edytor)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="11" t="inlineStr">
@@ -4373,7 +4373,11 @@
           <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
         </is>
       </c>
-      <c r="O46" s="11" t="inlineStr"/>
+      <c r="O46" s="11" t="inlineStr">
+        <is>
+          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+        </is>
+      </c>
       <c r="P46" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4383,12 +4387,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Webmail — auto-logowanie (SSO)</t>
+          <t>Rekordy SRV / CAA</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4398,12 +4402,12 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
@@ -4429,29 +4433,25 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-01 (ten sam edytor)</t>
         </is>
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O47" s="11" t="inlineStr">
-        <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
-        </is>
-      </c>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+        </is>
+      </c>
+      <c r="O47" s="11" t="inlineStr"/>
       <c r="P47" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4461,12 +4461,12 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per domena</t>
+          <t>Webmail — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>B — Runtime WWW</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr">
@@ -4539,12 +4539,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SPF — kreator</t>
+          <t>Zmiana wersji PHP per domena</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -4554,19 +4554,19 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
@@ -4575,22 +4575,22 @@
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
+          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
@@ -4617,12 +4617,12 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Rekordy DKIM — konfiguracja</t>
+          <t>Rekordy SPF — kreator</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="M50" s="11" t="inlineStr">
         <is>
-          <t>E-15 (ten sam panel dostarczalności)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N50" s="11" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O50" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr">
@@ -4695,12 +4695,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Rekord DMARC — konfiguracja</t>
+          <t>Rekordy DKIM — konfiguracja</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-15 (ten sam panel dostarczalności)</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
@@ -4773,12 +4773,12 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
+          <t>Rekord DMARC — konfiguracja</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4819,27 +4819,27 @@
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M52" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="N52" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr">
@@ -4851,12 +4851,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Usunięcie zapisanej karty przez klienta</t>
+          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>wymóg konsumencki</t>
+          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
@@ -4929,12 +4929,12 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>M-26</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Ręczne zawieszenie usługi przez operatora</t>
+          <t>Usunięcie zapisanej karty przez klienta</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -4956,7 +4956,7 @@
         <v>6</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
@@ -4965,22 +4965,22 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:192</t>
+          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
         </is>
       </c>
       <c r="M54" s="11" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
+          <t>wymóg konsumencki</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
@@ -5007,12 +5007,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>A-25</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Ręczne odwieszenie usługi przez operatora</t>
+          <t>Ręczne zawieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:210</t>
+          <t>subscriptions.admin.controller.ts:192</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>A-25 (ten sam widok)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="11" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
+          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>A-26</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Ręczne odwieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>subscriptions.admin.controller.ts:210</t>
         </is>
       </c>
       <c r="M56" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-25 (ten sam widok)</t>
         </is>
       </c>
       <c r="N56" s="11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -5163,12 +5163,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -5241,12 +5241,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>H-22</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Panel odtwarzania w widocznym miejscu</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="N58" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>klient w kryzysie tego nie znajdzie</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
@@ -5319,12 +5319,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>H-09</t>
+          <t>H-22</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
+          <t>Panel odtwarzania w widocznym miejscu</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
@@ -5355,12 +5355,12 @@
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>hosting-restore.service.ts:167</t>
+          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
+          <t>klient w kryzysie tego nie znajdzie</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -5397,12 +5397,12 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>H-17</t>
+          <t>H-09</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
+          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -5443,27 +5443,27 @@
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
+          <t>hosting-restore.service.ts:167</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
         <is>
-          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
+          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -5475,12 +5475,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>G-20</t>
+          <t>H-17</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Ochrona przed atakiem słownikowym na panel</t>
+          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -5521,27 +5521,27 @@
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>rate-limit.guard.ts — ZERO testów</t>
+          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
         </is>
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>brak dowodu D2 na krytycznym guardzie</t>
+          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>G-20</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Staging — publikacja na produkcję</t>
+          <t>Ochrona przed atakiem słownikowym na panel</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:187</t>
+          <t>rate-limit.guard.ts — ZERO testów</t>
         </is>
       </c>
       <c r="M62" s="11" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+          <t>brak dowodu D2 na krytycznym guardzie</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr">
@@ -5631,27 +5631,27 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
+          <t>Staging — publikacja na produkcję</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
@@ -5677,27 +5677,27 @@
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:187</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L63" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
+          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
@@ -5709,73 +5709,73 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M64" s="11" t="inlineStr">
         <is>
-          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
         </is>
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr">
@@ -5787,12 +5787,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwarka wolnych domen</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:54</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
         </is>
       </c>
       <c r="N65" s="11" t="inlineStr">
@@ -5851,7 +5851,11 @@
           <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
         </is>
       </c>
-      <c r="O65" s="11" t="inlineStr"/>
+      <c r="O65" s="11" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -5861,12 +5865,12 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Spakowanie do archiwum</t>
+          <t>Wyszukiwarka wolnych domen</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -5876,12 +5880,12 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
@@ -5907,12 +5911,12 @@
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
-          <t>files.service.ts:320 — tylko extract</t>
+          <t>domains.controller.ts:54</t>
         </is>
       </c>
       <c r="M66" s="11" t="inlineStr">
@@ -5922,14 +5926,10 @@
       </c>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O66" s="11" t="inlineStr">
-        <is>
-          <t>standard we wszystkich panelach</t>
-        </is>
-      </c>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+        </is>
+      </c>
+      <c r="O66" s="11" t="inlineStr"/>
       <c r="P66" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -5939,31 +5939,31 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+          <t>Spakowanie do archiwum</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>15</v>
@@ -5985,27 +5985,27 @@
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>files.service.ts:320 — tylko extract</t>
+        </is>
+      </c>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L67" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O67" s="11" t="inlineStr">
         <is>
-          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+          <t>standard we wszystkich panelach</t>
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr">
@@ -6017,12 +6017,12 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -6037,14 +6037,14 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K68" s="10" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="N68" s="11" t="inlineStr">
         <is>
-          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
+          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
         </is>
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
+          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
         </is>
       </c>
       <c r="P68" s="10" t="inlineStr">
@@ -6095,12 +6095,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Treści i cennik na verris.pl</t>
+          <t>Finalizacja dokumentów prawnych 1.0.0</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>PB-01 (cennik zależy od unit economics)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
         </is>
       </c>
       <c r="O69" s="11" t="inlineStr">
         <is>
-          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
         </is>
       </c>
       <c r="P69" s="10" t="inlineStr">
@@ -6173,12 +6173,12 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Landing /przenies-strone</t>
+          <t>Treści i cennik na verris.pl</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -6200,7 +6200,7 @@
         <v>16</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K70" s="10" t="inlineStr">
@@ -6229,17 +6229,17 @@
       </c>
       <c r="M70" s="11" t="inlineStr">
         <is>
-          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
+          <t>PB-01 (cennik zależy od unit economics)</t>
         </is>
       </c>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
         </is>
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+          <t>Landing /przenies-strone</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
@@ -6307,17 +6307,17 @@
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
         </is>
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
         </is>
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr">
@@ -6329,34 +6329,34 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>KSeF — walidacja XSD przed wysyłką</t>
+          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
@@ -6365,37 +6365,37 @@
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K72" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
-          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="11" t="inlineStr">
         <is>
-          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
         </is>
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>smoke na api-test MF nie został wykonany</t>
+          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>KSeF — tryb offline/awaryjny</t>
+          <t>KSeF — walidacja XSD przed wysyłką</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G73" s="10" t="n">
         <v>18</v>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
         </is>
       </c>
       <c r="N73" s="11" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+          <t>smoke na api-test MF nie został wykonany</t>
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr">
@@ -6485,12 +6485,12 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>KSeF — pobranie UPO przez operatora</t>
+          <t>KSeF — tryb offline/awaryjny</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -6505,11 +6505,11 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>18</v>
@@ -6531,27 +6531,27 @@
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M74" s="11" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
         </is>
       </c>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr">
@@ -6563,12 +6563,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>KSeF — numer i UPO widoczne dla klienta</t>
+          <t>KSeF — pobranie UPO przez operatora</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -6583,14 +6583,14 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
@@ -6599,37 +6599,37 @@
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień „ksef” w apps/client-panel</t>
+          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr">
@@ -6641,31 +6641,31 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy — 20 artykułów startowych</t>
+          <t>KSeF — numer i UPO widoczne dla klienta</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>19</v>
@@ -6687,27 +6687,27 @@
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zero wystąpień „ksef” w apps/client-panel</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
         </is>
       </c>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr">
@@ -6719,12 +6719,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+          <t>Baza wiedzy — 20 artykułów startowych</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>19</v>
@@ -6775,17 +6775,17 @@
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>PB-06 (kampania kieruje na landing)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
         </is>
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr">
@@ -6797,12 +6797,12 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Test end-to-end „pierwszy klient”</t>
+          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -6817,24 +6817,28 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H78" s="10" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="K78" s="10" t="inlineStr">
@@ -6849,17 +6853,17 @@
       </c>
       <c r="M78" s="11" t="inlineStr">
         <is>
-          <t>wszystkie blokery zamknięte (sprint 8)</t>
+          <t>PB-06 (kampania kieruje na landing)</t>
         </is>
       </c>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
         </is>
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr">
@@ -6871,12 +6875,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Runbook startu i decyzja GO</t>
+          <t>Test end-to-end „pierwszy klient”</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -6895,7 +6899,7 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>20</v>
@@ -6923,28 +6927,102 @@
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
+          <t>wszystkie blokery zamknięte (sprint 8)</t>
+        </is>
+      </c>
+      <c r="N79" s="11" t="inlineStr">
+        <is>
+          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+        </is>
+      </c>
+      <c r="O79" s="11" t="inlineStr">
+        <is>
+          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+        </is>
+      </c>
+      <c r="P79" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>PB-12</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>Runbook startu i decyzja GO</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H80" s="10" t="inlineStr"/>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="11" t="inlineStr">
+        <is>
           <t>PB-05 (decyzja GO po przejściu ścieżki na produkcji)</t>
         </is>
       </c>
-      <c r="N79" s="11" t="inlineStr">
+      <c r="N80" s="11" t="inlineStr">
         <is>
           <t>Każdy z 11 blokerów ma wpis: co zrobiono, gdzie jest dowód, kto potwierdził. Bez formuły „warunkowe GO”.</t>
         </is>
       </c>
-      <c r="O79" s="11" t="inlineStr">
+      <c r="O80" s="11" t="inlineStr">
         <is>
           <t>Domknięcie: przegląd wszystkich blokerów z dowodem zamknięcia, decyzja GO/NO-GO zapisana z datą.</t>
         </is>
       </c>
-      <c r="P79" s="10" t="inlineStr">
+      <c r="P80" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P79"/>
-  <conditionalFormatting sqref="E2:E79">
+  <autoFilter ref="A1:P80"/>
+  <conditionalFormatting sqref="E2:E80">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>
@@ -6964,7 +7042,7 @@
       <formula>"ŚREDNI"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P79">
+  <conditionalFormatting sqref="P2:P80">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"zrobione"</formula>
     </cfRule>
@@ -7074,11 +7152,11 @@
         </is>
       </c>
       <c r="F2" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A2)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A2)</f>
         <v/>
       </c>
       <c r="G2" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A2,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A2,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H2" s="10" t="n">
@@ -7119,11 +7197,11 @@
         </is>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A3)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A3)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A3,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A3,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H3" s="10" t="n">
@@ -7135,7 +7213,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o osiem pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał.</t>
+          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziewięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł.</t>
         </is>
       </c>
     </row>
@@ -7164,11 +7242,11 @@
         </is>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A4)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A4)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A4,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A4,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H4" s="10" t="n">
@@ -7209,11 +7287,11 @@
         </is>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A5)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A5)</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A5,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A5,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n">
@@ -7254,11 +7332,11 @@
         </is>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A6)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A6)</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A6,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A6,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n">
@@ -7299,11 +7377,11 @@
         </is>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A7)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A7,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A7,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n">
@@ -7344,11 +7422,11 @@
         </is>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A8)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A8)</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A8,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A8,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n">
@@ -7389,11 +7467,11 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A9)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A9)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A9,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A9,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n">
@@ -7434,11 +7512,11 @@
         </is>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A10)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A10)</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A10,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A10,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n">
@@ -7479,11 +7557,11 @@
         </is>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A11)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A11)</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A11,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A11,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n">
@@ -7524,11 +7602,11 @@
         </is>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A12)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A12)</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A12,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A12,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n">
@@ -7569,11 +7647,11 @@
         </is>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A13)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A13)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A13,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A13,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n">
@@ -7614,11 +7692,11 @@
         </is>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A14)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A14)</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A14,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A14,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n">
@@ -7659,11 +7737,11 @@
         </is>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A15)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A15)</f>
         <v/>
       </c>
       <c r="G15" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A15,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A15,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n">
@@ -7704,11 +7782,11 @@
         </is>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A16)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A16)</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A16,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A16,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n">
@@ -7749,11 +7827,11 @@
         </is>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A17)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A17)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A17,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A17,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n">
@@ -7794,11 +7872,11 @@
         </is>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A18)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A18)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A18,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A18,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n">
@@ -7839,11 +7917,11 @@
         </is>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A19)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A19)</f>
         <v/>
       </c>
       <c r="G19" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A19,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A19,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n">
@@ -7884,11 +7962,11 @@
         </is>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A20)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A20)</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A20,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A20,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n">
@@ -7925,11 +8003,11 @@
         </is>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$79,A21)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A21)</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$79,A21,'Backlog do startu'!$F$2:$F$79)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A21,'Backlog do startu'!$F$2:$F$80)</f>
         <v/>
       </c>
       <c r="H21" s="10" t="n">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20 sprintów · 30 h netto na sprint · wygenerowane 2026-08-22 z audyt/dane/</t>
+          <t>20 sprintów · 30 h netto na sprint · wygenerowane 2026-08-23 z audyt/dane/</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$80)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$81)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$80,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$80,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$81,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$81,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$80,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$81,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$80,"zrobione",'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$81,"zrobione",'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2675,12 +2675,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Z-12</t>
+          <t>X-29</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+          <t>Wdrożenie dowozi konfigurację obserwowalności na serwer</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
+          <t>ops/scripts/prod-deploy-ghcr.sh — krok 4.5: OBS_SERVICES, promtool check config przed restartem, compose up -d + compose restart, sprawdzenie /api/health i /-/healthy po restarcie, exit 1 gdy nie wrócą; apps/api/src/test/wdrozenie-obserwowalnosci.spec.ts (8)</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
+          <t>Zamknięte 2026-08-23. Wykryte przy X-28, pytaniem kontrolnym: co się właściwie stanie po wdrożeniu poprawki, która przenosi reguły alertowe do Grafany? Odpowiedź: NIC. | MECHANIZM: prod-deploy-ghcr.sh robi na serwerze checkout repozytorium do wdrażanego SHA, więc nowe pliki lądują na dysku — po czym restartuje wyłącznie APP_SERVICES="api client-panel staff-panel admin-panel status-page www". Prometheusa i Grafany na tej liście nie ma, a oba czytają konfigurację TYLKO przy starcie kontenera i oba mają ją podmontowaną z repozytorium. | ZASIĘG SZERSZY NIŻ ALERTY: tą samą drogą nie docierało na produkcję wszystko pod ops/observability/ — cele scrapowania i retencja w prometheus.yml, źródła danych, dwadzieścia kilka dashboardów Grafany, punkty kontaktowe i polityki. Każda zmiana w tych plikach od ostatniego RĘCZNEGO restartu Grafany istniała wyłącznie w repozytorium. | RODZINA: ten sam kształt co X-28 (alarm bez odbiorcy), X-14 i X-23 (kontrola, która melduje zamiast zatrzymywać) i H-20 (procedura bez dowodu wykonania) — COŚ WYGLĄDA NA ZROBIONE, BO ISTNIEJE. Zielone CI, zielony deploy, plik na dysku, pozycja zamknięta — i zero zmiany w działającym systemie. Różnica: tu zawodziło ostatnie ogniwo, nie budowa ani test, tylko DOSTARCZENIE. | POPRAWKA: krok 4.5, dwa polecenia zamiast jednego. `up -d` odtwarza kontener, gdy zmieniła się DEFINICJA usługi (X-28 usunęło montowanie alerts.yml); `restart` wymusza ponowne wczytanie, gdy zmieniła się tylko TREŚĆ podmontowanego pliku — tego compose nie widzi. | BEZWARUNKOWO, nie „gdy się zmieniło": porównanie z poprzednim SHA wymagałoby obu wersji w repozytorium na serwerze, a fetch jest tam płytki (--depth 1); nieudane porównanie skończyłoby się cichym „brak zmian → nie restartuj", czyli dokładnie tym błędem, który ta pozycja naprawia. Kilkanaście sekund przerwy w metrykach kontra miesiąc bez kopii bazy. | SPRAWDZENIE PRZED: promtool check config przez `compose run --rm --no-deps --entrypoint promtool`, a nie `exec` — świeży kontener z tą samą definicją, więc sprawdzenie działa także wtedy, gdy Prometheus akurat leży; przy `exec` padałoby w jedynym momencie, w którym naprawdę zależy nam na restarcie. Restart na zepsutej konfiguracji zdejmuje monitoring, a zauważyć to miał właśnie monitoring. | SPRAWDZENIE PO: „wydałem polecenie restartu" to nie to samo co „wróciły" — /api/health Grafany i /-/healthy Prometheusa (pytany Z KONTENERA Grafany, bo obraz Prometheusa nie ma czym wykonać zapytania HTTP), 20 prób co 3 s, potem exit 1. | KOLEJNOŚĆ W DWIE STRONY: krok jest PO bramce zdrowia i PO zapisaniu .last-good-image-tag, żeby awaria monitoringu nie wywróciła sprawnego wdrożenia; kończy się exit 1, a nie ostrzeżeniem, żeby wdrożenie nie uchodziło za skończone, zanim monitoring dostanie nową konfigurację. | Czerwieni się na starym kodzie: 6 z 8. Dwie przechodziły i przedtem — w tym ta o APP_SERVICES, bo Prometheusa i Grafany naprawdę tam nie było (tyle że nie było ich też nigdzie indziej). | CZEGO NIE DOWODZI: że po najbliższym wdrożeniu Grafana MA reguły — to obserwacja na produkcji (D3): Alerting → Alert rules powinno pokazać trzynaście reguł w folderze Verris. | Deploy #66 (scalenie X-28) poszedł jeszcze STARYM skryptem, więc pliki wjechały na serwer, a monitoring został z poprzednią konfiguracją; naprawia się to samo przy pierwszym wdrożeniu z tą zmianą. Dokumentacja: docs/zadania/X-29-obserwowalnosc-nie-docierala-na-produkcje.md</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Z-13</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>3</v>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr">
@@ -2831,12 +2831,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Z-16</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>3</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
@@ -2909,31 +2909,31 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>3</v>
@@ -2955,27 +2955,27 @@
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+        </is>
+      </c>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr">
@@ -2987,58 +2987,58 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -3065,12 +3065,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3085,11 +3085,11 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>4</v>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3129,7 +3129,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O30" s="11" t="inlineStr"/>
+      <c r="O30" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+        </is>
+      </c>
       <c r="P30" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3139,12 +3143,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3154,7 +3158,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -3190,24 +3194,20 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M31" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr">
-        <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
-        </is>
-      </c>
+      <c r="O31" s="11" t="inlineStr"/>
       <c r="P31" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3217,12 +3217,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3232,48 +3232,48 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
-        </is>
-      </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="11" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr">
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
@@ -3331,12 +3331,12 @@
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
@@ -3373,12 +3373,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -3388,16 +3388,16 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G34" s="10" t="n">
         <v>6</v>
@@ -3419,17 +3419,17 @@
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -3451,27 +3451,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
@@ -3497,27 +3497,27 @@
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -3529,73 +3529,73 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
@@ -3685,31 +3685,31 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>8</v>
@@ -3731,27 +3731,27 @@
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3763,73 +3763,73 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>H-20</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
         <v>16</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>PB-02 (drill wykonujemy na węźle #1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>H-20</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>9</v>
@@ -3887,27 +3887,27 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-02 (drill wykonujemy na węźle #1)</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -3919,12 +3919,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Dodatkowy użytkownik bazy — utworzenie</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -3934,50 +3934,50 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L41" s="11" t="inlineStr">
-        <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
-        </is>
-      </c>
-      <c r="M41" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
@@ -3997,12 +3997,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — usunięcie</t>
+          <t>Dodatkowy użytkownik bazy — utworzenie</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="11" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — zmiana hasła</t>
+          <t>Użytkownik bazy — usunięcie</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -4153,12 +4153,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — lista</t>
+          <t>Użytkownik bazy — zmiana hasła</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
@@ -4231,12 +4231,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — auto-logowanie (SSO)</t>
+          <t>Użytkownik bazy — lista</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
+          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N45" s="11" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
+          <t>phpMyAdmin — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4324,19 +4324,19 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
@@ -4345,22 +4345,22 @@
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="N46" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
@@ -4387,12 +4387,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SRV / CAA</t>
+          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>F-01 (ten sam edytor)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N47" s="11" t="inlineStr">
@@ -4451,7 +4451,11 @@
           <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
         </is>
       </c>
-      <c r="O47" s="11" t="inlineStr"/>
+      <c r="O47" s="11" t="inlineStr">
+        <is>
+          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+        </is>
+      </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4461,12 +4465,12 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Webmail — auto-logowanie (SSO)</t>
+          <t>Rekordy SRV / CAA</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -4476,12 +4480,12 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
@@ -4507,29 +4511,25 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-01 (ten sam edytor)</t>
         </is>
       </c>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O48" s="11" t="inlineStr">
-        <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
-        </is>
-      </c>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+        </is>
+      </c>
+      <c r="O48" s="11" t="inlineStr"/>
       <c r="P48" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4539,12 +4539,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per domena</t>
+          <t>Webmail — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>B — Runtime WWW</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
@@ -4617,12 +4617,12 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SPF — kreator</t>
+          <t>Zmiana wersji PHP per domena</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -4632,19 +4632,19 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
@@ -4653,22 +4653,22 @@
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="N50" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O50" s="11" t="inlineStr">
         <is>
-          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
+          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr">
@@ -4695,12 +4695,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Rekordy DKIM — konfiguracja</t>
+          <t>Rekordy SPF — kreator</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>E-15 (ten sam panel dostarczalności)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
@@ -4773,12 +4773,12 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Rekord DMARC — konfiguracja</t>
+          <t>Rekordy DKIM — konfiguracja</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="M52" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-15 (ten sam panel dostarczalności)</t>
         </is>
       </c>
       <c r="N52" s="11" t="inlineStr">
@@ -4851,12 +4851,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
+          <t>Rekord DMARC — konfiguracja</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4897,27 +4897,27 @@
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
@@ -4929,12 +4929,12 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Usunięcie zapisanej karty przez klienta</t>
+          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
         </is>
       </c>
       <c r="M54" s="11" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>wymóg konsumencki</t>
+          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
@@ -5007,12 +5007,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>M-26</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Ręczne zawieszenie usługi przez operatora</t>
+          <t>Usunięcie zapisanej karty przez klienta</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -5034,7 +5034,7 @@
         <v>6</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
@@ -5043,22 +5043,22 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:192</t>
+          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
+          <t>wymóg konsumencki</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>A-25</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Ręczne odwieszenie usługi przez operatora</t>
+          <t>Ręczne zawieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:210</t>
+          <t>subscriptions.admin.controller.ts:192</t>
         </is>
       </c>
       <c r="M56" s="11" t="inlineStr">
         <is>
-          <t>A-25 (ten sam widok)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N56" s="11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
+          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -5163,12 +5163,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>A-26</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Ręczne odwieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>subscriptions.admin.controller.ts:210</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-25 (ten sam widok)</t>
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -5241,12 +5241,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
@@ -5319,12 +5319,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>H-22</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Panel odtwarzania w widocznym miejscu</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>klient w kryzysie tego nie znajdzie</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -5397,12 +5397,12 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>H-09</t>
+          <t>H-22</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
+          <t>Panel odtwarzania w widocznym miejscu</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -5424,7 +5424,7 @@
         <v>6</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
@@ -5433,12 +5433,12 @@
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K60" s="10" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>hosting-restore.service.ts:167</t>
+          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
+          <t>klient w kryzysie tego nie znajdzie</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -5475,12 +5475,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>H-17</t>
+          <t>H-09</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
+          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -5521,27 +5521,27 @@
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
+          <t>hosting-restore.service.ts:167</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
+          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>G-20</t>
+          <t>H-17</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Ochrona przed atakiem słownikowym na panel</t>
+          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -5599,27 +5599,27 @@
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
-          <t>rate-limit.guard.ts — ZERO testów</t>
+          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
         </is>
       </c>
       <c r="M62" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
         </is>
       </c>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>brak dowodu D2 na krytycznym guardzie</t>
+          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr">
@@ -5631,12 +5631,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>G-20</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Staging — publikacja na produkcję</t>
+          <t>Ochrona przed atakiem słownikowym na panel</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:187</t>
+          <t>rate-limit.guard.ts — ZERO testów</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+          <t>brak dowodu D2 na krytycznym guardzie</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
@@ -5709,27 +5709,27 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
+          <t>Staging — publikacja na produkcję</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
@@ -5755,27 +5755,27 @@
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:187</t>
+        </is>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L64" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
+          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr">
@@ -5787,73 +5787,73 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
         </is>
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
         </is>
       </c>
       <c r="P65" s="10" t="inlineStr">
@@ -5865,12 +5865,12 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwarka wolnych domen</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:54</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="M66" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
         </is>
       </c>
       <c r="N66" s="11" t="inlineStr">
@@ -5929,7 +5929,11 @@
           <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
         </is>
       </c>
-      <c r="O66" s="11" t="inlineStr"/>
+      <c r="O66" s="11" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -5939,12 +5943,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Spakowanie do archiwum</t>
+          <t>Wyszukiwarka wolnych domen</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -5954,12 +5958,12 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
@@ -5985,12 +5989,12 @@
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>files.service.ts:320 — tylko extract</t>
+          <t>domains.controller.ts:54</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
@@ -6000,14 +6004,10 @@
       </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O67" s="11" t="inlineStr">
-        <is>
-          <t>standard we wszystkich panelach</t>
-        </is>
-      </c>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+        </is>
+      </c>
+      <c r="O67" s="11" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -6017,31 +6017,31 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+          <t>Spakowanie do archiwum</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G68" s="10" t="n">
         <v>15</v>
@@ -6063,27 +6063,27 @@
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>files.service.ts:320 — tylko extract</t>
+        </is>
+      </c>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L68" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N68" s="11" t="inlineStr">
         <is>
-          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+          <t>standard we wszystkich panelach</t>
         </is>
       </c>
       <c r="P68" s="10" t="inlineStr">
@@ -6095,12 +6095,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -6115,14 +6115,14 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
@@ -6131,12 +6131,12 @@
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
+          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
         </is>
       </c>
       <c r="O69" s="11" t="inlineStr">
         <is>
-          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
+          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
         </is>
       </c>
       <c r="P69" s="10" t="inlineStr">
@@ -6173,12 +6173,12 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Treści i cennik na verris.pl</t>
+          <t>Finalizacja dokumentów prawnych 1.0.0</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
@@ -6229,17 +6229,17 @@
       </c>
       <c r="M70" s="11" t="inlineStr">
         <is>
-          <t>PB-01 (cennik zależy od unit economics)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
         </is>
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Landing /przenies-strone</t>
+          <t>Treści i cennik na verris.pl</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -6278,7 +6278,7 @@
         <v>16</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
@@ -6287,12 +6287,12 @@
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
@@ -6307,17 +6307,17 @@
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
+          <t>PB-01 (cennik zależy od unit economics)</t>
         </is>
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
         </is>
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr">
@@ -6329,12 +6329,12 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+          <t>Landing /przenies-strone</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="M72" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
         </is>
       </c>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
         </is>
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr">
@@ -6407,34 +6407,34 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>KSeF — walidacja XSD przed wysyłką</t>
+          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
@@ -6443,37 +6443,37 @@
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
         </is>
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>smoke na api-test MF nie został wykonany</t>
+          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr">
@@ -6485,12 +6485,12 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>KSeF — tryb offline/awaryjny</t>
+          <t>KSeF — walidacja XSD przed wysyłką</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G74" s="10" t="n">
         <v>18</v>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
         </is>
       </c>
       <c r="M74" s="11" t="inlineStr">
         <is>
-          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
         </is>
       </c>
       <c r="N74" s="11" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+          <t>smoke na api-test MF nie został wykonany</t>
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr">
@@ -6563,12 +6563,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>KSeF — pobranie UPO przez operatora</t>
+          <t>KSeF — tryb offline/awaryjny</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -6583,11 +6583,11 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>18</v>
@@ -6609,27 +6609,27 @@
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
         </is>
       </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr">
@@ -6641,12 +6641,12 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>KSeF — numer i UPO widoczne dla klienta</t>
+          <t>KSeF — pobranie UPO przez operatora</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
@@ -6677,37 +6677,37 @@
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień „ksef” w apps/client-panel</t>
+          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr">
         <is>
-          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr">
@@ -6719,31 +6719,31 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy — 20 artykułów startowych</t>
+          <t>KSeF — numer i UPO widoczne dla klienta</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>19</v>
@@ -6765,27 +6765,27 @@
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zero wystąpień „ksef” w apps/client-panel</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
         </is>
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr">
@@ -6797,12 +6797,12 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+          <t>Baza wiedzy — 20 artykułów startowych</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>19</v>
@@ -6853,17 +6853,17 @@
       </c>
       <c r="M78" s="11" t="inlineStr">
         <is>
-          <t>PB-06 (kampania kieruje na landing)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
         </is>
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr">
@@ -6875,12 +6875,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Test end-to-end „pierwszy klient”</t>
+          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -6895,24 +6895,28 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H79" s="10" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
@@ -6927,17 +6931,17 @@
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>wszystkie blokery zamknięte (sprint 8)</t>
+          <t>PB-06 (kampania kieruje na landing)</t>
         </is>
       </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
         </is>
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr">
@@ -6949,12 +6953,12 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Runbook startu i decyzja GO</t>
+          <t>Test end-to-end „pierwszy klient”</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -6973,7 +6977,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>20</v>
@@ -7001,28 +7005,102 @@
       </c>
       <c r="M80" s="11" t="inlineStr">
         <is>
+          <t>wszystkie blokery zamknięte (sprint 8)</t>
+        </is>
+      </c>
+      <c r="N80" s="11" t="inlineStr">
+        <is>
+          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+        </is>
+      </c>
+      <c r="O80" s="11" t="inlineStr">
+        <is>
+          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+        </is>
+      </c>
+      <c r="P80" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>PB-12</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>Runbook startu i decyzja GO</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H81" s="10" t="inlineStr"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
           <t>PB-05 (decyzja GO po przejściu ścieżki na produkcji)</t>
         </is>
       </c>
-      <c r="N80" s="11" t="inlineStr">
+      <c r="N81" s="11" t="inlineStr">
         <is>
           <t>Każdy z 11 blokerów ma wpis: co zrobiono, gdzie jest dowód, kto potwierdził. Bez formuły „warunkowe GO”.</t>
         </is>
       </c>
-      <c r="O80" s="11" t="inlineStr">
+      <c r="O81" s="11" t="inlineStr">
         <is>
           <t>Domknięcie: przegląd wszystkich blokerów z dowodem zamknięcia, decyzja GO/NO-GO zapisana z datą.</t>
         </is>
       </c>
-      <c r="P80" s="10" t="inlineStr">
+      <c r="P81" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P80"/>
-  <conditionalFormatting sqref="E2:E80">
+  <autoFilter ref="A1:P81"/>
+  <conditionalFormatting sqref="E2:E81">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>
@@ -7042,7 +7120,7 @@
       <formula>"ŚREDNI"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P80">
+  <conditionalFormatting sqref="P2:P81">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"zrobione"</formula>
     </cfRule>
@@ -7152,11 +7230,11 @@
         </is>
       </c>
       <c r="F2" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A2)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A2)</f>
         <v/>
       </c>
       <c r="G2" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A2,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A2,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H2" s="10" t="n">
@@ -7197,11 +7275,11 @@
         </is>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A3)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A3)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A3,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A3,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H3" s="10" t="n">
@@ -7213,7 +7291,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziewięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł.</t>
+          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziesięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł. X-29 wyszło godzinę po X-28 i z tego samego pytania: skoro reguły są w repo, to czy wdrożenie w ogóle je dowozi? Nie dowoziło — wdrożenie restartowało tylko aplikacje, a Prometheus i Grafana czytają konfigurację wyłącznie przy starcie.</t>
         </is>
       </c>
     </row>
@@ -7242,11 +7320,11 @@
         </is>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A4)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A4)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A4,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A4,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H4" s="10" t="n">
@@ -7287,11 +7365,11 @@
         </is>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A5)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A5)</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A5,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A5,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n">
@@ -7332,11 +7410,11 @@
         </is>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A6)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A6)</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A6,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A6,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n">
@@ -7377,11 +7455,11 @@
         </is>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A7)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A7,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A7,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n">
@@ -7422,11 +7500,11 @@
         </is>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A8)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A8)</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A8,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A8,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n">
@@ -7467,11 +7545,11 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A9)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A9)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A9,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A9,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n">
@@ -7512,11 +7590,11 @@
         </is>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A10)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A10)</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A10,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A10,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n">
@@ -7557,11 +7635,11 @@
         </is>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A11)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A11)</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A11,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A11,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n">
@@ -7602,11 +7680,11 @@
         </is>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A12)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A12)</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A12,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A12,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n">
@@ -7647,11 +7725,11 @@
         </is>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A13)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A13)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A13,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A13,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n">
@@ -7692,11 +7770,11 @@
         </is>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A14)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A14)</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A14,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A14,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n">
@@ -7737,11 +7815,11 @@
         </is>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A15)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A15)</f>
         <v/>
       </c>
       <c r="G15" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A15,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A15,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n">
@@ -7782,11 +7860,11 @@
         </is>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A16)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A16)</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A16,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A16,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n">
@@ -7827,11 +7905,11 @@
         </is>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A17)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A17)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A17,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A17,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n">
@@ -7872,11 +7950,11 @@
         </is>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A18)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A18)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A18,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A18,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n">
@@ -7917,11 +7995,11 @@
         </is>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A19)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A19)</f>
         <v/>
       </c>
       <c r="G19" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A19,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A19,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n">
@@ -7962,11 +8040,11 @@
         </is>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A20)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A20)</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A20,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A20,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n">
@@ -8003,11 +8081,11 @@
         </is>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$80,A21)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A21)</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$80,A21,'Backlog do startu'!$F$2:$F$80)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A21,'Backlog do startu'!$F$2:$F$81)</f>
         <v/>
       </c>
       <c r="H21" s="10" t="n">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -2753,12 +2753,12 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Z-12</t>
+          <t>H-20</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2768,19 +2768,19 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
         <v>16</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
+          <t>DOWÓD D4 — wiersz w bazie PRODUKCYJNEJ, odczytany 2026-08-23: finishedAt=2026-08-22 23:19:45, result=OK, owner=Dominik Kowalski, durationSec=9, objectName=latest.sql.gz.age. W tabeli stoi też wiersz poprzedni: 2026-08-22 19:57:36 / FAILED / durationSec=1 / objectName=latest.sql.gz — próba sprzed H-24, która szła po nieistniejący obiekt. | MECHANIZM (D2): admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach, suma kontrolna, deszyfrowanie age, zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8)</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-02 (drill wykonujemy na węźle #1)</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
+          <t>ZAMKNIĘTE 2026-08-23. Pierwsze w historii projektu odtworzenie bazy z kopii — i pierwszy dowód, że warstwa DR w ogóle działa. Przebieg: MinIO stat latest.sql.gz.age (4,3 MiB, 2026-08-22 21:24:12), suma kontrolna zgodna, deszyfrowanie kluczem operacyjnym, odtworzenie do izolowanej bazy verris_restore_drill w 9 sekund, progi wierszy na pięciu tabelach: Invoice 0 (min 0), Plan 5 (min 1), Account 3 (min 0), User 10 (min 1), Subscription 7 (min 0), baza drillowa skasowana, produkcyjna verris_db nietknięta. | DZIEWIĘĆ SEKUND TO REALNE RTO — dolne oszacowanie, bo drill biegnie na tym samym hoście. To jest liczba, którą trzeba znać PRZED awarią, nie w jej trakcie. | DWA WIERSZE W TABELI, NIE JEDEN — i to jest część dowodu. Pierwsza próba (19:57, FAILED, 1 s, latest.sql.gz) padła, bo skrypt pytał o obiekt, którego produkcja NIGDY nie tworzy; naprawione w H-24, druga próba (23:19, OK, 9 s, latest.sql.gz.age) przeszła. Mechanizm zapisał własną porażkę zamiast ją przemilczeć — dokładnie po to powstał wymóg, żeby ślad powstawał RÓWNIEŻ przy niepowodzeniu. Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna. | DOWÓD ODCZYTANY Z BAZY, NIE Z KOMUNIKATU SKRYPTU. Skrypt drukuje „ślad próby zapisany" — to jest zdanie o zamiarze, nie o wyniku. Cała ta pozycja i cała awaria kopii z H-23 wzięły się z ufania takim zdaniom. | DOWÓD SIĘ STARZEJE: termin ważności 30 dni (MAKS_WIEK_PROBY_DNI), czyli do 2026-09-21, potem gotowość do startu znów zwraca go: false. Przypomnienie idzie mailem 7 dni przed terminem. Odtworzenie sprzed schematu, którego już nie ma, nie dowodzi niczego o dzisiejszej kopii. | ZROBIONE POZA KOLEJNOŚCIĄ — pozycja planowana na sprint 9 (po postawieniu węzła produkcyjnego w sprincie 8), wykonana w sprincie 2, bo H-23 wymusiło odtworzenie kopii tu i teraz. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej; nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr">
@@ -2831,12 +2831,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Z-13</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>3</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Z-16</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>3</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr">
@@ -2987,31 +2987,31 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>3</v>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -3065,58 +3065,58 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3143,12 +3143,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3163,11 +3163,11 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>4</v>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
@@ -3207,7 +3207,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O31" s="11" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+        </is>
+      </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3217,12 +3221,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3232,7 +3236,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -3268,24 +3272,20 @@
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O32" s="11" t="inlineStr">
-        <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
-        </is>
-      </c>
+      <c r="O32" s="11" t="inlineStr"/>
       <c r="P32" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3295,12 +3295,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3310,48 +3310,48 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
-        </is>
-      </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
@@ -3451,12 +3451,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3466,16 +3466,16 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>6</v>
@@ -3497,17 +3497,17 @@
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -3529,27 +3529,27 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
@@ -3575,27 +3575,27 @@
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
@@ -3607,73 +3607,73 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
@@ -3721,12 +3721,12 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
@@ -3763,31 +3763,31 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>8</v>
@@ -3809,27 +3809,27 @@
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
@@ -3841,73 +3841,73 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>H-20</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Test odtworzeniowy z datą ostatniego wykonania</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
         <v>16</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>admin-readiness/proba-odtworzenia.ts — ocenProby/brakujaceWiersze/MINIMALNE_WIERSZE; live-readiness.service.ts — pozycja restore_drill z blocking: true; proba-odtworzenia.scheduler.ts — przypomnienie codziennie 08:30, tylko gdy jest co robić; ops/scripts/restore-drill-isolated.sh — progi wierszy na 5 tabelach + zapis śladu; migracja 20260823000000_proba_odtworzenia (tabela RestoreDrill + 2 CHECK); ops/docs/OFFSITE_RESTORE_RUNBOOK.md — procedura z właścicielem i cyklem 30 dni; proba-odtworzenia.spec.ts (20) + test/integration/proba-odtworzenia.int-spec.ts (8). BRAK: ani jednego wiersza w RestoreDrill — nikt jeszcze nie odtworzył bazy z kopii.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>PB-02 (drill wykonujemy na węźle #1)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>Stan 2026-08-22: MECHANIZM ZAMKNIĘTY (D2), POZYCJA NADAL OTWARTA. Zrobione wszystko poza jedną rzeczą, której nie da się zrobić za kogoś: nikt nadal nie odtworzył bazy z kopii. Reguła audytu wymaga dla DR poziomu D4 — data, wynik, właściciel — a zapis powstaje dopiero przy uruchomieniu drilla. Pusta tabela znaczy dokładnie to samo co przed zmianą: nie wiemy, czy potrafimy odtworzyć bazę. Oznaczenie tej pozycji jako DZIAŁA byłoby rozumowaniem zakazanym w tym projekcie pod nazwą „warunkowe GO": mamy narzędzie, więc uznajmy, że mamy wynik. | CO SIĘ REALNIE ZMIENIŁO: blokada przestała być notatką w runbooku i stała się bramką w kodzie. Wcześniej można było wystartować sprzedaż bez drilla i nikt by nie zauważył; teraz gotowość do startu zwraca go: false, dopóki próby nie ma. | JAK ZAMKNĄĆ: jedno polecenie na control-plane — `cd /opt/verris &amp;&amp; ./ops/scripts/restore-drill-isolated.sh --owner "Dominik Kowalski"`. Skrypt sam zapisze wynik. | DWIE CICHE WADY SKRYPTU, które naprawiłem przy okazji: (1) LICZYŁ I NIE SPRAWDZAŁ — wykonywał SELECT COUNT(*) FROM "User" i tylko logował wynik, po czym i tak drukował RESTORE DRILL OK; psql kończy się zerem także wtedy, gdy wgrał pusty plik, więc odtworzenie NICZEGO meldowało sukces (ta sama klasa co X-14: kontrola istnieje, ale niczego nie bramkuje); (2) PATRZYŁ NA JEDNĄ TABELĘ — sam User nie mówi nic o tym, czy przetrwały faktury i subskrypcje, a to one bolą przy utracie. Teraz progi na pięciu tabelach i przerwanie z konkretnym komunikatem. | ŚLAD: tabela RestoreDrill z czasem trwania (to jest REALNE RTO — liczba, którą trzeba znać przed awarią, nie w jej trakcie), właścicielem i liczbami wierszy. Zapis idzie do bazy PRODUKCYJNEJ i powstaje RÓWNIEŻ przy niepowodzeniu, łącznie z pułapką na przerwanie w połowie: brak wpisu nie może znaczyć jednocześnie „nigdy nie było" i „padło". Dwa CHECK w bazie: durationSec &gt; 0 (zero sekund to zapis, nie pomiar) i niepusty owner (D4 wymaga właściciela; pusty napis spełniałby NOT NULL i nie spełniałby reguły). | BRAMKA, NIE OSTRZEŻENIE: blocking: true. Ostrzeżenie zamiast bramki to TRZECIE wystąpienie tego błędu — macierz wytknęła je przy H-19, naprawiałem w X-23 przy jobie bezpieczeństwa, tu wracało. | Ocena patrzy na OSTATNIĄ próbę, nie na ostatnią udaną: gdyby patrzyła tylko na udane, wczorajsza awaria odtwarzania byłaby niewidoczna, a raport pokazywałby zieloną próbę sprzed dwóch tygodni. Dowód się starzeje — odtworzenie sprzed roku nie mówi nic o dzisiejszej kopii, bo schemat się zmienił i migracje doszły; stąd termin 30 dni. | TEST, KTÓRY NAJPIERW NIC NIE DOWODZIŁ (drugi raz po Z-01): pierwsza wersja sprawdzała raport.go === false, a w środowisku testowym `go` jest fałszem niezależnie od tej pozycji — asercja przechodziła także po zdjęciu blokady. Zamiana bramki na ostrzeżenie zapalała wtedy JEDEN test zamiast trzech. Poprawione na check.blocking &amp;&amp; check.status === 'fail'. | Czerwieni się na starym kodzie: brak sprawdzenia → 5 z 8 integracyjnych; blocking: false → 3 z 8; skrypt bez asercji progów → 4 z 20 jednostkowych. | CZEGO NIE ROBI: nie odtwarza konta hostingowego (pliki, poczta, bazy klienta — osobna ścieżka w runbooku); nie mierzy RTO na maszynie zastępczej (drill biegnie na tym samym hoście, więc czas to DOLNE oszacowanie); nie sprawdza poprawności danych ponad to, że tabele nie są puste; nie uruchamia się sam — świadomie, bo drill zajmuje zasoby control-plane i kasuje bazę drillową. Przypomina, nie wykonuje. Dokumentacja: docs/zadania/H-20-proba-odtworzenia.md</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziesięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł. X-29 wyszło godzinę po X-28 i z tego samego pytania: skoro reguły są w repo, to czy wdrożenie w ogóle je dowozi? Nie dowoziło — wdrożenie restartowało tylko aplikacje, a Prometheus i Grafana czytają konfigurację wyłącznie przy starcie.</t>
+          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziesięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł. X-29 wyszło godzinę po X-28 i z tego samego pytania: skoro reguły są w repo, to czy wdrożenie w ogóle je dowozi? Nie dowoziło — wdrożenie restartowało tylko aplikacje, a Prometheus i Grafana czytają konfigurację wyłącznie przy starcie. H-20 wykonane tu, a nie w sprincie 9: awaria kopii z H-23 wymusiła odtworzenie bazy tu i teraz, więc dowód D4 powstał jedenaście sprintów przed terminem.</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Dowód odtworzenia kopii i domknięcie DPA</t>
+          <t>Domknięcie DPA</t>
         </is>
       </c>
       <c r="F10" s="10">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>Kamień milowy: po tym sprincie zamknięte są wszystkie blokery poza KSeF-em, który świadomie stoi na końcu. Drill może wykazać, że odtworzenie nie działa — wtedy sprint się przedłuża i tak ma być.</t>
+          <t>H-20 wypadło z tego sprintu 2026-08-23 — dowód odtworzenia z kopii powstał w sprincie 2, bo awaria kopii (H-23) wymusiła odtworzenie bazy natychmiast. Zostaje P-15, którego tempo zależy od dostawców, nie od nas. Kamień milowy się nie zmienia: po tym sprincie zamknięte są wszystkie blokery poza KSeF-em, który świadomie stoi na końcu.</t>
         </is>
       </c>
     </row>

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$81)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$82)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$81,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$81,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$82,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$82,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$81,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$82,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$81,"zrobione",'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$82,"zrobione",'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2831,12 +2831,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Z-12</t>
+          <t>X-30</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+          <t>Reguły alertowe nie tylko są wczytane, ale się liczą</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
@@ -2867,22 +2867,22 @@
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
+          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). BRAK: zielonego wdrożenia z czystym logiem Grafany — dowód D3 jeszcze nie powstał.</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
+          <t>Stan 2026-08-23: NAPRAWIONE W KODZIE (D2), POZYCJA OTWARTA do czasu zielonego wdrożenia z czystym logiem Grafany (D3). Wpisanie DZIAŁA teraz byłoby powtórzeniem dokładnie tego błędu, który ta pozycja opisuje. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Z-13</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>3</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Z-16</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>3</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -3065,31 +3065,31 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>3</v>
@@ -3111,27 +3111,27 @@
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3143,58 +3143,58 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>4</v>
@@ -3267,12 +3267,12 @@
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr">
@@ -3285,7 +3285,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O32" s="11" t="inlineStr"/>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+        </is>
+      </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3295,12 +3299,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3310,7 +3314,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -3346,24 +3350,20 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O33" s="11" t="inlineStr">
-        <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
-        </is>
-      </c>
+      <c r="O33" s="11" t="inlineStr"/>
       <c r="P33" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3373,12 +3373,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -3388,48 +3388,48 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L34" s="11" t="inlineStr">
-        <is>
-          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
-        </is>
-      </c>
       <c r="M34" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -3487,12 +3487,12 @@
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
@@ -3529,12 +3529,12 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -3544,16 +3544,16 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>6</v>
@@ -3575,17 +3575,17 @@
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N36" s="11" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
@@ -3607,27 +3607,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
@@ -3653,27 +3653,27 @@
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M37" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
@@ -3685,73 +3685,73 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
@@ -3841,31 +3841,31 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>8</v>
@@ -3887,27 +3887,27 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
@@ -3919,58 +3919,58 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G41" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="G41" s="10" t="n">
-        <v>9</v>
-      </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
@@ -3997,12 +3997,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Dodatkowy użytkownik bazy — utworzenie</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -4012,50 +4012,50 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L42" s="11" t="inlineStr">
-        <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
-        </is>
-      </c>
-      <c r="M42" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N42" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — usunięcie</t>
+          <t>Dodatkowy użytkownik bazy — utworzenie</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="11" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
@@ -4153,12 +4153,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — zmiana hasła</t>
+          <t>Użytkownik bazy — usunięcie</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
@@ -4231,12 +4231,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — lista</t>
+          <t>Użytkownik bazy — zmiana hasła</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — auto-logowanie (SSO)</t>
+          <t>Użytkownik bazy — lista</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
+          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N46" s="11" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
@@ -4387,12 +4387,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
+          <t>phpMyAdmin — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4402,19 +4402,19 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
@@ -4423,22 +4423,22 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P47" s="10" t="inlineStr">
@@ -4465,12 +4465,12 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SRV / CAA</t>
+          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
         <is>
-          <t>F-01 (ten sam edytor)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N48" s="11" t="inlineStr">
@@ -4529,7 +4529,11 @@
           <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
         </is>
       </c>
-      <c r="O48" s="11" t="inlineStr"/>
+      <c r="O48" s="11" t="inlineStr">
+        <is>
+          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+        </is>
+      </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4539,12 +4543,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Webmail — auto-logowanie (SSO)</t>
+          <t>Rekordy SRV / CAA</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -4554,12 +4558,12 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
@@ -4585,29 +4589,25 @@
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-01 (ten sam edytor)</t>
         </is>
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O49" s="11" t="inlineStr">
-        <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
-        </is>
-      </c>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+        </is>
+      </c>
+      <c r="O49" s="11" t="inlineStr"/>
       <c r="P49" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4617,12 +4617,12 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per domena</t>
+          <t>Webmail — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>B — Runtime WWW</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O50" s="11" t="inlineStr">
         <is>
-          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr">
@@ -4695,12 +4695,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SPF — kreator</t>
+          <t>Zmiana wersji PHP per domena</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4710,19 +4710,19 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
@@ -4731,22 +4731,22 @@
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
+          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
@@ -4773,12 +4773,12 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Rekordy DKIM — konfiguracja</t>
+          <t>Rekordy SPF — kreator</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="M52" s="11" t="inlineStr">
         <is>
-          <t>E-15 (ten sam panel dostarczalności)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="11" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr">
@@ -4851,12 +4851,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Rekord DMARC — konfiguracja</t>
+          <t>Rekordy DKIM — konfiguracja</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-15 (ten sam panel dostarczalności)</t>
         </is>
       </c>
       <c r="N53" s="11" t="inlineStr">
@@ -4929,12 +4929,12 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
+          <t>Rekord DMARC — konfiguracja</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -4975,27 +4975,27 @@
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
-          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M54" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="N54" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
@@ -5007,12 +5007,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Usunięcie zapisanej karty przez klienta</t>
+          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>wymóg konsumencki</t>
+          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>M-26</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Ręczne zawieszenie usługi przez operatora</t>
+          <t>Usunięcie zapisanej karty przez klienta</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -5112,7 +5112,7 @@
         <v>6</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
@@ -5121,22 +5121,22 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:192</t>
+          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
         </is>
       </c>
       <c r="M56" s="11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="N56" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
+          <t>wymóg konsumencki</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -5163,12 +5163,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>A-25</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Ręczne odwieszenie usługi przez operatora</t>
+          <t>Ręczne zawieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:210</t>
+          <t>subscriptions.admin.controller.ts:192</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>A-25 (ten sam widok)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
+          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -5241,12 +5241,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>A-26</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Ręczne odwieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>subscriptions.admin.controller.ts:210</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-25 (ten sam widok)</t>
         </is>
       </c>
       <c r="N58" s="11" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
@@ -5319,12 +5319,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -5397,12 +5397,12 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>H-22</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Panel odtwarzania w widocznym miejscu</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="N60" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>klient w kryzysie tego nie znajdzie</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -5475,12 +5475,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>H-09</t>
+          <t>H-22</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
+          <t>Panel odtwarzania w widocznym miejscu</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -5502,7 +5502,7 @@
         <v>6</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>hosting-restore.service.ts:167</t>
+          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
+          <t>klient w kryzysie tego nie znajdzie</t>
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>H-17</t>
+          <t>H-09</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
+          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -5599,27 +5599,27 @@
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
-          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
+          <t>hosting-restore.service.ts:167</t>
         </is>
       </c>
       <c r="M62" s="11" t="inlineStr">
         <is>
-          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
+          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr">
@@ -5631,12 +5631,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>G-20</t>
+          <t>H-17</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Ochrona przed atakiem słownikowym na panel</t>
+          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -5677,27 +5677,27 @@
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>rate-limit.guard.ts — ZERO testów</t>
+          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
         </is>
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>brak dowodu D2 na krytycznym guardzie</t>
+          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
@@ -5709,12 +5709,12 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>G-20</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Staging — publikacja na produkcję</t>
+          <t>Ochrona przed atakiem słownikowym na panel</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:187</t>
+          <t>rate-limit.guard.ts — ZERO testów</t>
         </is>
       </c>
       <c r="M64" s="11" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+          <t>brak dowodu D2 na krytycznym guardzie</t>
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr">
@@ -5787,27 +5787,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
+          <t>Staging — publikacja na produkcję</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
@@ -5833,27 +5833,27 @@
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:187</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L65" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
+          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
         </is>
       </c>
       <c r="P65" s="10" t="inlineStr">
@@ -5865,73 +5865,73 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M66" s="11" t="inlineStr">
         <is>
-          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
         </is>
       </c>
       <c r="O66" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr">
@@ -5943,12 +5943,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwarka wolnych domen</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:54</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
         </is>
       </c>
       <c r="N67" s="11" t="inlineStr">
@@ -6007,7 +6007,11 @@
           <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
         </is>
       </c>
-      <c r="O67" s="11" t="inlineStr"/>
+      <c r="O67" s="11" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
       <c r="P67" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -6017,12 +6021,12 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Spakowanie do archiwum</t>
+          <t>Wyszukiwarka wolnych domen</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -6032,12 +6036,12 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
@@ -6063,12 +6067,12 @@
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>files.service.ts:320 — tylko extract</t>
+          <t>domains.controller.ts:54</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr">
@@ -6078,14 +6082,10 @@
       </c>
       <c r="N68" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>standard we wszystkich panelach</t>
-        </is>
-      </c>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+        </is>
+      </c>
+      <c r="O68" s="11" t="inlineStr"/>
       <c r="P68" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -6095,31 +6095,31 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+          <t>Spakowanie do archiwum</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G69" s="10" t="n">
         <v>15</v>
@@ -6141,27 +6141,27 @@
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>files.service.ts:320 — tylko extract</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O69" s="11" t="inlineStr">
         <is>
-          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+          <t>standard we wszystkich panelach</t>
         </is>
       </c>
       <c r="P69" s="10" t="inlineStr">
@@ -6173,12 +6173,12 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -6193,14 +6193,14 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K70" s="10" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
+          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
         </is>
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
+          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Treści i cennik na verris.pl</t>
+          <t>Finalizacja dokumentów prawnych 1.0.0</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
@@ -6307,17 +6307,17 @@
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>PB-01 (cennik zależy od unit economics)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
         </is>
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr">
@@ -6329,12 +6329,12 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Landing /przenies-strone</t>
+          <t>Treści i cennik na verris.pl</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -6356,7 +6356,7 @@
         <v>16</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
@@ -6365,12 +6365,12 @@
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K72" s="10" t="inlineStr">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="M72" s="11" t="inlineStr">
         <is>
-          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
+          <t>PB-01 (cennik zależy od unit economics)</t>
         </is>
       </c>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
         </is>
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+          <t>Landing /przenies-strone</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
@@ -6463,17 +6463,17 @@
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
         </is>
       </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
         </is>
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr">
@@ -6485,34 +6485,34 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>KSeF — walidacja XSD przed wysyłką</t>
+          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
@@ -6521,37 +6521,37 @@
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M74" s="11" t="inlineStr">
         <is>
-          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
         </is>
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>smoke na api-test MF nie został wykonany</t>
+          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr">
@@ -6563,12 +6563,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>KSeF — tryb offline/awaryjny</t>
+          <t>KSeF — walidacja XSD przed wysyłką</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G75" s="10" t="n">
         <v>18</v>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
         </is>
       </c>
       <c r="N75" s="11" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+          <t>smoke na api-test MF nie został wykonany</t>
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr">
@@ -6641,12 +6641,12 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>KSeF — pobranie UPO przez operatora</t>
+          <t>KSeF — tryb offline/awaryjny</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -6661,11 +6661,11 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>18</v>
@@ -6687,27 +6687,27 @@
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
         </is>
       </c>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr">
@@ -6719,12 +6719,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>KSeF — numer i UPO widoczne dla klienta</t>
+          <t>KSeF — pobranie UPO przez operatora</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -6739,14 +6739,14 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
@@ -6755,37 +6755,37 @@
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień „ksef” w apps/client-panel</t>
+          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr">
@@ -6797,31 +6797,31 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy — 20 artykułów startowych</t>
+          <t>KSeF — numer i UPO widoczne dla klienta</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G78" s="10" t="n">
         <v>19</v>
@@ -6843,27 +6843,27 @@
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zero wystąpień „ksef” w apps/client-panel</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
         </is>
       </c>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr">
@@ -6875,12 +6875,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+          <t>Baza wiedzy — 20 artykułów startowych</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>19</v>
@@ -6931,17 +6931,17 @@
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>PB-06 (kampania kieruje na landing)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
         </is>
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr">
@@ -6953,12 +6953,12 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Test end-to-end „pierwszy klient”</t>
+          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -6973,24 +6973,28 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H80" s="10" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="K80" s="10" t="inlineStr">
@@ -7005,17 +7009,17 @@
       </c>
       <c r="M80" s="11" t="inlineStr">
         <is>
-          <t>wszystkie blokery zamknięte (sprint 8)</t>
+          <t>PB-06 (kampania kieruje na landing)</t>
         </is>
       </c>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
         </is>
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
         </is>
       </c>
       <c r="P80" s="10" t="inlineStr">
@@ -7027,12 +7031,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Runbook startu i decyzja GO</t>
+          <t>Test end-to-end „pierwszy klient”</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -7051,7 +7055,7 @@
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>20</v>
@@ -7079,28 +7083,102 @@
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
+          <t>wszystkie blokery zamknięte (sprint 8)</t>
+        </is>
+      </c>
+      <c r="N81" s="11" t="inlineStr">
+        <is>
+          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+        </is>
+      </c>
+      <c r="O81" s="11" t="inlineStr">
+        <is>
+          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+        </is>
+      </c>
+      <c r="P81" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>PB-12</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>Runbook startu i decyzja GO</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H82" s="10" t="inlineStr"/>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="11" t="inlineStr">
+        <is>
           <t>PB-05 (decyzja GO po przejściu ścieżki na produkcji)</t>
         </is>
       </c>
-      <c r="N81" s="11" t="inlineStr">
+      <c r="N82" s="11" t="inlineStr">
         <is>
           <t>Każdy z 11 blokerów ma wpis: co zrobiono, gdzie jest dowód, kto potwierdził. Bez formuły „warunkowe GO”.</t>
         </is>
       </c>
-      <c r="O81" s="11" t="inlineStr">
+      <c r="O82" s="11" t="inlineStr">
         <is>
           <t>Domknięcie: przegląd wszystkich blokerów z dowodem zamknięcia, decyzja GO/NO-GO zapisana z datą.</t>
         </is>
       </c>
-      <c r="P81" s="10" t="inlineStr">
+      <c r="P82" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P81"/>
-  <conditionalFormatting sqref="E2:E81">
+  <autoFilter ref="A1:P82"/>
+  <conditionalFormatting sqref="E2:E82">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>
@@ -7120,7 +7198,7 @@
       <formula>"ŚREDNI"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P81">
+  <conditionalFormatting sqref="P2:P82">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"zrobione"</formula>
     </cfRule>
@@ -7230,11 +7308,11 @@
         </is>
       </c>
       <c r="F2" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A2)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A2)</f>
         <v/>
       </c>
       <c r="G2" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A2,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A2,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H2" s="10" t="n">
@@ -7275,11 +7353,11 @@
         </is>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A3)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A3)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A3,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A3,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H3" s="10" t="n">
@@ -7291,7 +7369,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziesięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł. X-29 wyszło godzinę po X-28 i z tego samego pytania: skoro reguły są w repo, to czy wdrożenie w ogóle je dowozi? Nie dowoziło — wdrożenie restartowało tylko aplikacje, a Prometheus i Grafana czytają konfigurację wyłącznie przy starcie. H-20 wykonane tu, a nie w sprincie 9: awaria kopii z H-23 wymusiła odtworzenie bazy tu i teraz, więc dowód D4 powstał jedenaście sprintów przed terminem.</t>
+          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziesięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł. X-29 wyszło godzinę po X-28 i z tego samego pytania: skoro reguły są w repo, to czy wdrożenie w ogóle je dowozi? Nie dowoziło — wdrożenie restartowało tylko aplikacje, a Prometheus i Grafana czytają konfigurację wyłącznie przy starcie. H-20 wykonane tu, a nie w sprincie 9: awaria kopii z H-23 wymusiła odtworzenie bazy tu i teraz, więc dowód D4 powstał jedenaście sprintów przed terminem. X-30 wyszło przy sprawdzaniu, czy X-29 faktycznie coś zmieniło: reguły były wczytane i żadna się nie liczyła. Trzeci raz tego dnia to samo pytanie — czy to, co wygląda na zrobione, jest zrobione — i trzeci raz odpowiedź brzmiała nie.</t>
         </is>
       </c>
     </row>
@@ -7320,11 +7398,11 @@
         </is>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A4)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A4)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A4,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A4,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H4" s="10" t="n">
@@ -7365,11 +7443,11 @@
         </is>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A5)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A5)</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A5,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A5,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n">
@@ -7410,11 +7488,11 @@
         </is>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A6)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A6)</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A6,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A6,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n">
@@ -7455,11 +7533,11 @@
         </is>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A7)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A7,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A7,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n">
@@ -7500,11 +7578,11 @@
         </is>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A8)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A8)</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A8,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A8,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n">
@@ -7545,11 +7623,11 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A9)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A9)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A9,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A9,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n">
@@ -7590,11 +7668,11 @@
         </is>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A10)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A10)</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A10,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A10,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n">
@@ -7635,11 +7713,11 @@
         </is>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A11)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A11)</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A11,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A11,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n">
@@ -7680,11 +7758,11 @@
         </is>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A12)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A12)</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A12,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A12,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n">
@@ -7725,11 +7803,11 @@
         </is>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A13)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A13)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A13,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A13,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n">
@@ -7770,11 +7848,11 @@
         </is>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A14)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A14)</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A14,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A14,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n">
@@ -7815,11 +7893,11 @@
         </is>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A15)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A15)</f>
         <v/>
       </c>
       <c r="G15" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A15,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A15,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n">
@@ -7860,11 +7938,11 @@
         </is>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A16)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A16)</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A16,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A16,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n">
@@ -7905,11 +7983,11 @@
         </is>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A17)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A17)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A17,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A17,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n">
@@ -7950,11 +8028,11 @@
         </is>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A18)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A18)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A18,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A18,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n">
@@ -7995,11 +8073,11 @@
         </is>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A19)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A19)</f>
         <v/>
       </c>
       <c r="G19" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A19,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A19,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n">
@@ -8040,11 +8118,11 @@
         </is>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A20)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A20)</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A20,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A20,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n">
@@ -8081,11 +8159,11 @@
         </is>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$81,A21)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A21)</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$81,A21,'Backlog do startu'!$F$2:$F$81)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A21,'Backlog do startu'!$F$2:$F$82)</f>
         <v/>
       </c>
       <c r="H21" s="10" t="n">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$82)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$83)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$82,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$82,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$83,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$83,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$82,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$83,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$82,"zrobione",'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$83,"zrobione",'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md</t>
+          <t>Zamknięte 2026-08-22. Wykryte przy zamykaniu H-23: kopia bazy nie wykonała się ani razu przez ponad miesiąc, a reguła VerrisPostgresBackupStale z severity: critical i progiem 25 h zapaliła się POPRAWNIE — tylko nie miała dokąd. | DWIE POŁOWY JEDNEGO MECHANIZMU, ŻADNA NIE DZIAŁA BEZ DRUGIEJ. Prometheus miał trzynaście reguł (pięć krytycznych) ładowanych przez rule_files i NIE MIAŁ sekcji `alerting:`; w całym repozytorium nie było usługi alertmanager. Grafana miała punkt kontaktowy (dominik@hvln.pl), politykę powiadomień i działający SMTP — i ZERO reguł. | DOKUMENT BYŁ CZĘŚCIĄ PROBLEMU: docs/ops/GRAFANA_ALERTING.md kazał „ręcznie odzwierciedlić progi z pliku YAML". Instrukcja ręcznego przepisania trzynastu progów przez człowieka to opis długu, nie procedura; nikt tego nie zrobił i nie było jak zauważyć, że nie zrobił. | RODZINA: ta sama co X-14, X-23, H-19, H-20, X-27 — kontrola, która melduje zamiast zatrzymywać — tylko o krok dalej. Tam mechanizm istniał i niczego nie bramkował; tu alarm istnieje, działa i nie ma odbiorcy. Sygnał bez odbiorcy jest gorszy od braku sygnału, bo wygląda jak zabezpieczenie. | PRZENIESIONE, NIE SKOPIOWANE. Reguły stoją teraz po stronie Grafany, alerts.yml usunięty, rule_files wycięte, montowanie wyjęte z compose. Skopiowanie dałoby SZÓSTE wystąpienie „bliźniaczych miejsc" (Z-12, Z-16, M-06, X-24, H-24): dwa egzemplarze jednej reguły, jeden poprawiony przy zmianie progu, drugi zapomniany. | UID ŹRÓDŁA DANYCH wpisany wprost — bez niego Grafana nadaje go losowo, a odwołanie do nieistniejącego źródła nie rzuca błędem: panel jest pusty, reguła nie ma czego policzyć. Ten sam cichy tryb awarii co reszta pozycji. | JEDNA REGUŁA INNA OD POZOSTAŁYCH: VerrisPostgresBackupStale ma noDataState: Alerting, reszta OK. Dla dwunastu reguł brak serii poprawnie znaczy „warunek niespełniony"; dla kopii bazy „metryka zniknęła" i „kopia jest świeża" wyglądałyby identycznie — a to jest dokładnie ten przypadek, który kosztował miesiąc. `for: 30m` chroni przed alarmem przy restarcie API. | PRZEPISYWANIE SKRYPTOWE, nie ręczne: trzynaście progów przepisanych palcami to trzynaście okazji na literówkę, której nikt nie sprawdzi. | Czerwieni się na starym kodzie: 26 z 31. Pięć asercji przechodziło i przed poprawką (punkt kontaktowy, polityka) — bo ta połowa naprawdę była w porządku; strażnik, który czerwieni się cały, zwykle sprawdza własną tezę zamiast kodu. | CZEGO NIE DOWODZI: że mail DOCHODZI. To dowód D3 — wymaga zapalonego alertu na produkcji i listu w skrzynce, z datą. Otwarty punkt w docs/ops/GRAFANA_ALERTING.md §3; najtaniej sprawdzić na VerrisSecurityWatchStale (zatrzymać timer na 20 minut). Uznanie pozycji za domkniętą na podstawie samego provisioningu byłoby rozumowaniem zakazanym w tym projekcie. | CZEGO NIE OBEJMUJE: eskalacji i dyżurów (jeden odbiorca, jeden adres — przy jednoosobowym zespole to właściwa wielkość), Slacka (wyłączony do czasu kanału), wyciszeń. Dokumentacja: docs/zadania/X-28-alert-bez-adresata.md | DOWÓD D3 DOSTARCZALNOŚCI — 2026-08-23, dostarczony przez awarię, nie przez test. Przy X-30 reguły z execErrState: Alerting zapaliły się na błędzie ewaluacji i DZIESIĘĆ maili dotarło na dominik@hvln.pl z tematami [FIRING:1] &lt;alertname&gt; &lt;severity&gt; (Verris). Droga Grafana → SMTP → Postfix na panelu → mail.hvln.pl → skrzynka jest potwierdzona na całej długości. | TEN PRZYPADEK POTWIERDZIŁ TRZY RZECZY, KTÓRYCH PLANOWANY TEST JEDNEGO ALERTU BY NIE POTWIERDZIŁ: (1) droga do skrzynki działa; (2) migracja nie pogubiła nazw ani wag — tematy pokazały critical przy VerrisRuntimeErrorsHigh, VerrisOpenMajorIncident, VerrisSecurityWatchFindings i VerrisProvisioningQueueFailed oraz warning przy pozostałych, dokładnie jak w usuniętym alerts.yml; (3) progi `for:` przetrwały migrację — zapaliło się DZIESIĘĆ z trzynastu, a nie zapaliły się dokładnie te trzy z najdłuższym for: VerrisPostgresBackupStale (30 m), VerrisStatusWebhookFailed (30 m) i VerrisSecurityWatchStale (20 m), bo od restartu nie minęło tyle czasu. Skrypt migracyjny mógł te wartości po cichu przekręcić i żaden test w CI by tego nie zobaczył — zobaczyła to skrzynka.</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Z-12</t>
+          <t>X-31</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+          <t>Kanał alertów daje znak życia (dead man's switch)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>X — Infrastruktura jakości</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
@@ -2945,22 +2945,22 @@
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
+          <t>ops/observability/grafana/provisioning/alerting/rules.yaml — grupa verris_kanal_alertow, reguła VerrisKanalAlertowZyje (vector(1), for: 0s, oba stany awaryjne na Alerting, etykieta kanal: heartbeat); policies.yaml — gałąź object_matchers kanal=heartbeat, repeat_interval 24h; apps/api/src/test/routing-alertow.spec.ts (5 asercji X-31); docs/ops/GRAFANA_ALERTING.md §4. BRAK: pierwszego maila [FIRING:1] VerrisKanalAlertowZyje — dowód D3 jeszcze nie powstał.</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
+          <t>Stan 2026-08-23: ZROBIONE W KODZIE (D2), D3 powstanie przy pierwszym mailu. Decyzja właściciela produktu: wariant „jeden mail na dobę". | PROBLEM: po naprawie X-30 alerty ucichną, a cisza będzie znaczyła „nic się nie pali" — i będzie wyglądała IDENTYCZNIE jak: Grafana padła, Postfix przestał przyjmować, mail.hvln.pl zaczął odrzucać albo wrzucać do spamu, ktoś zmienił adres w punkcie kontaktowym, polityka przestała pasować do etykiet. To dokładnie ta sama cisza, która przez miesiąc znaczyła „kopia bazy jest w porządku" (H-23) i kosztowała wszystkie kopie zapasowe. | ROZWIĄZANIE: VerrisKanalAlertowZyje — reguła vector(1), pali się ZAWSZE, jej BRAK jest sygnałem. for: 0s, noDataState: Alerting, execErrState: Alerting — nie da się jej „nie zapalić": normalnie warunek jest spełniony, a gdyby źródło danych przestało odpowiadać, oba stany awaryjne też prowadzą do Alerting. Milczenie ma znaczyć awarię, nigdy spokój. | JEDEN MAIL NA DOBĘ, NIE SZEŚĆ: osobna gałąź polityki na etykiecie kanal: heartbeat z repeat_interval 24h. Na domyślnej (4h) byłoby sześć dziennie, a alert przychodzący sześć razy dziennie przestaje być czytany po tygodniu — wtedy przestaje cokolwiek dawać, bo jego BRAK jest jedyną informacją, jaką niesie. Strażnik pilnuje osobno, że polityka domyślna NIE została przy okazji przestawiona na dobę: prawdziwy alarm ma się przypominać co cztery godziny. | HACZYK, KTÓRY TRZEBA NAZWAĆ: mail, którego się nie czyta, wraca do punktu wyjścia. Jeśli po tygodniu przestanie być zauważany, reguła przestaje działać — nie dlatego, że jest zepsuta, tylko dlatego, że przestała być czytana. Tego nie da się naprawić kodem. | CZEGO NIE OBEJMUJE: awarii całego serwera (heartbeat mieszka na tej samej maszynie co Grafana i milczy razem z nią — odporny byłby watchdog SPOZA naszej infrastruktury, pukany cronem; nie ma go i to świadoma decyzja, nie przeoczenie) ani poprawności pozostałych reguł (tego pilnuje bramka z X-30). | Czerwieni się na starym kodzie: 5 z 36. | Doszła lista DOPISANE_POZNIEJ, trzymana osobno od ALERTY: tamta odpowiada na pytanie „czy migracja czegoś nie zgubiła" i ma zostać zamrożona, ta na „czy ktoś czegoś po cichu nie dołożył". Dokumentacja: docs/zadania/X-31-znak-zycia-kanalu-alertow.md</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Z-13</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>3</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -3065,12 +3065,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Z-16</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>3</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3143,31 +3143,31 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>3</v>
@@ -3189,27 +3189,27 @@
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M31" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
@@ -3221,58 +3221,58 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Z-05</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
+          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr">
@@ -3299,12 +3299,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Z-05</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Anulowanie faktury (VOID) z panelu</t>
+          <t>Odporność webhooka płatności na błąd w trakcie obsługi</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -3319,11 +3319,11 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>4</v>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+          <t>billing.service.ts — zajmijZdarzenie/zakonczZdarzenie/oznaczNieudane/przetworzPonownie; libs/database/prisma/schema.prisma — StripeWebhookEventStatus + payload/attempts/claimedAt/nextAttemptAt; migracja 20260822180000_odpornosc_webhooka; stripe-webhook-ponowienia.scheduler.ts — ponowienia, alerty, retencja; stripe-webhook-events.admin.controller.ts + admin-panel/billing/webhooki — lista i „Ponów"; ops/scripts/uzgodnij-platnosci-stripe.mjs; webhook-ewidencja.spec.ts (27) + test/integration/webhook-odpornosc.int-spec.ts (11)</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
@@ -3363,7 +3363,11 @@
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O33" s="11" t="inlineStr"/>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Zamknięte 2026-08-22. MECHANIZM BŁĘDU: wiersz stripeWebhookEvent powstawał PRZED handlerem i NIE MIAŁ STANU — jego istnienie znaczyło „widziałem", a kod czytał je jako „obsłużyłem", bo ponowna dostawa trafiała w unikalny indeks i dostawała {duplicate:true} + 200. Handler, który rzucił wyjątkiem (timeout bazy, niedostępny MinIO), zostawiał wiersz na miejscu: Stripe ponawiał, dostawał 200, uznawał zdarzenie za doręczone i kończył. Klient zapłacił, saldo się nie pojawiło, system uważał zdarzenie za obsłużone. Awaria CICHA i JEDNOKIERUNKOWA — żadna z tych rzeczy nie jest błędem z osobna, więc nic nie krzyczało. | ROZWIĄZANIE: wiersz dostaje stan (PENDING → PROCESSED albo → FAILED → ponowienie). PENDING znaczy „zajęte, w trakcie", nie „obsłużone"; dopiero PROCESSED odrzuca ponowienia. | CZTERY DECYZJE: (1) handler, który padł, propaguje wyjątek — endpoint zwraca 5xx i Stripe ponawia; odpowiedź 200 z zapisanym błędem byłaby wygodniejsza w logach i stworzyłaby ten sam błąd od nowa. (2) Dostawa trafiająca na zdarzenie właśnie obsługiwane dostaje 409, nie „duplikat" — tamta dostawa może paść. (3) DZIERŻAWA: proces ubity między zajęciem a zakończeniem zostawia PENDING, którego nikt by nie ruszył — ta sama pułapka co przed Z-05 pod inną nazwą; PENDING starszy niż 5 min wolno przejąć. (4) Treść zdarzenia zapisujemy u siebie, bo pobieranie ze Stripe'a przy ponowieniu wymaga żywego Stripe'a, a Stripe leżący to dokładnie ta sytuacja, w której webhooki padają; retencja czyści treść 90 dni po przetworzeniu, id i status zostają na zawsze. | Ponowienia automatyczne 1→5→15→60 min. Alert do adminów po 3 próbach ALBO 15 minutach — dwa progi, bo handler wywalający się natychmiast daje dużo prób w krótkim czasie, a wiszący na timeoucie mało prób przy upływającym czasie; jeden próg przespałby drugi kształt awarii. | PANEL: lista zaciętych zdarzeń i przycisk „Ponów" (macierz opisała stan sprzed zmiany jako „odzysk wyłącznie ręcznie w bazie"). | CZEGO MIGRACJA NIE ROBI: oznacza wiersze historyczne jako PROCESSED, i to jest ZAŁOŻENIE, nie ustalenie — stary wiersz nie miał ani treści, ani id sesji, więc nie ma jak skorelować go z transakcją portfela. Odpowiedź na przeszłość to ops/scripts/uzgodnij-platnosci-stripe.mjs: pyta Stripe'a o opłacone sesje i sprawdza, czy dla każdej istnieje transakcja z kluczem stripe:checkout:&lt;id&gt;. Świadomie NIE księguje automatycznie — ruch pieniędzy na podstawie skryptu z konsoli powinien mieć po drugiej stronie człowieka i wpis w audycie. Kontrola miesięczna, nie narzędzie awaryjne. | Czerwieni się na starym kodzie: przywrócenie semantyki „istnienie wiersza == obsłużone" daje 3 czerwone z 11 integracyjnych, w tym „PONOWIENIE PO AWARII KSIĘGUJE PORTFEL". | Strażnik po raz PIĄTY trafił nie w to, co trzeba — endsWith('billing.service.ts') łapało autoscaling/autoscaling-billing.service.ts. Po „jest" (X-17), archiver.create (X-21) i --audit-level (X-23) reguła rośnie: strażnik czytający repozytorium dopasowuje DOKŁADNIE — ścieżkę, nie sufiks; kod, nie prozę. | CZEGO NIE ROBI: ponowienie może wysłać drugi mail (księgowanie idempotentne, wysyłka nie — dwa maile tańsze niż nieksięgowana wpłata); nie obejmuje webhooków DirectAdmina i KSeF-a; brak D3, bo wymaga produkcji — dopisane do PB-12. Zgodnie z regułą „pieniądze wymagają D3" pozycja jest domknięta jako BLOKER, nie jako dowód produkcyjny. | Weryfikacja: 484 testy jednostkowe, 26 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8, asercja SQL po migracji. Dokumentacja: docs/zadania/Z-05-odpornosc-webhooka-platnosci.md</t>
+        </is>
+      </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3373,12 +3377,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>C-18</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Konto FTP — zmiana hasła</t>
+          <t>Anulowanie faktury (VOID) z panelu</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -3388,7 +3392,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -3424,24 +3428,20 @@
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
+          <t>InvoiceStatus.VOID w schema.prisma:1354 nigdy nie ustawiany</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
-      <c r="O34" s="11" t="inlineStr">
-        <is>
-          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
-        </is>
-      </c>
+      <c r="O34" s="11" t="inlineStr"/>
       <c r="P34" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -3451,12 +3451,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>C-18</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Faktura VAT dla płatności portfelem (część)</t>
+          <t>Konto FTP — zmiana hasła</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -3466,48 +3466,48 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
+          <t>WYSOKA</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
-        </is>
-      </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
+          <t>brak jakiejkolwiek ścieżki edycji istniejącego konta</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
@@ -3607,12 +3607,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Faktura VAT dla płatności portfelem (część)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -3622,16 +3622,16 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>6</v>
@@ -3653,17 +3653,17 @@
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>wallet-ledger.service.ts:applyEntry — faktura wystawiana w TEJ SAMEJ transakcji co obciążenie; faktura-za-portfel.ts — trybFaktury/rozbicieVat/pozycjeZbiorcze/pozycjeReczne/nadajNumerFaktury; faktury.scheduler.ts — dokańczanie z ponawianiem, alerty, faktury zbiorcze 1. dnia miesiąca; invoices.service.ts — wystawReczna(), dokonczFakture(), numeracja współdzielona; invoices.admin.controller.ts — POST /reczna i POST /:id/dokoncz; admin-panel/(dashboard)/invoices/reczna — formularz; migracja 20260822200000_faktura_za_portfel; faktura-za-portfel.spec.ts (29) + wallet-ledger.service.spec.ts (+3) + test/integration/faktura-portfel.int-spec.ts (14) + asercja SQL Z-01</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>X-01 (bez CI nie ma jak potwierdzić tej zmiany)</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Zamknięte 2026-08-22. TRZYNAŚCIE MIEJSC, NIE CZTERY: macierz wymieniała cztery wywołania debit(), a jest ich trzynaście (domeny, dodatki, autoskalowanie, VPS ×2, monitoring ×2, trial, subskrypcje ×3, odnowienia). To nie zarzut wobec macierzy, tylko dowód, że lista miejsc, w których rusza się pieniądz, rozjeżdża się z rzeczywistością szybciej, niż ktokolwiek ją aktualizuje — tu o 225% w dwa dni. | ROZWIĄZANIE: reguła w JEDNYM miejscu, w księdze portfela, czyli tam, gdzie i tak jako jedyne miejsce zmienia się saldo. Dopisanie wystawiania faktury w trzynastu miejscach byłoby czwartym wystąpieniem wzorca, który wyprodukował już Z-12, Z-16 i błąd w plan-change: dwie kopie tej samej reguły, jedna poprawiona, druga zapomniana. | MODEL: abonament, zmiana planu, domena, VPS, monitoring od 5 zł → faktura od razu; autoskalowanie (zawsze) i drobne zużycie poniżej 5 zł → jedna faktura zbiorcza 1. dnia następnego miesiąca, z pozycjami. Rozdział jest arytmetyczny: autoskalowanie obciąża co blok kilkunastominutowy, więc faktura za każde obciążenie to kilkadziesiąt dokumentów miesięcznie na klienta. | DOŁADOWANIE nie dostaje faktury — to wpłata na poczet usług, VAT powstaje przy świadczeniu. To DECYZJA, nie fakt: do potwierdzenia z księgową, patrz M-34. | ATOMOWOŚĆ: wiersz faktury powstaje w tej samej transakcji co ruch pieniądza; PDF, MinIO, KSeF i mail dowozi scheduler z ponawianiem (lekcja z Z-05). | TEST, KTÓRY ZA PIERWSZYM RAZEM NIC NIE DOWODZIŁ: pierwsza wersja testu atomowości sprawdzała odrzucone obciążenie i przechodziła RÓWNIEŻ wtedy, gdy faktura powstawała poza transakcją — bo skoro obciążenie rzuciło, do wystawiania i tak nie dochodziło. Sprawdzone realnie: przeniosłem wystawianie za transakcję i zestaw został zielony. Test, który przechodzi na obu wersjach kodu, nie mówi nic o żadnej z nich. Właściwy test wywala SAMO wystawianie (podłożony numer kolidujący) i wtedy widać różnicę: w transakcji saldo wraca do 100,00, poza transakcją spada do 55,00 przy braku dokumentu — czyli Z-01 z powrotem. | NUMERACJA: allocateInvoiceNumber przeniesiony do wspólnego modułu, bo numeru potrzebuje też księga portfela. Druga kopia oznaczałaby dwie serie rozjeżdżające się przy pierwszym równoległym wystawieniu (art. 106e ust. 1 pkt 2). Test integracyjny wystawia osiem faktur równolegle i sprawdza ciągłość numerów. | PRZY OKAZJI NAPRAWIONA STARA DZIURA: finalizeAsVerrisInvoice była wołana raz, z .catch(log) — błąd generowania PDF-u kończył się linijką w logu i fakturą bez pliku, także dla faktur ze Stripe'a. Teraz ponawianie 2→10→30→120 min i alert po 3 próbach. Licznik prób rośnie PRZED wywołaniem, bo rosnąc po błędzie nie rósłby przy awarii ubijającej proces i alert nigdy by nie padł. | FAKTURA RĘCZNA: POST /admin/billing/invoices/reczna + formularz. Kwoty brutto (jak w cenniku), powód wystawienia wymagany i trafia do audytu, nie na fakturę. Zakres: dokument opłacony; faktura z terminem płatności to inna funkcja i celowo jej nie ma. | ARYTMETYKA: VAT jest RESZTĄ po odjęciu netto od brutto, nie osobnym zaokrągleniem — liczony niezależnie potrafi dać sumę różniącą się o grosz, a faktura, która się nie sumuje, jest wadliwa. Niezmiennik sprawdzany na 28 572 kwotach, nie na trzech przykładach; kod produkcyjny faktury zbiorczej RZUCA, gdy pozycje nie sumują się do kwoty. | Czerwieni się na starym kodzie w trzech wariantach: bez wystawiania w księdze 6 z 14, przy wystawianiu poza transakcją 1 z 14, przy niespójnym netto+VAT — asercja SQL. | CZEGO NIE ROBI: brak korekt (M-06), brak faktury z terminem płatności, brak podglądu zbiorczej przed wystawieniem, brak D3 (wymaga produkcji — dopisane do PB-12). | Weryfikacja: 516 testów jednostkowych, 40 integracyjnych, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/Z-01-faktura-za-platnosc-portfelem.md</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
@@ -3685,27 +3685,27 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
@@ -3731,27 +3731,27 @@
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L38" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N38" s="11" t="inlineStr">
         <is>
-          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
@@ -3763,73 +3763,73 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>FAKTURA KORYGUJĄCA (część)</t>
+          <t>Procedura obsługi nadużyć (abuse) — dokument</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
+          <t>WYSOKI</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Dokument w ops/docs z właścicielem i czasami reakcji. Test: zgłoszenie wysłane na abuse@ trafia do kogoś i ma odpowiedź w deklarowanym czasie.</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
+          <t>Adres abuse@ obsługiwany, ścieżka od zgłoszenia do reakcji, czasy reakcji, kto decyduje o zawieszeniu, wzory odpowiedzi do CERT i rejestratorów.</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
@@ -3877,12 +3877,12 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
@@ -3919,31 +3919,31 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
+          <t>FAKTURA KORYGUJĄCA (część)</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>8</v>
@@ -3965,27 +3965,27 @@
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>korekta-faktury.ts — bladKorygowalnosci/przeliczKorekte/korektaFormalna/kwotaDoZwrotu; korekty.service.ts — wystawianie ze zwrotem w tej samej transakcji; wallet-ledger.service.ts — zapiszWpis(tx, …) wydzielone, jedno miejsce zmieniające saldo; ksef/fa3-xml.builder.ts — RodzajFaktury KOR + DaneFaKorygowanej + PrzyczynaKorekty; invoice-pdf.service.ts — układ korekty (przed/po/różnica); invoices.admin.controller.ts — POST /:id/korekta i GET /:id/korekty; admin-panel/(dashboard)/invoices/[invoiceId]/korekta — formularz; migracja 20260822220000_faktura_korygujaca (seria VFK + 2 ograniczenia CHECK); korekta-faktury.spec.ts (18) + fa3-xml.builder.spec.ts (+7) + test/integration/korekta.int-spec.ts (13) + asercja SQL M-06</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Z-01 (korekta korzysta z tej samej ścieżki wystawiania)</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
+          <t>Zamknięte 2026-08-22. Macierz wskazywała trzy różne braki i wszystkie były prawdziwe: zero wystąpień korekty w kodzie i schemacie, RodzajFaktury=VAT na sztywno w builderze KSeF-a, brak drogi wewnątrz systemu. | DWA RODZAJE: WARTOŚCIOWA zmienia kwoty (zwrot, rezygnacja, rabat) i przy różnicy ujemnej zwraca do portfela; FORMALNA poprawia dane nabywcy, kwoty bez zmian, różnica zero. | W `amount` korekty siedzi RÓŻNICA ZE ZNAKIEM, nie nowa kwota — to ona wchodzi do rejestru VAT i to ona mówi, ile pieniędzy się rusza. Kwota po korekcie odtwarza się z dwóch pól: correctedAmount + amount. Trzymanie w `amount` nowej kwoty wyglądałoby naturalniej i psuło sumowanie rejestru, asercję netto+VAT=brutto oraz oczywistość kierunku pieniędzy. | ZWROT W TEJ SAMEJ TRANSAKCJI co dokument. Wymagało wydzielenia z applyEntry metody zapiszWpis(tx, …) działającej wewnątrz podanej transakcji — nie da się otworzyć transakcji w transakcji, a druga kopia blokowania wiersza byłaby PIĄTYM wystąpieniem wzorca bliźniaczych miejsc. Miejsce zmieniające saldo nadal jedno. | KOREKTA W GÓRĘ NIE RUSZA PORTFELA — dopłata to zobowiązanie klienta, nie automatyczne pobranie; ściąganie pieniędzy przy korekcie zwiększającej byłoby obciążeniem bez zamówienia. | OSOBNA SERIA VFK: InvoiceCounter dostał kolumnę series i klucz (series, year, month). Test sprawdza, że wystawienie korekty nie rusza licznika faktur. | NAJGROŹNIEJSZE ZNALEZISKO: korekta wysłana do KSeF-a z RodzajFaktury=VAT zostałaby przyjęta jako NOWA SPRZEDAŻ, nie jako zmiana poprzedniej — czyli PODWOIŁABY PRZYCHÓD w rejestrze, milcząco, bo dokument jest formalnie poprawny. Teraz KOR + DaneFaKorygowanej + PrzyczynaKorekty, a builder ODMAWIA zbudowania korekty bez numeru pierwotnej albo bez przyczyny. | REGUŁY W BAZIE: dwa ograniczenia CHECK (korekta musi mieć correctedId/correctionKind/correctionReason; correctedId &lt;&gt; id), bo kod można obejść nowym serwisem, a ograniczeń nie. Bez drugiego jeden błąd w serwisie tworzyłby dokument odsyłający do siebie i pętlę przy liczeniu kwoty po korekcie. | ŚWIADOMIE NIE MA: korekty do korekty (dokument odnosiłby się do dokumentu, który sam już coś zmienia — odmowa jest uczciwsza niż dokument, którego nie umiem policzyć) ani anulowania faktury (w polskim prawie faktury w obrocie się nie anuluje, koryguje do zera — a to ten mechanizm już potrafi). | PRZY OKAZJI ZNALEZIONY BŁĄD: formularz faktury ręcznej z Z-01 wołał /admin/billing/invoices/reczna zamiast /admin/invoices/reczna. Kod się kompilował, testy przechodziły, panel się budował — 404 wyszłoby pod palcem operatora. Stąd X-24. | Czerwieni się na starym kodzie: RodzajFaktury na sztywno → 4 z 20 w builderze; zła ścieżka panelu → 1 z 5 w strażniku; korekta bez faktury pierwotnej → CHECK + asercja SQL. | CZEGO NIE ROBI: brak zmiany stawki VAT na korekcie (wszystko 23%), brak osobnego powiadomienia o zwrocie, brak D3 (wymaga produkcji — PB-12). | Weryfikacja: 546 testów jednostkowych, 53 integracyjne, lint 7/7 (0 błędów), typecheck 8/8. Dokumentacja: docs/zadania/M-06-faktura-korygujaca.md</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
@@ -3997,58 +3997,58 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Podpisane DPA z subprocesorami (część)</t>
+          <t>Onboarding produkcyjnego węzła #1 (EX63)</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>P — Zgodność</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="G42" s="10" t="n">
-        <v>9</v>
-      </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+          <t>Faza 1 — Rozliczenia i dowód odtworzenia</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="N42" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Węzeł przechodzi wszystkie 14 checków live-readiness. /etc/verris-backup.conf istnieje, pierwszy backup off-site wykonany i zaraportowany do control-plane.</t>
         </is>
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
+          <t>Pełny przebieg node-onboard-live.sh na docelowym serwerze, z konfiguracją backupu off-site jako krokiem obowiązkowym.</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Dodatkowy użytkownik bazy — utworzenie</t>
+          <t>Podpisane DPA z subprocesorami (część)</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4090,50 +4090,50 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>D — Bazy danych</t>
+          <t>P — Zgodność</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>docs/legal/dpa-subprocessors-tracking.md — wszystkie pozycje w statusie „do podpisania” lub „do akceptacji”, kolumna Data pusta</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G43" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L43" s="11" t="inlineStr">
-        <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
-        </is>
-      </c>
-      <c r="M43" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
           <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>POTWIERDZONE jako bloker, dowód poprawiony: tracker istnieje (wcześniejszy zapis „brak w repo” był fałszywy), ale ani jedno DPA nie jest podpisane — Stripe, dostawca VPS, dostawca backupu off-site, OpenProvider. Bez tego DPA podpisywane z klientem jest niekompletne.</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
@@ -4153,12 +4153,12 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — usunięcie</t>
+          <t>Dodatkowy użytkownik bazy — utworzenie</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users; serwis directadmin.service.ts:1900</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="11" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Nie było to martwe UI, tylko niedokończona praca z 25–26.07 — brakowało samego kontrolera. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -4231,12 +4231,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — zmiana hasła</t>
+          <t>Użytkownik bazy — usunięcie</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/remove; serwis directadmin.service.ts:1925</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Użytkownik bazy — lista</t>
+          <t>Użytkownik bazy — zmiana hasła</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
+          <t>services.controller.ts — POST /services/:id/hosting-db-users/password; serwis directadmin.service.ts:1945</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr">
@@ -4387,12 +4387,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>phpMyAdmin — auto-logowanie (SSO)</t>
+          <t>Użytkownik bazy — lista</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
+          <t>services.controller.ts — GET /services/:id/hosting-db-users</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="N47" s="11" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P47" s="10" t="inlineStr">
@@ -4465,12 +4465,12 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
+          <t>phpMyAdmin — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -4480,19 +4480,19 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>F — DNS</t>
+          <t>D — Bazy danych</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
@@ -4501,22 +4501,22 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>ATRAPA</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url; directadmin.service.ts:1977</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="N48" s="11" t="inlineStr">
         <is>
-          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+          <t>Cichy fallback „Auto-logowanie niedostępne" (DatabasesTab.tsx:65) sprawiał, że nikt tego nie zgłaszał — dlatego strażnik tras jest ważniejszy niż pojedynczy test. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr">
@@ -4543,12 +4543,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SRV / CAA</t>
+          <t>Edytor rekordów DNS (A/CNAME/MX/TXT)</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>dns-manager.tsx:79,91 — komponent osierocony; dns/page.tsx:15 przekierowuje gdzie indziej</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>F-01 (ten sam edytor)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="11" t="inlineStr">
@@ -4607,7 +4607,11 @@
           <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
         </is>
       </c>
-      <c r="O49" s="11" t="inlineStr"/>
+      <c r="O49" s="11" t="inlineStr">
+        <is>
+          <t>Skorygowane: obejściem jest link do DirectAdmina (services.controller.ts:350) z poświadczeniami z „dane dostępowe”. Uwaga — SSO nie działa, trasa hosting-sso-url nie istnieje w API, więc klient trafia do obcego panelu i loguje się ręcznie.</t>
+        </is>
+      </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4617,12 +4621,12 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>E-14</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Webmail — auto-logowanie (SSO)</t>
+          <t>Rekordy SRV / CAA</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -4632,12 +4636,12 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>F — DNS</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
@@ -4663,29 +4667,25 @@
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>DZIAŁA</t>
+          <t>ATRAPA</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-01 (ten sam edytor)</t>
         </is>
       </c>
       <c r="N50" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O50" s="11" t="inlineStr">
-        <is>
-          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
-        </is>
-      </c>
+          <t>Kontroler rejestruje trasę, którą woła panel; kliknięcie kończy się realnym efektem, nie 404. Test pokrywa ścieżkę UI→API→zasób.</t>
+        </is>
+      </c>
+      <c r="O50" s="11" t="inlineStr"/>
       <c r="P50" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -4695,12 +4695,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-14</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Zmiana wersji PHP per domena</t>
+          <t>Webmail — auto-logowanie (SSO)</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>B — Runtime WWW</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
+          <t>services.controller.ts — POST /services/:id/hosting-sso-url (wspólna trasa z D-11); MailTab.tsx:68</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
+          <t>Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
@@ -4773,12 +4773,12 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Rekordy SPF — kreator</t>
+          <t>Zmiana wersji PHP per domena</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4788,19 +4788,19 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>E — Poczta</t>
+          <t>B — Runtime WWW</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
@@ -4809,22 +4809,22 @@
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:114</t>
+          <t>services.controller.ts — GET/POST /services/:id/hosting-domain-php; directadmin.service.ts:2058</t>
         </is>
       </c>
       <c r="M52" s="11" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="N52" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
+          <t>Decyzja produktowa: ustawienie per domena wygrywa nad ustawieniem konta, a UI musi to pokazywać — php-client.tsx wypisuje domeny z własną wersją PHP przy karcie konta. Zamknięte 2026-08-21 (commit 6f2833d). Strażnik: apps/api/src/test/ui-routes-coverage.spec.ts porównuje wszystkie wywołania apiFetch z panelu ze wszystkimi trasami API — nawrót tej klasy błędu zapala test.</t>
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr">
@@ -4851,12 +4851,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>E-16</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Rekordy DKIM — konfiguracja</t>
+          <t>Rekordy SPF — kreator</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>E-15 (ten sam panel dostarczalności)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N53" s="11" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>j.w.</t>
+          <t>deliverability-panel.tsx:26 to komponent osierocony — nikt go nie importuje</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
@@ -4929,12 +4929,12 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>E-17</t>
+          <t>E-16</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Rekord DMARC — konfiguracja</t>
+          <t>Rekordy DKIM — konfiguracja</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="M54" s="11" t="inlineStr">
         <is>
-          <t>E-15</t>
+          <t>E-15 (ten sam panel dostarczalności)</t>
         </is>
       </c>
       <c r="N54" s="11" t="inlineStr">
@@ -5007,12 +5007,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>E-05</t>
+          <t>E-17</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
+          <t>Rekord DMARC — konfiguracja</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -5053,27 +5053,27 @@
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
+          <t>services.controller.ts:114</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>E-15</t>
         </is>
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
+          <t>j.w.</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>M-26</t>
+          <t>E-05</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Usunięcie zapisanej karty przez klienta</t>
+          <t>Zmiana quoty ISTNIEJĄCEJ skrzynki</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>E — Poczta</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
+          <t>hosting-email-actions.ts:41 zachowuje starą quotę</t>
         </is>
       </c>
       <c r="M56" s="11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>wymóg konsumencki</t>
+          <t>brak jakiejkolwiek ścieżki edycji — klient musi usunąć i odtworzyć skrzynkę</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
@@ -5163,12 +5163,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>A-25</t>
+          <t>M-26</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Ręczne zawieszenie usługi przez operatora</t>
+          <t>Usunięcie zapisanej karty przez klienta</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -5190,7 +5190,7 @@
         <v>6</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
@@ -5199,22 +5199,22 @@
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:192</t>
+          <t>billing.controller.ts:38 tylko GET, brak DELETE</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
+          <t>wymóg konsumencki</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
@@ -5241,12 +5241,12 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>A-25</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Ręczne odwieszenie usługi przez operatora</t>
+          <t>Ręczne zawieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>subscriptions.admin.controller.ts:210</t>
+          <t>subscriptions.admin.controller.ts:192</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>A-25 (ten sam widok)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="11" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
+          <t>Skorygowane: endpoint działa i jest osiągalny (curl + DirectAdmin), auto-suspend za brak płatności działa. Brakuje UI, nie możliwości zatrzymania szkody.</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
@@ -5319,12 +5319,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>N-07</t>
+          <t>A-26</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Ręczne tworzenie incydentu na status page</t>
+          <t>Ręczne odwieszenie usługi przez operatora</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
+          <t>subscriptions.admin.controller.ts:210</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A-25 (ten sam widok)</t>
         </is>
       </c>
       <c r="N59" s="11" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>w kryzysie nie ma jak zakomunikować awarii</t>
+          <t>Skorygowane: jak A-25, endpoint subscriptions.admin.controller.ts:210 działa z chargeRenewal.</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
@@ -5397,12 +5397,12 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>N-14</t>
+          <t>N-07</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
+          <t>Ręczne tworzenie incydentu na status page</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="L60" s="11" t="inlineStr">
         <is>
-          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
+          <t>product-ops.admin.controller.ts:371; brak UI tworzenia</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
+          <t>w kryzysie nie ma jak zakomunikować awarii</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
@@ -5475,12 +5475,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>H-22</t>
+          <t>N-14</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Panel odtwarzania w widocznym miejscu</t>
+          <t>Cordon wysyłki poczty (auto-blokada spamu)</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>H — Backup i odtwarzanie</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
+          <t>outbound-cordon.admin.controller.ts:20,25,32; zero „cordon” w admin-panel</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>klient w kryzysie tego nie znajdzie</t>
+          <t>mechanizm działa, operator nie może go zobaczyć ani zdjąć</t>
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>H-09</t>
+          <t>H-22</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
+          <t>Panel odtwarzania w widocznym miejscu</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -5580,7 +5580,7 @@
         <v>6</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
@@ -5589,12 +5589,12 @@
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K62" s="10" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
-          <t>hosting-restore.service.ts:167</t>
+          <t>panel off-site siedzi w zakładce „Usage”, nie „Kopie zapasowe” (page.tsx:74,128,313,319)</t>
         </is>
       </c>
       <c r="M62" s="11" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
+          <t>klient w kryzysie tego nie znajdzie</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr">
@@ -5631,12 +5631,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>H-17</t>
+          <t>H-09</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
+          <t>Kopia bezpieczeństwa przed odtworzeniem</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -5677,27 +5677,27 @@
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>CZĘŚCIOWE</t>
         </is>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
+          <t>hosting-restore.service.ts:167</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
+          <t>OSŁABIONE: hosting-restore.service.ts:167 tylko KOLEJKUJE backup w DA i nie czeka na wynik — destrukcyjne odtworzenie rusza mimo nieudanej kopii. Job dostaje COMPLETED (:182) w chwili przyjęcia zadania, nie po odtworzeniu.</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
@@ -5709,12 +5709,12 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>G-20</t>
+          <t>H-17</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Ochrona przed atakiem słownikowym na panel</t>
+          <t>Tryb restore skryptu odtwarzającego osiągalny z produktu</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>G — SSL i bezpieczeństwo</t>
+          <t>H — Backup i odtwarzanie</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
@@ -5755,27 +5755,27 @@
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
-          <t>rate-limit.guard.ts — ZERO testów</t>
+          <t>node-account-restore.sh:82-99 ma tryb restore; offsite-restore.service.ts:94 przyjmuje wyłącznie list|fetch</t>
         </is>
       </c>
       <c r="M64" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>H-20 (najpierw potwierdzone odtworzenie, potem wystawienie trybu w produkcie)</t>
         </is>
       </c>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>brak dowodu D2 na krytycznym guardzie</t>
+          <t>Skorygowane: tryb restore jest martwy z poziomu produktu, ale żywy z CLI (node-account-restore.sh:120-124) i udokumentowany w runbooku.</t>
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr">
@@ -5787,12 +5787,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>I-11</t>
+          <t>G-20</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Staging — publikacja na produkcję</t>
+          <t>Ochrona przed atakiem słownikowym na panel</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>I — Aplikacje i WordPress</t>
+          <t>G — SSL i bezpieczeństwo</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>services.controller.ts:187</t>
+          <t>rate-limit.guard.ts — ZERO testów</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
+          <t>brak dowodu D2 na krytycznym guardzie</t>
         </is>
       </c>
       <c r="P65" s="10" t="inlineStr">
@@ -5865,27 +5865,27 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>I-11</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
+          <t>Staging — publikacja na produkcję</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>I — Aplikacje i WordPress</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
@@ -5911,27 +5911,27 @@
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>services.controller.ts:187</t>
+        </is>
+      </c>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O66" s="11" t="inlineStr">
         <is>
-          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
+          <t>OSŁABIONE: node-staging-sync.sh:141-142 backup plików jest twardą bramką, ale :152-153 backup bazy LIVE jest best-effort — linia 158 robi wp db import na produkcji mimo braku kopii.</t>
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr">
@@ -5943,73 +5943,73 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>N-16</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>SLA z zapisanymi kredytami</t>
+          <t>Decyzja: własny KSeF czy integracja z programem księgowym</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>N — Wsparcie i ops</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Faza 3 — Wejście na rynek</t>
+          <t>Faza 2 — Odzyskanie funkcji-widm i luki pierwszego tygodnia</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>FLAGA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+          <t>Decyzja zapisana w repo z uzasadnieniem i datą. Jeśli wybrana integracja — sprint 18 zmienia zakres z dokończenia modułu na wdrożenie eksportu do programu księgowego. Decyzja musi zapaść przed sprintem 18, inaczej blokuje start.</t>
         </is>
       </c>
       <c r="O67" s="11" t="inlineStr">
         <is>
-          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+          <t>Porównać dwie ścieżki: dokończenie własnego modułu KSeF (tryb offline, walidacja XSD, UPO) kontra przekazanie fakturowania do programu księgowego z gotową integracją KSeF. Kryteria: koszt, czas, ryzyko zgodności, kto odpowiada za błąd wysyłki, co się dzieje przy awarii MF.</t>
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr">
@@ -6021,12 +6021,12 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>N-16</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Wyszukiwarka wolnych domen</t>
+          <t>SLA z zapisanymi kredytami</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>A — Domeny i konta</t>
+          <t>N — Wsparcie i ops</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>domains.controller.ts:54</t>
+          <t>sla-credit.scheduler.ts:79 — if (!policy.enabled) return; SLA_CREDITS_ENABLED default '0' (platform-settings.keys.ts:116)</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-03 (kredyty SLA muszą być zgodne z opublikowanym regulaminem)</t>
         </is>
       </c>
       <c r="N68" s="11" t="inlineStr">
@@ -6085,7 +6085,11 @@
           <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
         </is>
       </c>
-      <c r="O68" s="11" t="inlineStr"/>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>OSŁABIONE: funkcja jest domyślnie martwa, a live-readiness nie ma checka SLA — flaga może zostać wyłączona bez żadnego sygnału. Regulamin obiecuje kredyty, kod ich nie nalicza.</t>
+        </is>
+      </c>
       <c r="P68" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -6095,12 +6099,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Spakowanie do archiwum</t>
+          <t>Wyszukiwarka wolnych domen</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -6110,12 +6114,12 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>C — Pliki, FTP, SSH, Git</t>
+          <t>A — Domeny i konta</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
@@ -6141,12 +6145,12 @@
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>FLAGA</t>
         </is>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>files.service.ts:320 — tylko extract</t>
+          <t>domains.controller.ts:54</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
@@ -6156,14 +6160,10 @@
       </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
-        </is>
-      </c>
-      <c r="O69" s="11" t="inlineStr">
-        <is>
-          <t>standard we wszystkich panelach</t>
-        </is>
-      </c>
+          <t>Wartość domyślna włączona albo check w live-readiness pilnuje konfiguracji — flaga nie może po cichu wyłączyć funkcji.</t>
+        </is>
+      </c>
+      <c r="O69" s="11" t="inlineStr"/>
       <c r="P69" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
@@ -6173,31 +6173,31 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
+          <t>Spakowanie do archiwum</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>C — Pliki, FTP, SSH, Git</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G70" s="10" t="n">
         <v>15</v>
@@ -6219,27 +6219,27 @@
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
+          <t>BRAK</t>
+        </is>
+      </c>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>files.service.ts:320 — tylko extract</t>
+        </is>
+      </c>
+      <c r="M70" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N70" s="11" t="inlineStr">
         <is>
-          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
+          <t>standard we wszystkich panelach</t>
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Finalizacja dokumentów prawnych 1.0.0</t>
+          <t>Bus factor: drugi kanał alertów i procedura zastępstwa</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
@@ -6287,12 +6287,12 @@
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
+          <t>Alert testowy dociera dwoma kanałami. Dokument zastępstwa zawiera dostęp awaryjny i listę rzeczy, które muszą się dziać codziennie.</t>
         </is>
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
+          <t>Alerty na więcej niż jeden adres, przetestowane. Dokument: co robi ktoś inny, gdy Ciebie nie ma przez tydzień.</t>
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr">
@@ -6329,12 +6329,12 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Treści i cennik na verris.pl</t>
+          <t>Finalizacja dokumentów prawnych 1.0.0</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>BLOKER BIZNESOWY</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="M72" s="11" t="inlineStr">
         <is>
-          <t>PB-01 (cennik zależy od unit economics)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
+          <t>Wszystkie dokumenty w statusie opublikowanym z numerem wersji i datą. Panel /legal nie pokazuje ani jednego „Dokument w przygotowaniu”.</t>
         </is>
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
+          <t>Regulamin, polityka prywatności, SLA, DPA, polityka cookies — wyjście z DRAFT-u, wersjonowanie i publikacja w panelu.</t>
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Landing /przenies-strone</t>
+          <t>Treści i cennik na verris.pl</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -6434,7 +6434,7 @@
         <v>16</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
@@ -6463,17 +6463,17 @@
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
+          <t>PB-01 (cennik zależy od unit economics)</t>
         </is>
       </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
+          <t>Cennik zgodny z wynikiem PB-01. Specyfikacja techniczna publiczna, jak u cyber_Folks — to jest element zaufania, którego rynek oczekuje.</t>
         </is>
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
+          <t>Strona główna, cennik, specyfikacja techniczna pakietu, strona SLA. Narracja: cena stała, bez skoku po roku.</t>
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr">
@@ -6485,12 +6485,12 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
+          <t>Landing /przenies-strone</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKI</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
@@ -6541,17 +6541,17 @@
       </c>
       <c r="M74" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PB-07 (landing korzysta z ustalonego cennika)</t>
         </is>
       </c>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
+          <t>Strona opublikowana, pomiar działa, formularz i CTA prowadzą do rejestracji. Żadne twierdzenie na stronie nie jest oznaczone w macierzy jako LUKA lub ATRAPA.</t>
         </is>
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
+          <t>Strona docelowa kampanii Google Ads na osi migracji. Treść oparta na realnych przewagach z audytu, nie na obietnicach.</t>
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr">
@@ -6563,34 +6563,34 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>M-17</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>KSeF — walidacja XSD przed wysyłką</t>
+          <t>Pomiar: Consent Mode v2 + GTM + dedup event_id</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>audyt</t>
+          <t>poza audytem</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>Praca spoza audytu</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>BLOKER STARTU</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
@@ -6599,37 +6599,37 @@
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Zdarzenie zakupu dociera raz, nie dwa. Consent Mode nie blokuje pomiaru po zgodzie. Zweryfikowane w GTM Preview i w raporcie.</t>
         </is>
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>smoke na api-test MF nie został wykonany</t>
+          <t>Wdrożenie ustaleń z audytu pomiaru: www linkuje, panel działa, deduplikacja po event_id, cookie Domain=.verris.pl.</t>
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr">
@@ -6641,12 +6641,12 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>M-16</t>
+          <t>M-17</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>KSeF — tryb offline/awaryjny</t>
+          <t>KSeF — walidacja XSD przed wysyłką</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G76" s="10" t="n">
         <v>18</v>
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
+          <t>fa3-xml.builder.ts składa XML stringowo; komentarz ksef-v2.client.ts:61-62 sam to wskazuje</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr">
         <is>
-          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
+          <t>M-16 (najpierw obsługa awarii, potem walidacja schematu)</t>
         </is>
       </c>
       <c r="N76" s="11" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
+          <t>smoke na api-test MF nie został wykonany</t>
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr">
@@ -6719,12 +6719,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>M-15</t>
+          <t>M-16</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>KSeF — pobranie UPO przez operatora</t>
+          <t>KSeF — tryb offline/awaryjny</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -6739,11 +6739,11 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNIA</t>
+          <t>BLOKER STARTU</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G77" s="10" t="n">
         <v>18</v>
@@ -6765,27 +6765,27 @@
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>ENDPOINT BEZ UI</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
+          <t>KsefStatus.OFFLINE w schema.prisma:1432 nigdy nie ustawiany</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>PB-13 (zakres zależy od kierunku fakturowania)</t>
         </is>
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
+          <t>awaria KSeF zostawia fakturę w PENDING, bez kodu QR offline</t>
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr">
@@ -6797,12 +6797,12 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>M-14</t>
+          <t>M-15</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>KSeF — numer i UPO widoczne dla klienta</t>
+          <t>KSeF — pobranie UPO przez operatora</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>WYSOKA</t>
+          <t>ŚREDNIA</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
@@ -6833,37 +6833,37 @@
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>BRAK</t>
+          <t>ENDPOINT BEZ UI</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>zero wystąpień „ksef” w apps/client-panel</t>
+          <t>ksef.admin.controller.ts:38; zero wystąpień UPO w admin-panel</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr">
         <is>
-          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Panel wywołuje istniejący endpoint; akcja zostawia wpis w logu audytu. Test potwierdza, że guard nadal blokuje nieuprawnionych.</t>
         </is>
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
+          <t>Skorygowane: UPO jest dostępne w portalu MF, więc warunek dokumentu księgowego nie jest naruszony. Brakuje wygody.</t>
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr">
@@ -6875,31 +6875,31 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>M-14</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Baza wiedzy — 20 artykułów startowych</t>
+          <t>KSeF — numer i UPO widoczne dla klienta</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>ŚREDNI</t>
+          <t>WYSOKA</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G79" s="10" t="n">
         <v>19</v>
@@ -6921,27 +6921,27 @@
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRAK</t>
         </is>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zero wystąpień „ksef” w apps/client-panel</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M-17 (numer KSeF pokazujemy dopiero po potwierdzonej wysyłce)</t>
         </is>
       </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
+          <t>dhosting pokazuje numer KSeF i QR na fakturze</t>
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr">
@@ -6953,12 +6953,12 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
+          <t>Baza wiedzy — 20 artykułów startowych</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G80" s="10" t="n">
         <v>19</v>
@@ -7009,17 +7009,17 @@
       </c>
       <c r="M80" s="11" t="inlineStr">
         <is>
-          <t>PB-06 (kampania kieruje na landing)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
+          <t>20 artykułów opublikowanych i zaindeksowanych do asystenta AI. Każdy opisuje funkcję, która w macierzy ma status DZIAŁA.</t>
         </is>
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
+          <t>Artykuły pokrywające najczęstsze pytania pierwszego tygodnia: skierowanie domeny, SSL, poczta, FTP, backup, migracja, faktury.</t>
         </is>
       </c>
       <c r="P80" s="10" t="inlineStr">
@@ -7031,12 +7031,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Test end-to-end „pierwszy klient”</t>
+          <t>Kampania gads-search-hosting-202607 — uruchomienie</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -7051,24 +7051,28 @@
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>BLOKER BIZNESOWY</t>
+          <t>ŚREDNI</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H81" s="10" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Faza 3 — Wejście na rynek</t>
+        </is>
+      </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
@@ -7083,17 +7087,17 @@
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>wszystkie blokery zamknięte (sprint 8)</t>
+          <t>PB-06 (kampania kieruje na landing)</t>
         </is>
       </c>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+          <t>Kampania utworzona wstrzymana, konwersje podpięte, budżet i stawki ustawione. Start dopiero po PB-05.</t>
         </is>
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+          <t>Konfiguracja kampanii wyszukiwarkowej, budżet 500–1000 zł/mies., oś przekazu: migracja bez przestoju.</t>
         </is>
       </c>
       <c r="P81" s="10" t="inlineStr">
@@ -7105,12 +7109,12 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>Runbook startu i decyzja GO</t>
+          <t>Test end-to-end „pierwszy klient”</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -7129,7 +7133,7 @@
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>20</v>
@@ -7157,28 +7161,102 @@
       </c>
       <c r="M82" s="11" t="inlineStr">
         <is>
+          <t>wszystkie blokery zamknięte (sprint 8)</t>
+        </is>
+      </c>
+      <c r="N82" s="11" t="inlineStr">
+        <is>
+          <t>Zapisany przebieg z timestampami dla każdego kroku — to jest dowód poziomu D3, jedyny w całym projekcie. Każdy nieudany krok wraca do backlogu jako bloker.</t>
+        </is>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>Przejście całej ścieżki na produkcji jako realny klient: rejestracja, zakup, płatność, provisioning, migracja strony, wystawienie faktury, KSeF, backup, odtworzenie.</t>
+        </is>
+      </c>
+      <c r="P82" s="10" t="inlineStr">
+        <is>
+          <t>do zrobienia</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>PB-12</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>Runbook startu i decyzja GO</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>poza audytem</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Praca spoza audytu</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>BLOKER BIZNESOWY</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H83" s="10" t="inlineStr"/>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
           <t>PB-05 (decyzja GO po przejściu ścieżki na produkcji)</t>
         </is>
       </c>
-      <c r="N82" s="11" t="inlineStr">
+      <c r="N83" s="11" t="inlineStr">
         <is>
           <t>Każdy z 11 blokerów ma wpis: co zrobiono, gdzie jest dowód, kto potwierdził. Bez formuły „warunkowe GO”.</t>
         </is>
       </c>
-      <c r="O82" s="11" t="inlineStr">
+      <c r="O83" s="11" t="inlineStr">
         <is>
           <t>Domknięcie: przegląd wszystkich blokerów z dowodem zamknięcia, decyzja GO/NO-GO zapisana z datą.</t>
         </is>
       </c>
-      <c r="P82" s="10" t="inlineStr">
+      <c r="P83" s="10" t="inlineStr">
         <is>
           <t>do zrobienia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P82"/>
-  <conditionalFormatting sqref="E2:E82">
+  <autoFilter ref="A1:P83"/>
+  <conditionalFormatting sqref="E2:E83">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BLOKER STARTU"</formula>
     </cfRule>
@@ -7198,7 +7276,7 @@
       <formula>"ŚREDNI"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P82">
+  <conditionalFormatting sqref="P2:P83">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
       <formula>"zrobione"</formula>
     </cfRule>
@@ -7308,11 +7386,11 @@
         </is>
       </c>
       <c r="F2" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A2)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A2)</f>
         <v/>
       </c>
       <c r="G2" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A2,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A2,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H2" s="10" t="n">
@@ -7353,11 +7431,11 @@
         </is>
       </c>
       <c r="F3" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A3)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A3)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A3,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A3,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H3" s="10" t="n">
@@ -7369,7 +7447,7 @@
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziesięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł. X-29 wyszło godzinę po X-28 i z tego samego pytania: skoro reguły są w repo, to czy wdrożenie w ogóle je dowozi? Nie dowoziło — wdrożenie restartowało tylko aplikacje, a Prometheus i Grafana czytają konfigurację wyłącznie przy starcie. H-20 wykonane tu, a nie w sprincie 9: awaria kopii z H-23 wymusiła odtworzenie bazy tu i teraz, więc dowód D4 powstał jedenaście sprintów przed terminem. X-30 wyszło przy sprawdzaniu, czy X-29 faktycznie coś zmieniło: reguły były wczytane i żadna się nie liczyła. Trzeci raz tego dnia to samo pytanie — czy to, co wygląda na zrobione, jest zrobione — i trzeci raz odpowiedź brzmiała nie.</t>
+          <t>Z-03 dotyka skryptów na węźle — zmiana wymaga przetestowania całej ścieżki migracji, nie tylko walidacji DTO. Sprint urósł o dziesięć pozycji odkrytych w trakcie: podatności, strażniki, bramki wdrożeniowe i awaria kopii bazy (H-23/H-24). Przeciążenie jest prawdziwe i celowo widoczne — praca została wykonana, plan jej nie przewidywał. X-28 doszło jako odpowiedź na pytanie, które zostawiło H-23: dlaczego alarm o braku kopii nie dotarł do nikogo. Odpowiedź — nie miał dokąd; w repo nie było Alertmanagera, a Grafana miała odbiorcę i zero reguł. X-29 wyszło godzinę po X-28 i z tego samego pytania: skoro reguły są w repo, to czy wdrożenie w ogóle je dowozi? Nie dowoziło — wdrożenie restartowało tylko aplikacje, a Prometheus i Grafana czytają konfigurację wyłącznie przy starcie. H-20 wykonane tu, a nie w sprincie 9: awaria kopii z H-23 wymusiła odtworzenie bazy tu i teraz, więc dowód D4 powstał jedenaście sprintów przed terminem. X-30 wyszło przy sprawdzaniu, czy X-29 faktycznie coś zmieniło: reguły były wczytane i żadna się nie liczyła. Trzeci raz tego dnia to samo pytanie — czy to, co wygląda na zrobione, jest zrobione — i trzeci raz odpowiedź brzmiała nie. X-31 domyka dzień: po naprawie X-30 alerty ucichną, a cisza wygląda tak samo jak awaria kanału — więc dokładamy regułę, która pali się zawsze i której brak jest sygnałem. Decyzja właściciela produktu: jeden mail na dobę.</t>
         </is>
       </c>
     </row>
@@ -7398,11 +7476,11 @@
         </is>
       </c>
       <c r="F4" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A4)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A4)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A4,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A4,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H4" s="10" t="n">
@@ -7443,11 +7521,11 @@
         </is>
       </c>
       <c r="F5" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A5)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A5)</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A5,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A5,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H5" s="10" t="n">
@@ -7488,11 +7566,11 @@
         </is>
       </c>
       <c r="F6" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A6)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A6)</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A6,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A6,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H6" s="10" t="n">
@@ -7533,11 +7611,11 @@
         </is>
       </c>
       <c r="F7" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A7)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A7)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A7,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A7,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H7" s="10" t="n">
@@ -7578,11 +7656,11 @@
         </is>
       </c>
       <c r="F8" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A8)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A8)</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A8,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A8,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H8" s="10" t="n">
@@ -7623,11 +7701,11 @@
         </is>
       </c>
       <c r="F9" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A9)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A9)</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A9,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A9,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H9" s="10" t="n">
@@ -7668,11 +7746,11 @@
         </is>
       </c>
       <c r="F10" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A10)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A10)</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A10,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A10,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H10" s="10" t="n">
@@ -7713,11 +7791,11 @@
         </is>
       </c>
       <c r="F11" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A11)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A11)</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A11,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A11,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H11" s="10" t="n">
@@ -7758,11 +7836,11 @@
         </is>
       </c>
       <c r="F12" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A12)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A12)</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A12,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A12,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H12" s="10" t="n">
@@ -7803,11 +7881,11 @@
         </is>
       </c>
       <c r="F13" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A13)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A13)</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A13,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A13,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H13" s="10" t="n">
@@ -7848,11 +7926,11 @@
         </is>
       </c>
       <c r="F14" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A14)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A14)</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A14,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A14,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H14" s="10" t="n">
@@ -7893,11 +7971,11 @@
         </is>
       </c>
       <c r="F15" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A15)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A15)</f>
         <v/>
       </c>
       <c r="G15" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A15,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A15,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H15" s="10" t="n">
@@ -7938,11 +8016,11 @@
         </is>
       </c>
       <c r="F16" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A16)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A16)</f>
         <v/>
       </c>
       <c r="G16" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A16,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A16,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H16" s="10" t="n">
@@ -7983,11 +8061,11 @@
         </is>
       </c>
       <c r="F17" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A17)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A17)</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A17,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A17,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H17" s="10" t="n">
@@ -8028,11 +8106,11 @@
         </is>
       </c>
       <c r="F18" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A18)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A18)</f>
         <v/>
       </c>
       <c r="G18" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A18,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A18,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H18" s="10" t="n">
@@ -8073,11 +8151,11 @@
         </is>
       </c>
       <c r="F19" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A19)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A19)</f>
         <v/>
       </c>
       <c r="G19" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A19,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A19,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H19" s="10" t="n">
@@ -8118,11 +8196,11 @@
         </is>
       </c>
       <c r="F20" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A20)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A20)</f>
         <v/>
       </c>
       <c r="G20" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A20,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A20,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H20" s="10" t="n">
@@ -8159,11 +8237,11 @@
         </is>
       </c>
       <c r="F21" s="10">
-        <f>COUNTIF('Backlog do startu'!$G$2:$G$82,A21)</f>
+        <f>COUNTIF('Backlog do startu'!$G$2:$G$83,A21)</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>SUMIF('Backlog do startu'!$G$2:$G$82,A21,'Backlog do startu'!$F$2:$F$82)</f>
+        <f>SUMIF('Backlog do startu'!$G$2:$G$83,A21,'Backlog do startu'!$F$2:$F$83)</f>
         <v/>
       </c>
       <c r="H21" s="10" t="n">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -2877,12 +2877,12 @@
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>CZĘŚCIOWE</t>
+          <t>DZIAŁA</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). BRAK: zielonego wdrożenia z czystym logiem Grafany — dowód D3 jeszcze nie powstał.</t>
+          <t>ops/observability/grafana/provisioning/datasources/datasources.yml — deleteDatasources przed deklaracją, uid: Prometheus; ops/scripts/prod-deploy-ghcr.sh — krok 4.6: grafana_alerting_rule_group_rules &gt; 0 oraz podwójny odczyt grafana_alerting_rule_evaluation_failures_total w odstępie 75 s, exit 1 przy przyroście; apps/api/src/test/reguly-alertowe-licza-sie.spec.ts (11). DOWÓD D3: wdrożenie #68 zielone przez krok 4.6; log Grafany po restarcie 11:01:46 bez „Failed to build rule evaluator" (wszystkie wystąpienia 10:58–11:01:39, czyli sprzed restartu); „inserting datasource from configuration" name=Prometheus uid=Prometheus.</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Stan 2026-08-23: NAPRAWIONE W KODZIE (D2), POZYCJA OTWARTA do czasu zielonego wdrożenia z czystym logiem Grafany (D3). Wpisanie DZIAŁA teraz byłoby powtórzeniem dokładnie tego błędu, który ta pozycja opisuje. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md</t>
+          <t>ZAMKNIĘTE 2026-08-23. | CO SIĘ STAŁO: wdrożenie #67 przeszło na zielono, krok X-29 zrobił swoje (promtool przyjął konfigurację, oba kontenery wstały, oba odpowiedziały na health-check), Grafana zalogowała „starting to provision alerting" i „finished", trzynaście reguł stanęło w jej bazie — i wszystkie trzynaście waliło się co trzydzieści sekund: „Failed to build rule evaluator / failed to build query 'A': data source not found". Łącznie z VerrisPostgresBackupStale, czyli tą jedyną, dla której to wszystko było robione. | PRZYCZYNA: reguły odwołują się do źródła danych po uid. X-28 dopisało uid: Prometheus do datasources.yml i to NIE WYSTARCZYŁO — Grafana przy provisioningu aktualizuje istniejące źródło po NAZWIE i zostawia mu uid nadany przy pierwszym utworzeniu, czyli losowy. Dashboardy tego nie zauważyły, bo mają starą, nazwową ścieżkę zgodności; reguły alertowe takiej nie mają. | MÓJ BŁĄD, NAZWANY WPROST: strażnik X-28 sprawdzał, że datasourceUid użyty w regułach WYSTĘPUJE w datasources.yml. Występował. Plik był spójny z plikiem — i to nie dowodziło niczego o działającym systemie, bo pytanie nie brzmiało „czy napis się zgadza", tylko „czy Grafana rozwiąże to odwołanie". Test zgodności plików nie widzi semantyki upsertu Grafany. Ta sama pułapka co Z-01, H-20 i dwa razy przy diagnozie @prisma/client: test przechodzi, system nie działa. Napisałem o niej w komentarzu do X-28 i wpadłem w nią godzinę później. | POPRAWKA 1 — źródło danych jest ODTWARZANE, nie aktualizowane: deleteDatasources wykonuje się PRZED wstawieniem, więc źródło powstaje od nowa z uid-em z repozytorium. Rekord jest w całości zadeklarowany w pliku, więc nie ma czego stracić. Przy okazji naprawia dashboardy: przestają zależeć od ścieżki zgodności. | POPRAWKA 2 — krok 4.6 pyta DZIAŁAJĄCĄ Grafanę: grafana_alerting_rule_group_rules musi być &gt; 0 (pusty provisioning wygląda identycznie jak zdrowa Grafana), a grafana_alerting_rule_evaluation_failures_total odczytywany DWA RAZY w odstępie 75 s — liczy się PRZYROST, nie wartość, bo pojedyncze niepowodzenie tuż po restarcie jest normalne, a odstęp musi być dłuższy niż cykl najkrótszej grupy (30 s), inaczej zero błędów znaczy tylko „nic się jeszcze nie policzyło". | CZEGO SIĘ NIE DA ZROBIĆ INACZEJ: naturalny odruch to „alarm o niedziałających alarmach", czyli reguła na increase(...failures_total). NIE ZADZIAŁA w tym przypadku — meta-reguła jest regułą Grafany i liczy się z tego samego źródła danych; gdy źródło jest zepsute, ona też milczy. Łapie pojedynczą regułę z błędnym wyrażeniem, nie łapie złamanego źródła. Ten przypadek łapie WYŁĄCZNIE bramka we wdrożeniu, bo pyta z zewnątrz. Nie dokładam meta-reguły, bo dałaby poczucie pokrycia, którego nie ma. | Czerwieni się na starym kodzie: 7 z 11. routing-alertow.spec.ts zostaje bez zmian — sprawdzanie zgodności plików jest POTRZEBNE, okazało się tylko NIEWYSTARCZAJĄCE. | JAK ZAMKNĄĆ: zielony deploy + brak „Failed to build rule evaluator" w logu Grafany. Dokumentacja: docs/zadania/X-30-reguly-wczytane-ale-nieliczace-sie.md | ZAMKNIĘTE 2026-08-23 — DOWÓD D3 Z LOGU PRODUKCYJNEJ GRAFANY. Wdrożenie #68 (2788011) przeszło przez nowy krok 4.6 i trwało 9m54s, czyli o te 75 sekund dłużej — krok przechodzi tylko wtedy, gdy Grafana ma reguły I licznik nieudanych ewaluacji nie urósł. W logu: 11:01:46 „deleted datasource based on configuration" name=Prometheus, zaraz po tym „inserting datasource from configuration" name=Prometheus uid=Prometheus. Wszystkie wpisy „Failed to build rule evaluator" mają znacznik 10:58–11:01:39, czyli SPRZED restartu; po 11:01:46 nie ma ANI JEDNEGO. Wpisy „Detected stale state entry ... reason=Error" o 11:02–11:03 to Grafana sprzątająca stare wpisy w stanie Alerting-z-powodu-błędu, stąd wiadomości [RESOLVED]. | POTWIERDZENIE UBOCZNE, MOCNIEJSZE OD SAMEGO LOGU: reguła VerrisProvisioningQueueFailed NIE ucichła po naprawie — wysyła alarm co minutę od 11:12, a ma for: 10m przy restarcie 11:01:46, więc pierwsze zapalenie o 11:12 zgadza się co do sekundy. To znaczy, że warunek verris_provisioning_queue_depth{state="failed"} &gt; 0 jest PRAWDZIWIE spełniony: alerting zaczął działać i w ciągu dziesięciu minut znalazł na produkcji coś realnego. Reguła, która zapala się z właściwego powodu, dowodzi więcej niż cisza. Osobna pozycja.</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">

--- a/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
+++ b/plan-startowy-2026-08/VERRIS_BACKLOG_STARTOWY.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Poza zakresem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Backlog do startu'!$A$1:$P$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprinty'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Po starcie'!$A$1:$K$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Poza zakresem'!$A$1:$D$13</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTA('Backlog do startu'!$A$2:$A$83)</f>
+        <f>COUNTA('Backlog do startu'!$A$2:$A$85)</f>
         <v/>
       </c>
     </row>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUM('Backlog do startu'!$F$2:$F$83)</f>
+        <f>SUM('Backlog do startu'!$F$2:$F$85)</f>
         <v/>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF('Backlog do startu'!$E$2:$E$83,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$83,"BLOKER BIZNESOWY")</f>
+        <f>COUNTIF('Backlog do startu'!$E$2:$E$85,"BLOKER STARTU")+COUNTIF('Backlog do startu'!$E$2:$E$85,"BLOKER BIZNESOWY")</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF('Backlog do startu'!$P$2:$P$83,"zrobione")</f>
+        <f>COUNTIF('Backlog do startu'!$P$2:$P$85,"zrobione")</f>
         <v/>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF('Backlog do startu'!$P$2:$P$83,"zrobione",'Backlog do startu'!$F$2:$F$83)</f>
+        <f>SUMIF('Backlog do startu'!$P$2:$P$85,"zrobione",'Backlog do startu'!$F$2:$F$85)</f>
         <v/>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2987,12 +2987,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Z-12</t>
+          <t>Z-18</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
+          <t>Prawdziwa przyczyna błędu provisioningu nie ginie po drodze</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3002,58 +3002,58 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>K — Statystyki, logi, limity</t>
+          <t>Z — Pass adwersaryjny</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
+          <t>BLOKER STARTU</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Faza 0 — Zatrzymać krwawienie</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>CZĘŚCIOWE</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>apps/api/src/subscriptions/provisioning-error.ts — BladEtapuProvisioningu (etap, przyczyna, message z doklejoną przyczyną); provisioning-queue.service.ts — kategoriaBledu(err), klasyfikacja obiektu zamiast napisu, pole przyczyna w audycie ponowienia i twardej porażki; provisioning.service.ts — trzy etapy DA (ensureUserPackage, createAccount, setAccountLimits) bez prania przyczyny; apps/api/src/test/blad-provisioningu-nie-klamie.spec.ts (18). BRAK: dowodu D3 — nie ma węzła obliczeniowego, więc ścieżki provisioningu nie da się dziś przejść na produkcji.</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Faza 0 — Zatrzymać krwawienie</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>DZIAŁA</t>
-        </is>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
-        </is>
-      </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
+          <t>Ograniczenie opisane w uwagach macierzy zniknęło; test potwierdza zachowanie także w scenariuszu awaryjnym.</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
+          <t>Stan 2026-08-23: NAPRAWIONE W KODZIE (D2), POZYCJA OTWARTA — bloker startu do czasu dowodu D3 na węźle #1 (sprint 8). Krytyczność nadana decyzją właściciela produktu 2026-08-23. | JAK TO WYSZŁO: X-30 naprawiło alerting i w ciągu dziesięciu minut zapaliła się pierwsza reguła z PRAWDZIWEGO powodu — VerrisProvisioningQueueFailed. W kolejce leżały cztery martwe joby, a w panelu operatora stało przy nich „DirectAdmin package "starter" is missing on the node and could not be created automatically". W audycie stało co innego: ensureUserPackage / connect ECONNREFUSED 62.238.0.223:2222 (2026-07-07 i 07-10) oraz createAccount / „DirectAdmin API Error: Unable to Create User — A valid IP was not provided" (2026-05-30). Węzeł nie przyjmował połączeń; z pakietem nie było nic nie tak. Same joby są nieszkodliwe — konto testowe właściciela, domeny test.pl/testowa.pl/hvln.pl, sprzed trzech miesięcy, z czasów gdy węzeł testowy jeszcze istniał (dziś nie ma go wcale). Ale komunikat doprowadził mnie do hipotezy o złym mapowaniu planów na pakiety DA — całkowicie chybionej. Na tym polega koszt takiego błędu: nie na tym, że coś nie działa, tylko że wszyscy patrzą nie tam. | MECHANIZM: provisioning.service.ts łapał prawdziwy błąd, zapisywał go do audytu i rzucał dalej STAŁY NAPIS. Prawda zostawała w bazie, w górę szła zmyślona przyczyna. A wyżej: const errCategory = categorizeProvisioningError(msg) — klasyfikator dostawał ten wyprany napis. Jest napisany POPRAWNIE, ma econnrefused na liście błędów przejściowych; tylko nigdy nie widzi tego słowa. | DLACZEGO DOTYKA PIENIĘDZY: przy kliencie i chwilowym zerwaniu sieci — próba 1 → ECONNREFUSED przebrany za brak pakietu → permanent → ścieżka twardej porażki JUŻ PRZY PIERWSZEJ PRÓBIE: subskrypcja na FAILED, ZWROT ŚRODKÓW do portfela, status PENDING_PAYMENT; potem throw err i BullMQ i tak ponawia (attempts: 3, backoff wykładniczy); próba 2 przechodzi, konto powstaje, provisioning.service.ts:299 ustawia subskrypcję na ACTIVE. Klient ma działający hosting i odzyskane pieniądze, a zwrot jest idempotentny (sub-{id}-initial-refund), więc nic go nie cofnie. Wada uśpiona — nie ma dowodu, że się zdarzyła (te joby padły do końca, węzeł był wyłączony na dobre) — ale leży dokładnie na ścieżce pierwszego płacącego klienta. | RODZINA, NOWY WARIANT: to NIE jest „kontrola, która melduje zamiast zatrzymywać" (X-14, X-23, H-19, X-27), gdzie mechanizm istniał i niczego nie bramkował. To POPRAWNA KONTROLA, KTÓREJ SIĘ KŁAMIE: guard dobry, decyzja dobra, lista wyjątków kompletna — a wejście wyprane po drodze. Blisko też rodzinie „strażnik dopasowuje własną prozę" (dziesiąte wystąpienie): jeden z trzech komunikatów był ułożony tak, żeby TRAFIĆ w listę przejściowych — 'CloudLinux LVE limits could not be applied on this node.' kontra lower.includes('cloudlinux lve limits could not be applied'). Działało przypadkiem, dopóki ktoś nie poprawiłby zdania. | POPRAWKA: BladEtapuProvisioningu(etap, przyczyna, komunikatDlaCzlowieka) — klasa niosąca ORYGINALNĄ treść błędu; kategoriaBledu(err) pyta obiekt o przyczynę i dopiero na niej odpala istniejący klasyfikator, a napis zostaje ścieżką zapasową. Przyczyna jest DOKLEJONA także do message, bo panel pokazuje job.failedReason z BullMQ (czyli Error.message), a failedCategory liczy się z tego samego napisu — gdyby przyczyna została tylko we właściwości, panel dalej opowiadałby zmyśloną historię. Audyt dostał osobne pole przyczyna obok error. | Czerwieni się na starym kodzie: 4 z 18. Czternaście przechodziło, bo dotyczą zachowania kategoriaBledu, której przed poprawką nie było — redness siedzi w asercjach strukturalnych. Mówię o tym wprost, żeby „4 z 18" nie wyglądało słabiej, niż jest. | CZEGO NIE OBEJMUJE: innych miejsc, gdzie prawdziwy błąd może być prany (Stripe, migracje, autoskalowanie mają własne bloki catch i nie były przeglądane pod tym kątem — warte osobnego przejścia); sensowności samego zwrotu przy twardej porażce (zwrot jest właściwy, gdy błąd NAPRAWDĘ jest trwały — ta pozycja naprawia rozpoznanie, nie decyzję); czterech martwych jobów w kolejce (sprzątane po tej poprawce, decyzją właściciela produktu, żeby czyścić już na kodzie zapisującym prawdziwą przyczynę). | JAK ZAMKNĄĆ: na węźle #1 uruchomić provisioning, przerwać połączenie do DA w trakcie i pokazać w audycie PONOWIENIE zamiast zwrotu środków, a potem konto założone przy drugiej próbie. Dokumentacja: docs/zadania/Z-18-blad-provisioningu-nie-klamie.md</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
@@ -3065,12 +3065,12 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Z-13</t>
+          <t>Z-12</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
+          <t>Placement kont nadsubskrybuje zasoby węzła zamiast rezerwować pełne limity planu</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>M — Rozliczenia</t>
+          <t>K — Statystyki, logi, limity</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>3</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
+          <t>node-capacity.ts — czyZmiesciSie z dwiema bramkami (handlową: sprzedane + limit planu ≤ pojemność × overcommit; fizyczną: realne zużycie ≤ pojemność × (1 − headroom)); node-selector.service.ts — realneZuzycieWezlow z okna 30 min, jedna najnowsza próbka na subskrypcję; schema.prisma — Server.overcommitCpu/Ram/Disk Float @default(1); migracja 20260822090000_node_overcommit; node-capacity.spec.ts (21 testów) + node-selector.service.spec.ts (9 testów)</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane po wdrożeniu (pozycja dotyczy pojemności produkcyjnej i pieniędzy). Błąd był kategorii, nie arytmetyki: allocated* to suma limitów planów, czyli ZOBOWIĄZANIE HANDLOWE, a kod porównywał je z pojemnością fizyczną tak, jakby były zajętością maszyny. W LVE MemoryMax i SPEED są sufitami burst — rezerwowanie sufitu to to samo, co trzymanie stolika dla każdego, kto MÓGŁBY przyjść. | Rozwiązanie ma dwie bramki, nie jedną: sama handlowa to hazard, sama fizyczna to stan sprzed poprawki z inną etykietą. | Zmiana semantyki headroomu: wcześniej pomniejszał księgę handlową (mieszanie jednostek), teraz chroni realne zużycie. Arkusz PB-01 podaje przez to 51 kont tam, gdzie kod daje 64 — model jest zachowawczy wobec implementacji, nie sprzeczny; uwaga dopisana w zakładce Gestosc. | Dysk ma osobny, niższy limit overcommitu (3× wobec 8×), bo quota dyskowa jest realnie egzekwowana i klient MOŻE ją wypełnić w całości. | Domyślne 1,0 celowo: migracja nie zmienia zachowania placementu, nadsubskrypcję włącza admin świadomie per węzeł. Wycofanie = przestawienie pola w panelu, bez rollbacku. | Brak telemetrii degraduje overcommit do 1,0 zamiast blokować sprzedaż — awaria agenta nie ma zatrzymywać firmy. Węzeł z zerem kont traktowany jako zużycie ZNANE i zerowe, nie nieznane. | Przy okazji naprawiony planer drenażu (OPS-4) w servers.service.ts, który miał DOKŁADNIE tę samą arytmetykę — plan ewakuacji mówiłby „nie ma dokąd przenieść kont” w chwili, gdy miejsce jest. Drugi raz w tym audycie poprawka miała bliźniaka; stąd wyniesienie arytmetyki do osobnego modułu. | 6 z 30 testów czerwieniło się na kodzie sprzed zmiany. Dokumentacja: docs/zadania/Z-12-nadsubskrypcja-pojemnosci-wezla.md</t>
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr">
@@ -3143,12 +3143,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Z-16</t>
+          <t>Z-13</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
+          <t>Pakiet sprzedawany na stronie istnieje jako plan w bazie</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>J — Wydajność i cache</t>
+          <t>M — Rozliczenia</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>3</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+          <t>apps/api/src/plans/plan-produkcyjny.ts — PLAN_PRODUKCYJNY jako źródło prawdy; migracja 20260822120000_plan_produkcyjny (INSERT ... ON CONFLICT DO UPDATE, wycofanie planów prototypowych z isPublic); seed.ts — starter/pro/business isPublic: false; plan-produkcyjny.spec.ts — 20 testów uzgadniających treść strony, definicję w kodzie i migrację SQL</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit bez zabezpieczenia pojemności powiększyłby promień rażenia. Ten test zapalił się przy zmianie progu dokładnie tak, jak miał — ratchet zadziałał. | Przycinanie zamiast odmowy: brak pojemności węzła nie jest winą klienta i nie może mu wyłączać autoskalowania. Konto dostaje mniej, nie traci usługi; każde obcięcie zostawia wpis AUTOSCALING_OGRANICZONE_POJEMNOSCIA_WEZLA — to sygnał do dołożenia węzła. | Zmiana znaczenia księgi allocated* wymusiła przegląd wszystkich jej pisarzy i wyszły CZTERY przecieki: (1) autoskalowanie nie dopisywało nadwyżki, (2) usunięcie konta nigdy nie zwalniało limitów — węzeł z czasem przestawał przyjmować konta mając miejsce, (3) maxAccounts liczył konta DELETED, (4) zmiana planu liczyła deltę od baz planów, co było poprawne PRZED Z-16 i stałoby się błędem PO. Czwarty nie istniał — powstałby przez tę poprawkę. | Migracja PRZELICZA księgę z limitów efektywnych kont żywych, więc prostuje też przeszłość; LEFT JOIN, bo węzeł bez kont też mógł mieć allocated* &gt; 0. | 27 nowych testów, czerwień na starym kodzie zebrana trzykrotnie (1/20, 3/21, 4/11). Dokumentacja: docs/zadania/Z-16-autoskalowanie-pyta-wezel.md</t>
+          <t>Zamknięte 2026-08-22. Strona sprzedawała pakiet, którego nie było gdzie kupić: w bazie istniały wyłącznie trzy plany z czasów prototypu (19,99/49,99/99,99 zł) o innych limitach, i to one były jedynymi publicznymi. | Sprawa nie kończyła się na cenniku — z rekordu Plan czyta wycena zamówienia i odnowienia, placement konta na węźle (limity bazowe), synchronizacja pakietów DirectAdmina (prod-sync-server-da-packages.sh) i sufity autoskalowania. | Ceny są BRUTTO: invoices.service.ts:293 traktuje kwotę obciążenia jako brutto i rozbija ją na netto + VAT 23%. Wpisanie netto zawyżyłoby każdą fakturę o 23%. Sprawdzone w kodzie, nie założone. | Plan powstaje w MIGRACJI, nie w seedzie — dzięki temu istnieje na każdym środowisku bez uruchamiania seeda, a ON CONFLICT DO UPDATE sprawia, że migracja jest źródłem prawdy także przy zmianie ceny. | Plany prototypowe wycofane przez isPublic=false, a NIE isActive=false: dezaktywacja planu wywróciłaby odnowienie ewentualnej subskrypcji na nim założonej. | Test uzgadnia TRZY warstwy, które mówiły trzy różne rzeczy: treść strony, definicję w kodzie i migrację SQL. Sprawdzone przez podmianę ceny w SQL — test zapala się na czerwono. | Przy okazji odkryte Z-16: sufit autoskalowania z oferty (24 vCPU, 1000 GB) jest nieosiągalny, bo silnik przycina krotność do 10×. Dokumentacja: docs/zadania/Z-13-plan-produkcyjny-w-bazie.md</t>
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
@@ -3221,31 +3221,31 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>Z-16</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Wybór dostawcy i lokalizacji węzła produkcyjnego #1</t>
+          <t>Autoskalowanie pyta węzeł o pojemność i dowozi sufit obiecany w ofercie</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>poza audytem</t>
+          <t>audyt</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Praca spoza audytu</t>
+          <t>J — Wydajność i cache</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>WYSOKI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>3</v>
@@ -3267,27 +3267,27 @@
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
+          <t>DZIAŁA</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>node-capacity.ts — wolneDoZadysponowania + krotnoscAutoskalowania (MAKS 32×, koniec zaszytego sufitu 10×); autoscaling-engine.service.ts — ogranicznikPojemnosciWezla przed guardScaleUp, realneZuzycieWezla, allocated* incrementowane w tej samej transakcji co zapis konta; account-deletion.service.ts — zwolnienie limitów efektywnych przy DELETED; node-selector.service.ts — maxAccounts pomija DELETED; plan-change.service.ts — delta od limitów efektywnych; migracja 20260822150000_uzgodnienie_ksiegi_wezla; node-capacity-z16.spec.ts + ksiega-wezla.spec.ts + przepisany blok w plan-produkcyjny.spec.ts</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>Decyzja zapisana w repo z datą, przed zamówieniem serwera. Jeśli wybrany dostawca spoza Polski — polityka prywatności i DPA opisują lokalizację przetwarzania przed startem sprzedaży.</t>
+          <t>Funkcja dostępna z panelu klienta bez wychodzenia do DirectAdmina; test uruchamiany w CI.</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>PB-01 pokazało, że wybór dostawcy przesądza o rentowności przy cenie 45 zł. Hetzner AX102 ma cenę progową 44,20 zł, OVH Advance-2 w WAW1 — 67,76 zł, bo 960 GB dysku ogranicza węzeł do 30 kont. Sprawdzić realną cenę opcji dysku 1,92 TB w WAW1 (wzrosła o ok. 89% w lipcu 2026) i zestawić premię za lokalizację w Polsce z jej wartością sprzedażową i wpływem na RODO oraz DPA.</t>
+          <t>Zamknięte 2026-08-22, D3 wymagane. Silnik autoskalowania nie miał w całym pliku ani jednego odwołania do Server ani do allocated*. Dwa skutki, jedna przyczyna. | PIERWSZY: sufit 10× zaszyty w silniku niezależnie od planu sprawiał, że oferta (24 vCPU, 1000 GB) była nieosiągalna — realnie 20 vCPU i 500 GB. Klient płacił godzinowo za nadwyżkę, której nie dostawał. | DRUGI: silnik podnosił limity w DirectAdminie bez pytania węzła o pojemność i bez zapisu w księdze. Po Z-12 znaczyło to dwie warstwy nadsubskrybujące ten sam węzeł bez wiedzy o sobie; jedno konto mogło urosnąć do 1000 GB na węźle 1,92 TB. | KOLEJNOŚĆ MIAŁA ZNACZENIE: przy Z-13 świadomie NIE podniosłem sufitu i utrwaliłem rozbieżność testem, bo wyższy sufit be